--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99CF65D5-FC4B-4A92-BB23-813D215865C1}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9095ED9A-6729-4A8C-A2D3-9475BCD53776}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2460" uniqueCount="1276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="1281">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -2542,9 +2542,6 @@
     <t>MEM-211</t>
   </si>
   <si>
-    <t xml:space="preserve"> Alimi Fatimoh</t>
-  </si>
-  <si>
     <t>08182430202</t>
   </si>
   <si>
@@ -2581,21 +2578,9 @@
     <t>MEM-215</t>
   </si>
   <si>
-    <t>Mukalia Ramota</t>
-  </si>
-  <si>
-    <t>08077222321</t>
-  </si>
-  <si>
     <t>MEM-216</t>
   </si>
   <si>
-    <t xml:space="preserve">Ahmed Omowunmi </t>
-  </si>
-  <si>
-    <t>09023087137</t>
-  </si>
-  <si>
     <t>MEM-217</t>
   </si>
   <si>
@@ -3854,6 +3839,36 @@
   </si>
   <si>
     <t>Misc fees Savings</t>
+  </si>
+  <si>
+    <t>Alimi Fatimoh</t>
+  </si>
+  <si>
+    <t>Kehinde Afolabi</t>
+  </si>
+  <si>
+    <t>Ojei Elizabeth</t>
+  </si>
+  <si>
+    <t>Weekly 12W</t>
+  </si>
+  <si>
+    <t>09047690900</t>
+  </si>
+  <si>
+    <t>08050412130</t>
+  </si>
+  <si>
+    <t>Weekly 24W</t>
+  </si>
+  <si>
+    <t>Koleosho Sherifat</t>
+  </si>
+  <si>
+    <t>35925</t>
+  </si>
+  <si>
+    <t>25125</t>
   </si>
 </sst>
 </file>
@@ -4053,7 +4068,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4134,36 +4149,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4171,6 +4156,42 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -4663,28 +4684,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -4704,13 +4725,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
+      <c r="E4" s="37"/>
+      <c r="F4" s="37"/>
+      <c r="G4" s="37"/>
+      <c r="H4" s="37"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -4718,13 +4739,13 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="32"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="35"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4732,13 +4753,13 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="32"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -4746,13 +4767,13 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="31"/>
-      <c r="H7" s="32"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -4760,13 +4781,13 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="32"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="35"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -4774,25 +4795,25 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -4805,142 +4826,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="32"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="35"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="32"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="35"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="32"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="35"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="32"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="32"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="35"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="32"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="35"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="33" t="s">
+      <c r="B20" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="32"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="35"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="37" t="s">
+      <c r="B21" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="32"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -4953,6 +4974,13 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:H4"/>
@@ -4965,13 +4993,6 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4994,30 +5015,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5733,7 +5754,9 @@
       <c r="C31" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D31" s="6"/>
+      <c r="D31" s="6" t="s">
+        <v>1278</v>
+      </c>
       <c r="E31" s="6" t="s">
         <v>114</v>
       </c>
@@ -5746,7 +5769,9 @@
       <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="14"/>
+      <c r="I31" s="48" t="s">
+        <v>1279</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
@@ -5758,7 +5783,9 @@
       <c r="C32" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="D32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>864</v>
+      </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
       </c>
@@ -5771,7 +5798,9 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="14"/>
+      <c r="I32" s="48" t="s">
+        <v>1280</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -8514,34 +8543,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
+      <c r="J2" s="45"/>
+      <c r="K2" s="45"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -13811,23 +13840,27 @@
         <v>174</v>
       </c>
       <c r="D214" s="22" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E214" s="21" t="s">
         <v>838</v>
       </c>
-      <c r="E214" s="21" t="s">
+      <c r="F214" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="F214" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G214" s="20"/>
-      <c r="H214" s="23"/>
+      <c r="G214" s="20">
+        <v>38100</v>
+      </c>
+      <c r="H214" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I214" s="23"/>
       <c r="J214" s="23"/>
       <c r="K214" s="23"/>
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="21" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B215" s="21" t="s">
         <v>112</v>
@@ -13836,23 +13869,33 @@
         <v>179</v>
       </c>
       <c r="D215" s="22" t="s">
+        <v>841</v>
+      </c>
+      <c r="E215" s="21" t="s">
         <v>842</v>
       </c>
-      <c r="E215" s="21" t="s">
-        <v>843</v>
-      </c>
       <c r="F215" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G215" s="20"/>
-      <c r="H215" s="23"/>
-      <c r="I215" s="23"/>
-      <c r="J215" s="23"/>
-      <c r="K215" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G215" s="20">
+        <v>14100</v>
+      </c>
+      <c r="H215" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I215" s="47">
+        <v>200000</v>
+      </c>
+      <c r="J215" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K215" s="23">
+        <v>148500</v>
+      </c>
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="21" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B216" s="21" t="s">
         <v>112</v>
@@ -13861,23 +13904,33 @@
         <v>190</v>
       </c>
       <c r="D216" s="22" t="s">
+        <v>844</v>
+      </c>
+      <c r="E216" s="21" t="s">
         <v>845</v>
       </c>
-      <c r="E216" s="21" t="s">
-        <v>846</v>
-      </c>
       <c r="F216" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G216" s="20"/>
-      <c r="H216" s="23"/>
-      <c r="I216" s="23"/>
-      <c r="J216" s="23"/>
-      <c r="K216" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G216" s="20">
+        <v>16000</v>
+      </c>
+      <c r="H216" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I216" s="47">
+        <v>200000</v>
+      </c>
+      <c r="J216" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K216" s="23">
+        <v>148500</v>
+      </c>
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B217" s="21" t="s">
         <v>112</v>
@@ -13886,23 +13939,27 @@
         <v>194</v>
       </c>
       <c r="D217" s="22" t="s">
+        <v>847</v>
+      </c>
+      <c r="E217" s="21" t="s">
         <v>848</v>
       </c>
-      <c r="E217" s="21" t="s">
-        <v>849</v>
-      </c>
       <c r="F217" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G217" s="20"/>
-      <c r="H217" s="23"/>
-      <c r="I217" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G217" s="20">
+        <v>35000</v>
+      </c>
+      <c r="H217" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I217" s="47"/>
       <c r="J217" s="23"/>
       <c r="K217" s="23"/>
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="21" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B218" s="21" t="s">
         <v>112</v>
@@ -13911,23 +13968,25 @@
         <v>198</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>851</v>
+        <v>1272</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>852</v>
+        <v>1275</v>
       </c>
       <c r="F218" s="22" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G218" s="20"/>
-      <c r="H218" s="23"/>
-      <c r="I218" s="23"/>
+      <c r="H218" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I218" s="47"/>
       <c r="J218" s="23"/>
       <c r="K218" s="23"/>
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="B219" s="21" t="s">
         <v>112</v>
@@ -13936,23 +13995,27 @@
         <v>202</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>854</v>
+        <v>1273</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>855</v>
+        <v>1276</v>
       </c>
       <c r="F219" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G219" s="20"/>
-      <c r="H219" s="23"/>
-      <c r="I219" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G219" s="20">
+        <v>15500</v>
+      </c>
+      <c r="H219" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I219" s="47"/>
       <c r="J219" s="23"/>
       <c r="K219" s="23"/>
     </row>
     <row r="220" spans="1:11">
       <c r="A220" s="21" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="B220" s="21" t="s">
         <v>112</v>
@@ -13961,23 +14024,33 @@
         <v>206</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="F220" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G220" s="20"/>
-      <c r="H220" s="23"/>
-      <c r="I220" s="23"/>
-      <c r="J220" s="23"/>
-      <c r="K220" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G220" s="20">
+        <v>52000</v>
+      </c>
+      <c r="H220" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I220" s="47">
+        <v>250000</v>
+      </c>
+      <c r="J220" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K220" s="23">
+        <v>102500</v>
+      </c>
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="21" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="B221" s="21" t="s">
         <v>112</v>
@@ -13986,23 +14059,33 @@
         <v>210</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="F221" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G221" s="20"/>
-      <c r="H221" s="23"/>
-      <c r="I221" s="23"/>
-      <c r="J221" s="23"/>
-      <c r="K221" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G221" s="20">
+        <v>30900</v>
+      </c>
+      <c r="H221" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I221" s="47">
+        <v>250000</v>
+      </c>
+      <c r="J221" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K221" s="23">
+        <v>112750</v>
+      </c>
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="B222" s="21" t="s">
         <v>112</v>
@@ -14011,23 +14094,33 @@
         <v>258</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F222" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G222" s="20"/>
-      <c r="H222" s="23"/>
-      <c r="I222" s="23"/>
-      <c r="J222" s="23"/>
-      <c r="K222" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G222" s="20">
+        <v>19750</v>
+      </c>
+      <c r="H222" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I222" s="47">
+        <v>200000</v>
+      </c>
+      <c r="J222" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K222" s="23">
+        <v>115500</v>
+      </c>
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="B223" s="21" t="s">
         <v>115</v>
@@ -14036,23 +14129,33 @@
         <v>174</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="F223" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G223" s="20"/>
-      <c r="H223" s="23"/>
-      <c r="I223" s="23"/>
-      <c r="J223" s="23"/>
-      <c r="K223" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G223" s="20">
+        <v>10750</v>
+      </c>
+      <c r="H223" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I223" s="47">
+        <v>100000</v>
+      </c>
+      <c r="J223" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K223" s="23">
+        <v>57750</v>
+      </c>
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="B224" s="21" t="s">
         <v>115</v>
@@ -14061,23 +14164,33 @@
         <v>179</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="F224" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G224" s="20"/>
-      <c r="H224" s="23"/>
-      <c r="I224" s="23"/>
-      <c r="J224" s="23"/>
-      <c r="K224" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G224" s="20">
+        <v>7200</v>
+      </c>
+      <c r="H224" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I224" s="47">
+        <v>50000</v>
+      </c>
+      <c r="J224" s="23">
+        <v>48000</v>
+      </c>
+      <c r="K224" s="23">
+        <v>36000</v>
+      </c>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="B225" s="21" t="s">
         <v>115</v>
@@ -14086,23 +14199,33 @@
         <v>190</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="F225" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G225" s="20"/>
-      <c r="H225" s="23"/>
-      <c r="I225" s="23"/>
-      <c r="J225" s="23"/>
-      <c r="K225" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G225" s="20">
+        <v>10900</v>
+      </c>
+      <c r="H225" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I225" s="47">
+        <v>80000</v>
+      </c>
+      <c r="J225" s="23">
+        <v>78000</v>
+      </c>
+      <c r="K225" s="23">
+        <v>45500</v>
+      </c>
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="B226" s="21" t="s">
         <v>115</v>
@@ -14111,23 +14234,33 @@
         <v>194</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F226" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G226" s="20"/>
-      <c r="H226" s="23"/>
-      <c r="I226" s="23"/>
-      <c r="J226" s="23"/>
-      <c r="K226" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G226" s="20">
+        <v>8925</v>
+      </c>
+      <c r="H226" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I226" s="47">
+        <v>100000</v>
+      </c>
+      <c r="J226" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K226" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="B227" s="21" t="s">
         <v>115</v>
@@ -14136,21 +14269,25 @@
         <v>198</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="E227" s="21"/>
       <c r="F227" s="22" t="s">
-        <v>840</v>
-      </c>
-      <c r="G227" s="20"/>
-      <c r="H227" s="23"/>
+        <v>839</v>
+      </c>
+      <c r="G227" s="20">
+        <v>42925</v>
+      </c>
+      <c r="H227" s="23" t="s">
+        <v>1277</v>
+      </c>
       <c r="I227" s="23"/>
       <c r="J227" s="23"/>
       <c r="K227" s="23"/>
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="21" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="B228" s="21" t="s">
         <v>117</v>
@@ -14159,13 +14296,13 @@
         <v>174</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="F228" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G228" s="20"/>
       <c r="H228" s="23"/>
@@ -14175,7 +14312,7 @@
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="21" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="B229" s="21" t="s">
         <v>117</v>
@@ -14184,13 +14321,13 @@
         <v>179</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="E229" s="21" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="F229" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G229" s="20"/>
       <c r="H229" s="23"/>
@@ -14200,7 +14337,7 @@
     </row>
     <row r="230" spans="1:11">
       <c r="A230" s="21" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="B230" s="21" t="s">
         <v>117</v>
@@ -14209,13 +14346,13 @@
         <v>190</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="F230" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G230" s="20"/>
       <c r="H230" s="23"/>
@@ -14225,7 +14362,7 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" s="21" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="B231" s="21" t="s">
         <v>117</v>
@@ -14234,13 +14371,13 @@
         <v>194</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="F231" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G231" s="20"/>
       <c r="H231" s="23"/>
@@ -14250,7 +14387,7 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" s="21" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="B232" s="21" t="s">
         <v>117</v>
@@ -14259,13 +14396,13 @@
         <v>198</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="F232" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G232" s="20"/>
       <c r="H232" s="23"/>
@@ -14275,7 +14412,7 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" s="21" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="B233" s="21" t="s">
         <v>117</v>
@@ -14284,13 +14421,13 @@
         <v>202</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="F233" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G233" s="20"/>
       <c r="H233" s="23"/>
@@ -14300,7 +14437,7 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" s="21" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="B234" s="21" t="s">
         <v>117</v>
@@ -14309,13 +14446,13 @@
         <v>206</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="F234" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G234" s="20"/>
       <c r="H234" s="23"/>
@@ -14325,7 +14462,7 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" s="21" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="B235" s="21" t="s">
         <v>117</v>
@@ -14334,13 +14471,13 @@
         <v>210</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="E235" s="21" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="F235" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G235" s="20"/>
       <c r="H235" s="23"/>
@@ -14350,7 +14487,7 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" s="21" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="B236" s="21" t="s">
         <v>117</v>
@@ -14359,13 +14496,13 @@
         <v>258</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="F236" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G236" s="20"/>
       <c r="H236" s="23"/>
@@ -14375,7 +14512,7 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" s="21" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>117</v>
@@ -14384,13 +14521,13 @@
         <v>262</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="E237" s="21" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="F237" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G237" s="20"/>
       <c r="H237" s="23"/>
@@ -14400,7 +14537,7 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" s="21" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="B238" s="21" t="s">
         <v>117</v>
@@ -14409,13 +14546,13 @@
         <v>296</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F238" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G238" s="20"/>
       <c r="H238" s="23"/>
@@ -14425,7 +14562,7 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" s="21" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="B239" s="21" t="s">
         <v>117</v>
@@ -14434,13 +14571,13 @@
         <v>300</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="F239" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G239" s="20"/>
       <c r="H239" s="23"/>
@@ -14450,7 +14587,7 @@
     </row>
     <row r="240" spans="1:11">
       <c r="A240" s="21" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="B240" s="21" t="s">
         <v>117</v>
@@ -14459,13 +14596,13 @@
         <v>304</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="F240" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G240" s="20"/>
       <c r="H240" s="23"/>
@@ -14475,7 +14612,7 @@
     </row>
     <row r="241" spans="1:11">
       <c r="A241" s="21" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="B241" s="21" t="s">
         <v>117</v>
@@ -14484,13 +14621,13 @@
         <v>308</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="F241" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G241" s="20"/>
       <c r="H241" s="23"/>
@@ -14500,7 +14637,7 @@
     </row>
     <row r="242" spans="1:11">
       <c r="A242" s="21" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="B242" s="21" t="s">
         <v>122</v>
@@ -14509,13 +14646,13 @@
         <v>174</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="F242" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G242" s="20"/>
       <c r="H242" s="23"/>
@@ -14525,7 +14662,7 @@
     </row>
     <row r="243" spans="1:11">
       <c r="A243" s="21" t="s">
-        <v>926</v>
+        <v>921</v>
       </c>
       <c r="B243" s="21" t="s">
         <v>122</v>
@@ -14534,13 +14671,13 @@
         <v>179</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="F243" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G243" s="20"/>
       <c r="H243" s="23"/>
@@ -14550,7 +14687,7 @@
     </row>
     <row r="244" spans="1:11">
       <c r="A244" s="21" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="B244" s="21" t="s">
         <v>122</v>
@@ -14559,13 +14696,13 @@
         <v>190</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="F244" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G244" s="20"/>
       <c r="H244" s="23"/>
@@ -14575,7 +14712,7 @@
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="21" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="B245" s="21" t="s">
         <v>122</v>
@@ -14584,13 +14721,13 @@
         <v>194</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="F245" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G245" s="20"/>
       <c r="H245" s="23"/>
@@ -14600,7 +14737,7 @@
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="21" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="B246" s="21" t="s">
         <v>122</v>
@@ -14609,13 +14746,13 @@
         <v>198</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="F246" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G246" s="20"/>
       <c r="H246" s="23"/>
@@ -14625,7 +14762,7 @@
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="21" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="B247" s="21" t="s">
         <v>122</v>
@@ -14634,13 +14771,13 @@
         <v>202</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="F247" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G247" s="20"/>
       <c r="H247" s="23"/>
@@ -14650,7 +14787,7 @@
     </row>
     <row r="248" spans="1:11">
       <c r="A248" s="21" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B248" s="21" t="s">
         <v>122</v>
@@ -14659,13 +14796,13 @@
         <v>206</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="F248" s="22" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G248" s="20"/>
       <c r="H248" s="23"/>
@@ -14675,7 +14812,7 @@
     </row>
     <row r="249" spans="1:11">
       <c r="A249" s="21" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="B249" s="21" t="s">
         <v>125</v>
@@ -14684,13 +14821,13 @@
         <v>174</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="F249" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G249" s="20"/>
       <c r="H249" s="23"/>
@@ -14700,7 +14837,7 @@
     </row>
     <row r="250" spans="1:11">
       <c r="A250" s="21" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="B250" s="21" t="s">
         <v>125</v>
@@ -14709,13 +14846,13 @@
         <v>179</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="F250" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G250" s="20"/>
       <c r="H250" s="23"/>
@@ -14725,7 +14862,7 @@
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="21" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="B251" s="21" t="s">
         <v>125</v>
@@ -14734,13 +14871,13 @@
         <v>190</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="F251" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G251" s="20"/>
       <c r="H251" s="23"/>
@@ -14750,7 +14887,7 @@
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="21" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="B252" s="21" t="s">
         <v>125</v>
@@ -14759,13 +14896,13 @@
         <v>194</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="F252" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G252" s="20"/>
       <c r="H252" s="23"/>
@@ -14775,7 +14912,7 @@
     </row>
     <row r="253" spans="1:11">
       <c r="A253" s="21" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="B253" s="21" t="s">
         <v>125</v>
@@ -14784,13 +14921,13 @@
         <v>198</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="F253" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G253" s="20"/>
       <c r="H253" s="23"/>
@@ -14800,7 +14937,7 @@
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="21" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="B254" s="21" t="s">
         <v>125</v>
@@ -14809,13 +14946,13 @@
         <v>202</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F254" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G254" s="20"/>
       <c r="H254" s="23"/>
@@ -14825,7 +14962,7 @@
     </row>
     <row r="255" spans="1:11">
       <c r="A255" s="21" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="B255" s="21" t="s">
         <v>125</v>
@@ -14834,13 +14971,13 @@
         <v>206</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
       <c r="F255" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G255" s="20"/>
       <c r="H255" s="23"/>
@@ -14850,7 +14987,7 @@
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="21" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="B256" s="21" t="s">
         <v>125</v>
@@ -14859,13 +14996,13 @@
         <v>210</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="F256" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G256" s="20"/>
       <c r="H256" s="23"/>
@@ -14875,7 +15012,7 @@
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="21" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="B257" s="21" t="s">
         <v>125</v>
@@ -14884,13 +15021,13 @@
         <v>258</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="F257" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G257" s="20"/>
       <c r="H257" s="23"/>
@@ -14900,7 +15037,7 @@
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="21" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="B258" s="21" t="s">
         <v>125</v>
@@ -14909,13 +15046,13 @@
         <v>262</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="F258" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G258" s="20"/>
       <c r="H258" s="23"/>
@@ -14925,7 +15062,7 @@
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="21" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="B259" s="21" t="s">
         <v>125</v>
@@ -14934,13 +15071,13 @@
         <v>296</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="F259" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G259" s="20"/>
       <c r="H259" s="23"/>
@@ -14950,7 +15087,7 @@
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="21" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="B260" s="21" t="s">
         <v>125</v>
@@ -14959,13 +15096,13 @@
         <v>300</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="F260" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G260" s="20"/>
       <c r="H260" s="23"/>
@@ -14975,7 +15112,7 @@
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="21" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="B261" s="21" t="s">
         <v>125</v>
@@ -14984,13 +15121,13 @@
         <v>304</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="F261" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G261" s="20"/>
       <c r="H261" s="23"/>
@@ -15000,7 +15137,7 @@
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="21" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="B262" s="21" t="s">
         <v>125</v>
@@ -15009,13 +15146,13 @@
         <v>308</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="F262" s="22" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="G262" s="20"/>
       <c r="H262" s="23"/>
@@ -15025,7 +15162,7 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="21" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="B263" s="21" t="s">
         <v>128</v>
@@ -15034,13 +15171,13 @@
         <v>174</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="F263" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G263" s="20"/>
       <c r="H263" s="23"/>
@@ -15050,7 +15187,7 @@
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="21" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="B264" s="21" t="s">
         <v>128</v>
@@ -15059,13 +15196,13 @@
         <v>179</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G264" s="20"/>
       <c r="H264" s="23"/>
@@ -15075,7 +15212,7 @@
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="21" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="B265" s="21" t="s">
         <v>128</v>
@@ -15084,13 +15221,13 @@
         <v>190</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="F265" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G265" s="20"/>
       <c r="H265" s="23"/>
@@ -15100,7 +15237,7 @@
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="21" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="B266" s="21" t="s">
         <v>128</v>
@@ -15109,13 +15246,13 @@
         <v>194</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="F266" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G266" s="20"/>
       <c r="H266" s="23"/>
@@ -15125,7 +15262,7 @@
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="21" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="B267" s="21" t="s">
         <v>128</v>
@@ -15134,13 +15271,13 @@
         <v>198</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F267" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G267" s="20"/>
       <c r="H267" s="23"/>
@@ -15150,7 +15287,7 @@
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="21" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="B268" s="21" t="s">
         <v>128</v>
@@ -15159,13 +15296,13 @@
         <v>202</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="F268" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G268" s="20"/>
       <c r="H268" s="23"/>
@@ -15175,7 +15312,7 @@
     </row>
     <row r="269" spans="1:11">
       <c r="A269" s="21" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="B269" s="21" t="s">
         <v>128</v>
@@ -15184,13 +15321,13 @@
         <v>206</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="F269" s="22" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="G269" s="20"/>
       <c r="H269" s="23"/>
@@ -15200,7 +15337,7 @@
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="21" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="B270" s="21" t="s">
         <v>130</v>
@@ -15209,13 +15346,13 @@
         <v>174</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="F270" s="22" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="G270" s="20"/>
       <c r="H270" s="23"/>
@@ -15225,7 +15362,7 @@
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="21" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="B271" s="21" t="s">
         <v>130</v>
@@ -15234,13 +15371,13 @@
         <v>179</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="F271" s="22" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="G271" s="20"/>
       <c r="H271" s="23"/>
@@ -15250,7 +15387,7 @@
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="21" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="B272" s="21" t="s">
         <v>132</v>
@@ -15259,13 +15396,13 @@
         <v>174</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="F272" s="22" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G272" s="20"/>
       <c r="H272" s="23"/>
@@ -15275,7 +15412,7 @@
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="21" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="B273" s="21" t="s">
         <v>132</v>
@@ -15284,13 +15421,13 @@
         <v>179</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="F273" s="22" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G273" s="20"/>
       <c r="H273" s="23"/>
@@ -15300,7 +15437,7 @@
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="21" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="B274" s="21" t="s">
         <v>132</v>
@@ -15309,13 +15446,13 @@
         <v>190</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="F274" s="22" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G274" s="20"/>
       <c r="H274" s="23"/>
@@ -15325,7 +15462,7 @@
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="21" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="B275" s="21" t="s">
         <v>132</v>
@@ -15334,13 +15471,13 @@
         <v>194</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="F275" s="22" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="G275" s="20"/>
       <c r="H275" s="23"/>
@@ -15350,7 +15487,7 @@
     </row>
     <row r="276" spans="1:11">
       <c r="A276" s="21" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="B276" s="21" t="s">
         <v>134</v>
@@ -15359,13 +15496,13 @@
         <v>174</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="F276" s="22" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="G276" s="20"/>
       <c r="H276" s="23"/>
@@ -15375,7 +15512,7 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="21" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="B277" s="21" t="s">
         <v>135</v>
@@ -15384,13 +15521,13 @@
         <v>174</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="F277" s="22" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G277" s="20"/>
       <c r="H277" s="23"/>
@@ -15400,7 +15537,7 @@
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="21" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="B278" s="21" t="s">
         <v>135</v>
@@ -15409,13 +15546,13 @@
         <v>179</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G278" s="20"/>
       <c r="H278" s="23"/>
@@ -15425,7 +15562,7 @@
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="21" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="B279" s="21" t="s">
         <v>135</v>
@@ -15434,13 +15571,13 @@
         <v>190</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G279" s="20"/>
       <c r="H279" s="23"/>
@@ -15450,7 +15587,7 @@
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="21" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="B280" s="21" t="s">
         <v>135</v>
@@ -15459,13 +15596,13 @@
         <v>194</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G280" s="20"/>
       <c r="H280" s="23"/>
@@ -15475,7 +15612,7 @@
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="21" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="B281" s="21" t="s">
         <v>135</v>
@@ -15484,13 +15621,13 @@
         <v>198</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G281" s="20"/>
       <c r="H281" s="23"/>
@@ -15500,7 +15637,7 @@
     </row>
     <row r="282" spans="1:11">
       <c r="A282" s="21" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="B282" s="21" t="s">
         <v>137</v>
@@ -15509,13 +15646,13 @@
         <v>174</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G282" s="20"/>
       <c r="H282" s="23"/>
@@ -15525,7 +15662,7 @@
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="21" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B283" s="21" t="s">
         <v>137</v>
@@ -15534,13 +15671,13 @@
         <v>179</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G283" s="20"/>
       <c r="H283" s="23"/>
@@ -15550,7 +15687,7 @@
     </row>
     <row r="284" spans="1:11">
       <c r="A284" s="21" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B284" s="21" t="s">
         <v>137</v>
@@ -15559,13 +15696,13 @@
         <v>190</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="F284" s="22" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G284" s="20"/>
       <c r="H284" s="23"/>
@@ -15575,7 +15712,7 @@
     </row>
     <row r="285" spans="1:11">
       <c r="A285" s="21" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B285" s="21" t="s">
         <v>137</v>
@@ -15584,13 +15721,13 @@
         <v>194</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G285" s="20"/>
       <c r="H285" s="23"/>
@@ -15600,7 +15737,7 @@
     </row>
     <row r="286" spans="1:11">
       <c r="A286" s="21" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="B286" s="21" t="s">
         <v>140</v>
@@ -15609,13 +15746,13 @@
         <v>174</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G286" s="20"/>
       <c r="H286" s="23"/>
@@ -15625,7 +15762,7 @@
     </row>
     <row r="287" spans="1:11">
       <c r="A287" s="21" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="B287" s="21" t="s">
         <v>140</v>
@@ -15634,13 +15771,13 @@
         <v>179</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="F287" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G287" s="20"/>
       <c r="H287" s="23"/>
@@ -15650,7 +15787,7 @@
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="21" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="B288" s="21" t="s">
         <v>140</v>
@@ -15659,13 +15796,13 @@
         <v>190</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="F288" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G288" s="20"/>
       <c r="H288" s="23"/>
@@ -15675,7 +15812,7 @@
     </row>
     <row r="289" spans="1:11">
       <c r="A289" s="21" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="B289" s="21" t="s">
         <v>140</v>
@@ -15684,13 +15821,13 @@
         <v>194</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="F289" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G289" s="20"/>
       <c r="H289" s="23"/>
@@ -15700,7 +15837,7 @@
     </row>
     <row r="290" spans="1:11">
       <c r="A290" s="21" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="B290" s="21" t="s">
         <v>142</v>
@@ -15709,13 +15846,13 @@
         <v>174</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="F290" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G290" s="20"/>
       <c r="H290" s="23"/>
@@ -15725,7 +15862,7 @@
     </row>
     <row r="291" spans="1:11">
       <c r="A291" s="21" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="B291" s="21" t="s">
         <v>142</v>
@@ -15734,13 +15871,13 @@
         <v>179</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="F291" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G291" s="20"/>
       <c r="H291" s="23"/>
@@ -15750,7 +15887,7 @@
     </row>
     <row r="292" spans="1:11">
       <c r="A292" s="21" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="B292" s="21" t="s">
         <v>142</v>
@@ -15759,13 +15896,13 @@
         <v>190</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="F292" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G292" s="20"/>
       <c r="H292" s="23"/>
@@ -15775,7 +15912,7 @@
     </row>
     <row r="293" spans="1:11">
       <c r="A293" s="21" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="B293" s="21" t="s">
         <v>142</v>
@@ -15784,13 +15921,13 @@
         <v>194</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="F293" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G293" s="20"/>
       <c r="H293" s="23"/>
@@ -15800,7 +15937,7 @@
     </row>
     <row r="294" spans="1:11">
       <c r="A294" s="21" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="B294" s="21" t="s">
         <v>142</v>
@@ -15809,13 +15946,13 @@
         <v>198</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="F294" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G294" s="20"/>
       <c r="H294" s="23"/>
@@ -15825,7 +15962,7 @@
     </row>
     <row r="295" spans="1:11">
       <c r="A295" s="21" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="B295" s="21" t="s">
         <v>142</v>
@@ -15834,13 +15971,13 @@
         <v>202</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="F295" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G295" s="20"/>
       <c r="H295" s="23"/>
@@ -15850,7 +15987,7 @@
     </row>
     <row r="296" spans="1:11">
       <c r="A296" s="21" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="B296" s="21" t="s">
         <v>142</v>
@@ -15859,13 +15996,13 @@
         <v>206</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="F296" s="22" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="G296" s="20"/>
       <c r="H296" s="23"/>
@@ -15875,7 +16012,7 @@
     </row>
     <row r="297" spans="1:11">
       <c r="A297" s="21" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="B297" s="21" t="s">
         <v>144</v>
@@ -15884,13 +16021,13 @@
         <v>174</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="F297" s="22" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="G297" s="20"/>
       <c r="H297" s="23"/>
@@ -15900,7 +16037,7 @@
     </row>
     <row r="298" spans="1:11">
       <c r="A298" s="21" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="B298" s="21" t="s">
         <v>146</v>
@@ -15909,13 +16046,13 @@
         <v>174</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="F298" s="22" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="G298" s="20"/>
       <c r="H298" s="23"/>
@@ -15925,7 +16062,7 @@
     </row>
     <row r="299" spans="1:11">
       <c r="A299" s="21" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="B299" s="21" t="s">
         <v>146</v>
@@ -15934,13 +16071,13 @@
         <v>179</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="F299" s="22" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="G299" s="20"/>
       <c r="H299" s="23"/>
@@ -15950,7 +16087,7 @@
     </row>
     <row r="300" spans="1:11">
       <c r="A300" s="21" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="B300" s="21" t="s">
         <v>146</v>
@@ -15959,13 +16096,13 @@
         <v>190</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="F300" s="22" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="G300" s="20"/>
       <c r="H300" s="23"/>
@@ -15975,7 +16112,7 @@
     </row>
     <row r="301" spans="1:11">
       <c r="A301" s="21" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="B301" s="21" t="s">
         <v>147</v>
@@ -15984,13 +16121,13 @@
         <v>174</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="F301" s="22" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="G301" s="20"/>
       <c r="H301" s="23"/>
@@ -16000,7 +16137,7 @@
     </row>
     <row r="302" spans="1:11">
       <c r="A302" s="21" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="B302" s="21" t="s">
         <v>147</v>
@@ -16009,13 +16146,13 @@
         <v>179</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="F302" s="22" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="G302" s="20"/>
       <c r="H302" s="23"/>
@@ -16025,7 +16162,7 @@
     </row>
     <row r="303" spans="1:11">
       <c r="A303" s="21" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="B303" s="21" t="s">
         <v>147</v>
@@ -16034,13 +16171,13 @@
         <v>190</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="F303" s="22" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="G303" s="20"/>
       <c r="H303" s="23"/>
@@ -16050,7 +16187,7 @@
     </row>
     <row r="304" spans="1:11">
       <c r="A304" s="21" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="B304" s="21" t="s">
         <v>148</v>
@@ -16059,13 +16196,13 @@
         <v>174</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="F304" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G304" s="20"/>
       <c r="H304" s="23"/>
@@ -16075,7 +16212,7 @@
     </row>
     <row r="305" spans="1:11">
       <c r="A305" s="21" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="B305" s="21" t="s">
         <v>148</v>
@@ -16084,13 +16221,13 @@
         <v>179</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G305" s="20"/>
       <c r="H305" s="23"/>
@@ -16100,7 +16237,7 @@
     </row>
     <row r="306" spans="1:11">
       <c r="A306" s="21" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="B306" s="21" t="s">
         <v>148</v>
@@ -16109,13 +16246,13 @@
         <v>190</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G306" s="20"/>
       <c r="H306" s="23"/>
@@ -16125,7 +16262,7 @@
     </row>
     <row r="307" spans="1:11">
       <c r="A307" s="21" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="B307" s="21" t="s">
         <v>148</v>
@@ -16134,13 +16271,13 @@
         <v>194</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="F307" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G307" s="20"/>
       <c r="H307" s="23"/>
@@ -16150,7 +16287,7 @@
     </row>
     <row r="308" spans="1:11">
       <c r="A308" s="21" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="B308" s="21" t="s">
         <v>148</v>
@@ -16159,13 +16296,13 @@
         <v>198</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="F308" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G308" s="20"/>
       <c r="H308" s="23"/>
@@ -16175,7 +16312,7 @@
     </row>
     <row r="309" spans="1:11">
       <c r="A309" s="21" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="B309" s="21" t="s">
         <v>148</v>
@@ -16184,13 +16321,13 @@
         <v>202</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="F309" s="22" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="G309" s="20"/>
       <c r="H309" s="23"/>
@@ -16200,7 +16337,7 @@
     </row>
     <row r="310" spans="1:11">
       <c r="A310" s="21" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="B310" s="21" t="s">
         <v>150</v>
@@ -16209,13 +16346,13 @@
         <v>174</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="G310" s="20"/>
       <c r="H310" s="23"/>
@@ -16225,7 +16362,7 @@
     </row>
     <row r="311" spans="1:11">
       <c r="A311" s="21" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="B311" s="21" t="s">
         <v>150</v>
@@ -16234,13 +16371,13 @@
         <v>179</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="F311" s="22" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="G311" s="20"/>
       <c r="H311" s="23"/>
@@ -16250,7 +16387,7 @@
     </row>
     <row r="312" spans="1:11">
       <c r="A312" s="21" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="B312" s="21" t="s">
         <v>153</v>
@@ -16259,13 +16396,13 @@
         <v>174</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="G312" s="20"/>
       <c r="H312" s="23"/>
@@ -16275,7 +16412,7 @@
     </row>
     <row r="313" spans="1:11">
       <c r="A313" s="21" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="B313" s="21" t="s">
         <v>153</v>
@@ -16284,13 +16421,13 @@
         <v>179</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="G313" s="20"/>
       <c r="H313" s="23"/>
@@ -16300,7 +16437,7 @@
     </row>
     <row r="314" spans="1:11">
       <c r="A314" s="21" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="B314" s="21" t="s">
         <v>155</v>
@@ -16309,13 +16446,13 @@
         <v>174</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="F314" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G314" s="20"/>
       <c r="H314" s="23"/>
@@ -16325,7 +16462,7 @@
     </row>
     <row r="315" spans="1:11">
       <c r="A315" s="21" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="B315" s="21" t="s">
         <v>155</v>
@@ -16334,13 +16471,13 @@
         <v>179</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="F315" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G315" s="20"/>
       <c r="H315" s="23"/>
@@ -16350,7 +16487,7 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="21" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="B316" s="21" t="s">
         <v>155</v>
@@ -16359,13 +16496,13 @@
         <v>190</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="F316" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G316" s="20"/>
       <c r="H316" s="23"/>
@@ -16375,7 +16512,7 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="21" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="B317" s="21" t="s">
         <v>155</v>
@@ -16384,13 +16521,13 @@
         <v>194</v>
       </c>
       <c r="D317" s="22" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="E317" s="21" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="F317" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G317" s="20"/>
       <c r="H317" s="23"/>
@@ -16400,7 +16537,7 @@
     </row>
     <row r="318" spans="1:11">
       <c r="A318" s="21" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="B318" s="21" t="s">
         <v>155</v>
@@ -16409,13 +16546,13 @@
         <v>198</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="F318" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G318" s="20"/>
       <c r="H318" s="23"/>
@@ -16425,7 +16562,7 @@
     </row>
     <row r="319" spans="1:11">
       <c r="A319" s="21" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="B319" s="21" t="s">
         <v>155</v>
@@ -16434,13 +16571,13 @@
         <v>202</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="F319" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G319" s="20"/>
       <c r="H319" s="23"/>
@@ -16450,7 +16587,7 @@
     </row>
     <row r="320" spans="1:11">
       <c r="A320" s="21" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="B320" s="21" t="s">
         <v>155</v>
@@ -16459,13 +16596,13 @@
         <v>206</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="F320" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G320" s="20"/>
       <c r="H320" s="23"/>
@@ -16475,7 +16612,7 @@
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="21" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
       <c r="B321" s="21" t="s">
         <v>155</v>
@@ -16484,13 +16621,13 @@
         <v>210</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="F321" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G321" s="20"/>
       <c r="H321" s="23"/>
@@ -16500,7 +16637,7 @@
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="21" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="B322" s="21" t="s">
         <v>155</v>
@@ -16509,13 +16646,13 @@
         <v>258</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="F322" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G322" s="20"/>
       <c r="H322" s="23"/>
@@ -16525,7 +16662,7 @@
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="21" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="B323" s="21" t="s">
         <v>155</v>
@@ -16534,13 +16671,13 @@
         <v>262</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="F323" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G323" s="20"/>
       <c r="H323" s="23"/>
@@ -16550,7 +16687,7 @@
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="21" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="B324" s="21" t="s">
         <v>155</v>
@@ -16559,13 +16696,13 @@
         <v>296</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="F324" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G324" s="20"/>
       <c r="H324" s="23"/>
@@ -16575,7 +16712,7 @@
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="21" t="s">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="B325" s="21" t="s">
         <v>155</v>
@@ -16584,13 +16721,13 @@
         <v>300</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1185</v>
+        <v>1180</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1186</v>
+        <v>1181</v>
       </c>
       <c r="F325" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G325" s="20"/>
       <c r="H325" s="23"/>
@@ -16600,7 +16737,7 @@
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="21" t="s">
-        <v>1187</v>
+        <v>1182</v>
       </c>
       <c r="B326" s="21" t="s">
         <v>155</v>
@@ -16609,13 +16746,13 @@
         <v>304</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1188</v>
+        <v>1183</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="F326" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G326" s="20"/>
       <c r="H326" s="23"/>
@@ -16625,7 +16762,7 @@
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="21" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="B327" s="21" t="s">
         <v>155</v>
@@ -16634,13 +16771,13 @@
         <v>308</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="F327" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G327" s="20"/>
       <c r="H327" s="23"/>
@@ -16650,7 +16787,7 @@
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="21" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>155</v>
@@ -16659,13 +16796,13 @@
         <v>312</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="F328" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G328" s="20"/>
       <c r="H328" s="23"/>
@@ -16675,7 +16812,7 @@
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="21" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>155</v>
@@ -16684,13 +16821,13 @@
         <v>316</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="F329" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G329" s="20"/>
       <c r="H329" s="23"/>
@@ -16700,7 +16837,7 @@
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="21" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="B330" s="21" t="s">
         <v>155</v>
@@ -16709,13 +16846,13 @@
         <v>320</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="F330" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G330" s="20"/>
       <c r="H330" s="23"/>
@@ -16725,7 +16862,7 @@
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="21" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>155</v>
@@ -16734,13 +16871,13 @@
         <v>324</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="E331" s="21" t="s">
         <v>188</v>
       </c>
       <c r="F331" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G331" s="20"/>
       <c r="H331" s="23"/>
@@ -16750,7 +16887,7 @@
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="21" t="s">
-        <v>1204</v>
+        <v>1199</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>155</v>
@@ -16759,13 +16896,13 @@
         <v>328</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="F332" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G332" s="20"/>
       <c r="H332" s="23"/>
@@ -16775,7 +16912,7 @@
     </row>
     <row r="333" spans="1:11">
       <c r="A333" s="21" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>155</v>
@@ -16784,13 +16921,13 @@
         <v>332</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F333" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G333" s="20"/>
       <c r="H333" s="23"/>
@@ -16800,7 +16937,7 @@
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="21" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>155</v>
@@ -16809,13 +16946,13 @@
         <v>336</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F334" s="22" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="G334" s="20"/>
       <c r="H334" s="23"/>
@@ -16825,7 +16962,7 @@
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="21" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>156</v>
@@ -16834,13 +16971,13 @@
         <v>174</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="F335" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G335" s="20"/>
       <c r="H335" s="23"/>
@@ -16850,7 +16987,7 @@
     </row>
     <row r="336" spans="1:11">
       <c r="A336" s="21" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>156</v>
@@ -16859,13 +16996,13 @@
         <v>179</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="F336" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G336" s="20"/>
       <c r="H336" s="23"/>
@@ -16875,7 +17012,7 @@
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="21" t="s">
-        <v>1219</v>
+        <v>1214</v>
       </c>
       <c r="B337" s="21" t="s">
         <v>156</v>
@@ -16884,13 +17021,13 @@
         <v>190</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="F337" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G337" s="20"/>
       <c r="H337" s="23"/>
@@ -16900,7 +17037,7 @@
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="21" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="B338" s="21" t="s">
         <v>156</v>
@@ -16909,13 +17046,13 @@
         <v>194</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
       <c r="F338" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G338" s="20"/>
       <c r="H338" s="23"/>
@@ -16925,7 +17062,7 @@
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="21" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="B339" s="21" t="s">
         <v>156</v>
@@ -16934,13 +17071,13 @@
         <v>198</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F339" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G339" s="20"/>
       <c r="H339" s="23"/>
@@ -16950,7 +17087,7 @@
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="21" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="B340" s="21" t="s">
         <v>156</v>
@@ -16959,13 +17096,13 @@
         <v>202</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="F340" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G340" s="20"/>
       <c r="H340" s="23"/>
@@ -16975,7 +17112,7 @@
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="21" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="B341" s="21" t="s">
         <v>156</v>
@@ -16984,13 +17121,13 @@
         <v>206</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="F341" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G341" s="20"/>
       <c r="H341" s="23"/>
@@ -17000,7 +17137,7 @@
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="21" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="B342" s="21" t="s">
         <v>156</v>
@@ -17009,13 +17146,13 @@
         <v>210</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F342" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G342" s="20"/>
       <c r="H342" s="23"/>
@@ -17025,7 +17162,7 @@
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="21" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="B343" s="21" t="s">
         <v>156</v>
@@ -17034,13 +17171,13 @@
         <v>258</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="F343" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G343" s="20"/>
       <c r="H343" s="23"/>
@@ -17050,7 +17187,7 @@
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="21" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="B344" s="21" t="s">
         <v>156</v>
@@ -17059,13 +17196,13 @@
         <v>262</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="F344" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G344" s="20"/>
       <c r="H344" s="23"/>
@@ -17075,7 +17212,7 @@
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="21" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="B345" s="21" t="s">
         <v>156</v>
@@ -17084,13 +17221,13 @@
         <v>296</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F345" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G345" s="20"/>
       <c r="H345" s="23"/>
@@ -17100,7 +17237,7 @@
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="21" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="B346" s="21" t="s">
         <v>156</v>
@@ -17109,13 +17246,13 @@
         <v>300</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="F346" s="22" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="G346" s="20"/>
       <c r="H346" s="23"/>
@@ -17125,7 +17262,7 @@
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="21" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="B347" s="21" t="s">
         <v>158</v>
@@ -17134,13 +17271,13 @@
         <v>174</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1251</v>
+        <v>1246</v>
       </c>
       <c r="F347" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G347" s="20"/>
       <c r="H347" s="23"/>
@@ -17150,7 +17287,7 @@
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="21" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="B348" s="21" t="s">
         <v>158</v>
@@ -17159,13 +17296,13 @@
         <v>179</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="F348" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G348" s="20"/>
       <c r="H348" s="23"/>
@@ -17175,7 +17312,7 @@
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="21" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="B349" s="21" t="s">
         <v>158</v>
@@ -17184,13 +17321,13 @@
         <v>190</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="F349" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G349" s="20"/>
       <c r="H349" s="23"/>
@@ -17200,7 +17337,7 @@
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="21" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="B350" s="21" t="s">
         <v>158</v>
@@ -17209,13 +17346,13 @@
         <v>194</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="F350" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G350" s="20"/>
       <c r="H350" s="23"/>
@@ -17225,7 +17362,7 @@
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="21" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="B351" s="21" t="s">
         <v>158</v>
@@ -17234,13 +17371,13 @@
         <v>198</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="F351" s="22" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G351" s="20"/>
       <c r="H351" s="23"/>
@@ -38696,6 +38833,11 @@
   <conditionalFormatting sqref="A4:A1995">
     <cfRule type="duplicateValues" dxfId="0" priority="40"/>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H214:H227" xr:uid="{904F9C07-3432-407C-9B6A-2B1BA8B10BD0}">
+      <formula1>"Daily 60 Days, Daily 120 Days, Weekly 12W, Weekly 24W, Monthly 3M, Monthly 6M, 60-Day Asset, 120-Day Asset, Weekly 12W Asset, Weekly 24W Asset, Monthly 3M Asset, Monthly 6M Asset"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
@@ -38718,60 +38860,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="34" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
+      <c r="A1" s="42" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="A2" s="36" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B2" s="36"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="28" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>1266</v>
-      </c>
-      <c r="H3" s="44"/>
+        <v>1261</v>
+      </c>
+      <c r="H3" s="30"/>
     </row>
     <row r="4" spans="1:8" ht="14.4" customHeight="1">
       <c r="A4" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="s">
@@ -38783,17 +38925,17 @@
       <c r="G4" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="45"/>
+      <c r="H4" s="31"/>
     </row>
     <row r="5" spans="1:8" ht="14.4" customHeight="1">
       <c r="A5" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9" t="s">
@@ -38805,21 +38947,21 @@
       <c r="G5" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="45"/>
+      <c r="H5" s="31"/>
     </row>
     <row r="6" spans="1:8" ht="14.4" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="9" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>70</v>
@@ -38827,17 +38969,17 @@
       <c r="G6" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="45"/>
+      <c r="H6" s="31"/>
     </row>
     <row r="7" spans="1:8" ht="14.4" customHeight="1">
       <c r="A7" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9" t="s">
@@ -38849,7 +38991,7 @@
       <c r="G7" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H7" s="45"/>
+      <c r="H7" s="31"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="3"/>
@@ -38859,7 +39001,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="12"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="46"/>
+      <c r="H8" s="32"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="3"/>
@@ -38869,7 +39011,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="12"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="46"/>
+      <c r="H9" s="32"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="3"/>
@@ -38879,21 +39021,21 @@
       <c r="E10" s="3"/>
       <c r="F10" s="12"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="46"/>
+      <c r="H10" s="32"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="28" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2"/>
       <c r="E11" s="3"/>
       <c r="F11" s="12"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="46"/>
+      <c r="H11" s="32"/>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="3"/>
@@ -38903,7 +39045,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="12"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="46"/>
+      <c r="H12" s="32"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="3"/>
@@ -38913,7 +39055,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="12"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="46"/>
+      <c r="H13" s="32"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="3"/>
@@ -38923,7 +39065,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="12"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="46"/>
+      <c r="H14" s="32"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="3"/>
@@ -38933,7 +39075,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="12"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="46"/>
+      <c r="H15" s="32"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="3"/>
@@ -38943,7 +39085,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="12"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="46"/>
+      <c r="H16" s="32"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
@@ -38953,7 +39095,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="12"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="46"/>
+      <c r="H17" s="32"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>
@@ -38963,7 +39105,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="12"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="46"/>
+      <c r="H18" s="32"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2"/>
@@ -38973,7 +39115,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="12"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="46"/>
+      <c r="H19" s="32"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2"/>
@@ -38983,7 +39125,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="12"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="46"/>
+      <c r="H20" s="32"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="3"/>
@@ -38993,7 +39135,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="12"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="46"/>
+      <c r="H21" s="32"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="3"/>
@@ -39003,7 +39145,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="12"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="46"/>
+      <c r="H22" s="32"/>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="3"/>
@@ -39013,7 +39155,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="12"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="46"/>
+      <c r="H23" s="32"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="3"/>
@@ -39023,7 +39165,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="12"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="46"/>
+      <c r="H24" s="32"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="3"/>
@@ -39033,7 +39175,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="12"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="46"/>
+      <c r="H25" s="32"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="3"/>
@@ -39043,7 +39185,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="12"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="46"/>
+      <c r="H26" s="32"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="3"/>
@@ -39053,7 +39195,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="12"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="46"/>
+      <c r="H27" s="32"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="3"/>
@@ -39063,7 +39205,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="12"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="46"/>
+      <c r="H28" s="32"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="3"/>
@@ -39073,7 +39215,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="12"/>
       <c r="G29" s="3"/>
-      <c r="H29" s="46"/>
+      <c r="H29" s="32"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="3"/>
@@ -39083,7 +39225,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="12"/>
       <c r="G30" s="3"/>
-      <c r="H30" s="46"/>
+      <c r="H30" s="32"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="3"/>
@@ -39093,7 +39235,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="12"/>
       <c r="G31" s="3"/>
-      <c r="H31" s="46"/>
+      <c r="H31" s="32"/>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="3"/>
@@ -39103,7 +39245,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="12"/>
       <c r="G32" s="3"/>
-      <c r="H32" s="46"/>
+      <c r="H32" s="32"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="3"/>
@@ -39113,7 +39255,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="12"/>
       <c r="G33" s="3"/>
-      <c r="H33" s="46"/>
+      <c r="H33" s="32"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="3"/>
@@ -39123,7 +39265,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="12"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="46"/>
+      <c r="H34" s="32"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="3"/>
@@ -39133,7 +39275,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="12"/>
       <c r="G35" s="3"/>
-      <c r="H35" s="46"/>
+      <c r="H35" s="32"/>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="3"/>
@@ -39143,7 +39285,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="12"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="46"/>
+      <c r="H36" s="32"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="3"/>
@@ -39153,7 +39295,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="12"/>
       <c r="G37" s="3"/>
-      <c r="H37" s="46"/>
+      <c r="H37" s="32"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="3"/>
@@ -39163,7 +39305,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="12"/>
       <c r="G38" s="3"/>
-      <c r="H38" s="46"/>
+      <c r="H38" s="32"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="3"/>
@@ -39173,7 +39315,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="12"/>
       <c r="G39" s="3"/>
-      <c r="H39" s="46"/>
+      <c r="H39" s="32"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="3"/>
@@ -39183,7 +39325,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="12"/>
       <c r="G40" s="3"/>
-      <c r="H40" s="46"/>
+      <c r="H40" s="32"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="3"/>
@@ -39193,7 +39335,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="12"/>
       <c r="G41" s="3"/>
-      <c r="H41" s="46"/>
+      <c r="H41" s="32"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="3"/>
@@ -39203,7 +39345,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="12"/>
       <c r="G42" s="3"/>
-      <c r="H42" s="46"/>
+      <c r="H42" s="32"/>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="3"/>
@@ -39213,7 +39355,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="12"/>
       <c r="G43" s="3"/>
-      <c r="H43" s="46"/>
+      <c r="H43" s="32"/>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="3"/>
@@ -39223,7 +39365,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="12"/>
       <c r="G44" s="3"/>
-      <c r="H44" s="46"/>
+      <c r="H44" s="32"/>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="3"/>
@@ -39233,7 +39375,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="12"/>
       <c r="G45" s="3"/>
-      <c r="H45" s="46"/>
+      <c r="H45" s="32"/>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="3"/>
@@ -39243,7 +39385,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="12"/>
       <c r="G46" s="3"/>
-      <c r="H46" s="46"/>
+      <c r="H46" s="32"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="3"/>
@@ -39253,7 +39395,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="12"/>
       <c r="G47" s="3"/>
-      <c r="H47" s="46"/>
+      <c r="H47" s="32"/>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="3"/>
@@ -39263,7 +39405,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="12"/>
       <c r="G48" s="3"/>
-      <c r="H48" s="46"/>
+      <c r="H48" s="32"/>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="3"/>
@@ -39273,7 +39415,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="12"/>
       <c r="G49" s="3"/>
-      <c r="H49" s="46"/>
+      <c r="H49" s="32"/>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="3"/>
@@ -39283,7 +39425,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="12"/>
       <c r="G50" s="3"/>
-      <c r="H50" s="46"/>
+      <c r="H50" s="32"/>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="3"/>
@@ -39293,7 +39435,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="12"/>
       <c r="G51" s="3"/>
-      <c r="H51" s="46"/>
+      <c r="H51" s="32"/>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="3"/>
@@ -39303,7 +39445,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="12"/>
       <c r="G52" s="3"/>
-      <c r="H52" s="46"/>
+      <c r="H52" s="32"/>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="3"/>
@@ -39313,7 +39455,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="12"/>
       <c r="G53" s="3"/>
-      <c r="H53" s="46"/>
+      <c r="H53" s="32"/>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="3"/>
@@ -39323,7 +39465,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="12"/>
       <c r="G54" s="3"/>
-      <c r="H54" s="46"/>
+      <c r="H54" s="32"/>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="3"/>
@@ -39333,7 +39475,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="12"/>
       <c r="G55" s="3"/>
-      <c r="H55" s="46"/>
+      <c r="H55" s="32"/>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="3"/>
@@ -39343,7 +39485,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="12"/>
       <c r="G56" s="3"/>
-      <c r="H56" s="46"/>
+      <c r="H56" s="32"/>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="3"/>
@@ -39353,7 +39495,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="12"/>
       <c r="G57" s="3"/>
-      <c r="H57" s="46"/>
+      <c r="H57" s="32"/>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="3"/>
@@ -39363,7 +39505,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="12"/>
       <c r="G58" s="3"/>
-      <c r="H58" s="46"/>
+      <c r="H58" s="32"/>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="3"/>
@@ -39373,7 +39515,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="12"/>
       <c r="G59" s="3"/>
-      <c r="H59" s="46"/>
+      <c r="H59" s="32"/>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="3"/>
@@ -39383,7 +39525,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="12"/>
       <c r="G60" s="3"/>
-      <c r="H60" s="46"/>
+      <c r="H60" s="32"/>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="3"/>
@@ -39393,7 +39535,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="12"/>
       <c r="G61" s="3"/>
-      <c r="H61" s="46"/>
+      <c r="H61" s="32"/>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="3"/>
@@ -39403,7 +39545,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="12"/>
       <c r="G62" s="3"/>
-      <c r="H62" s="46"/>
+      <c r="H62" s="32"/>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="3"/>
@@ -39413,7 +39555,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="12"/>
       <c r="G63" s="3"/>
-      <c r="H63" s="46"/>
+      <c r="H63" s="32"/>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="3"/>
@@ -39423,7 +39565,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="12"/>
       <c r="G64" s="3"/>
-      <c r="H64" s="46"/>
+      <c r="H64" s="32"/>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="3"/>
@@ -39433,7 +39575,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="12"/>
       <c r="G65" s="3"/>
-      <c r="H65" s="46"/>
+      <c r="H65" s="32"/>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="3"/>
@@ -39443,7 +39585,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="12"/>
       <c r="G66" s="3"/>
-      <c r="H66" s="46"/>
+      <c r="H66" s="32"/>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="3"/>
@@ -39453,7 +39595,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="12"/>
       <c r="G67" s="3"/>
-      <c r="H67" s="46"/>
+      <c r="H67" s="32"/>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="3"/>
@@ -39463,7 +39605,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="12"/>
       <c r="G68" s="3"/>
-      <c r="H68" s="46"/>
+      <c r="H68" s="32"/>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="3"/>
@@ -39473,7 +39615,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="12"/>
       <c r="G69" s="3"/>
-      <c r="H69" s="46"/>
+      <c r="H69" s="32"/>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="3"/>
@@ -39483,7 +39625,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="12"/>
       <c r="G70" s="3"/>
-      <c r="H70" s="46"/>
+      <c r="H70" s="32"/>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="3"/>
@@ -39493,7 +39635,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="12"/>
       <c r="G71" s="3"/>
-      <c r="H71" s="46"/>
+      <c r="H71" s="32"/>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="3"/>
@@ -39503,7 +39645,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="12"/>
       <c r="G72" s="3"/>
-      <c r="H72" s="46"/>
+      <c r="H72" s="32"/>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="3"/>
@@ -39513,7 +39655,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="12"/>
       <c r="G73" s="3"/>
-      <c r="H73" s="46"/>
+      <c r="H73" s="32"/>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="3"/>
@@ -39523,7 +39665,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="12"/>
       <c r="G74" s="3"/>
-      <c r="H74" s="46"/>
+      <c r="H74" s="32"/>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="3"/>
@@ -39533,7 +39675,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="12"/>
       <c r="G75" s="3"/>
-      <c r="H75" s="46"/>
+      <c r="H75" s="32"/>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="3"/>
@@ -39543,7 +39685,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="12"/>
       <c r="G76" s="3"/>
-      <c r="H76" s="46"/>
+      <c r="H76" s="32"/>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="3"/>
@@ -39553,7 +39695,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="12"/>
       <c r="G77" s="3"/>
-      <c r="H77" s="46"/>
+      <c r="H77" s="32"/>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="3"/>
@@ -39563,7 +39705,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="12"/>
       <c r="G78" s="3"/>
-      <c r="H78" s="46"/>
+      <c r="H78" s="32"/>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="3"/>
@@ -39573,7 +39715,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="12"/>
       <c r="G79" s="3"/>
-      <c r="H79" s="46"/>
+      <c r="H79" s="32"/>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="3"/>
@@ -39583,7 +39725,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="12"/>
       <c r="G80" s="3"/>
-      <c r="H80" s="46"/>
+      <c r="H80" s="32"/>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="3"/>
@@ -39593,7 +39735,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="12"/>
       <c r="G81" s="3"/>
-      <c r="H81" s="46"/>
+      <c r="H81" s="32"/>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="3"/>
@@ -39603,7 +39745,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="12"/>
       <c r="G82" s="3"/>
-      <c r="H82" s="46"/>
+      <c r="H82" s="32"/>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="3"/>
@@ -39613,7 +39755,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="12"/>
       <c r="G83" s="3"/>
-      <c r="H83" s="46"/>
+      <c r="H83" s="32"/>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="3"/>
@@ -39623,7 +39765,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="12"/>
       <c r="G84" s="3"/>
-      <c r="H84" s="46"/>
+      <c r="H84" s="32"/>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="3"/>
@@ -39633,7 +39775,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="12"/>
       <c r="G85" s="3"/>
-      <c r="H85" s="46"/>
+      <c r="H85" s="32"/>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="3"/>
@@ -39643,7 +39785,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="12"/>
       <c r="G86" s="3"/>
-      <c r="H86" s="46"/>
+      <c r="H86" s="32"/>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="3"/>
@@ -39653,7 +39795,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="12"/>
       <c r="G87" s="3"/>
-      <c r="H87" s="46"/>
+      <c r="H87" s="32"/>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="3"/>
@@ -39663,7 +39805,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="12"/>
       <c r="G88" s="3"/>
-      <c r="H88" s="46"/>
+      <c r="H88" s="32"/>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="3"/>
@@ -39673,7 +39815,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="12"/>
       <c r="G89" s="3"/>
-      <c r="H89" s="46"/>
+      <c r="H89" s="32"/>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="3"/>
@@ -39683,7 +39825,7 @@
       <c r="E90" s="3"/>
       <c r="F90" s="12"/>
       <c r="G90" s="3"/>
-      <c r="H90" s="46"/>
+      <c r="H90" s="32"/>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="3"/>
@@ -39693,7 +39835,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="12"/>
       <c r="G91" s="3"/>
-      <c r="H91" s="46"/>
+      <c r="H91" s="32"/>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="3"/>
@@ -39703,7 +39845,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="12"/>
       <c r="G92" s="3"/>
-      <c r="H92" s="46"/>
+      <c r="H92" s="32"/>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="3"/>
@@ -39713,7 +39855,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="12"/>
       <c r="G93" s="3"/>
-      <c r="H93" s="46"/>
+      <c r="H93" s="32"/>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="3"/>
@@ -39723,7 +39865,7 @@
       <c r="E94" s="3"/>
       <c r="F94" s="12"/>
       <c r="G94" s="3"/>
-      <c r="H94" s="46"/>
+      <c r="H94" s="32"/>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="3"/>
@@ -39733,7 +39875,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="12"/>
       <c r="G95" s="3"/>
-      <c r="H95" s="46"/>
+      <c r="H95" s="32"/>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="3"/>
@@ -39743,7 +39885,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="12"/>
       <c r="G96" s="3"/>
-      <c r="H96" s="46"/>
+      <c r="H96" s="32"/>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="3"/>
@@ -39753,7 +39895,7 @@
       <c r="E97" s="3"/>
       <c r="F97" s="12"/>
       <c r="G97" s="3"/>
-      <c r="H97" s="46"/>
+      <c r="H97" s="32"/>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="3"/>
@@ -39763,7 +39905,7 @@
       <c r="E98" s="3"/>
       <c r="F98" s="12"/>
       <c r="G98" s="3"/>
-      <c r="H98" s="46"/>
+      <c r="H98" s="32"/>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="3"/>
@@ -39773,7 +39915,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="12"/>
       <c r="G99" s="3"/>
-      <c r="H99" s="46"/>
+      <c r="H99" s="32"/>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="3"/>
@@ -39783,7 +39925,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="12"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="46"/>
+      <c r="H100" s="32"/>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="3"/>
@@ -39793,7 +39935,7 @@
       <c r="E101" s="3"/>
       <c r="F101" s="12"/>
       <c r="G101" s="3"/>
-      <c r="H101" s="46"/>
+      <c r="H101" s="32"/>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="3"/>
@@ -39803,7 +39945,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="12"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="46"/>
+      <c r="H102" s="32"/>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="3"/>
@@ -39813,7 +39955,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="12"/>
       <c r="G103" s="3"/>
-      <c r="H103" s="46"/>
+      <c r="H103" s="32"/>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="2"/>
@@ -39823,7 +39965,7 @@
       <c r="E104" s="3"/>
       <c r="F104" s="12"/>
       <c r="G104" s="3"/>
-      <c r="H104" s="46"/>
+      <c r="H104" s="32"/>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="2"/>
@@ -39833,7 +39975,7 @@
       <c r="E105" s="3"/>
       <c r="F105" s="12"/>
       <c r="G105" s="3"/>
-      <c r="H105" s="46"/>
+      <c r="H105" s="32"/>
     </row>
     <row r="106" spans="1:8" ht="38.1" customHeight="1">
       <c r="A106" s="28"/>
@@ -39843,7 +39985,7 @@
       <c r="E106" s="3"/>
       <c r="F106" s="12"/>
       <c r="G106" s="3"/>
-      <c r="H106" s="46"/>
+      <c r="H106" s="32"/>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="3"/>
@@ -39853,7 +39995,7 @@
       <c r="E107" s="3"/>
       <c r="F107" s="12"/>
       <c r="G107" s="3"/>
-      <c r="H107" s="46"/>
+      <c r="H107" s="32"/>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="3"/>
@@ -39863,7 +40005,7 @@
       <c r="E108" s="3"/>
       <c r="F108" s="12"/>
       <c r="G108" s="3"/>
-      <c r="H108" s="46"/>
+      <c r="H108" s="32"/>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="3"/>
@@ -39873,7 +40015,7 @@
       <c r="E109" s="3"/>
       <c r="F109" s="12"/>
       <c r="G109" s="3"/>
-      <c r="H109" s="46"/>
+      <c r="H109" s="32"/>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="3"/>
@@ -39883,7 +40025,7 @@
       <c r="E110" s="3"/>
       <c r="F110" s="12"/>
       <c r="G110" s="3"/>
-      <c r="H110" s="46"/>
+      <c r="H110" s="32"/>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="3"/>
@@ -39893,7 +40035,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="12"/>
       <c r="G111" s="3"/>
-      <c r="H111" s="46"/>
+      <c r="H111" s="32"/>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="3"/>
@@ -39903,7 +40045,7 @@
       <c r="E112" s="3"/>
       <c r="F112" s="12"/>
       <c r="G112" s="3"/>
-      <c r="H112" s="46"/>
+      <c r="H112" s="32"/>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="3"/>
@@ -39913,7 +40055,7 @@
       <c r="E113" s="3"/>
       <c r="F113" s="12"/>
       <c r="G113" s="3"/>
-      <c r="H113" s="46"/>
+      <c r="H113" s="32"/>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="2"/>
@@ -39923,7 +40065,7 @@
       <c r="E114" s="3"/>
       <c r="F114" s="12"/>
       <c r="G114" s="3"/>
-      <c r="H114" s="46"/>
+      <c r="H114" s="32"/>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="2"/>
@@ -39933,7 +40075,7 @@
       <c r="E115" s="3"/>
       <c r="F115" s="12"/>
       <c r="G115" s="3"/>
-      <c r="H115" s="46"/>
+      <c r="H115" s="32"/>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="2"/>
@@ -39943,7 +40085,7 @@
       <c r="E116" s="3"/>
       <c r="F116" s="12"/>
       <c r="G116" s="3"/>
-      <c r="H116" s="46"/>
+      <c r="H116" s="32"/>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="2"/>
@@ -39953,7 +40095,7 @@
       <c r="E117" s="3"/>
       <c r="F117" s="12"/>
       <c r="G117" s="3"/>
-      <c r="H117" s="46"/>
+      <c r="H117" s="32"/>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="2"/>
@@ -39963,7 +40105,7 @@
       <c r="E118" s="3"/>
       <c r="F118" s="12"/>
       <c r="G118" s="3"/>
-      <c r="H118" s="46"/>
+      <c r="H118" s="32"/>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="2"/>
@@ -39973,7 +40115,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="12"/>
       <c r="G119" s="3"/>
-      <c r="H119" s="46"/>
+      <c r="H119" s="32"/>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="2"/>
@@ -39983,7 +40125,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="12"/>
       <c r="G120" s="3"/>
-      <c r="H120" s="46"/>
+      <c r="H120" s="32"/>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="2"/>
@@ -39993,7 +40135,7 @@
       <c r="E121" s="3"/>
       <c r="F121" s="12"/>
       <c r="G121" s="3"/>
-      <c r="H121" s="46"/>
+      <c r="H121" s="32"/>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="2"/>
@@ -40003,7 +40145,7 @@
       <c r="E122" s="3"/>
       <c r="F122" s="12"/>
       <c r="G122" s="3"/>
-      <c r="H122" s="46"/>
+      <c r="H122" s="32"/>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="2"/>
@@ -40013,7 +40155,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="12"/>
       <c r="G123" s="3"/>
-      <c r="H123" s="46"/>
+      <c r="H123" s="32"/>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="2"/>
@@ -40023,7 +40165,7 @@
       <c r="E124" s="3"/>
       <c r="F124" s="12"/>
       <c r="G124" s="3"/>
-      <c r="H124" s="46"/>
+      <c r="H124" s="32"/>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="2"/>
@@ -40033,7 +40175,7 @@
       <c r="E125" s="3"/>
       <c r="F125" s="12"/>
       <c r="G125" s="3"/>
-      <c r="H125" s="46"/>
+      <c r="H125" s="32"/>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="2"/>
@@ -40043,7 +40185,7 @@
       <c r="E126" s="3"/>
       <c r="F126" s="12"/>
       <c r="G126" s="3"/>
-      <c r="H126" s="46"/>
+      <c r="H126" s="32"/>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="2"/>
@@ -40053,7 +40195,7 @@
       <c r="E127" s="3"/>
       <c r="F127" s="12"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="46"/>
+      <c r="H127" s="32"/>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="2"/>
@@ -40063,7 +40205,7 @@
       <c r="E128" s="3"/>
       <c r="F128" s="12"/>
       <c r="G128" s="3"/>
-      <c r="H128" s="46"/>
+      <c r="H128" s="32"/>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="2"/>
@@ -40073,7 +40215,7 @@
       <c r="E129" s="3"/>
       <c r="F129" s="12"/>
       <c r="G129" s="3"/>
-      <c r="H129" s="46"/>
+      <c r="H129" s="32"/>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="2"/>
@@ -40083,7 +40225,7 @@
       <c r="E130" s="3"/>
       <c r="F130" s="12"/>
       <c r="G130" s="3"/>
-      <c r="H130" s="46"/>
+      <c r="H130" s="32"/>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="2"/>
@@ -40093,7 +40235,7 @@
       <c r="E131" s="3"/>
       <c r="F131" s="12"/>
       <c r="G131" s="3"/>
-      <c r="H131" s="46"/>
+      <c r="H131" s="32"/>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="2"/>
@@ -40103,7 +40245,7 @@
       <c r="E132" s="3"/>
       <c r="F132" s="12"/>
       <c r="G132" s="3"/>
-      <c r="H132" s="46"/>
+      <c r="H132" s="32"/>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="2"/>
@@ -40113,7 +40255,7 @@
       <c r="E133" s="3"/>
       <c r="F133" s="12"/>
       <c r="G133" s="3"/>
-      <c r="H133" s="46"/>
+      <c r="H133" s="32"/>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="2"/>
@@ -40123,7 +40265,7 @@
       <c r="E134" s="3"/>
       <c r="F134" s="12"/>
       <c r="G134" s="3"/>
-      <c r="H134" s="46"/>
+      <c r="H134" s="32"/>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="2"/>
@@ -40133,7 +40275,7 @@
       <c r="E135" s="3"/>
       <c r="F135" s="12"/>
       <c r="G135" s="3"/>
-      <c r="H135" s="46"/>
+      <c r="H135" s="32"/>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="2"/>
@@ -40143,7 +40285,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="12"/>
       <c r="G136" s="3"/>
-      <c r="H136" s="46"/>
+      <c r="H136" s="32"/>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="2"/>
@@ -40153,7 +40295,7 @@
       <c r="E137" s="3"/>
       <c r="F137" s="12"/>
       <c r="G137" s="3"/>
-      <c r="H137" s="46"/>
+      <c r="H137" s="32"/>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="2"/>
@@ -40163,7 +40305,7 @@
       <c r="E138" s="3"/>
       <c r="F138" s="12"/>
       <c r="G138" s="3"/>
-      <c r="H138" s="46"/>
+      <c r="H138" s="32"/>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="2"/>
@@ -40173,7 +40315,7 @@
       <c r="E139" s="3"/>
       <c r="F139" s="12"/>
       <c r="G139" s="3"/>
-      <c r="H139" s="46"/>
+      <c r="H139" s="32"/>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="2"/>
@@ -40183,7 +40325,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="12"/>
       <c r="G140" s="3"/>
-      <c r="H140" s="46"/>
+      <c r="H140" s="32"/>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="2"/>
@@ -40193,7 +40335,7 @@
       <c r="E141" s="3"/>
       <c r="F141" s="12"/>
       <c r="G141" s="3"/>
-      <c r="H141" s="46"/>
+      <c r="H141" s="32"/>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="2"/>
@@ -40203,7 +40345,7 @@
       <c r="E142" s="3"/>
       <c r="F142" s="12"/>
       <c r="G142" s="3"/>
-      <c r="H142" s="46"/>
+      <c r="H142" s="32"/>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="2"/>
@@ -40213,7 +40355,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="12"/>
       <c r="G143" s="3"/>
-      <c r="H143" s="46"/>
+      <c r="H143" s="32"/>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="2"/>
@@ -40223,7 +40365,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="12"/>
       <c r="G144" s="3"/>
-      <c r="H144" s="46"/>
+      <c r="H144" s="32"/>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="2"/>
@@ -40233,7 +40375,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="12"/>
       <c r="G145" s="3"/>
-      <c r="H145" s="46"/>
+      <c r="H145" s="32"/>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="2"/>
@@ -40243,7 +40385,7 @@
       <c r="E146" s="3"/>
       <c r="F146" s="12"/>
       <c r="G146" s="3"/>
-      <c r="H146" s="46"/>
+      <c r="H146" s="32"/>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="2"/>
@@ -40253,7 +40395,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="12"/>
       <c r="G147" s="3"/>
-      <c r="H147" s="46"/>
+      <c r="H147" s="32"/>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="2"/>
@@ -40263,7 +40405,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="12"/>
       <c r="G148" s="3"/>
-      <c r="H148" s="46"/>
+      <c r="H148" s="32"/>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="2"/>
@@ -40273,7 +40415,7 @@
       <c r="E149" s="3"/>
       <c r="F149" s="12"/>
       <c r="G149" s="3"/>
-      <c r="H149" s="46"/>
+      <c r="H149" s="32"/>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="2"/>
@@ -40283,7 +40425,7 @@
       <c r="E150" s="3"/>
       <c r="F150" s="12"/>
       <c r="G150" s="3"/>
-      <c r="H150" s="46"/>
+      <c r="H150" s="32"/>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="2"/>
@@ -40293,7 +40435,7 @@
       <c r="E151" s="3"/>
       <c r="F151" s="12"/>
       <c r="G151" s="3"/>
-      <c r="H151" s="46"/>
+      <c r="H151" s="32"/>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="2"/>
@@ -40303,7 +40445,7 @@
       <c r="E152" s="3"/>
       <c r="F152" s="12"/>
       <c r="G152" s="3"/>
-      <c r="H152" s="46"/>
+      <c r="H152" s="32"/>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="2"/>
@@ -40313,7 +40455,7 @@
       <c r="E153" s="3"/>
       <c r="F153" s="12"/>
       <c r="G153" s="3"/>
-      <c r="H153" s="46"/>
+      <c r="H153" s="32"/>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="2"/>
@@ -40323,7 +40465,7 @@
       <c r="E154" s="3"/>
       <c r="F154" s="12"/>
       <c r="G154" s="3"/>
-      <c r="H154" s="46"/>
+      <c r="H154" s="32"/>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="2"/>
@@ -40333,7 +40475,7 @@
       <c r="E155" s="3"/>
       <c r="F155" s="12"/>
       <c r="G155" s="3"/>
-      <c r="H155" s="46"/>
+      <c r="H155" s="32"/>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="2"/>
@@ -40343,7 +40485,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="12"/>
       <c r="G156" s="3"/>
-      <c r="H156" s="46"/>
+      <c r="H156" s="32"/>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="2"/>
@@ -40353,7 +40495,7 @@
       <c r="E157" s="3"/>
       <c r="F157" s="12"/>
       <c r="G157" s="3"/>
-      <c r="H157" s="46"/>
+      <c r="H157" s="32"/>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="2"/>
@@ -40363,7 +40505,7 @@
       <c r="E158" s="3"/>
       <c r="F158" s="12"/>
       <c r="G158" s="3"/>
-      <c r="H158" s="46"/>
+      <c r="H158" s="32"/>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="2"/>
@@ -40373,7 +40515,7 @@
       <c r="E159" s="3"/>
       <c r="F159" s="12"/>
       <c r="G159" s="3"/>
-      <c r="H159" s="46"/>
+      <c r="H159" s="32"/>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="2"/>
@@ -40383,7 +40525,7 @@
       <c r="E160" s="3"/>
       <c r="F160" s="12"/>
       <c r="G160" s="3"/>
-      <c r="H160" s="46"/>
+      <c r="H160" s="32"/>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="2"/>
@@ -40393,7 +40535,7 @@
       <c r="E161" s="3"/>
       <c r="F161" s="12"/>
       <c r="G161" s="3"/>
-      <c r="H161" s="46"/>
+      <c r="H161" s="32"/>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="2"/>
@@ -40403,7 +40545,7 @@
       <c r="E162" s="3"/>
       <c r="F162" s="12"/>
       <c r="G162" s="3"/>
-      <c r="H162" s="46"/>
+      <c r="H162" s="32"/>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="2"/>
@@ -40413,7 +40555,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="12"/>
       <c r="G163" s="3"/>
-      <c r="H163" s="46"/>
+      <c r="H163" s="32"/>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="2"/>
@@ -40423,7 +40565,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="12"/>
       <c r="G164" s="3"/>
-      <c r="H164" s="46"/>
+      <c r="H164" s="32"/>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="2"/>
@@ -40433,7 +40575,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="12"/>
       <c r="G165" s="3"/>
-      <c r="H165" s="46"/>
+      <c r="H165" s="32"/>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="2"/>
@@ -40443,7 +40585,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="12"/>
       <c r="G166" s="3"/>
-      <c r="H166" s="46"/>
+      <c r="H166" s="32"/>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="2"/>
@@ -40453,7 +40595,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="12"/>
       <c r="G167" s="3"/>
-      <c r="H167" s="46"/>
+      <c r="H167" s="32"/>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="2"/>
@@ -40463,7 +40605,7 @@
       <c r="E168" s="3"/>
       <c r="F168" s="12"/>
       <c r="G168" s="3"/>
-      <c r="H168" s="46"/>
+      <c r="H168" s="32"/>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="2"/>
@@ -40473,7 +40615,7 @@
       <c r="E169" s="3"/>
       <c r="F169" s="12"/>
       <c r="G169" s="3"/>
-      <c r="H169" s="46"/>
+      <c r="H169" s="32"/>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="2"/>
@@ -40483,7 +40625,7 @@
       <c r="E170" s="3"/>
       <c r="F170" s="12"/>
       <c r="G170" s="3"/>
-      <c r="H170" s="46"/>
+      <c r="H170" s="32"/>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="2"/>
@@ -40493,7 +40635,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="12"/>
       <c r="G171" s="3"/>
-      <c r="H171" s="46"/>
+      <c r="H171" s="32"/>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="2"/>
@@ -40503,7 +40645,7 @@
       <c r="E172" s="3"/>
       <c r="F172" s="12"/>
       <c r="G172" s="3"/>
-      <c r="H172" s="46"/>
+      <c r="H172" s="32"/>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="2"/>
@@ -40513,7 +40655,7 @@
       <c r="E173" s="3"/>
       <c r="F173" s="12"/>
       <c r="G173" s="3"/>
-      <c r="H173" s="46"/>
+      <c r="H173" s="32"/>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="2"/>
@@ -40523,7 +40665,7 @@
       <c r="E174" s="3"/>
       <c r="F174" s="12"/>
       <c r="G174" s="3"/>
-      <c r="H174" s="46"/>
+      <c r="H174" s="32"/>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="2"/>
@@ -40533,7 +40675,7 @@
       <c r="E175" s="3"/>
       <c r="F175" s="12"/>
       <c r="G175" s="3"/>
-      <c r="H175" s="46"/>
+      <c r="H175" s="32"/>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="2"/>
@@ -40543,7 +40685,7 @@
       <c r="E176" s="3"/>
       <c r="F176" s="12"/>
       <c r="G176" s="3"/>
-      <c r="H176" s="46"/>
+      <c r="H176" s="32"/>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="2"/>
@@ -40553,7 +40695,7 @@
       <c r="E177" s="3"/>
       <c r="F177" s="12"/>
       <c r="G177" s="3"/>
-      <c r="H177" s="46"/>
+      <c r="H177" s="32"/>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="2"/>
@@ -40563,7 +40705,7 @@
       <c r="E178" s="3"/>
       <c r="F178" s="12"/>
       <c r="G178" s="3"/>
-      <c r="H178" s="46"/>
+      <c r="H178" s="32"/>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="2"/>
@@ -40573,7 +40715,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="12"/>
       <c r="G179" s="3"/>
-      <c r="H179" s="46"/>
+      <c r="H179" s="32"/>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="2"/>
@@ -40583,7 +40725,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="12"/>
       <c r="G180" s="3"/>
-      <c r="H180" s="46"/>
+      <c r="H180" s="32"/>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="2"/>
@@ -40593,7 +40735,7 @@
       <c r="E181" s="3"/>
       <c r="F181" s="12"/>
       <c r="G181" s="3"/>
-      <c r="H181" s="46"/>
+      <c r="H181" s="32"/>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="2"/>
@@ -40603,7 +40745,7 @@
       <c r="E182" s="3"/>
       <c r="F182" s="12"/>
       <c r="G182" s="3"/>
-      <c r="H182" s="46"/>
+      <c r="H182" s="32"/>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="2"/>
@@ -40613,7 +40755,7 @@
       <c r="E183" s="3"/>
       <c r="F183" s="12"/>
       <c r="G183" s="3"/>
-      <c r="H183" s="46"/>
+      <c r="H183" s="32"/>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="2"/>
@@ -40623,7 +40765,7 @@
       <c r="E184" s="3"/>
       <c r="F184" s="12"/>
       <c r="G184" s="3"/>
-      <c r="H184" s="46"/>
+      <c r="H184" s="32"/>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="2"/>
@@ -40633,7 +40775,7 @@
       <c r="E185" s="3"/>
       <c r="F185" s="12"/>
       <c r="G185" s="3"/>
-      <c r="H185" s="46"/>
+      <c r="H185" s="32"/>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="2"/>
@@ -40643,7 +40785,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="12"/>
       <c r="G186" s="3"/>
-      <c r="H186" s="46"/>
+      <c r="H186" s="32"/>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="2"/>
@@ -40653,7 +40795,7 @@
       <c r="E187" s="3"/>
       <c r="F187" s="12"/>
       <c r="G187" s="3"/>
-      <c r="H187" s="46"/>
+      <c r="H187" s="32"/>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="2"/>
@@ -40663,7 +40805,7 @@
       <c r="E188" s="3"/>
       <c r="F188" s="12"/>
       <c r="G188" s="3"/>
-      <c r="H188" s="46"/>
+      <c r="H188" s="32"/>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="2"/>
@@ -40673,7 +40815,7 @@
       <c r="E189" s="3"/>
       <c r="F189" s="12"/>
       <c r="G189" s="3"/>
-      <c r="H189" s="46"/>
+      <c r="H189" s="32"/>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="2"/>
@@ -40683,7 +40825,7 @@
       <c r="E190" s="3"/>
       <c r="F190" s="12"/>
       <c r="G190" s="3"/>
-      <c r="H190" s="46"/>
+      <c r="H190" s="32"/>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="2"/>
@@ -40693,7 +40835,7 @@
       <c r="E191" s="3"/>
       <c r="F191" s="12"/>
       <c r="G191" s="3"/>
-      <c r="H191" s="46"/>
+      <c r="H191" s="32"/>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="2"/>
@@ -40703,7 +40845,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="12"/>
       <c r="G192" s="3"/>
-      <c r="H192" s="46"/>
+      <c r="H192" s="32"/>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="2"/>
@@ -40713,7 +40855,7 @@
       <c r="E193" s="3"/>
       <c r="F193" s="12"/>
       <c r="G193" s="3"/>
-      <c r="H193" s="46"/>
+      <c r="H193" s="32"/>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="2"/>
@@ -40723,7 +40865,7 @@
       <c r="E194" s="3"/>
       <c r="F194" s="12"/>
       <c r="G194" s="3"/>
-      <c r="H194" s="46"/>
+      <c r="H194" s="32"/>
     </row>
     <row r="195" spans="1:8">
       <c r="A195" s="2"/>
@@ -40733,7 +40875,7 @@
       <c r="E195" s="3"/>
       <c r="F195" s="12"/>
       <c r="G195" s="3"/>
-      <c r="H195" s="46"/>
+      <c r="H195" s="32"/>
     </row>
     <row r="196" spans="1:8">
       <c r="A196" s="2"/>
@@ -40743,7 +40885,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="12"/>
       <c r="G196" s="3"/>
-      <c r="H196" s="46"/>
+      <c r="H196" s="32"/>
     </row>
     <row r="197" spans="1:8">
       <c r="A197" s="2"/>
@@ -40753,7 +40895,7 @@
       <c r="E197" s="3"/>
       <c r="F197" s="12"/>
       <c r="G197" s="3"/>
-      <c r="H197" s="46"/>
+      <c r="H197" s="32"/>
     </row>
     <row r="198" spans="1:8">
       <c r="A198" s="2"/>
@@ -40763,7 +40905,7 @@
       <c r="E198" s="3"/>
       <c r="F198" s="12"/>
       <c r="G198" s="3"/>
-      <c r="H198" s="46"/>
+      <c r="H198" s="32"/>
     </row>
     <row r="199" spans="1:8">
       <c r="A199" s="2"/>
@@ -40773,7 +40915,7 @@
       <c r="E199" s="3"/>
       <c r="F199" s="12"/>
       <c r="G199" s="3"/>
-      <c r="H199" s="46"/>
+      <c r="H199" s="32"/>
     </row>
     <row r="200" spans="1:8">
       <c r="A200" s="2"/>
@@ -40783,7 +40925,7 @@
       <c r="E200" s="3"/>
       <c r="F200" s="12"/>
       <c r="G200" s="3"/>
-      <c r="H200" s="46"/>
+      <c r="H200" s="32"/>
     </row>
     <row r="201" spans="1:8">
       <c r="A201" s="2"/>
@@ -40793,7 +40935,7 @@
       <c r="E201" s="3"/>
       <c r="F201" s="12"/>
       <c r="G201" s="3"/>
-      <c r="H201" s="46"/>
+      <c r="H201" s="32"/>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="2"/>
@@ -40803,7 +40945,7 @@
       <c r="E202" s="3"/>
       <c r="F202" s="12"/>
       <c r="G202" s="3"/>
-      <c r="H202" s="46"/>
+      <c r="H202" s="32"/>
     </row>
     <row r="203" spans="1:8">
       <c r="A203" s="2"/>
@@ -40813,7 +40955,7 @@
       <c r="E203" s="3"/>
       <c r="F203" s="12"/>
       <c r="G203" s="3"/>
-      <c r="H203" s="46"/>
+      <c r="H203" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9095ED9A-6729-4A8C-A2D3-9475BCD53776}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229BF08-1474-4D13-8242-FD8CCC815105}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="1289">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -3850,25 +3850,49 @@
     <t>Ojei Elizabeth</t>
   </si>
   <si>
+    <t>09047690900</t>
+  </si>
+  <si>
+    <t>08050412130</t>
+  </si>
+  <si>
+    <t>Koleosho Sherifat</t>
+  </si>
+  <si>
+    <t>11750</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
     <t>Weekly 12W</t>
   </si>
   <si>
-    <t>09047690900</t>
-  </si>
-  <si>
-    <t>08050412130</t>
-  </si>
-  <si>
     <t>Weekly 24W</t>
   </si>
   <si>
-    <t>Koleosho Sherifat</t>
-  </si>
-  <si>
-    <t>35925</t>
-  </si>
-  <si>
-    <t>25125</t>
+    <t>Weekly 12W Asset</t>
+  </si>
+  <si>
+    <t>Osho Bunmi</t>
+  </si>
+  <si>
+    <t>09049017436</t>
+  </si>
+  <si>
+    <t>Oguntamo Modina</t>
+  </si>
+  <si>
+    <t>09035527146</t>
+  </si>
+  <si>
+    <t>MEM-349</t>
+  </si>
+  <si>
+    <t>MEM-350</t>
   </si>
 </sst>
 </file>
@@ -4068,7 +4092,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4158,6 +4182,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4188,26 +4218,327 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFD9E2F3"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -4263,161 +4594,27 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="left" vertical="top"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top"/>
-      <border>
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos"/>
+        <color rgb="FF9C0006"/>
       </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFCE4D6"/>
         </patternFill>
       </fill>
-      <alignment horizontal="left" vertical="top"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD9E2F3"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top"/>
     </dxf>
     <dxf>
       <font>
@@ -4476,6 +4673,16 @@
         <horizontal/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4495,31 +4702,31 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Group Reference*"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Branch Name*"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Group Name*"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="16"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="17"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Meeting Day*"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Formation Date*"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Credit Officer Name*"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Credit Officer Phone"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2000" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2002" dataDxfId="13">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="8"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="6"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="5"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="4"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="3"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="2"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="0"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4684,28 +4891,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -4725,13 +4932,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="38" t="s">
+      <c r="D4" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -4739,13 +4946,13 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="37"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4753,13 +4960,13 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="37"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -4767,13 +4974,13 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="35"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -4781,13 +4988,13 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="37"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -4795,25 +5002,25 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="34"/>
-      <c r="H9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="37"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="35"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="37"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -4826,142 +5033,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="37"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="37"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="40" t="s">
+      <c r="B14" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="40" t="s">
+      <c r="B15" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="37"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="40" t="s">
+      <c r="B16" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="37"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="40" t="s">
+      <c r="B17" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="37"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="40" t="s">
+      <c r="B18" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="40" t="s">
+      <c r="B19" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="35"/>
+      <c r="C20" s="36"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="37"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="34"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="35"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="37"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -5015,30 +5222,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5679,7 +5886,9 @@
       <c r="C28" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="6" t="s">
+        <v>774</v>
+      </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
       </c>
@@ -5692,7 +5901,9 @@
       <c r="H28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="14"/>
+      <c r="I28" s="14" t="s">
+        <v>1277</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
@@ -5704,7 +5915,9 @@
       <c r="C29" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D29" s="6"/>
+      <c r="D29" s="6" t="s">
+        <v>804</v>
+      </c>
       <c r="E29" s="6" t="s">
         <v>107</v>
       </c>
@@ -5717,7 +5930,9 @@
       <c r="H29" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="14"/>
+      <c r="I29" s="14" t="s">
+        <v>1278</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
@@ -5729,7 +5944,9 @@
       <c r="C30" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D30" s="6"/>
+      <c r="D30" s="6" t="s">
+        <v>823</v>
+      </c>
       <c r="E30" s="6" t="s">
         <v>107</v>
       </c>
@@ -5742,7 +5959,9 @@
       <c r="H30" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="14"/>
+      <c r="I30" s="14" t="s">
+        <v>1279</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
@@ -5755,7 +5974,7 @@
         <v>113</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>114</v>
@@ -5769,9 +5988,7 @@
       <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="48" t="s">
-        <v>1279</v>
-      </c>
+      <c r="I31" s="34"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
@@ -5798,9 +6015,7 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="48" t="s">
-        <v>1280</v>
-      </c>
+      <c r="I32" s="34"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -8519,7 +8734,7 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A253">
-    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8531,7 +8746,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2000"/>
+  <dimension ref="A1:K2002"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22.09765625" style="27" customWidth="1"/>
@@ -8543,34 +8758,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="46"/>
-      <c r="K1" s="46"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -13325,10 +13540,18 @@
       <c r="F193" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G193" s="20"/>
-      <c r="H193" s="23"/>
-      <c r="I193" s="23"/>
-      <c r="J193" s="23"/>
+      <c r="G193" s="20">
+        <v>24550</v>
+      </c>
+      <c r="H193" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I193" s="23">
+        <v>198000</v>
+      </c>
+      <c r="J193" s="23">
+        <v>82500</v>
+      </c>
       <c r="K193" s="23"/>
     </row>
     <row r="194" spans="1:11">
@@ -13350,10 +13573,18 @@
       <c r="F194" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G194" s="20"/>
-      <c r="H194" s="23"/>
-      <c r="I194" s="23"/>
-      <c r="J194" s="23"/>
+      <c r="G194" s="20">
+        <v>22200</v>
+      </c>
+      <c r="H194" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I194" s="23">
+        <v>48000</v>
+      </c>
+      <c r="J194" s="23">
+        <v>4000</v>
+      </c>
       <c r="K194" s="23"/>
     </row>
     <row r="195" spans="1:11">
@@ -13375,10 +13606,18 @@
       <c r="F195" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G195" s="20"/>
-      <c r="H195" s="23"/>
-      <c r="I195" s="23"/>
-      <c r="J195" s="23"/>
+      <c r="G195" s="20">
+        <v>15000</v>
+      </c>
+      <c r="H195" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I195" s="23">
+        <v>288000</v>
+      </c>
+      <c r="J195" s="23">
+        <v>288000</v>
+      </c>
       <c r="K195" s="23"/>
     </row>
     <row r="196" spans="1:11">
@@ -13400,10 +13639,18 @@
       <c r="F196" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G196" s="20"/>
-      <c r="H196" s="23"/>
-      <c r="I196" s="23"/>
-      <c r="J196" s="23"/>
+      <c r="G196" s="20">
+        <v>13000</v>
+      </c>
+      <c r="H196" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I196" s="23">
+        <v>60000</v>
+      </c>
+      <c r="J196" s="23">
+        <v>10000</v>
+      </c>
       <c r="K196" s="23"/>
     </row>
     <row r="197" spans="1:11">
@@ -13423,10 +13670,18 @@
       <c r="F197" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G197" s="20"/>
-      <c r="H197" s="23"/>
-      <c r="I197" s="23"/>
-      <c r="J197" s="23"/>
+      <c r="G197" s="20">
+        <v>9500</v>
+      </c>
+      <c r="H197" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I197" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J197" s="23">
+        <v>100000</v>
+      </c>
       <c r="K197" s="23"/>
     </row>
     <row r="198" spans="1:11">
@@ -13449,7 +13704,9 @@
         <v>776</v>
       </c>
       <c r="G198" s="20"/>
-      <c r="H198" s="23"/>
+      <c r="H198" s="23" t="s">
+        <v>1281</v>
+      </c>
       <c r="I198" s="23"/>
       <c r="J198" s="23"/>
       <c r="K198" s="23"/>
@@ -13473,10 +13730,18 @@
       <c r="F199" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G199" s="20"/>
-      <c r="H199" s="23"/>
-      <c r="I199" s="23"/>
-      <c r="J199" s="23"/>
+      <c r="G199" s="20">
+        <v>23600</v>
+      </c>
+      <c r="H199" s="23" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I199" s="23">
+        <v>198000</v>
+      </c>
+      <c r="J199" s="23">
+        <v>41250</v>
+      </c>
       <c r="K199" s="23"/>
     </row>
     <row r="200" spans="1:11">
@@ -13498,8 +13763,12 @@
       <c r="F200" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G200" s="20"/>
-      <c r="H200" s="23"/>
+      <c r="G200" s="20">
+        <v>63400</v>
+      </c>
+      <c r="H200" s="23" t="s">
+        <v>1281</v>
+      </c>
       <c r="I200" s="23"/>
       <c r="J200" s="23"/>
       <c r="K200" s="23"/>
@@ -13523,10 +13792,18 @@
       <c r="F201" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G201" s="20"/>
-      <c r="H201" s="23"/>
-      <c r="I201" s="23"/>
-      <c r="J201" s="23"/>
+      <c r="G201" s="20">
+        <v>18725</v>
+      </c>
+      <c r="H201" s="23" t="s">
+        <v>1281</v>
+      </c>
+      <c r="I201" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J201" s="23">
+        <v>28875</v>
+      </c>
       <c r="K201" s="23"/>
     </row>
     <row r="202" spans="1:11">
@@ -13548,8 +13825,12 @@
       <c r="F202" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G202" s="20"/>
-      <c r="H202" s="23"/>
+      <c r="G202" s="20">
+        <v>89000</v>
+      </c>
+      <c r="H202" s="23" t="s">
+        <v>1281</v>
+      </c>
       <c r="I202" s="23"/>
       <c r="J202" s="23"/>
       <c r="K202" s="23"/>
@@ -13573,10 +13854,18 @@
       <c r="F203" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G203" s="20"/>
-      <c r="H203" s="23"/>
-      <c r="I203" s="23"/>
-      <c r="J203" s="23"/>
+      <c r="G203" s="20">
+        <v>5950</v>
+      </c>
+      <c r="H203" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I203" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J203" s="23">
+        <v>24750</v>
+      </c>
       <c r="K203" s="23"/>
     </row>
     <row r="204" spans="1:11">
@@ -13598,10 +13887,18 @@
       <c r="F204" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G204" s="20"/>
-      <c r="H204" s="23"/>
-      <c r="I204" s="23"/>
-      <c r="J204" s="23"/>
+      <c r="G204" s="20">
+        <v>4750</v>
+      </c>
+      <c r="H204" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I204" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J204" s="23">
+        <v>33000</v>
+      </c>
       <c r="K204" s="23"/>
     </row>
     <row r="205" spans="1:11">
@@ -13624,9 +13921,15 @@
         <v>806</v>
       </c>
       <c r="G205" s="20"/>
-      <c r="H205" s="23"/>
-      <c r="I205" s="23"/>
-      <c r="J205" s="23"/>
+      <c r="H205" s="23" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I205" s="23">
+        <v>279000</v>
+      </c>
+      <c r="J205" s="23">
+        <v>46500</v>
+      </c>
       <c r="K205" s="23"/>
     </row>
     <row r="206" spans="1:11">
@@ -13648,10 +13951,18 @@
       <c r="F206" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G206" s="20"/>
-      <c r="H206" s="23"/>
-      <c r="I206" s="23"/>
-      <c r="J206" s="23"/>
+      <c r="G206" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H206" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I206" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J206" s="23">
+        <v>24750</v>
+      </c>
       <c r="K206" s="23"/>
     </row>
     <row r="207" spans="1:11">
@@ -13673,10 +13984,18 @@
       <c r="F207" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G207" s="20"/>
-      <c r="H207" s="23"/>
-      <c r="I207" s="23"/>
-      <c r="J207" s="23"/>
+      <c r="G207" s="20">
+        <v>4750</v>
+      </c>
+      <c r="H207" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I207" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J207" s="23">
+        <v>33000</v>
+      </c>
       <c r="K207" s="23"/>
     </row>
     <row r="208" spans="1:11">
@@ -13698,10 +14017,18 @@
       <c r="F208" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G208" s="20"/>
-      <c r="H208" s="23"/>
-      <c r="I208" s="23"/>
-      <c r="J208" s="23"/>
+      <c r="G208" s="20">
+        <v>3000</v>
+      </c>
+      <c r="H208" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I208" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J208" s="23">
+        <v>57750</v>
+      </c>
       <c r="K208" s="23"/>
     </row>
     <row r="209" spans="1:11">
@@ -13709,24 +14036,32 @@
         <v>822</v>
       </c>
       <c r="B209" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>823</v>
+        <v>1283</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>824</v>
+        <v>1284</v>
       </c>
       <c r="F209" s="22" t="s">
-        <v>711</v>
-      </c>
-      <c r="G209" s="20"/>
-      <c r="H209" s="23"/>
-      <c r="I209" s="23"/>
-      <c r="J209" s="23"/>
+        <v>806</v>
+      </c>
+      <c r="G209" s="49">
+        <v>2750</v>
+      </c>
+      <c r="H209" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I209" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J209" s="33">
+        <v>66000</v>
+      </c>
       <c r="K209" s="23"/>
     </row>
     <row r="210" spans="1:11">
@@ -13734,24 +14069,32 @@
         <v>825</v>
       </c>
       <c r="B210" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>826</v>
+        <v>1285</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>827</v>
+        <v>1286</v>
       </c>
       <c r="F210" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G210" s="20"/>
-      <c r="H210" s="23"/>
-      <c r="I210" s="23"/>
-      <c r="J210" s="23"/>
+        <v>806</v>
+      </c>
+      <c r="G210" s="49">
+        <v>2750</v>
+      </c>
+      <c r="H210" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I210" s="23">
+        <v>99000</v>
+      </c>
+      <c r="J210" s="33">
+        <v>66000</v>
+      </c>
       <c r="K210" s="23"/>
     </row>
     <row r="211" spans="1:11">
@@ -13762,21 +14105,29 @@
         <v>110</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="E211" s="21" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="F211" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G211" s="20"/>
-      <c r="H211" s="23"/>
-      <c r="I211" s="23"/>
-      <c r="J211" s="23"/>
+        <v>711</v>
+      </c>
+      <c r="G211" s="20">
+        <v>19200</v>
+      </c>
+      <c r="H211" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I211" s="23">
+        <v>288000</v>
+      </c>
+      <c r="J211" s="23">
+        <v>288000</v>
+      </c>
       <c r="K211" s="23"/>
     </row>
     <row r="212" spans="1:11">
@@ -13787,21 +14138,29 @@
         <v>110</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D212" s="22" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="F212" s="22" t="s">
-        <v>711</v>
-      </c>
-      <c r="G212" s="20"/>
-      <c r="H212" s="23"/>
-      <c r="I212" s="23"/>
-      <c r="J212" s="23"/>
+        <v>698</v>
+      </c>
+      <c r="G212" s="20">
+        <v>11700</v>
+      </c>
+      <c r="H212" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I212" s="23">
+        <v>288000</v>
+      </c>
+      <c r="J212" s="23">
+        <v>288000</v>
+      </c>
       <c r="K212" s="23"/>
     </row>
     <row r="213" spans="1:11">
@@ -13812,21 +14171,29 @@
         <v>110</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D213" s="22" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E213" s="21" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="F213" s="22" t="s">
-        <v>711</v>
-      </c>
-      <c r="G213" s="20"/>
-      <c r="H213" s="23"/>
-      <c r="I213" s="23"/>
-      <c r="J213" s="23"/>
+        <v>698</v>
+      </c>
+      <c r="G213" s="20">
+        <v>11700</v>
+      </c>
+      <c r="H213" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="I213" s="23">
+        <v>246000</v>
+      </c>
+      <c r="J213" s="23">
+        <v>246000</v>
+      </c>
       <c r="K213" s="23"/>
     </row>
     <row r="214" spans="1:11">
@@ -13834,28 +14201,32 @@
         <v>837</v>
       </c>
       <c r="B214" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>1271</v>
+        <v>832</v>
       </c>
       <c r="E214" s="21" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="F214" s="22" t="s">
-        <v>839</v>
+        <v>711</v>
       </c>
       <c r="G214" s="20">
-        <v>38100</v>
+        <v>11000</v>
       </c>
       <c r="H214" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I214" s="23"/>
-      <c r="J214" s="23"/>
+        <v>1280</v>
+      </c>
+      <c r="I214" s="23">
+        <v>288000</v>
+      </c>
+      <c r="J214" s="23">
+        <v>288000</v>
+      </c>
       <c r="K214" s="23"/>
     </row>
     <row r="215" spans="1:11">
@@ -13863,35 +14234,33 @@
         <v>840</v>
       </c>
       <c r="B215" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="E215" s="21" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="F215" s="22" t="s">
-        <v>839</v>
+        <v>711</v>
       </c>
       <c r="G215" s="20">
-        <v>14100</v>
+        <v>9250</v>
       </c>
       <c r="H215" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I215" s="47">
-        <v>200000</v>
+        <v>1280</v>
+      </c>
+      <c r="I215" s="23">
+        <v>99000</v>
       </c>
       <c r="J215" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K215" s="23">
-        <v>148500</v>
-      </c>
+        <v>24750</v>
+      </c>
+      <c r="K215" s="23"/>
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="21" t="s">
@@ -13901,32 +14270,22 @@
         <v>112</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D216" s="22" t="s">
-        <v>844</v>
+        <v>1271</v>
       </c>
       <c r="E216" s="21" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="F216" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G216" s="20">
-        <v>16000</v>
-      </c>
-      <c r="H216" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I216" s="47">
-        <v>200000</v>
-      </c>
-      <c r="J216" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K216" s="23">
-        <v>148500</v>
-      </c>
+      <c r="G216" s="20"/>
+      <c r="H216" s="23"/>
+      <c r="I216" s="23"/>
+      <c r="J216" s="23"/>
+      <c r="K216" s="23"/>
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
@@ -13936,24 +14295,20 @@
         <v>112</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E217" s="21" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="F217" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G217" s="20">
-        <v>35000</v>
-      </c>
-      <c r="H217" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I217" s="47"/>
+      <c r="G217" s="20"/>
+      <c r="H217" s="23"/>
+      <c r="I217" s="23"/>
       <c r="J217" s="23"/>
       <c r="K217" s="23"/>
     </row>
@@ -13965,22 +14320,20 @@
         <v>112</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>1272</v>
+        <v>844</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>1275</v>
+        <v>845</v>
       </c>
       <c r="F218" s="22" t="s">
         <v>839</v>
       </c>
       <c r="G218" s="20"/>
-      <c r="H218" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I218" s="47"/>
+      <c r="H218" s="23"/>
+      <c r="I218" s="23"/>
       <c r="J218" s="23"/>
       <c r="K218" s="23"/>
     </row>
@@ -13992,24 +14345,20 @@
         <v>112</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>1273</v>
+        <v>847</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>1276</v>
+        <v>848</v>
       </c>
       <c r="F219" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G219" s="20">
-        <v>15500</v>
-      </c>
-      <c r="H219" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I219" s="47"/>
+      <c r="G219" s="20"/>
+      <c r="H219" s="23"/>
+      <c r="I219" s="23"/>
       <c r="J219" s="23"/>
       <c r="K219" s="23"/>
     </row>
@@ -14021,32 +14370,22 @@
         <v>112</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>852</v>
+        <v>1272</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>853</v>
+        <v>1274</v>
       </c>
       <c r="F220" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G220" s="20">
-        <v>52000</v>
-      </c>
-      <c r="H220" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I220" s="47">
-        <v>250000</v>
-      </c>
-      <c r="J220" s="23">
-        <v>246000</v>
-      </c>
-      <c r="K220" s="23">
-        <v>102500</v>
-      </c>
+      <c r="G220" s="20"/>
+      <c r="H220" s="23"/>
+      <c r="I220" s="23"/>
+      <c r="J220" s="23"/>
+      <c r="K220" s="23"/>
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="21" t="s">
@@ -14056,32 +14395,22 @@
         <v>112</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>855</v>
+        <v>1273</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>856</v>
+        <v>1275</v>
       </c>
       <c r="F221" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G221" s="20">
-        <v>30900</v>
-      </c>
-      <c r="H221" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I221" s="47">
-        <v>250000</v>
-      </c>
-      <c r="J221" s="23">
-        <v>246000</v>
-      </c>
-      <c r="K221" s="23">
-        <v>112750</v>
-      </c>
+      <c r="G221" s="20"/>
+      <c r="H221" s="23"/>
+      <c r="I221" s="23"/>
+      <c r="J221" s="23"/>
+      <c r="K221" s="23"/>
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
@@ -14091,102 +14420,72 @@
         <v>112</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="F222" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G222" s="20">
-        <v>19750</v>
-      </c>
-      <c r="H222" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I222" s="47">
-        <v>200000</v>
-      </c>
-      <c r="J222" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K222" s="23">
-        <v>115500</v>
-      </c>
+      <c r="G222" s="20"/>
+      <c r="H222" s="23"/>
+      <c r="I222" s="23"/>
+      <c r="J222" s="23"/>
+      <c r="K222" s="23"/>
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
         <v>860</v>
       </c>
       <c r="B223" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="F223" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G223" s="20">
-        <v>10750</v>
-      </c>
-      <c r="H223" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I223" s="47">
-        <v>100000</v>
-      </c>
-      <c r="J223" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K223" s="23">
-        <v>57750</v>
-      </c>
+      <c r="G223" s="20"/>
+      <c r="H223" s="23"/>
+      <c r="I223" s="23"/>
+      <c r="J223" s="23"/>
+      <c r="K223" s="23"/>
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
         <v>863</v>
       </c>
       <c r="B224" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="F224" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G224" s="20">
-        <v>7200</v>
-      </c>
-      <c r="H224" s="23" t="s">
-        <v>1274</v>
-      </c>
-      <c r="I224" s="47">
-        <v>50000</v>
-      </c>
-      <c r="J224" s="23">
-        <v>48000</v>
-      </c>
-      <c r="K224" s="23">
-        <v>36000</v>
-      </c>
+      <c r="G224" s="20"/>
+      <c r="H224" s="23"/>
+      <c r="I224" s="23"/>
+      <c r="J224" s="23"/>
+      <c r="K224" s="23"/>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
@@ -14196,32 +14495,22 @@
         <v>115</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="F225" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G225" s="20">
-        <v>10900</v>
-      </c>
-      <c r="H225" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I225" s="47">
-        <v>80000</v>
-      </c>
-      <c r="J225" s="23">
-        <v>78000</v>
-      </c>
-      <c r="K225" s="23">
-        <v>45500</v>
-      </c>
+      <c r="G225" s="20"/>
+      <c r="H225" s="23"/>
+      <c r="I225" s="23"/>
+      <c r="J225" s="23"/>
+      <c r="K225" s="23"/>
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
@@ -14231,32 +14520,22 @@
         <v>115</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="F226" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G226" s="20">
-        <v>8925</v>
-      </c>
-      <c r="H226" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I226" s="47">
-        <v>100000</v>
-      </c>
-      <c r="J226" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K226" s="23">
-        <v>49500</v>
-      </c>
+      <c r="G226" s="20"/>
+      <c r="H226" s="23"/>
+      <c r="I226" s="23"/>
+      <c r="J226" s="23"/>
+      <c r="K226" s="23"/>
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
@@ -14266,21 +14545,19 @@
         <v>115</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>873</v>
-      </c>
-      <c r="E227" s="21"/>
+        <v>867</v>
+      </c>
+      <c r="E227" s="21" t="s">
+        <v>868</v>
+      </c>
       <c r="F227" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G227" s="20">
-        <v>42925</v>
-      </c>
-      <c r="H227" s="23" t="s">
-        <v>1277</v>
-      </c>
+      <c r="G227" s="20"/>
+      <c r="H227" s="23"/>
       <c r="I227" s="23"/>
       <c r="J227" s="23"/>
       <c r="K227" s="23"/>
@@ -14290,19 +14567,19 @@
         <v>874</v>
       </c>
       <c r="B228" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="F228" s="22" t="s">
-        <v>877</v>
+        <v>839</v>
       </c>
       <c r="G228" s="20"/>
       <c r="H228" s="23"/>
@@ -14315,19 +14592,17 @@
         <v>878</v>
       </c>
       <c r="B229" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>879</v>
-      </c>
-      <c r="E229" s="21" t="s">
-        <v>880</v>
-      </c>
+        <v>873</v>
+      </c>
+      <c r="E229" s="21"/>
       <c r="F229" s="22" t="s">
-        <v>877</v>
+        <v>839</v>
       </c>
       <c r="G229" s="20"/>
       <c r="H229" s="23"/>
@@ -14343,13 +14618,13 @@
         <v>117</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>882</v>
+        <v>875</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>883</v>
+        <v>876</v>
       </c>
       <c r="F230" s="22" t="s">
         <v>877</v>
@@ -14368,13 +14643,13 @@
         <v>117</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="F231" s="22" t="s">
         <v>877</v>
@@ -14393,13 +14668,13 @@
         <v>117</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="F232" s="22" t="s">
         <v>877</v>
@@ -14418,13 +14693,13 @@
         <v>117</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="F233" s="22" t="s">
         <v>877</v>
@@ -14443,13 +14718,13 @@
         <v>117</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="F234" s="22" t="s">
         <v>877</v>
@@ -14468,13 +14743,13 @@
         <v>117</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="E235" s="21" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="F235" s="22" t="s">
         <v>877</v>
@@ -14493,13 +14768,13 @@
         <v>117</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="F236" s="22" t="s">
         <v>877</v>
@@ -14518,13 +14793,13 @@
         <v>117</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="E237" s="21" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="F237" s="22" t="s">
         <v>877</v>
@@ -14543,13 +14818,13 @@
         <v>117</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="F238" s="22" t="s">
         <v>877</v>
@@ -14568,13 +14843,13 @@
         <v>117</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="F239" s="22" t="s">
         <v>877</v>
@@ -14593,13 +14868,13 @@
         <v>117</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="F240" s="22" t="s">
         <v>877</v>
@@ -14618,13 +14893,13 @@
         <v>117</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="F241" s="22" t="s">
         <v>877</v>
@@ -14640,19 +14915,19 @@
         <v>917</v>
       </c>
       <c r="B242" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="F242" s="22" t="s">
-        <v>920</v>
+        <v>877</v>
       </c>
       <c r="G242" s="20"/>
       <c r="H242" s="23"/>
@@ -14665,19 +14940,19 @@
         <v>921</v>
       </c>
       <c r="B243" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>923</v>
+        <v>916</v>
       </c>
       <c r="F243" s="22" t="s">
-        <v>920</v>
+        <v>877</v>
       </c>
       <c r="G243" s="20"/>
       <c r="H243" s="23"/>
@@ -14693,13 +14968,13 @@
         <v>122</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>925</v>
+        <v>918</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>926</v>
+        <v>919</v>
       </c>
       <c r="F244" s="22" t="s">
         <v>920</v>
@@ -14718,13 +14993,13 @@
         <v>122</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="F245" s="22" t="s">
         <v>920</v>
@@ -14743,13 +15018,13 @@
         <v>122</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="F246" s="22" t="s">
         <v>920</v>
@@ -14768,13 +15043,13 @@
         <v>122</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="F247" s="22" t="s">
         <v>920</v>
@@ -14793,13 +15068,13 @@
         <v>122</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="F248" s="22" t="s">
         <v>920</v>
@@ -14815,19 +15090,19 @@
         <v>939</v>
       </c>
       <c r="B249" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="F249" s="22" t="s">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="G249" s="20"/>
       <c r="H249" s="23"/>
@@ -14840,19 +15115,19 @@
         <v>943</v>
       </c>
       <c r="B250" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>944</v>
+        <v>937</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>945</v>
+        <v>938</v>
       </c>
       <c r="F250" s="22" t="s">
-        <v>942</v>
+        <v>920</v>
       </c>
       <c r="G250" s="20"/>
       <c r="H250" s="23"/>
@@ -14868,13 +15143,13 @@
         <v>125</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>947</v>
+        <v>940</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>948</v>
+        <v>941</v>
       </c>
       <c r="F251" s="22" t="s">
         <v>942</v>
@@ -14893,13 +15168,13 @@
         <v>125</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="F252" s="22" t="s">
         <v>942</v>
@@ -14918,13 +15193,13 @@
         <v>125</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>931</v>
+        <v>947</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="F253" s="22" t="s">
         <v>942</v>
@@ -14943,13 +15218,13 @@
         <v>125</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="F254" s="22" t="s">
         <v>942</v>
@@ -14968,13 +15243,13 @@
         <v>125</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>958</v>
+        <v>931</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="F255" s="22" t="s">
         <v>942</v>
@@ -14993,13 +15268,13 @@
         <v>125</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="F256" s="22" t="s">
         <v>942</v>
@@ -15018,13 +15293,13 @@
         <v>125</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="F257" s="22" t="s">
         <v>942</v>
@@ -15043,13 +15318,13 @@
         <v>125</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="F258" s="22" t="s">
         <v>942</v>
@@ -15068,13 +15343,13 @@
         <v>125</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="F259" s="22" t="s">
         <v>942</v>
@@ -15093,13 +15368,13 @@
         <v>125</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="F260" s="22" t="s">
         <v>942</v>
@@ -15118,13 +15393,13 @@
         <v>125</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="F261" s="22" t="s">
         <v>942</v>
@@ -15143,13 +15418,13 @@
         <v>125</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="F262" s="22" t="s">
         <v>942</v>
@@ -15165,19 +15440,19 @@
         <v>981</v>
       </c>
       <c r="B263" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>174</v>
+        <v>304</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="F263" s="22" t="s">
-        <v>984</v>
+        <v>942</v>
       </c>
       <c r="G263" s="20"/>
       <c r="H263" s="23"/>
@@ -15190,19 +15465,19 @@
         <v>985</v>
       </c>
       <c r="B264" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>986</v>
+        <v>979</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>984</v>
+        <v>942</v>
       </c>
       <c r="G264" s="20"/>
       <c r="H264" s="23"/>
@@ -15218,13 +15493,13 @@
         <v>128</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>989</v>
+        <v>982</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
       <c r="F265" s="22" t="s">
         <v>984</v>
@@ -15243,13 +15518,13 @@
         <v>128</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="F266" s="22" t="s">
         <v>984</v>
@@ -15268,13 +15543,13 @@
         <v>128</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="F267" s="22" t="s">
         <v>984</v>
@@ -15293,13 +15568,13 @@
         <v>128</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="F268" s="22" t="s">
         <v>984</v>
@@ -15318,13 +15593,13 @@
         <v>128</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="F269" s="22" t="s">
         <v>984</v>
@@ -15340,19 +15615,19 @@
         <v>1003</v>
       </c>
       <c r="B270" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="F270" s="22" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="G270" s="20"/>
       <c r="H270" s="23"/>
@@ -15365,19 +15640,19 @@
         <v>1007</v>
       </c>
       <c r="B271" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>1009</v>
+        <v>1002</v>
       </c>
       <c r="F271" s="22" t="s">
-        <v>1006</v>
+        <v>984</v>
       </c>
       <c r="G271" s="20"/>
       <c r="H271" s="23"/>
@@ -15390,19 +15665,19 @@
         <v>1010</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C272" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="F272" s="22" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="G272" s="20"/>
       <c r="H272" s="23"/>
@@ -15415,19 +15690,19 @@
         <v>1014</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C273" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>1015</v>
+        <v>1008</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>1016</v>
+        <v>1009</v>
       </c>
       <c r="F273" s="22" t="s">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="G273" s="20"/>
       <c r="H273" s="23"/>
@@ -15443,13 +15718,13 @@
         <v>132</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>1018</v>
+        <v>1011</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>1019</v>
+        <v>1012</v>
       </c>
       <c r="F274" s="22" t="s">
         <v>1013</v>
@@ -15468,13 +15743,13 @@
         <v>132</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="F275" s="22" t="s">
         <v>1013</v>
@@ -15490,19 +15765,19 @@
         <v>1023</v>
       </c>
       <c r="B276" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="F276" s="22" t="s">
-        <v>1026</v>
+        <v>1013</v>
       </c>
       <c r="G276" s="20"/>
       <c r="H276" s="23"/>
@@ -15515,19 +15790,19 @@
         <v>1027</v>
       </c>
       <c r="B277" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>1028</v>
+        <v>1021</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>1029</v>
+        <v>1022</v>
       </c>
       <c r="F277" s="22" t="s">
-        <v>1030</v>
+        <v>1013</v>
       </c>
       <c r="G277" s="20"/>
       <c r="H277" s="23"/>
@@ -15540,19 +15815,19 @@
         <v>1031</v>
       </c>
       <c r="B278" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>1032</v>
+        <v>1024</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>1033</v>
+        <v>1025</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="G278" s="20"/>
       <c r="H278" s="23"/>
@@ -15568,13 +15843,13 @@
         <v>135</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="F279" s="22" t="s">
         <v>1030</v>
@@ -15593,13 +15868,13 @@
         <v>135</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1038</v>
+        <v>1032</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
       <c r="F280" s="22" t="s">
         <v>1030</v>
@@ -15618,13 +15893,13 @@
         <v>135</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
       <c r="F281" s="22" t="s">
         <v>1030</v>
@@ -15640,19 +15915,19 @@
         <v>1043</v>
       </c>
       <c r="B282" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="G282" s="20"/>
       <c r="H282" s="23"/>
@@ -15665,19 +15940,19 @@
         <v>1047</v>
       </c>
       <c r="B283" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1048</v>
+        <v>1041</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1049</v>
+        <v>1042</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>1046</v>
+        <v>1030</v>
       </c>
       <c r="G283" s="20"/>
       <c r="H283" s="23"/>
@@ -15693,13 +15968,13 @@
         <v>137</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1051</v>
+        <v>1044</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1052</v>
+        <v>1045</v>
       </c>
       <c r="F284" s="22" t="s">
         <v>1046</v>
@@ -15718,13 +15993,13 @@
         <v>137</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="F285" s="22" t="s">
         <v>1046</v>
@@ -15740,19 +16015,19 @@
         <v>1056</v>
       </c>
       <c r="B286" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C286" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="G286" s="20"/>
       <c r="H286" s="23"/>
@@ -15765,19 +16040,19 @@
         <v>1060</v>
       </c>
       <c r="B287" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="F287" s="22" t="s">
-        <v>1059</v>
+        <v>1046</v>
       </c>
       <c r="G287" s="20"/>
       <c r="H287" s="23"/>
@@ -15793,13 +16068,13 @@
         <v>140</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1065</v>
+        <v>1058</v>
       </c>
       <c r="F288" s="22" t="s">
         <v>1059</v>
@@ -15818,13 +16093,13 @@
         <v>140</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="F289" s="22" t="s">
         <v>1059</v>
@@ -15840,16 +16115,16 @@
         <v>1069</v>
       </c>
       <c r="B290" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="F290" s="22" t="s">
         <v>1059</v>
@@ -15865,16 +16140,16 @@
         <v>1072</v>
       </c>
       <c r="B291" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="F291" s="22" t="s">
         <v>1059</v>
@@ -15893,13 +16168,13 @@
         <v>142</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="F292" s="22" t="s">
         <v>1059</v>
@@ -15918,13 +16193,13 @@
         <v>142</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F293" s="22" t="s">
         <v>1059</v>
@@ -15943,13 +16218,13 @@
         <v>142</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="F294" s="22" t="s">
         <v>1059</v>
@@ -15968,13 +16243,13 @@
         <v>142</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="F295" s="22" t="s">
         <v>1059</v>
@@ -15993,13 +16268,13 @@
         <v>142</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="F296" s="22" t="s">
         <v>1059</v>
@@ -16015,19 +16290,19 @@
         <v>1090</v>
       </c>
       <c r="B297" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="F297" s="22" t="s">
-        <v>1093</v>
+        <v>1059</v>
       </c>
       <c r="G297" s="20"/>
       <c r="H297" s="23"/>
@@ -16040,19 +16315,19 @@
         <v>1094</v>
       </c>
       <c r="B298" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1095</v>
+        <v>1088</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1096</v>
+        <v>1089</v>
       </c>
       <c r="F298" s="22" t="s">
-        <v>1097</v>
+        <v>1059</v>
       </c>
       <c r="G298" s="20"/>
       <c r="H298" s="23"/>
@@ -16065,19 +16340,19 @@
         <v>1098</v>
       </c>
       <c r="B299" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1099</v>
+        <v>1091</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1100</v>
+        <v>1092</v>
       </c>
       <c r="F299" s="22" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="G299" s="20"/>
       <c r="H299" s="23"/>
@@ -16093,13 +16368,13 @@
         <v>146</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1102</v>
+        <v>1095</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1103</v>
+        <v>1096</v>
       </c>
       <c r="F300" s="22" t="s">
         <v>1097</v>
@@ -16115,19 +16390,19 @@
         <v>1104</v>
       </c>
       <c r="B301" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="F301" s="22" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="G301" s="20"/>
       <c r="H301" s="23"/>
@@ -16140,19 +16415,19 @@
         <v>1108</v>
       </c>
       <c r="B302" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1109</v>
+        <v>1102</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1110</v>
+        <v>1103</v>
       </c>
       <c r="F302" s="22" t="s">
-        <v>1107</v>
+        <v>1097</v>
       </c>
       <c r="G302" s="20"/>
       <c r="H302" s="23"/>
@@ -16168,13 +16443,13 @@
         <v>147</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1112</v>
+        <v>1105</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1113</v>
+        <v>1106</v>
       </c>
       <c r="F303" s="22" t="s">
         <v>1107</v>
@@ -16190,19 +16465,19 @@
         <v>1114</v>
       </c>
       <c r="B304" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="F304" s="22" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="G304" s="20"/>
       <c r="H304" s="23"/>
@@ -16215,19 +16490,19 @@
         <v>1118</v>
       </c>
       <c r="B305" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1119</v>
+        <v>1112</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1120</v>
+        <v>1113</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>1117</v>
+        <v>1107</v>
       </c>
       <c r="G305" s="20"/>
       <c r="H305" s="23"/>
@@ -16243,13 +16518,13 @@
         <v>148</v>
       </c>
       <c r="C306" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1122</v>
+        <v>1115</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1123</v>
+        <v>1116</v>
       </c>
       <c r="F306" s="22" t="s">
         <v>1117</v>
@@ -16268,13 +16543,13 @@
         <v>148</v>
       </c>
       <c r="C307" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="F307" s="22" t="s">
         <v>1117</v>
@@ -16293,13 +16568,13 @@
         <v>148</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="F308" s="22" t="s">
         <v>1117</v>
@@ -16318,13 +16593,13 @@
         <v>148</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1129</v>
+        <v>1115</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1130</v>
+        <v>1116</v>
       </c>
       <c r="F309" s="22" t="s">
         <v>1117</v>
@@ -16340,19 +16615,19 @@
         <v>1131</v>
       </c>
       <c r="B310" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>1134</v>
+        <v>1117</v>
       </c>
       <c r="G310" s="20"/>
       <c r="H310" s="23"/>
@@ -16365,19 +16640,19 @@
         <v>1135</v>
       </c>
       <c r="B311" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1136</v>
+        <v>1129</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1137</v>
+        <v>1130</v>
       </c>
       <c r="F311" s="22" t="s">
-        <v>1134</v>
+        <v>1117</v>
       </c>
       <c r="G311" s="20"/>
       <c r="H311" s="23"/>
@@ -16390,19 +16665,19 @@
         <v>1138</v>
       </c>
       <c r="B312" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C312" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1140</v>
+        <v>1133</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G312" s="20"/>
       <c r="H312" s="23"/>
@@ -16415,19 +16690,19 @@
         <v>1142</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C313" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1143</v>
+        <v>1136</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1144</v>
+        <v>1137</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>1141</v>
+        <v>1134</v>
       </c>
       <c r="G313" s="20"/>
       <c r="H313" s="23"/>
@@ -16440,19 +16715,19 @@
         <v>1145</v>
       </c>
       <c r="B314" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C314" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1147</v>
+        <v>1140</v>
       </c>
       <c r="F314" s="22" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="G314" s="20"/>
       <c r="H314" s="23"/>
@@ -16465,19 +16740,19 @@
         <v>1149</v>
       </c>
       <c r="B315" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C315" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1150</v>
+        <v>1143</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1151</v>
+        <v>1144</v>
       </c>
       <c r="F315" s="22" t="s">
-        <v>1148</v>
+        <v>1141</v>
       </c>
       <c r="G315" s="20"/>
       <c r="H315" s="23"/>
@@ -16493,13 +16768,13 @@
         <v>155</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1153</v>
+        <v>1146</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1154</v>
+        <v>1147</v>
       </c>
       <c r="F316" s="22" t="s">
         <v>1148</v>
@@ -16518,13 +16793,13 @@
         <v>155</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D317" s="22" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="E317" s="21" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="F317" s="22" t="s">
         <v>1148</v>
@@ -16543,13 +16818,13 @@
         <v>155</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="F318" s="22" t="s">
         <v>1148</v>
@@ -16568,13 +16843,13 @@
         <v>155</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="F319" s="22" t="s">
         <v>1148</v>
@@ -16593,13 +16868,13 @@
         <v>155</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="F320" s="22" t="s">
         <v>1148</v>
@@ -16618,13 +16893,13 @@
         <v>155</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="F321" s="22" t="s">
         <v>1148</v>
@@ -16643,13 +16918,13 @@
         <v>155</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="F322" s="22" t="s">
         <v>1148</v>
@@ -16668,13 +16943,13 @@
         <v>155</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="F323" s="22" t="s">
         <v>1148</v>
@@ -16693,13 +16968,13 @@
         <v>155</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="F324" s="22" t="s">
         <v>1148</v>
@@ -16718,13 +16993,13 @@
         <v>155</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="F325" s="22" t="s">
         <v>1148</v>
@@ -16743,13 +17018,13 @@
         <v>155</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="F326" s="22" t="s">
         <v>1148</v>
@@ -16768,13 +17043,13 @@
         <v>155</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="F327" s="22" t="s">
         <v>1148</v>
@@ -16793,13 +17068,13 @@
         <v>155</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="F328" s="22" t="s">
         <v>1148</v>
@@ -16818,13 +17093,13 @@
         <v>155</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="F329" s="22" t="s">
         <v>1148</v>
@@ -16843,13 +17118,13 @@
         <v>155</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="F330" s="22" t="s">
         <v>1148</v>
@@ -16868,13 +17143,13 @@
         <v>155</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>188</v>
+        <v>1193</v>
       </c>
       <c r="F331" s="22" t="s">
         <v>1148</v>
@@ -16893,13 +17168,13 @@
         <v>155</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="F332" s="22" t="s">
         <v>1148</v>
@@ -16918,13 +17193,13 @@
         <v>155</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>1204</v>
+        <v>188</v>
       </c>
       <c r="F333" s="22" t="s">
         <v>1148</v>
@@ -16943,13 +17218,13 @@
         <v>155</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="F334" s="22" t="s">
         <v>1148</v>
@@ -16965,19 +17240,19 @@
         <v>1208</v>
       </c>
       <c r="B335" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>174</v>
+        <v>332</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1163</v>
+        <v>1204</v>
       </c>
       <c r="F335" s="22" t="s">
-        <v>1210</v>
+        <v>1148</v>
       </c>
       <c r="G335" s="20"/>
       <c r="H335" s="23"/>
@@ -16990,19 +17265,19 @@
         <v>1211</v>
       </c>
       <c r="B336" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>179</v>
+        <v>336</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="F336" s="22" t="s">
-        <v>1210</v>
+        <v>1148</v>
       </c>
       <c r="G336" s="20"/>
       <c r="H336" s="23"/>
@@ -17018,13 +17293,13 @@
         <v>156</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1216</v>
+        <v>1163</v>
       </c>
       <c r="F337" s="22" t="s">
         <v>1210</v>
@@ -17043,13 +17318,13 @@
         <v>156</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="F338" s="22" t="s">
         <v>1210</v>
@@ -17068,13 +17343,13 @@
         <v>156</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="F339" s="22" t="s">
         <v>1210</v>
@@ -17093,13 +17368,13 @@
         <v>156</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
       <c r="F340" s="22" t="s">
         <v>1210</v>
@@ -17118,13 +17393,13 @@
         <v>156</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="F341" s="22" t="s">
         <v>1210</v>
@@ -17143,13 +17418,13 @@
         <v>156</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
       <c r="F342" s="22" t="s">
         <v>1210</v>
@@ -17168,13 +17443,13 @@
         <v>156</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="F343" s="22" t="s">
         <v>1210</v>
@@ -17193,13 +17468,13 @@
         <v>156</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1236</v>
+        <v>1230</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1237</v>
+        <v>1231</v>
       </c>
       <c r="F344" s="22" t="s">
         <v>1210</v>
@@ -17218,13 +17493,13 @@
         <v>156</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>296</v>
+        <v>258</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1239</v>
+        <v>1233</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1240</v>
+        <v>1234</v>
       </c>
       <c r="F345" s="22" t="s">
         <v>1210</v>
@@ -17243,13 +17518,13 @@
         <v>156</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>300</v>
+        <v>262</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="F346" s="22" t="s">
         <v>1210</v>
@@ -17265,19 +17540,19 @@
         <v>1244</v>
       </c>
       <c r="B347" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="F347" s="22" t="s">
-        <v>877</v>
+        <v>1210</v>
       </c>
       <c r="G347" s="20"/>
       <c r="H347" s="23"/>
@@ -17290,19 +17565,19 @@
         <v>1247</v>
       </c>
       <c r="B348" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>179</v>
+        <v>300</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1248</v>
+        <v>1242</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1249</v>
+        <v>1243</v>
       </c>
       <c r="F348" s="22" t="s">
-        <v>877</v>
+        <v>1210</v>
       </c>
       <c r="G348" s="20"/>
       <c r="H348" s="23"/>
@@ -17318,13 +17593,13 @@
         <v>158</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="F349" s="22" t="s">
         <v>877</v>
@@ -17343,13 +17618,13 @@
         <v>158</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
       <c r="F350" s="22" t="s">
         <v>877</v>
@@ -17368,13 +17643,13 @@
         <v>158</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="F351" s="22" t="s">
         <v>877</v>
@@ -17386,12 +17661,24 @@
       <c r="K351" s="23"/>
     </row>
     <row r="352" spans="1:11">
-      <c r="A352" s="21"/>
-      <c r="B352" s="21"/>
-      <c r="C352" s="21"/>
-      <c r="D352" s="22"/>
-      <c r="E352" s="21"/>
-      <c r="F352" s="22"/>
+      <c r="A352" s="21" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B352" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C352" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D352" s="22" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E352" s="21" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F352" s="22" t="s">
+        <v>877</v>
+      </c>
       <c r="G352" s="20"/>
       <c r="H352" s="23"/>
       <c r="I352" s="23"/>
@@ -17399,12 +17686,24 @@
       <c r="K352" s="23"/>
     </row>
     <row r="353" spans="1:11">
-      <c r="A353" s="21"/>
-      <c r="B353" s="21"/>
-      <c r="C353" s="21"/>
-      <c r="D353" s="22"/>
-      <c r="E353" s="21"/>
-      <c r="F353" s="22"/>
+      <c r="A353" s="21" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B353" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C353" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D353" s="22" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E353" s="21" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F353" s="22" t="s">
+        <v>877</v>
+      </c>
       <c r="G353" s="20"/>
       <c r="H353" s="23"/>
       <c r="I353" s="23"/>
@@ -18107,7 +18406,7 @@
       <c r="D407" s="22"/>
       <c r="E407" s="21"/>
       <c r="F407" s="22"/>
-      <c r="G407" s="18"/>
+      <c r="G407" s="20"/>
       <c r="H407" s="23"/>
       <c r="I407" s="23"/>
       <c r="J407" s="23"/>
@@ -18120,7 +18419,7 @@
       <c r="D408" s="22"/>
       <c r="E408" s="21"/>
       <c r="F408" s="22"/>
-      <c r="G408" s="18"/>
+      <c r="G408" s="20"/>
       <c r="H408" s="23"/>
       <c r="I408" s="23"/>
       <c r="J408" s="23"/>
@@ -38822,26 +39121,52 @@
       <c r="J2000" s="23"/>
       <c r="K2000" s="23"/>
     </row>
+    <row r="2001" spans="1:11">
+      <c r="A2001" s="21"/>
+      <c r="B2001" s="21"/>
+      <c r="C2001" s="21"/>
+      <c r="D2001" s="22"/>
+      <c r="E2001" s="21"/>
+      <c r="F2001" s="22"/>
+      <c r="G2001" s="18"/>
+      <c r="H2001" s="23"/>
+      <c r="I2001" s="23"/>
+      <c r="J2001" s="23"/>
+      <c r="K2001" s="33"/>
+    </row>
+    <row r="2002" spans="1:11">
+      <c r="A2002" s="21"/>
+      <c r="B2002" s="21"/>
+      <c r="C2002" s="21"/>
+      <c r="D2002" s="22"/>
+      <c r="E2002" s="21"/>
+      <c r="F2002" s="22"/>
+      <c r="G2002" s="18"/>
+      <c r="H2002" s="23"/>
+      <c r="I2002" s="23"/>
+      <c r="J2002" s="23"/>
+      <c r="K2002" s="33"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1996:A2000">
-    <cfRule type="duplicateValues" dxfId="1" priority="5"/>
+  <conditionalFormatting sqref="A1998:A2002">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A1995">
-    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  <conditionalFormatting sqref="A4:A1997">
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H214:H227" xr:uid="{904F9C07-3432-407C-9B6A-2B1BA8B10BD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H2002" xr:uid="{74B10176-32C1-4DCE-B9A9-308EB3B34100}">
       <formula1>"Daily 60 Days, Daily 120 Days, Weekly 12W, Weekly 24W, Monthly 3M, Monthly 6M, 60-Day Asset, 120-Day Asset, Weekly 12W Asset, Weekly 24W Asset, Monthly 3M Asset, Monthly 6M Asset"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38860,27 +39185,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="44" t="s">
         <v>1259</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="38" t="s">
         <v>1260</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0229BF08-1474-4D13-8242-FD8CCC815105}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D51AD34-718B-40DD-B5C8-D54B3B8CF329}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2503" uniqueCount="1289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1287">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -3859,24 +3859,12 @@
     <t>Koleosho Sherifat</t>
   </si>
   <si>
-    <t>11750</t>
-  </si>
-  <si>
-    <t>7000</t>
-  </si>
-  <si>
-    <t>17000</t>
-  </si>
-  <si>
     <t>Weekly 12W</t>
   </si>
   <si>
     <t>Weekly 24W</t>
   </si>
   <si>
-    <t>Weekly 12W Asset</t>
-  </si>
-  <si>
     <t>Osho Bunmi</t>
   </si>
   <si>
@@ -3893,6 +3881,12 @@
   </si>
   <si>
     <t>MEM-350</t>
+  </si>
+  <si>
+    <t>36925</t>
+  </si>
+  <si>
+    <t>25125</t>
   </si>
 </sst>
 </file>
@@ -4188,6 +4182,9 @@
     <xf numFmtId="49" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -4218,14 +4215,44 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="17">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Aptos"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="top"/>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFD9E2F3"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4541,59 +4568,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Aptos"/>
-      </font>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="top"/>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFD9E2F3"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="top"/>
     </dxf>
     <dxf>
@@ -4702,31 +4676,31 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Group Reference*"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Branch Name*"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Group Name*"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="17"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="15"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Meeting Day*"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Formation Date*"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Credit Officer Name*"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Credit Officer Phone"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2002" dataDxfId="13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2002" dataDxfId="11">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="3"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="2"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="0"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="5"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="4"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="3"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4891,28 +4865,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -4932,13 +4906,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="40"/>
+      <c r="H4" s="40"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -4946,13 +4920,13 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="37"/>
+      <c r="G5" s="37"/>
+      <c r="H5" s="38"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4960,13 +4934,13 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="38"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -4974,13 +4948,13 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="38"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -4988,13 +4962,13 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="37"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
+      <c r="H8" s="38"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -5002,25 +4976,25 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="38"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="38"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -5033,142 +5007,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="45" t="s">
+      <c r="A12" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="37"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="38"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="38"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="38"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="37"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+      <c r="H16" s="38"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="38"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="37"/>
+      <c r="C18" s="37"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="37"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="38"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="38"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="38"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="38"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -5222,30 +5196,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5901,9 +5875,7 @@
       <c r="H28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="14" t="s">
-        <v>1277</v>
-      </c>
+      <c r="I28" s="14"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
@@ -5930,9 +5902,7 @@
       <c r="H29" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="14" t="s">
-        <v>1278</v>
-      </c>
+      <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
@@ -5959,9 +5929,7 @@
       <c r="H30" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="14" t="s">
-        <v>1279</v>
-      </c>
+      <c r="I30" s="14"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
@@ -5988,7 +5956,9 @@
       <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="34"/>
+      <c r="I31" s="34" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
@@ -6015,7 +5985,9 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="34"/>
+      <c r="I32" s="34" t="s">
+        <v>1286</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -8734,7 +8706,7 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A253">
-    <cfRule type="duplicateValues" dxfId="18" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8758,34 +8730,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="47" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -13540,18 +13512,10 @@
       <c r="F193" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G193" s="20">
-        <v>24550</v>
-      </c>
-      <c r="H193" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I193" s="23">
-        <v>198000</v>
-      </c>
-      <c r="J193" s="23">
-        <v>82500</v>
-      </c>
+      <c r="G193" s="20"/>
+      <c r="H193" s="23"/>
+      <c r="I193" s="23"/>
+      <c r="J193" s="23"/>
       <c r="K193" s="23"/>
     </row>
     <row r="194" spans="1:11">
@@ -13573,18 +13537,10 @@
       <c r="F194" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G194" s="20">
-        <v>22200</v>
-      </c>
-      <c r="H194" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I194" s="23">
-        <v>48000</v>
-      </c>
-      <c r="J194" s="23">
-        <v>4000</v>
-      </c>
+      <c r="G194" s="20"/>
+      <c r="H194" s="23"/>
+      <c r="I194" s="23"/>
+      <c r="J194" s="23"/>
       <c r="K194" s="23"/>
     </row>
     <row r="195" spans="1:11">
@@ -13606,18 +13562,10 @@
       <c r="F195" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G195" s="20">
-        <v>15000</v>
-      </c>
-      <c r="H195" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I195" s="23">
-        <v>288000</v>
-      </c>
-      <c r="J195" s="23">
-        <v>288000</v>
-      </c>
+      <c r="G195" s="20"/>
+      <c r="H195" s="23"/>
+      <c r="I195" s="23"/>
+      <c r="J195" s="23"/>
       <c r="K195" s="23"/>
     </row>
     <row r="196" spans="1:11">
@@ -13639,18 +13587,10 @@
       <c r="F196" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G196" s="20">
-        <v>13000</v>
-      </c>
-      <c r="H196" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I196" s="23">
-        <v>60000</v>
-      </c>
-      <c r="J196" s="23">
-        <v>10000</v>
-      </c>
+      <c r="G196" s="20"/>
+      <c r="H196" s="23"/>
+      <c r="I196" s="23"/>
+      <c r="J196" s="23"/>
       <c r="K196" s="23"/>
     </row>
     <row r="197" spans="1:11">
@@ -13670,18 +13610,10 @@
       <c r="F197" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G197" s="20">
-        <v>9500</v>
-      </c>
-      <c r="H197" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I197" s="23">
-        <v>150000</v>
-      </c>
-      <c r="J197" s="23">
-        <v>100000</v>
-      </c>
+      <c r="G197" s="20"/>
+      <c r="H197" s="23"/>
+      <c r="I197" s="23"/>
+      <c r="J197" s="23"/>
       <c r="K197" s="23"/>
     </row>
     <row r="198" spans="1:11">
@@ -13704,9 +13636,7 @@
         <v>776</v>
       </c>
       <c r="G198" s="20"/>
-      <c r="H198" s="23" t="s">
-        <v>1281</v>
-      </c>
+      <c r="H198" s="23"/>
       <c r="I198" s="23"/>
       <c r="J198" s="23"/>
       <c r="K198" s="23"/>
@@ -13730,18 +13660,10 @@
       <c r="F199" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G199" s="20">
-        <v>23600</v>
-      </c>
-      <c r="H199" s="23" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I199" s="23">
-        <v>198000</v>
-      </c>
-      <c r="J199" s="23">
-        <v>41250</v>
-      </c>
+      <c r="G199" s="20"/>
+      <c r="H199" s="23"/>
+      <c r="I199" s="23"/>
+      <c r="J199" s="23"/>
       <c r="K199" s="23"/>
     </row>
     <row r="200" spans="1:11">
@@ -13763,12 +13685,8 @@
       <c r="F200" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G200" s="20">
-        <v>63400</v>
-      </c>
-      <c r="H200" s="23" t="s">
-        <v>1281</v>
-      </c>
+      <c r="G200" s="20"/>
+      <c r="H200" s="23"/>
       <c r="I200" s="23"/>
       <c r="J200" s="23"/>
       <c r="K200" s="23"/>
@@ -13792,18 +13710,10 @@
       <c r="F201" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G201" s="20">
-        <v>18725</v>
-      </c>
-      <c r="H201" s="23" t="s">
-        <v>1281</v>
-      </c>
-      <c r="I201" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J201" s="23">
-        <v>28875</v>
-      </c>
+      <c r="G201" s="20"/>
+      <c r="H201" s="23"/>
+      <c r="I201" s="23"/>
+      <c r="J201" s="23"/>
       <c r="K201" s="23"/>
     </row>
     <row r="202" spans="1:11">
@@ -13825,12 +13735,8 @@
       <c r="F202" s="22" t="s">
         <v>776</v>
       </c>
-      <c r="G202" s="20">
-        <v>89000</v>
-      </c>
-      <c r="H202" s="23" t="s">
-        <v>1281</v>
-      </c>
+      <c r="G202" s="20"/>
+      <c r="H202" s="23"/>
       <c r="I202" s="23"/>
       <c r="J202" s="23"/>
       <c r="K202" s="23"/>
@@ -13854,18 +13760,10 @@
       <c r="F203" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G203" s="20">
-        <v>5950</v>
-      </c>
-      <c r="H203" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I203" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J203" s="23">
-        <v>24750</v>
-      </c>
+      <c r="G203" s="20"/>
+      <c r="H203" s="23"/>
+      <c r="I203" s="23"/>
+      <c r="J203" s="23"/>
       <c r="K203" s="23"/>
     </row>
     <row r="204" spans="1:11">
@@ -13887,18 +13785,10 @@
       <c r="F204" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G204" s="20">
-        <v>4750</v>
-      </c>
-      <c r="H204" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I204" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J204" s="23">
-        <v>33000</v>
-      </c>
+      <c r="G204" s="20"/>
+      <c r="H204" s="23"/>
+      <c r="I204" s="23"/>
+      <c r="J204" s="23"/>
       <c r="K204" s="23"/>
     </row>
     <row r="205" spans="1:11">
@@ -13921,15 +13811,9 @@
         <v>806</v>
       </c>
       <c r="G205" s="20"/>
-      <c r="H205" s="23" t="s">
-        <v>1282</v>
-      </c>
-      <c r="I205" s="23">
-        <v>279000</v>
-      </c>
-      <c r="J205" s="23">
-        <v>46500</v>
-      </c>
+      <c r="H205" s="23"/>
+      <c r="I205" s="23"/>
+      <c r="J205" s="23"/>
       <c r="K205" s="23"/>
     </row>
     <row r="206" spans="1:11">
@@ -13951,18 +13835,10 @@
       <c r="F206" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G206" s="20">
-        <v>5000</v>
-      </c>
-      <c r="H206" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I206" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J206" s="23">
-        <v>24750</v>
-      </c>
+      <c r="G206" s="20"/>
+      <c r="H206" s="23"/>
+      <c r="I206" s="23"/>
+      <c r="J206" s="23"/>
       <c r="K206" s="23"/>
     </row>
     <row r="207" spans="1:11">
@@ -13984,18 +13860,10 @@
       <c r="F207" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G207" s="20">
-        <v>4750</v>
-      </c>
-      <c r="H207" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I207" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J207" s="23">
-        <v>33000</v>
-      </c>
+      <c r="G207" s="20"/>
+      <c r="H207" s="23"/>
+      <c r="I207" s="23"/>
+      <c r="J207" s="23"/>
       <c r="K207" s="23"/>
     </row>
     <row r="208" spans="1:11">
@@ -14017,18 +13885,10 @@
       <c r="F208" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G208" s="20">
-        <v>3000</v>
-      </c>
-      <c r="H208" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I208" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J208" s="23">
-        <v>57750</v>
-      </c>
+      <c r="G208" s="20"/>
+      <c r="H208" s="23"/>
+      <c r="I208" s="23"/>
+      <c r="J208" s="23"/>
       <c r="K208" s="23"/>
     </row>
     <row r="209" spans="1:11">
@@ -14042,27 +13902,19 @@
         <v>206</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="F209" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G209" s="49">
-        <v>2750</v>
-      </c>
-      <c r="H209" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I209" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J209" s="33">
-        <v>66000</v>
-      </c>
-      <c r="K209" s="23"/>
+      <c r="G209" s="35"/>
+      <c r="H209" s="23"/>
+      <c r="I209" s="23"/>
+      <c r="J209" s="23"/>
+      <c r="K209" s="33"/>
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="21" t="s">
@@ -14075,27 +13927,19 @@
         <v>210</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>1285</v>
+        <v>1281</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="F210" s="22" t="s">
         <v>806</v>
       </c>
-      <c r="G210" s="49">
-        <v>2750</v>
-      </c>
-      <c r="H210" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I210" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J210" s="33">
-        <v>66000</v>
-      </c>
-      <c r="K210" s="23"/>
+      <c r="G210" s="35"/>
+      <c r="H210" s="23"/>
+      <c r="I210" s="23"/>
+      <c r="J210" s="23"/>
+      <c r="K210" s="33"/>
     </row>
     <row r="211" spans="1:11">
       <c r="A211" s="21" t="s">
@@ -14116,18 +13960,10 @@
       <c r="F211" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="G211" s="20">
-        <v>19200</v>
-      </c>
-      <c r="H211" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I211" s="23">
-        <v>288000</v>
-      </c>
-      <c r="J211" s="23">
-        <v>288000</v>
-      </c>
+      <c r="G211" s="20"/>
+      <c r="H211" s="23"/>
+      <c r="I211" s="23"/>
+      <c r="J211" s="23"/>
       <c r="K211" s="23"/>
     </row>
     <row r="212" spans="1:11">
@@ -14149,18 +13985,10 @@
       <c r="F212" s="22" t="s">
         <v>698</v>
       </c>
-      <c r="G212" s="20">
-        <v>11700</v>
-      </c>
-      <c r="H212" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I212" s="23">
-        <v>288000</v>
-      </c>
-      <c r="J212" s="23">
-        <v>288000</v>
-      </c>
+      <c r="G212" s="20"/>
+      <c r="H212" s="23"/>
+      <c r="I212" s="23"/>
+      <c r="J212" s="23"/>
       <c r="K212" s="23"/>
     </row>
     <row r="213" spans="1:11">
@@ -14182,18 +14010,10 @@
       <c r="F213" s="22" t="s">
         <v>698</v>
       </c>
-      <c r="G213" s="20">
-        <v>11700</v>
-      </c>
-      <c r="H213" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I213" s="23">
-        <v>246000</v>
-      </c>
-      <c r="J213" s="23">
-        <v>246000</v>
-      </c>
+      <c r="G213" s="20"/>
+      <c r="H213" s="23"/>
+      <c r="I213" s="23"/>
+      <c r="J213" s="23"/>
       <c r="K213" s="23"/>
     </row>
     <row r="214" spans="1:11">
@@ -14215,18 +14035,10 @@
       <c r="F214" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="G214" s="20">
-        <v>11000</v>
-      </c>
-      <c r="H214" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I214" s="23">
-        <v>288000</v>
-      </c>
-      <c r="J214" s="23">
-        <v>288000</v>
-      </c>
+      <c r="G214" s="20"/>
+      <c r="H214" s="23"/>
+      <c r="I214" s="23"/>
+      <c r="J214" s="23"/>
       <c r="K214" s="23"/>
     </row>
     <row r="215" spans="1:11">
@@ -14248,18 +14060,10 @@
       <c r="F215" s="22" t="s">
         <v>711</v>
       </c>
-      <c r="G215" s="20">
-        <v>9250</v>
-      </c>
-      <c r="H215" s="23" t="s">
-        <v>1280</v>
-      </c>
-      <c r="I215" s="23">
-        <v>99000</v>
-      </c>
-      <c r="J215" s="23">
-        <v>24750</v>
-      </c>
+      <c r="G215" s="20"/>
+      <c r="H215" s="23"/>
+      <c r="I215" s="23"/>
+      <c r="J215" s="23"/>
       <c r="K215" s="23"/>
     </row>
     <row r="216" spans="1:11">
@@ -14281,8 +14085,12 @@
       <c r="F216" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G216" s="20"/>
-      <c r="H216" s="23"/>
+      <c r="G216" s="20">
+        <v>40100</v>
+      </c>
+      <c r="H216" s="23" t="s">
+        <v>1277</v>
+      </c>
       <c r="I216" s="23"/>
       <c r="J216" s="23"/>
       <c r="K216" s="23"/>
@@ -14306,11 +14114,21 @@
       <c r="F217" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G217" s="20"/>
-      <c r="H217" s="23"/>
-      <c r="I217" s="23"/>
-      <c r="J217" s="23"/>
-      <c r="K217" s="23"/>
+      <c r="G217" s="20">
+        <v>15600</v>
+      </c>
+      <c r="H217" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I217" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J217" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K217" s="23">
+        <v>132000</v>
+      </c>
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="21" t="s">
@@ -14331,11 +14149,21 @@
       <c r="F218" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G218" s="20"/>
-      <c r="H218" s="23"/>
-      <c r="I218" s="23"/>
-      <c r="J218" s="23"/>
-      <c r="K218" s="23"/>
+      <c r="G218" s="20">
+        <v>17500</v>
+      </c>
+      <c r="H218" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I218" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J218" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K218" s="23">
+        <v>132000</v>
+      </c>
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
@@ -14356,8 +14184,12 @@
       <c r="F219" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G219" s="20"/>
-      <c r="H219" s="23"/>
+      <c r="G219" s="20">
+        <v>35500</v>
+      </c>
+      <c r="H219" s="23" t="s">
+        <v>1277</v>
+      </c>
       <c r="I219" s="23"/>
       <c r="J219" s="23"/>
       <c r="K219" s="23"/>
@@ -14382,7 +14214,9 @@
         <v>839</v>
       </c>
       <c r="G220" s="20"/>
-      <c r="H220" s="23"/>
+      <c r="H220" s="23" t="s">
+        <v>1277</v>
+      </c>
       <c r="I220" s="23"/>
       <c r="J220" s="23"/>
       <c r="K220" s="23"/>
@@ -14406,11 +14240,21 @@
       <c r="F221" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G221" s="20"/>
-      <c r="H221" s="23"/>
-      <c r="I221" s="23"/>
-      <c r="J221" s="23"/>
-      <c r="K221" s="23"/>
+      <c r="G221" s="20">
+        <v>3000</v>
+      </c>
+      <c r="H221" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I221" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J221" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K221" s="23">
+        <v>99000</v>
+      </c>
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
@@ -14431,11 +14275,21 @@
       <c r="F222" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G222" s="20"/>
-      <c r="H222" s="23"/>
-      <c r="I222" s="23"/>
-      <c r="J222" s="23"/>
-      <c r="K222" s="23"/>
+      <c r="G222" s="20">
+        <v>54250</v>
+      </c>
+      <c r="H222" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I222" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J222" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K222" s="23">
+        <v>92250</v>
+      </c>
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
@@ -14456,11 +14310,21 @@
       <c r="F223" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G223" s="20"/>
-      <c r="H223" s="23"/>
-      <c r="I223" s="23"/>
-      <c r="J223" s="23"/>
-      <c r="K223" s="23"/>
+      <c r="G223" s="20">
+        <v>31150</v>
+      </c>
+      <c r="H223" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I223" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J223" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K223" s="23">
+        <v>102500</v>
+      </c>
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
@@ -14481,11 +14345,21 @@
       <c r="F224" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G224" s="20"/>
-      <c r="H224" s="23"/>
-      <c r="I224" s="23"/>
-      <c r="J224" s="23"/>
-      <c r="K224" s="23"/>
+      <c r="G224" s="20">
+        <v>21250</v>
+      </c>
+      <c r="H224" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I224" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J224" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K224" s="23">
+        <v>99000</v>
+      </c>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
@@ -14506,11 +14380,21 @@
       <c r="F225" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G225" s="20"/>
-      <c r="H225" s="23"/>
-      <c r="I225" s="23"/>
-      <c r="J225" s="23"/>
-      <c r="K225" s="23"/>
+      <c r="G225" s="20">
+        <v>12500</v>
+      </c>
+      <c r="H225" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I225" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J225" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K225" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
@@ -14531,11 +14415,21 @@
       <c r="F226" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G226" s="20"/>
-      <c r="H226" s="23"/>
-      <c r="I226" s="23"/>
-      <c r="J226" s="23"/>
-      <c r="K226" s="23"/>
+      <c r="G226" s="20">
+        <v>7700</v>
+      </c>
+      <c r="H226" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="I226" s="23">
+        <v>50000</v>
+      </c>
+      <c r="J226" s="23">
+        <v>48000</v>
+      </c>
+      <c r="K226" s="23">
+        <v>32000</v>
+      </c>
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
@@ -14556,11 +14450,21 @@
       <c r="F227" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G227" s="20"/>
-      <c r="H227" s="23"/>
-      <c r="I227" s="23"/>
-      <c r="J227" s="23"/>
-      <c r="K227" s="23"/>
+      <c r="G227" s="20">
+        <v>11650</v>
+      </c>
+      <c r="H227" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I227" s="23">
+        <v>80000</v>
+      </c>
+      <c r="J227" s="23">
+        <v>78000</v>
+      </c>
+      <c r="K227" s="23">
+        <v>42250</v>
+      </c>
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="21" t="s">
@@ -14581,11 +14485,21 @@
       <c r="F228" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G228" s="20"/>
-      <c r="H228" s="23"/>
-      <c r="I228" s="23"/>
-      <c r="J228" s="23"/>
-      <c r="K228" s="23"/>
+      <c r="G228" s="20">
+        <v>9300</v>
+      </c>
+      <c r="H228" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I228" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J228" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K228" s="23">
+        <v>45375</v>
+      </c>
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="21" t="s">
@@ -14604,8 +14518,12 @@
       <c r="F229" s="22" t="s">
         <v>839</v>
       </c>
-      <c r="G229" s="20"/>
-      <c r="H229" s="23"/>
+      <c r="G229" s="20">
+        <v>42925</v>
+      </c>
+      <c r="H229" s="23" t="s">
+        <v>1278</v>
+      </c>
       <c r="I229" s="23"/>
       <c r="J229" s="23"/>
       <c r="K229" s="23"/>
@@ -17662,7 +17580,7 @@
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="21" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="B352" s="21" t="s">
         <v>158</v>
@@ -17687,7 +17605,7 @@
     </row>
     <row r="353" spans="1:11">
       <c r="A353" s="21" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="B353" s="21" t="s">
         <v>158</v>
@@ -39153,10 +39071,10 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <conditionalFormatting sqref="A1998:A2002">
-    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4:A1997">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H2002" xr:uid="{74B10176-32C1-4DCE-B9A9-308EB3B34100}">
@@ -39185,27 +39103,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>1259</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1260</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D51AD34-718B-40DD-B5C8-D54B3B8CF329}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8083B6CD-485B-4D51-A6A5-89C90FAF0EC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2493" uniqueCount="1287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="1297">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -2089,9 +2089,6 @@
     <t>07034328661</t>
   </si>
   <si>
-    <t>Idimogun Junction Ogijo</t>
-  </si>
-  <si>
     <t>MEM-162</t>
   </si>
   <si>
@@ -2101,9 +2098,6 @@
     <t>0708813676</t>
   </si>
   <si>
-    <t xml:space="preserve">Idimogun Junction Ogijo </t>
-  </si>
-  <si>
     <t>MEM-163</t>
   </si>
   <si>
@@ -3883,10 +3877,46 @@
     <t>MEM-350</t>
   </si>
   <si>
-    <t>36925</t>
-  </si>
-  <si>
-    <t>25125</t>
+    <t>Talabi Folashade</t>
+  </si>
+  <si>
+    <t>32550</t>
+  </si>
+  <si>
+    <t>23150</t>
+  </si>
+  <si>
+    <t>Mary Daramola</t>
+  </si>
+  <si>
+    <t>08062619265</t>
+  </si>
+  <si>
+    <t>MEM-351</t>
+  </si>
+  <si>
+    <t>Balogun Oluwakemi</t>
+  </si>
+  <si>
+    <t>MEM-352</t>
+  </si>
+  <si>
+    <t>Vivian Osazuwa</t>
+  </si>
+  <si>
+    <t>08167571066</t>
+  </si>
+  <si>
+    <t>Modinat Quadri</t>
+  </si>
+  <si>
+    <t>Olajide Bidemi</t>
+  </si>
+  <si>
+    <t>08079339079</t>
+  </si>
+  <si>
+    <t>09035404634</t>
   </si>
 </sst>
 </file>
@@ -4086,7 +4116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4185,41 +4215,81 @@
     <xf numFmtId="3" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -4572,26 +4642,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
@@ -4647,16 +4697,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4676,31 +4716,31 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Group Reference*"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Branch Name*"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Group Name*"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Group Leader Name*" dataDxfId="16"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Meeting Day*"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Formation Date*"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Credit Officer Name*"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Credit Officer Phone"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Group Savings" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2002" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2008" dataDxfId="14">
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="6"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="5"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="2"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="1"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Member Number" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Full Name*" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Phone Number*" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Home Address*" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0100-000011000000}" name="Savings Balance*" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0100-000015000000}" name="Loan Type (Product)*" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0100-000016000000}" name="Principal Loan*" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0100-000014000000}" name="Active Credit (Disbursed)*" dataDxfId="4"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0100-000013000000}" name="Current Credit Balance*" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4865,28 +4905,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -4906,13 +4946,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -4923,10 +4963,10 @@
       <c r="D5" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="41"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4937,10 +4977,10 @@
       <c r="D6" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="41"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -4951,10 +4991,10 @@
       <c r="D7" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="41"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -4965,10 +5005,10 @@
       <c r="D8" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -4979,10 +5019,10 @@
       <c r="D9" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="38"/>
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
@@ -4991,10 +5031,10 @@
       <c r="D10" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="38"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -5007,142 +5047,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="46" t="s">
+      <c r="A12" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="41"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="38"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="41"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="43" t="s">
+      <c r="B15" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="41"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="43" t="s">
+      <c r="B16" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="38"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="41"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="38"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="40"/>
+      <c r="H17" s="41"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="43" t="s">
+      <c r="B18" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="38"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="40"/>
+      <c r="H18" s="41"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="38"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="F19" s="40"/>
+      <c r="G19" s="40"/>
+      <c r="H19" s="41"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="43" t="s">
+      <c r="B20" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="38"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="F20" s="40"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="41"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="36" t="s">
+      <c r="B21" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="38"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="40"/>
+      <c r="H21" s="41"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -5155,13 +5195,6 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:H4"/>
@@ -5174,6 +5207,13 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5196,30 +5236,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="40"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5685,7 +5725,9 @@
       <c r="C21" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="6"/>
+      <c r="D21" s="6" t="s">
+        <v>648</v>
+      </c>
       <c r="E21" s="6" t="s">
         <v>87</v>
       </c>
@@ -5698,7 +5740,9 @@
       <c r="H21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="14"/>
+      <c r="I21" s="14" t="s">
+        <v>1284</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
@@ -5710,7 +5754,9 @@
       <c r="C22" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>1283</v>
+      </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
       </c>
@@ -5723,7 +5769,9 @@
       <c r="H22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="14"/>
+      <c r="I22" s="14" t="s">
+        <v>1285</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
@@ -5861,7 +5909,7 @@
         <v>106</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -5888,7 +5936,7 @@
         <v>109</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>107</v>
@@ -5915,7 +5963,7 @@
         <v>111</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>107</v>
@@ -5942,7 +5990,7 @@
         <v>113</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>114</v>
@@ -5956,9 +6004,7 @@
       <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="34" t="s">
-        <v>1285</v>
-      </c>
+      <c r="I31" s="34"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
@@ -5971,7 +6017,7 @@
         <v>116</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -5985,9 +6031,7 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="34" t="s">
-        <v>1286</v>
-      </c>
+      <c r="I32" s="51"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -6012,7 +6056,7 @@
       <c r="H33" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="I33" s="14"/>
+      <c r="I33" s="34"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6" t="s">
@@ -8706,7 +8750,7 @@
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:A253">
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="21"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -8718,7 +8762,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2002"/>
+  <dimension ref="A1:K2008"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22.09765625" style="27" customWidth="1"/>
@@ -8730,34 +8774,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="50"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -12472,11 +12516,21 @@
       <c r="F151" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G151" s="20"/>
-      <c r="H151" s="23"/>
-      <c r="I151" s="23"/>
-      <c r="J151" s="23"/>
-      <c r="K151" s="23"/>
+      <c r="G151" s="20">
+        <v>12500</v>
+      </c>
+      <c r="H151" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I151" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J151" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K151" s="23">
+        <v>50000</v>
+      </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="21" t="s">
@@ -12497,11 +12551,21 @@
       <c r="F152" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G152" s="20"/>
-      <c r="H152" s="23"/>
-      <c r="I152" s="23"/>
-      <c r="J152" s="23"/>
-      <c r="K152" s="23"/>
+      <c r="G152" s="20">
+        <v>33100</v>
+      </c>
+      <c r="H152" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I152" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J152" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K152" s="23">
+        <v>120000</v>
+      </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="21" t="s">
@@ -12522,8 +12586,12 @@
       <c r="F153" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G153" s="20"/>
-      <c r="H153" s="23"/>
+      <c r="G153" s="20">
+        <v>23950</v>
+      </c>
+      <c r="H153" s="23" t="s">
+        <v>1275</v>
+      </c>
       <c r="I153" s="23"/>
       <c r="J153" s="23"/>
       <c r="K153" s="23"/>
@@ -12547,11 +12615,21 @@
       <c r="F154" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G154" s="20"/>
-      <c r="H154" s="23"/>
-      <c r="I154" s="23"/>
-      <c r="J154" s="23"/>
-      <c r="K154" s="23"/>
+      <c r="G154" s="20">
+        <v>5650</v>
+      </c>
+      <c r="H154" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I154" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J154" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K154" s="23">
+        <v>41250</v>
+      </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="21" t="s">
@@ -12572,11 +12650,21 @@
       <c r="F155" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G155" s="20"/>
-      <c r="H155" s="23"/>
-      <c r="I155" s="23"/>
-      <c r="J155" s="23"/>
-      <c r="K155" s="23"/>
+      <c r="G155" s="20">
+        <v>16050</v>
+      </c>
+      <c r="H155" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I155" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J155" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K155" s="23">
+        <v>50000</v>
+      </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="21" t="s">
@@ -12597,11 +12685,21 @@
       <c r="F156" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G156" s="20"/>
-      <c r="H156" s="23"/>
-      <c r="I156" s="23"/>
-      <c r="J156" s="23"/>
-      <c r="K156" s="23"/>
+      <c r="G156" s="20">
+        <v>6750</v>
+      </c>
+      <c r="H156" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I156" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J156" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K156" s="23">
+        <v>57750</v>
+      </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="21" t="s">
@@ -12623,7 +12721,9 @@
         <v>650</v>
       </c>
       <c r="G157" s="20"/>
-      <c r="H157" s="23"/>
+      <c r="H157" s="23" t="s">
+        <v>1275</v>
+      </c>
       <c r="I157" s="23"/>
       <c r="J157" s="23"/>
       <c r="K157" s="23"/>
@@ -12647,8 +12747,12 @@
       <c r="F158" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G158" s="20"/>
-      <c r="H158" s="23"/>
+      <c r="G158" s="20">
+        <v>15750</v>
+      </c>
+      <c r="H158" s="23" t="s">
+        <v>1275</v>
+      </c>
       <c r="I158" s="23"/>
       <c r="J158" s="23"/>
       <c r="K158" s="23"/>
@@ -12672,11 +12776,21 @@
       <c r="F159" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G159" s="20"/>
-      <c r="H159" s="23"/>
-      <c r="I159" s="23"/>
-      <c r="J159" s="23"/>
-      <c r="K159" s="23"/>
+      <c r="G159" s="20">
+        <v>10550</v>
+      </c>
+      <c r="H159" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I159" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J159" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K159" s="23">
+        <v>8250</v>
+      </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="21" t="s">
@@ -12697,11 +12811,21 @@
       <c r="F160" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G160" s="20"/>
-      <c r="H160" s="23"/>
-      <c r="I160" s="23"/>
-      <c r="J160" s="23"/>
-      <c r="K160" s="23"/>
+      <c r="G160" s="20">
+        <v>24000</v>
+      </c>
+      <c r="H160" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I160" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J160" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K160" s="23">
+        <v>240000</v>
+      </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="21" t="s">
@@ -12720,11 +12844,21 @@
       <c r="F161" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G161" s="20"/>
-      <c r="H161" s="23"/>
-      <c r="I161" s="23"/>
-      <c r="J161" s="23"/>
-      <c r="K161" s="23"/>
+      <c r="G161" s="20">
+        <v>16575</v>
+      </c>
+      <c r="H161" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I161" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J161" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K161" s="23">
+        <v>45375</v>
+      </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="21" t="s">
@@ -12745,280 +12879,348 @@
       <c r="F162" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G162" s="20"/>
-      <c r="H162" s="23"/>
+      <c r="G162" s="20">
+        <v>29625</v>
+      </c>
+      <c r="H162" s="23" t="s">
+        <v>1276</v>
+      </c>
       <c r="I162" s="23"/>
       <c r="J162" s="23"/>
       <c r="K162" s="23"/>
     </row>
-    <row r="163" spans="1:11">
+    <row r="163" spans="1:11" s="36" customFormat="1">
       <c r="A163" s="21" t="s">
         <v>680</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C163" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D163" s="22" t="s">
-        <v>681</v>
-      </c>
-      <c r="E163" s="21" t="s">
-        <v>682</v>
+        <v>304</v>
+      </c>
+      <c r="D163" s="53" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E163" s="52" t="s">
+        <v>1287</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>683</v>
-      </c>
-      <c r="G163" s="20"/>
-      <c r="H163" s="23"/>
-      <c r="I163" s="23"/>
-      <c r="J163" s="23"/>
-      <c r="K163" s="23"/>
-    </row>
-    <row r="164" spans="1:11">
+        <v>650</v>
+      </c>
+      <c r="G163" s="35">
+        <v>4750</v>
+      </c>
+      <c r="H163" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I163" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J163" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K163" s="33">
+        <v>74250</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" s="36" customFormat="1">
       <c r="A164" s="21" t="s">
         <v>684</v>
       </c>
       <c r="B164" s="21" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C164" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="D164" s="22" t="s">
-        <v>685</v>
-      </c>
-      <c r="E164" s="21" t="s">
-        <v>686</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="D164" s="53" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E164" s="52"/>
       <c r="F164" s="22" t="s">
-        <v>687</v>
-      </c>
-      <c r="G164" s="20"/>
-      <c r="H164" s="23"/>
-      <c r="I164" s="23"/>
-      <c r="J164" s="23"/>
-      <c r="K164" s="23"/>
+        <v>650</v>
+      </c>
+      <c r="G164" s="35">
+        <v>6250</v>
+      </c>
+      <c r="H164" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I164" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J164" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K164" s="33">
+        <v>57750</v>
+      </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="21" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B165" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C165" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D165" s="22" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="E165" s="21" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="F165" s="22" t="s">
-        <v>691</v>
-      </c>
-      <c r="G165" s="20"/>
-      <c r="H165" s="23"/>
-      <c r="I165" s="23"/>
-      <c r="J165" s="23"/>
-      <c r="K165" s="23"/>
+        <v>683</v>
+      </c>
+      <c r="G165" s="20">
+        <v>6700</v>
+      </c>
+      <c r="H165" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I165" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J165" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K165" s="23">
+        <v>137500</v>
+      </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="21" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B166" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C166" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D166" s="22" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="E166" s="21" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="F166" s="22" t="s">
-        <v>687</v>
-      </c>
-      <c r="G166" s="20"/>
-      <c r="H166" s="23"/>
-      <c r="I166" s="23"/>
-      <c r="J166" s="23"/>
-      <c r="K166" s="23"/>
+        <v>683</v>
+      </c>
+      <c r="G166" s="20">
+        <v>24900</v>
+      </c>
+      <c r="H166" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I166" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J166" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K166" s="23">
+        <v>57750</v>
+      </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="21" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B167" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C167" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D167" s="22" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="E167" s="21" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="F167" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G167" s="20"/>
-      <c r="H167" s="23"/>
+        <v>683</v>
+      </c>
+      <c r="G167" s="20">
+        <v>41800</v>
+      </c>
+      <c r="H167" s="23" t="s">
+        <v>1276</v>
+      </c>
       <c r="I167" s="23"/>
       <c r="J167" s="23"/>
       <c r="K167" s="23"/>
     </row>
     <row r="168" spans="1:11">
       <c r="A168" s="21" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B168" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C168" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D168" s="22" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="E168" s="21" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
       <c r="F168" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G168" s="20"/>
-      <c r="H168" s="23"/>
-      <c r="I168" s="23"/>
-      <c r="J168" s="23"/>
-      <c r="K168" s="23"/>
-    </row>
-    <row r="169" spans="1:11">
-      <c r="A169" s="21" t="s">
-        <v>702</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="G168" s="20">
+        <v>22350</v>
+      </c>
+      <c r="H168" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I168" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J168" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K168" s="23">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" s="36" customFormat="1">
+      <c r="A169" s="52"/>
       <c r="B169" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C169" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D169" s="22" t="s">
-        <v>703</v>
-      </c>
-      <c r="E169" s="21" t="s">
-        <v>704</v>
+        <v>198</v>
+      </c>
+      <c r="D169" s="53" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E169" s="52" t="s">
+        <v>1292</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G169" s="20"/>
-      <c r="H169" s="23"/>
-      <c r="I169" s="23"/>
-      <c r="J169" s="23"/>
-      <c r="K169" s="23"/>
-    </row>
-    <row r="170" spans="1:11">
-      <c r="A170" s="21" t="s">
-        <v>705</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="G169" s="35">
+        <v>25600</v>
+      </c>
+      <c r="H169" s="33" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I169" s="33"/>
+      <c r="J169" s="33"/>
+      <c r="K169" s="33"/>
+    </row>
+    <row r="170" spans="1:11" s="36" customFormat="1">
+      <c r="A170" s="52"/>
       <c r="B170" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C170" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="D170" s="22" t="s">
-        <v>706</v>
-      </c>
-      <c r="E170" s="21" t="s">
-        <v>707</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="D170" s="53" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E170" s="52"/>
       <c r="F170" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G170" s="20"/>
-      <c r="H170" s="23"/>
-      <c r="I170" s="23"/>
-      <c r="J170" s="23"/>
-      <c r="K170" s="23"/>
-    </row>
-    <row r="171" spans="1:11">
-      <c r="A171" s="21" t="s">
-        <v>708</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="G170" s="35">
+        <v>4750</v>
+      </c>
+      <c r="H170" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I170" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J170" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K170" s="33">
+        <v>66000</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" s="36" customFormat="1">
+      <c r="A171" s="52"/>
       <c r="B171" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C171" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="D171" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="E171" s="21" t="s">
-        <v>710</v>
+        <v>206</v>
+      </c>
+      <c r="D171" s="53" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E171" s="52" t="s">
+        <v>1295</v>
       </c>
       <c r="F171" s="22" t="s">
-        <v>711</v>
-      </c>
-      <c r="G171" s="20"/>
-      <c r="H171" s="23"/>
-      <c r="I171" s="23"/>
-      <c r="J171" s="23"/>
-      <c r="K171" s="23"/>
-    </row>
-    <row r="172" spans="1:11">
-      <c r="A172" s="21" t="s">
-        <v>712</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="G171" s="35">
+        <v>3000</v>
+      </c>
+      <c r="H171" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I171" s="33"/>
+      <c r="J171" s="33"/>
+      <c r="K171" s="33"/>
+    </row>
+    <row r="172" spans="1:11" s="36" customFormat="1">
+      <c r="A172" s="52"/>
       <c r="B172" s="21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C172" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="D172" s="22" t="s">
-        <v>713</v>
-      </c>
-      <c r="E172" s="21" t="s">
-        <v>714</v>
+        <v>210</v>
+      </c>
+      <c r="D172" s="53" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E172" s="52" t="s">
+        <v>1296</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>698</v>
-      </c>
-      <c r="G172" s="20"/>
-      <c r="H172" s="23"/>
-      <c r="I172" s="23"/>
-      <c r="J172" s="23"/>
-      <c r="K172" s="23"/>
+        <v>683</v>
+      </c>
+      <c r="G172" s="35">
+        <v>5000</v>
+      </c>
+      <c r="H172" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I172" s="33"/>
+      <c r="J172" s="33"/>
+      <c r="K172" s="33"/>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="21" t="s">
-        <v>715</v>
+        <v>700</v>
       </c>
       <c r="B173" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C173" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D173" s="22" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="E173" s="21" t="s">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="F173" s="22" t="s">
-        <v>711</v>
+        <v>696</v>
       </c>
       <c r="G173" s="20"/>
       <c r="H173" s="23"/>
@@ -13028,22 +13230,22 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="21" t="s">
-        <v>718</v>
+        <v>703</v>
       </c>
       <c r="B174" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C174" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D174" s="22" t="s">
-        <v>719</v>
+        <v>698</v>
       </c>
       <c r="E174" s="21" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="F174" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G174" s="20"/>
       <c r="H174" s="23"/>
@@ -13053,22 +13255,22 @@
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="21" t="s">
-        <v>721</v>
+        <v>706</v>
       </c>
       <c r="B175" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C175" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D175" s="22" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="E175" s="21" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="F175" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G175" s="20"/>
       <c r="H175" s="23"/>
@@ -13078,22 +13280,22 @@
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="21" t="s">
-        <v>724</v>
+        <v>710</v>
       </c>
       <c r="B176" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C176" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D176" s="22" t="s">
-        <v>725</v>
+        <v>704</v>
       </c>
       <c r="E176" s="21" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="F176" s="22" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G176" s="20"/>
       <c r="H176" s="23"/>
@@ -13103,22 +13305,22 @@
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="21" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C177" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D177" s="22" t="s">
-        <v>728</v>
+        <v>707</v>
       </c>
       <c r="E177" s="21" t="s">
-        <v>729</v>
+        <v>708</v>
       </c>
       <c r="F177" s="22" t="s">
-        <v>730</v>
+        <v>709</v>
       </c>
       <c r="G177" s="20"/>
       <c r="H177" s="23"/>
@@ -13128,22 +13330,22 @@
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="21" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C178" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D178" s="22" t="s">
-        <v>732</v>
+        <v>711</v>
       </c>
       <c r="E178" s="21" t="s">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="F178" s="22" t="s">
-        <v>730</v>
+        <v>696</v>
       </c>
       <c r="G178" s="20"/>
       <c r="H178" s="23"/>
@@ -13153,22 +13355,22 @@
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="21" t="s">
-        <v>734</v>
+        <v>719</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C179" s="21" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D179" s="22" t="s">
-        <v>735</v>
+        <v>714</v>
       </c>
       <c r="E179" s="21" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="F179" s="22" t="s">
-        <v>737</v>
+        <v>709</v>
       </c>
       <c r="G179" s="20"/>
       <c r="H179" s="23"/>
@@ -13178,22 +13380,22 @@
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="21" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C180" s="21" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="D180" s="22" t="s">
-        <v>739</v>
+        <v>717</v>
       </c>
       <c r="E180" s="21" t="s">
-        <v>740</v>
+        <v>718</v>
       </c>
       <c r="F180" s="22" t="s">
-        <v>737</v>
+        <v>696</v>
       </c>
       <c r="G180" s="20"/>
       <c r="H180" s="23"/>
@@ -13203,22 +13405,22 @@
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="21" t="s">
-        <v>741</v>
+        <v>725</v>
       </c>
       <c r="B181" s="21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C181" s="21" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="D181" s="22" t="s">
-        <v>349</v>
+        <v>720</v>
       </c>
       <c r="E181" s="21" t="s">
-        <v>350</v>
+        <v>721</v>
       </c>
       <c r="F181" s="22" t="s">
-        <v>737</v>
+        <v>696</v>
       </c>
       <c r="G181" s="20"/>
       <c r="H181" s="23"/>
@@ -13228,22 +13430,22 @@
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="21" t="s">
-        <v>742</v>
+        <v>729</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C182" s="21" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="D182" s="22" t="s">
-        <v>743</v>
+        <v>723</v>
       </c>
       <c r="E182" s="21" t="s">
-        <v>744</v>
+        <v>724</v>
       </c>
       <c r="F182" s="22" t="s">
-        <v>745</v>
+        <v>696</v>
       </c>
       <c r="G182" s="20"/>
       <c r="H182" s="23"/>
@@ -13253,22 +13455,22 @@
     </row>
     <row r="183" spans="1:11">
       <c r="A183" s="21" t="s">
-        <v>746</v>
+        <v>732</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C183" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D183" s="22" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="E183" s="21" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="F183" s="22" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="G183" s="20"/>
       <c r="H183" s="23"/>
@@ -13278,22 +13480,22 @@
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="21" t="s">
-        <v>749</v>
+        <v>736</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D184" s="22" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="E184" s="21" t="s">
-        <v>751</v>
+        <v>731</v>
       </c>
       <c r="F184" s="22" t="s">
-        <v>745</v>
+        <v>728</v>
       </c>
       <c r="G184" s="20"/>
       <c r="H184" s="23"/>
@@ -13303,20 +13505,22 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="21" t="s">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>753</v>
-      </c>
-      <c r="E185" s="21"/>
+        <v>733</v>
+      </c>
+      <c r="E185" s="21" t="s">
+        <v>734</v>
+      </c>
       <c r="F185" s="22" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
       <c r="G185" s="20"/>
       <c r="H185" s="23"/>
@@ -13326,20 +13530,22 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="21" t="s">
-        <v>754</v>
+        <v>740</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D186" s="22" t="s">
-        <v>755</v>
-      </c>
-      <c r="E186" s="21"/>
+        <v>737</v>
+      </c>
+      <c r="E186" s="21" t="s">
+        <v>738</v>
+      </c>
       <c r="F186" s="22" t="s">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="G186" s="20"/>
       <c r="H186" s="23"/>
@@ -13349,20 +13555,22 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="21" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>757</v>
-      </c>
-      <c r="E187" s="21"/>
+        <v>349</v>
+      </c>
+      <c r="E187" s="21" t="s">
+        <v>350</v>
+      </c>
       <c r="F187" s="22" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="G187" s="20"/>
       <c r="H187" s="23"/>
@@ -13372,20 +13580,22 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="21" t="s">
-        <v>758</v>
+        <v>747</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>759</v>
-      </c>
-      <c r="E188" s="21"/>
+        <v>741</v>
+      </c>
+      <c r="E188" s="21" t="s">
+        <v>742</v>
+      </c>
       <c r="F188" s="22" t="s">
-        <v>698</v>
+        <v>743</v>
       </c>
       <c r="G188" s="20"/>
       <c r="H188" s="23"/>
@@ -13395,22 +13605,22 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="21" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>761</v>
+        <v>745</v>
       </c>
       <c r="E189" s="21" t="s">
-        <v>762</v>
+        <v>746</v>
       </c>
       <c r="F189" s="22" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="G189" s="20"/>
       <c r="H189" s="23"/>
@@ -13420,22 +13630,22 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="21" t="s">
-        <v>764</v>
+        <v>752</v>
       </c>
       <c r="B190" s="21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D190" s="22" t="s">
-        <v>765</v>
+        <v>748</v>
       </c>
       <c r="E190" s="21" t="s">
-        <v>766</v>
+        <v>749</v>
       </c>
       <c r="F190" s="22" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="G190" s="20"/>
       <c r="H190" s="23"/>
@@ -13445,22 +13655,20 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="21" t="s">
-        <v>767</v>
+        <v>754</v>
       </c>
       <c r="B191" s="21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>768</v>
-      </c>
-      <c r="E191" s="21" t="s">
-        <v>769</v>
-      </c>
+        <v>751</v>
+      </c>
+      <c r="E191" s="21"/>
       <c r="F191" s="22" t="s">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="G191" s="20"/>
       <c r="H191" s="23"/>
@@ -13470,22 +13678,20 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="21" t="s">
-        <v>770</v>
+        <v>756</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D192" s="22" t="s">
-        <v>771</v>
-      </c>
-      <c r="E192" s="21" t="s">
-        <v>772</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="E192" s="21"/>
       <c r="F192" s="22" t="s">
-        <v>763</v>
+        <v>709</v>
       </c>
       <c r="G192" s="20"/>
       <c r="H192" s="23"/>
@@ -13495,22 +13701,20 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="21" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D193" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="E193" s="21" t="s">
-        <v>775</v>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="E193" s="21"/>
       <c r="F193" s="22" t="s">
-        <v>776</v>
+        <v>696</v>
       </c>
       <c r="G193" s="20"/>
       <c r="H193" s="23"/>
@@ -13520,22 +13724,20 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="21" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D194" s="22" t="s">
-        <v>778</v>
-      </c>
-      <c r="E194" s="21" t="s">
-        <v>779</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="E194" s="21"/>
       <c r="F194" s="22" t="s">
-        <v>776</v>
+        <v>696</v>
       </c>
       <c r="G194" s="20"/>
       <c r="H194" s="23"/>
@@ -13545,22 +13747,22 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="21" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D195" s="22" t="s">
-        <v>781</v>
+        <v>759</v>
       </c>
       <c r="E195" s="21" t="s">
-        <v>782</v>
+        <v>760</v>
       </c>
       <c r="F195" s="22" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="G195" s="20"/>
       <c r="H195" s="23"/>
@@ -13570,22 +13772,22 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="21" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="B196" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D196" s="22" t="s">
-        <v>784</v>
+        <v>763</v>
       </c>
       <c r="E196" s="21" t="s">
-        <v>785</v>
+        <v>764</v>
       </c>
       <c r="F196" s="22" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="G196" s="20"/>
       <c r="H196" s="23"/>
@@ -13595,20 +13797,22 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="21" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D197" s="22" t="s">
-        <v>787</v>
-      </c>
-      <c r="E197" s="21"/>
+        <v>766</v>
+      </c>
+      <c r="E197" s="21" t="s">
+        <v>767</v>
+      </c>
       <c r="F197" s="22" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="G197" s="20"/>
       <c r="H197" s="23"/>
@@ -13618,22 +13822,22 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="21" t="s">
-        <v>788</v>
+        <v>775</v>
       </c>
       <c r="B198" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D198" s="22" t="s">
-        <v>789</v>
+        <v>769</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>790</v>
+        <v>770</v>
       </c>
       <c r="F198" s="22" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="G198" s="20"/>
       <c r="H198" s="23"/>
@@ -13643,22 +13847,22 @@
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="21" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
       <c r="B199" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D199" s="22" t="s">
-        <v>792</v>
+        <v>772</v>
       </c>
       <c r="E199" s="21" t="s">
-        <v>793</v>
+        <v>773</v>
       </c>
       <c r="F199" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G199" s="20"/>
       <c r="H199" s="23"/>
@@ -13668,22 +13872,22 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="21" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="B200" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D200" s="22" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="E200" s="21" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="F200" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G200" s="20"/>
       <c r="H200" s="23"/>
@@ -13693,22 +13897,22 @@
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="21" t="s">
-        <v>797</v>
+        <v>784</v>
       </c>
       <c r="B201" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D201" s="22" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="E201" s="21" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="F201" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G201" s="20"/>
       <c r="H201" s="23"/>
@@ -13718,22 +13922,22 @@
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="21" t="s">
-        <v>800</v>
+        <v>786</v>
       </c>
       <c r="B202" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="E202" s="21" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="F202" s="22" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G202" s="20"/>
       <c r="H202" s="23"/>
@@ -13743,22 +13947,20 @@
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="21" t="s">
-        <v>803</v>
+        <v>789</v>
       </c>
       <c r="B203" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D203" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="E203" s="21" t="s">
-        <v>805</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="E203" s="21"/>
       <c r="F203" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G203" s="20"/>
       <c r="H203" s="23"/>
@@ -13768,22 +13970,22 @@
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="21" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="B204" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D204" s="22" t="s">
-        <v>808</v>
+        <v>787</v>
       </c>
       <c r="E204" s="21" t="s">
-        <v>809</v>
+        <v>788</v>
       </c>
       <c r="F204" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G204" s="20"/>
       <c r="H204" s="23"/>
@@ -13793,22 +13995,22 @@
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="21" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="B205" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>811</v>
+        <v>790</v>
       </c>
       <c r="E205" s="21" t="s">
-        <v>812</v>
+        <v>791</v>
       </c>
       <c r="F205" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G205" s="20"/>
       <c r="H205" s="23"/>
@@ -13818,22 +14020,22 @@
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="21" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="B206" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>814</v>
+        <v>793</v>
       </c>
       <c r="E206" s="21" t="s">
-        <v>815</v>
+        <v>794</v>
       </c>
       <c r="F206" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G206" s="20"/>
       <c r="H206" s="23"/>
@@ -13843,22 +14045,22 @@
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="21" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="B207" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>198</v>
+        <v>258</v>
       </c>
       <c r="D207" s="22" t="s">
-        <v>817</v>
+        <v>796</v>
       </c>
       <c r="E207" s="21" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="F207" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G207" s="20"/>
       <c r="H207" s="23"/>
@@ -13868,22 +14070,22 @@
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="21" t="s">
-        <v>819</v>
+        <v>805</v>
       </c>
       <c r="B208" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="D208" s="22" t="s">
-        <v>820</v>
+        <v>799</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>821</v>
+        <v>800</v>
       </c>
       <c r="F208" s="22" t="s">
-        <v>806</v>
+        <v>774</v>
       </c>
       <c r="G208" s="20"/>
       <c r="H208" s="23"/>
@@ -13893,72 +14095,72 @@
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="21" t="s">
-        <v>822</v>
+        <v>808</v>
       </c>
       <c r="B209" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>1279</v>
+        <v>802</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>1280</v>
+        <v>803</v>
       </c>
       <c r="F209" s="22" t="s">
-        <v>806</v>
-      </c>
-      <c r="G209" s="35"/>
+        <v>804</v>
+      </c>
+      <c r="G209" s="20"/>
       <c r="H209" s="23"/>
       <c r="I209" s="23"/>
       <c r="J209" s="23"/>
-      <c r="K209" s="33"/>
+      <c r="K209" s="23"/>
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="21" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="B210" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>1281</v>
+        <v>806</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>1282</v>
+        <v>807</v>
       </c>
       <c r="F210" s="22" t="s">
-        <v>806</v>
-      </c>
-      <c r="G210" s="35"/>
+        <v>804</v>
+      </c>
+      <c r="G210" s="20"/>
       <c r="H210" s="23"/>
       <c r="I210" s="23"/>
       <c r="J210" s="23"/>
-      <c r="K210" s="33"/>
+      <c r="K210" s="23"/>
     </row>
     <row r="211" spans="1:11">
       <c r="A211" s="21" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="B211" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>823</v>
+        <v>809</v>
       </c>
       <c r="E211" s="21" t="s">
-        <v>824</v>
+        <v>810</v>
       </c>
       <c r="F211" s="22" t="s">
-        <v>711</v>
+        <v>804</v>
       </c>
       <c r="G211" s="20"/>
       <c r="H211" s="23"/>
@@ -13968,22 +14170,22 @@
     </row>
     <row r="212" spans="1:11">
       <c r="A212" s="21" t="s">
-        <v>831</v>
+        <v>817</v>
       </c>
       <c r="B212" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D212" s="22" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F212" s="22" t="s">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="G212" s="20"/>
       <c r="H212" s="23"/>
@@ -13993,22 +14195,22 @@
     </row>
     <row r="213" spans="1:11">
       <c r="A213" s="21" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="B213" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D213" s="22" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="E213" s="21" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="F213" s="22" t="s">
-        <v>698</v>
+        <v>804</v>
       </c>
       <c r="G213" s="20"/>
       <c r="H213" s="23"/>
@@ -14018,22 +14220,22 @@
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="21" t="s">
-        <v>837</v>
+        <v>823</v>
       </c>
       <c r="B214" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="E214" s="21" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="F214" s="22" t="s">
-        <v>711</v>
+        <v>804</v>
       </c>
       <c r="G214" s="20"/>
       <c r="H214" s="23"/>
@@ -14043,509 +14245,397 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="21" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="B215" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>835</v>
+        <v>1277</v>
       </c>
       <c r="E215" s="21" t="s">
-        <v>836</v>
+        <v>1278</v>
       </c>
       <c r="F215" s="22" t="s">
-        <v>711</v>
-      </c>
-      <c r="G215" s="20"/>
+        <v>804</v>
+      </c>
+      <c r="G215" s="35"/>
       <c r="H215" s="23"/>
       <c r="I215" s="23"/>
       <c r="J215" s="23"/>
-      <c r="K215" s="23"/>
+      <c r="K215" s="33"/>
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="21" t="s">
-        <v>843</v>
+        <v>829</v>
       </c>
       <c r="B216" s="21" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D216" s="22" t="s">
-        <v>1271</v>
+        <v>1279</v>
       </c>
       <c r="E216" s="21" t="s">
-        <v>838</v>
+        <v>1280</v>
       </c>
       <c r="F216" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G216" s="20">
-        <v>40100</v>
-      </c>
-      <c r="H216" s="23" t="s">
-        <v>1277</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="G216" s="35"/>
+      <c r="H216" s="23"/>
       <c r="I216" s="23"/>
       <c r="J216" s="23"/>
-      <c r="K216" s="23"/>
+      <c r="K216" s="33"/>
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
-        <v>846</v>
+        <v>832</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>841</v>
+        <v>821</v>
       </c>
       <c r="E217" s="21" t="s">
-        <v>842</v>
+        <v>822</v>
       </c>
       <c r="F217" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G217" s="20">
-        <v>15600</v>
-      </c>
-      <c r="H217" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I217" s="23">
-        <v>200000</v>
-      </c>
-      <c r="J217" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K217" s="23">
-        <v>132000</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="G217" s="20"/>
+      <c r="H217" s="23"/>
+      <c r="I217" s="23"/>
+      <c r="J217" s="23"/>
+      <c r="K217" s="23"/>
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="21" t="s">
-        <v>849</v>
+        <v>835</v>
       </c>
       <c r="B218" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>844</v>
+        <v>824</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>845</v>
+        <v>825</v>
       </c>
       <c r="F218" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G218" s="20">
-        <v>17500</v>
-      </c>
-      <c r="H218" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I218" s="23">
-        <v>200000</v>
-      </c>
-      <c r="J218" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K218" s="23">
-        <v>132000</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="G218" s="20"/>
+      <c r="H218" s="23"/>
+      <c r="I218" s="23"/>
+      <c r="J218" s="23"/>
+      <c r="K218" s="23"/>
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
-        <v>850</v>
+        <v>838</v>
       </c>
       <c r="B219" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="F219" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G219" s="20">
-        <v>35500</v>
-      </c>
-      <c r="H219" s="23" t="s">
-        <v>1277</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="G219" s="20"/>
+      <c r="H219" s="23"/>
       <c r="I219" s="23"/>
       <c r="J219" s="23"/>
       <c r="K219" s="23"/>
     </row>
     <row r="220" spans="1:11">
       <c r="A220" s="21" t="s">
-        <v>851</v>
+        <v>841</v>
       </c>
       <c r="B220" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>1272</v>
+        <v>830</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>1274</v>
+        <v>831</v>
       </c>
       <c r="F220" s="22" t="s">
-        <v>839</v>
+        <v>709</v>
       </c>
       <c r="G220" s="20"/>
-      <c r="H220" s="23" t="s">
-        <v>1277</v>
-      </c>
+      <c r="H220" s="23"/>
       <c r="I220" s="23"/>
       <c r="J220" s="23"/>
       <c r="K220" s="23"/>
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="21" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
       <c r="B221" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>1273</v>
+        <v>833</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>1275</v>
+        <v>834</v>
       </c>
       <c r="F221" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G221" s="20">
-        <v>3000</v>
-      </c>
-      <c r="H221" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I221" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J221" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K221" s="23">
-        <v>99000</v>
-      </c>
+        <v>709</v>
+      </c>
+      <c r="G221" s="20"/>
+      <c r="H221" s="23"/>
+      <c r="I221" s="23"/>
+      <c r="J221" s="23"/>
+      <c r="K221" s="23"/>
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
-        <v>857</v>
+        <v>847</v>
       </c>
       <c r="B222" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>852</v>
+        <v>1269</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>853</v>
+        <v>836</v>
       </c>
       <c r="F222" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G222" s="20">
-        <v>54250</v>
-      </c>
-      <c r="H222" s="23" t="s">
-        <v>1278</v>
-      </c>
-      <c r="I222" s="23">
-        <v>250000</v>
-      </c>
-      <c r="J222" s="23">
-        <v>246000</v>
-      </c>
-      <c r="K222" s="23">
-        <v>92250</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G222" s="20"/>
+      <c r="H222" s="23"/>
+      <c r="I222" s="23"/>
+      <c r="J222" s="23"/>
+      <c r="K222" s="23"/>
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
-        <v>860</v>
+        <v>848</v>
       </c>
       <c r="B223" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>855</v>
+        <v>839</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>856</v>
+        <v>840</v>
       </c>
       <c r="F223" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G223" s="20">
-        <v>31150</v>
-      </c>
-      <c r="H223" s="23" t="s">
-        <v>1278</v>
-      </c>
-      <c r="I223" s="23">
-        <v>250000</v>
-      </c>
-      <c r="J223" s="23">
-        <v>246000</v>
-      </c>
-      <c r="K223" s="23">
-        <v>102500</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G223" s="20"/>
+      <c r="H223" s="23"/>
+      <c r="I223" s="23"/>
+      <c r="J223" s="23"/>
+      <c r="K223" s="23"/>
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
-        <v>863</v>
+        <v>849</v>
       </c>
       <c r="B224" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>858</v>
+        <v>842</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>859</v>
+        <v>843</v>
       </c>
       <c r="F224" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G224" s="20">
-        <v>21250</v>
-      </c>
-      <c r="H224" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I224" s="23">
-        <v>200000</v>
-      </c>
-      <c r="J224" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K224" s="23">
-        <v>99000</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G224" s="20"/>
+      <c r="H224" s="23"/>
+      <c r="I224" s="23"/>
+      <c r="J224" s="23"/>
+      <c r="K224" s="23"/>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
-        <v>866</v>
+        <v>852</v>
       </c>
       <c r="B225" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>861</v>
+        <v>845</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>862</v>
+        <v>846</v>
       </c>
       <c r="F225" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G225" s="20">
-        <v>12500</v>
-      </c>
-      <c r="H225" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I225" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J225" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K225" s="23">
-        <v>49500</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G225" s="20"/>
+      <c r="H225" s="23"/>
+      <c r="I225" s="23"/>
+      <c r="J225" s="23"/>
+      <c r="K225" s="23"/>
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
-        <v>869</v>
+        <v>855</v>
       </c>
       <c r="B226" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>864</v>
+        <v>1270</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>865</v>
+        <v>1272</v>
       </c>
       <c r="F226" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G226" s="20">
-        <v>7700</v>
-      </c>
-      <c r="H226" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I226" s="23">
-        <v>50000</v>
-      </c>
-      <c r="J226" s="23">
-        <v>48000</v>
-      </c>
-      <c r="K226" s="23">
-        <v>32000</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G226" s="20"/>
+      <c r="H226" s="23"/>
+      <c r="I226" s="23"/>
+      <c r="J226" s="23"/>
+      <c r="K226" s="23"/>
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
-        <v>872</v>
+        <v>858</v>
       </c>
       <c r="B227" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>867</v>
+        <v>1271</v>
       </c>
       <c r="E227" s="21" t="s">
-        <v>868</v>
+        <v>1273</v>
       </c>
       <c r="F227" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G227" s="20">
-        <v>11650</v>
-      </c>
-      <c r="H227" s="23" t="s">
-        <v>1278</v>
-      </c>
-      <c r="I227" s="23">
-        <v>80000</v>
-      </c>
-      <c r="J227" s="23">
-        <v>78000</v>
-      </c>
-      <c r="K227" s="23">
-        <v>42250</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G227" s="20"/>
+      <c r="H227" s="23"/>
+      <c r="I227" s="23"/>
+      <c r="J227" s="23"/>
+      <c r="K227" s="23"/>
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="21" t="s">
-        <v>874</v>
+        <v>861</v>
       </c>
       <c r="B228" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>870</v>
+        <v>850</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>871</v>
+        <v>851</v>
       </c>
       <c r="F228" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G228" s="20">
-        <v>9300</v>
-      </c>
-      <c r="H228" s="23" t="s">
-        <v>1278</v>
-      </c>
-      <c r="I228" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J228" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K228" s="23">
-        <v>45375</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G228" s="20"/>
+      <c r="H228" s="23"/>
+      <c r="I228" s="23"/>
+      <c r="J228" s="23"/>
+      <c r="K228" s="23"/>
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="21" t="s">
-        <v>878</v>
+        <v>864</v>
       </c>
       <c r="B229" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>873</v>
-      </c>
-      <c r="E229" s="21"/>
+        <v>853</v>
+      </c>
+      <c r="E229" s="21" t="s">
+        <v>854</v>
+      </c>
       <c r="F229" s="22" t="s">
-        <v>839</v>
-      </c>
-      <c r="G229" s="20">
-        <v>42925</v>
-      </c>
-      <c r="H229" s="23" t="s">
-        <v>1278</v>
-      </c>
+        <v>837</v>
+      </c>
+      <c r="G229" s="20"/>
+      <c r="H229" s="23"/>
       <c r="I229" s="23"/>
       <c r="J229" s="23"/>
       <c r="K229" s="23"/>
     </row>
     <row r="230" spans="1:11">
       <c r="A230" s="21" t="s">
-        <v>881</v>
+        <v>867</v>
       </c>
       <c r="B230" s="21" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>875</v>
+        <v>856</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>876</v>
+        <v>857</v>
       </c>
       <c r="F230" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G230" s="20"/>
       <c r="H230" s="23"/>
@@ -14555,22 +14645,22 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" s="21" t="s">
-        <v>884</v>
+        <v>870</v>
       </c>
       <c r="B231" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>879</v>
+        <v>859</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>880</v>
+        <v>860</v>
       </c>
       <c r="F231" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G231" s="20"/>
       <c r="H231" s="23"/>
@@ -14580,22 +14670,22 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" s="21" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>882</v>
+        <v>862</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>883</v>
+        <v>863</v>
       </c>
       <c r="F232" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G232" s="20"/>
       <c r="H232" s="23"/>
@@ -14605,22 +14695,22 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" s="21" t="s">
-        <v>890</v>
+        <v>876</v>
       </c>
       <c r="B233" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>885</v>
+        <v>865</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>886</v>
+        <v>866</v>
       </c>
       <c r="F233" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G233" s="20"/>
       <c r="H233" s="23"/>
@@ -14630,22 +14720,22 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" s="21" t="s">
-        <v>893</v>
+        <v>879</v>
       </c>
       <c r="B234" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>888</v>
+        <v>868</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>889</v>
+        <v>869</v>
       </c>
       <c r="F234" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G234" s="20"/>
       <c r="H234" s="23"/>
@@ -14655,22 +14745,20 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" s="21" t="s">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="B235" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>891</v>
-      </c>
-      <c r="E235" s="21" t="s">
-        <v>892</v>
-      </c>
+        <v>871</v>
+      </c>
+      <c r="E235" s="21"/>
       <c r="F235" s="22" t="s">
-        <v>877</v>
+        <v>837</v>
       </c>
       <c r="G235" s="20"/>
       <c r="H235" s="23"/>
@@ -14680,22 +14768,22 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" s="21" t="s">
-        <v>899</v>
+        <v>885</v>
       </c>
       <c r="B236" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>894</v>
+        <v>873</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>895</v>
+        <v>874</v>
       </c>
       <c r="F236" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G236" s="20"/>
       <c r="H236" s="23"/>
@@ -14705,22 +14793,22 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" s="21" t="s">
-        <v>902</v>
+        <v>888</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>897</v>
+        <v>877</v>
       </c>
       <c r="E237" s="21" t="s">
-        <v>898</v>
+        <v>878</v>
       </c>
       <c r="F237" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G237" s="20"/>
       <c r="H237" s="23"/>
@@ -14730,22 +14818,22 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" s="21" t="s">
-        <v>905</v>
+        <v>891</v>
       </c>
       <c r="B238" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>900</v>
+        <v>880</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>901</v>
+        <v>881</v>
       </c>
       <c r="F238" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G238" s="20"/>
       <c r="H238" s="23"/>
@@ -14755,22 +14843,22 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" s="21" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
       <c r="B239" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>903</v>
+        <v>883</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>904</v>
+        <v>884</v>
       </c>
       <c r="F239" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G239" s="20"/>
       <c r="H239" s="23"/>
@@ -14780,22 +14868,22 @@
     </row>
     <row r="240" spans="1:11">
       <c r="A240" s="21" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
       <c r="B240" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>906</v>
+        <v>886</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>907</v>
+        <v>887</v>
       </c>
       <c r="F240" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G240" s="20"/>
       <c r="H240" s="23"/>
@@ -14805,22 +14893,22 @@
     </row>
     <row r="241" spans="1:11">
       <c r="A241" s="21" t="s">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="B241" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>909</v>
+        <v>889</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>910</v>
+        <v>890</v>
       </c>
       <c r="F241" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G241" s="20"/>
       <c r="H241" s="23"/>
@@ -14830,22 +14918,22 @@
     </row>
     <row r="242" spans="1:11">
       <c r="A242" s="21" t="s">
-        <v>917</v>
+        <v>903</v>
       </c>
       <c r="B242" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>912</v>
+        <v>892</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>913</v>
+        <v>893</v>
       </c>
       <c r="F242" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G242" s="20"/>
       <c r="H242" s="23"/>
@@ -14855,22 +14943,22 @@
     </row>
     <row r="243" spans="1:11">
       <c r="A243" s="21" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="B243" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>915</v>
+        <v>895</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>916</v>
+        <v>896</v>
       </c>
       <c r="F243" s="22" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G243" s="20"/>
       <c r="H243" s="23"/>
@@ -14880,22 +14968,22 @@
     </row>
     <row r="244" spans="1:11">
       <c r="A244" s="21" t="s">
-        <v>924</v>
+        <v>909</v>
       </c>
       <c r="B244" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>918</v>
+        <v>898</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>919</v>
+        <v>899</v>
       </c>
       <c r="F244" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G244" s="20"/>
       <c r="H244" s="23"/>
@@ -14905,22 +14993,22 @@
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="21" t="s">
-        <v>927</v>
+        <v>912</v>
       </c>
       <c r="B245" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>922</v>
+        <v>901</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>923</v>
+        <v>902</v>
       </c>
       <c r="F245" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G245" s="20"/>
       <c r="H245" s="23"/>
@@ -14930,22 +15018,22 @@
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="21" t="s">
-        <v>930</v>
+        <v>915</v>
       </c>
       <c r="B246" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>925</v>
+        <v>904</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>926</v>
+        <v>905</v>
       </c>
       <c r="F246" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G246" s="20"/>
       <c r="H246" s="23"/>
@@ -14955,22 +15043,22 @@
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="21" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="B247" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>928</v>
+        <v>907</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>929</v>
+        <v>908</v>
       </c>
       <c r="F247" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G247" s="20"/>
       <c r="H247" s="23"/>
@@ -14980,22 +15068,22 @@
     </row>
     <row r="248" spans="1:11">
       <c r="A248" s="21" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="B248" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>931</v>
+        <v>910</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>932</v>
+        <v>911</v>
       </c>
       <c r="F248" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G248" s="20"/>
       <c r="H248" s="23"/>
@@ -15005,22 +15093,22 @@
     </row>
     <row r="249" spans="1:11">
       <c r="A249" s="21" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="B249" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>934</v>
+        <v>913</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>935</v>
+        <v>914</v>
       </c>
       <c r="F249" s="22" t="s">
-        <v>920</v>
+        <v>875</v>
       </c>
       <c r="G249" s="20"/>
       <c r="H249" s="23"/>
@@ -15030,22 +15118,22 @@
     </row>
     <row r="250" spans="1:11">
       <c r="A250" s="21" t="s">
-        <v>943</v>
+        <v>928</v>
       </c>
       <c r="B250" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>937</v>
+        <v>916</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>938</v>
+        <v>917</v>
       </c>
       <c r="F250" s="22" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="G250" s="20"/>
       <c r="H250" s="23"/>
@@ -15055,22 +15143,22 @@
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="21" t="s">
-        <v>946</v>
+        <v>931</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>940</v>
+        <v>920</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>941</v>
+        <v>921</v>
       </c>
       <c r="F251" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G251" s="20"/>
       <c r="H251" s="23"/>
@@ -15080,22 +15168,22 @@
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="21" t="s">
-        <v>949</v>
+        <v>934</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>944</v>
+        <v>923</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>945</v>
+        <v>924</v>
       </c>
       <c r="F252" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G252" s="20"/>
       <c r="H252" s="23"/>
@@ -15105,22 +15193,22 @@
     </row>
     <row r="253" spans="1:11">
       <c r="A253" s="21" t="s">
-        <v>952</v>
+        <v>937</v>
       </c>
       <c r="B253" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>947</v>
+        <v>926</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>948</v>
+        <v>927</v>
       </c>
       <c r="F253" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G253" s="20"/>
       <c r="H253" s="23"/>
@@ -15130,22 +15218,22 @@
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="21" t="s">
-        <v>954</v>
+        <v>941</v>
       </c>
       <c r="B254" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>950</v>
+        <v>929</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>951</v>
+        <v>930</v>
       </c>
       <c r="F254" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G254" s="20"/>
       <c r="H254" s="23"/>
@@ -15155,22 +15243,22 @@
     </row>
     <row r="255" spans="1:11">
       <c r="A255" s="21" t="s">
-        <v>957</v>
+        <v>944</v>
       </c>
       <c r="B255" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>953</v>
+        <v>933</v>
       </c>
       <c r="F255" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G255" s="20"/>
       <c r="H255" s="23"/>
@@ -15180,22 +15268,22 @@
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="21" t="s">
-        <v>960</v>
+        <v>947</v>
       </c>
       <c r="B256" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>955</v>
+        <v>935</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>956</v>
+        <v>936</v>
       </c>
       <c r="F256" s="22" t="s">
-        <v>942</v>
+        <v>918</v>
       </c>
       <c r="G256" s="20"/>
       <c r="H256" s="23"/>
@@ -15205,22 +15293,22 @@
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="21" t="s">
-        <v>963</v>
+        <v>950</v>
       </c>
       <c r="B257" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>958</v>
+        <v>938</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>959</v>
+        <v>939</v>
       </c>
       <c r="F257" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G257" s="20"/>
       <c r="H257" s="23"/>
@@ -15230,22 +15318,22 @@
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="21" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="B258" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>961</v>
+        <v>942</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>962</v>
+        <v>943</v>
       </c>
       <c r="F258" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G258" s="20"/>
       <c r="H258" s="23"/>
@@ -15255,22 +15343,22 @@
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="21" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
       <c r="B259" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>964</v>
+        <v>945</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>965</v>
+        <v>946</v>
       </c>
       <c r="F259" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G259" s="20"/>
       <c r="H259" s="23"/>
@@ -15280,22 +15368,22 @@
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="21" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
       <c r="B260" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>967</v>
+        <v>948</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>968</v>
+        <v>949</v>
       </c>
       <c r="F260" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G260" s="20"/>
       <c r="H260" s="23"/>
@@ -15305,22 +15393,22 @@
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="21" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
       <c r="B261" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>970</v>
+        <v>929</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>971</v>
+        <v>951</v>
       </c>
       <c r="F261" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G261" s="20"/>
       <c r="H261" s="23"/>
@@ -15330,22 +15418,22 @@
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="21" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
       <c r="B262" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>973</v>
+        <v>953</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>974</v>
+        <v>954</v>
       </c>
       <c r="F262" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G262" s="20"/>
       <c r="H262" s="23"/>
@@ -15355,22 +15443,22 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="21" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
       <c r="B263" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>976</v>
+        <v>956</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>977</v>
+        <v>957</v>
       </c>
       <c r="F263" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G263" s="20"/>
       <c r="H263" s="23"/>
@@ -15380,22 +15468,22 @@
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="21" t="s">
-        <v>985</v>
+        <v>970</v>
       </c>
       <c r="B264" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>979</v>
+        <v>959</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>980</v>
+        <v>960</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G264" s="20"/>
       <c r="H264" s="23"/>
@@ -15405,22 +15493,22 @@
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="21" t="s">
-        <v>988</v>
+        <v>973</v>
       </c>
       <c r="B265" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>982</v>
+        <v>962</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>983</v>
+        <v>963</v>
       </c>
       <c r="F265" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G265" s="20"/>
       <c r="H265" s="23"/>
@@ -15430,22 +15518,22 @@
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="21" t="s">
-        <v>991</v>
+        <v>976</v>
       </c>
       <c r="B266" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>987</v>
+        <v>966</v>
       </c>
       <c r="F266" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G266" s="20"/>
       <c r="H266" s="23"/>
@@ -15455,22 +15543,22 @@
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="21" t="s">
-        <v>994</v>
+        <v>979</v>
       </c>
       <c r="B267" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>190</v>
+        <v>296</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>989</v>
+        <v>968</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>990</v>
+        <v>969</v>
       </c>
       <c r="F267" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G267" s="20"/>
       <c r="H267" s="23"/>
@@ -15480,22 +15568,22 @@
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="21" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
       <c r="B268" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>194</v>
+        <v>300</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>992</v>
+        <v>971</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>993</v>
+        <v>972</v>
       </c>
       <c r="F268" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G268" s="20"/>
       <c r="H268" s="23"/>
@@ -15505,22 +15593,22 @@
     </row>
     <row r="269" spans="1:11">
       <c r="A269" s="21" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
       <c r="B269" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>995</v>
+        <v>974</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>996</v>
+        <v>975</v>
       </c>
       <c r="F269" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G269" s="20"/>
       <c r="H269" s="23"/>
@@ -15530,22 +15618,22 @@
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="21" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
       <c r="B270" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>202</v>
+        <v>308</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>998</v>
+        <v>977</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>999</v>
+        <v>978</v>
       </c>
       <c r="F270" s="22" t="s">
-        <v>984</v>
+        <v>940</v>
       </c>
       <c r="G270" s="20"/>
       <c r="H270" s="23"/>
@@ -15555,22 +15643,22 @@
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="21" t="s">
-        <v>1007</v>
+        <v>992</v>
       </c>
       <c r="B271" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>1001</v>
+        <v>980</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>1002</v>
+        <v>981</v>
       </c>
       <c r="F271" s="22" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="G271" s="20"/>
       <c r="H271" s="23"/>
@@ -15580,22 +15668,22 @@
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="21" t="s">
-        <v>1010</v>
+        <v>995</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>1004</v>
+        <v>984</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>1005</v>
+        <v>985</v>
       </c>
       <c r="F272" s="22" t="s">
-        <v>1006</v>
+        <v>982</v>
       </c>
       <c r="G272" s="20"/>
       <c r="H272" s="23"/>
@@ -15605,22 +15693,22 @@
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="21" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>1008</v>
+        <v>987</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>1009</v>
+        <v>988</v>
       </c>
       <c r="F273" s="22" t="s">
-        <v>1006</v>
+        <v>982</v>
       </c>
       <c r="G273" s="20"/>
       <c r="H273" s="23"/>
@@ -15630,22 +15718,22 @@
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="21" t="s">
-        <v>1017</v>
+        <v>1001</v>
       </c>
       <c r="B274" s="21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>1011</v>
+        <v>990</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>1012</v>
+        <v>991</v>
       </c>
       <c r="F274" s="22" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
       <c r="G274" s="20"/>
       <c r="H274" s="23"/>
@@ -15655,22 +15743,22 @@
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="21" t="s">
-        <v>1020</v>
+        <v>1005</v>
       </c>
       <c r="B275" s="21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>1015</v>
+        <v>993</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>1016</v>
+        <v>994</v>
       </c>
       <c r="F275" s="22" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
       <c r="G275" s="20"/>
       <c r="H275" s="23"/>
@@ -15680,22 +15768,22 @@
     </row>
     <row r="276" spans="1:11">
       <c r="A276" s="21" t="s">
-        <v>1023</v>
+        <v>1008</v>
       </c>
       <c r="B276" s="21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>1018</v>
+        <v>996</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>1019</v>
+        <v>997</v>
       </c>
       <c r="F276" s="22" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
       <c r="G276" s="20"/>
       <c r="H276" s="23"/>
@@ -15705,22 +15793,22 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="21" t="s">
-        <v>1027</v>
+        <v>1012</v>
       </c>
       <c r="B277" s="21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>1021</v>
+        <v>999</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>1022</v>
+        <v>1000</v>
       </c>
       <c r="F277" s="22" t="s">
-        <v>1013</v>
+        <v>982</v>
       </c>
       <c r="G277" s="20"/>
       <c r="H277" s="23"/>
@@ -15730,22 +15818,22 @@
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="21" t="s">
-        <v>1031</v>
+        <v>1015</v>
       </c>
       <c r="B278" s="21" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C278" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>1024</v>
+        <v>1002</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>1025</v>
+        <v>1003</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>1026</v>
+        <v>1004</v>
       </c>
       <c r="G278" s="20"/>
       <c r="H278" s="23"/>
@@ -15755,22 +15843,22 @@
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="21" t="s">
-        <v>1034</v>
+        <v>1018</v>
       </c>
       <c r="B279" s="21" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>1028</v>
+        <v>1006</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1029</v>
+        <v>1007</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>1030</v>
+        <v>1004</v>
       </c>
       <c r="G279" s="20"/>
       <c r="H279" s="23"/>
@@ -15780,22 +15868,22 @@
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="21" t="s">
-        <v>1037</v>
+        <v>1021</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1032</v>
+        <v>1009</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1033</v>
+        <v>1010</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="G280" s="20"/>
       <c r="H280" s="23"/>
@@ -15805,22 +15893,22 @@
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="21" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1035</v>
+        <v>1013</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1036</v>
+        <v>1014</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="G281" s="20"/>
       <c r="H281" s="23"/>
@@ -15830,22 +15918,22 @@
     </row>
     <row r="282" spans="1:11">
       <c r="A282" s="21" t="s">
-        <v>1043</v>
+        <v>1029</v>
       </c>
       <c r="B282" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1038</v>
+        <v>1016</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1039</v>
+        <v>1017</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="G282" s="20"/>
       <c r="H282" s="23"/>
@@ -15855,22 +15943,22 @@
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="21" t="s">
-        <v>1047</v>
+        <v>1032</v>
       </c>
       <c r="B283" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1041</v>
+        <v>1019</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1042</v>
+        <v>1020</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>1030</v>
+        <v>1011</v>
       </c>
       <c r="G283" s="20"/>
       <c r="H283" s="23"/>
@@ -15880,22 +15968,22 @@
     </row>
     <row r="284" spans="1:11">
       <c r="A284" s="21" t="s">
-        <v>1050</v>
+        <v>1035</v>
       </c>
       <c r="B284" s="21" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C284" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1044</v>
+        <v>1022</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1045</v>
+        <v>1023</v>
       </c>
       <c r="F284" s="22" t="s">
-        <v>1046</v>
+        <v>1024</v>
       </c>
       <c r="G284" s="20"/>
       <c r="H284" s="23"/>
@@ -15905,22 +15993,22 @@
     </row>
     <row r="285" spans="1:11">
       <c r="A285" s="21" t="s">
-        <v>1053</v>
+        <v>1038</v>
       </c>
       <c r="B285" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1048</v>
+        <v>1026</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1049</v>
+        <v>1027</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="G285" s="20"/>
       <c r="H285" s="23"/>
@@ -15930,22 +16018,22 @@
     </row>
     <row r="286" spans="1:11">
       <c r="A286" s="21" t="s">
-        <v>1056</v>
+        <v>1041</v>
       </c>
       <c r="B286" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C286" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1051</v>
+        <v>1030</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1052</v>
+        <v>1031</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="G286" s="20"/>
       <c r="H286" s="23"/>
@@ -15955,22 +16043,22 @@
     </row>
     <row r="287" spans="1:11">
       <c r="A287" s="21" t="s">
-        <v>1060</v>
+        <v>1045</v>
       </c>
       <c r="B287" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1054</v>
+        <v>1033</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1055</v>
+        <v>1034</v>
       </c>
       <c r="F287" s="22" t="s">
-        <v>1046</v>
+        <v>1028</v>
       </c>
       <c r="G287" s="20"/>
       <c r="H287" s="23"/>
@@ -15980,22 +16068,22 @@
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="21" t="s">
-        <v>1063</v>
+        <v>1048</v>
       </c>
       <c r="B288" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1057</v>
+        <v>1036</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1058</v>
+        <v>1037</v>
       </c>
       <c r="F288" s="22" t="s">
-        <v>1059</v>
+        <v>1028</v>
       </c>
       <c r="G288" s="20"/>
       <c r="H288" s="23"/>
@@ -16005,22 +16093,22 @@
     </row>
     <row r="289" spans="1:11">
       <c r="A289" s="21" t="s">
-        <v>1066</v>
+        <v>1051</v>
       </c>
       <c r="B289" s="21" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1061</v>
+        <v>1039</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1062</v>
+        <v>1040</v>
       </c>
       <c r="F289" s="22" t="s">
-        <v>1059</v>
+        <v>1028</v>
       </c>
       <c r="G289" s="20"/>
       <c r="H289" s="23"/>
@@ -16030,22 +16118,22 @@
     </row>
     <row r="290" spans="1:11">
       <c r="A290" s="21" t="s">
-        <v>1069</v>
+        <v>1054</v>
       </c>
       <c r="B290" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1064</v>
+        <v>1042</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1065</v>
+        <v>1043</v>
       </c>
       <c r="F290" s="22" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="G290" s="20"/>
       <c r="H290" s="23"/>
@@ -16055,22 +16143,22 @@
     </row>
     <row r="291" spans="1:11">
       <c r="A291" s="21" t="s">
-        <v>1072</v>
+        <v>1058</v>
       </c>
       <c r="B291" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1067</v>
+        <v>1046</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1068</v>
+        <v>1047</v>
       </c>
       <c r="F291" s="22" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="G291" s="20"/>
       <c r="H291" s="23"/>
@@ -16080,22 +16168,22 @@
     </row>
     <row r="292" spans="1:11">
       <c r="A292" s="21" t="s">
-        <v>1075</v>
+        <v>1061</v>
       </c>
       <c r="B292" s="21" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1070</v>
+        <v>1049</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1071</v>
+        <v>1050</v>
       </c>
       <c r="F292" s="22" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="G292" s="20"/>
       <c r="H292" s="23"/>
@@ -16105,22 +16193,22 @@
     </row>
     <row r="293" spans="1:11">
       <c r="A293" s="21" t="s">
-        <v>1078</v>
+        <v>1064</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1073</v>
+        <v>1052</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1074</v>
+        <v>1053</v>
       </c>
       <c r="F293" s="22" t="s">
-        <v>1059</v>
+        <v>1044</v>
       </c>
       <c r="G293" s="20"/>
       <c r="H293" s="23"/>
@@ -16130,22 +16218,22 @@
     </row>
     <row r="294" spans="1:11">
       <c r="A294" s="21" t="s">
-        <v>1081</v>
+        <v>1067</v>
       </c>
       <c r="B294" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1076</v>
+        <v>1055</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1077</v>
+        <v>1056</v>
       </c>
       <c r="F294" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G294" s="20"/>
       <c r="H294" s="23"/>
@@ -16155,22 +16243,22 @@
     </row>
     <row r="295" spans="1:11">
       <c r="A295" s="21" t="s">
-        <v>1084</v>
+        <v>1070</v>
       </c>
       <c r="B295" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1079</v>
+        <v>1059</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1080</v>
+        <v>1060</v>
       </c>
       <c r="F295" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G295" s="20"/>
       <c r="H295" s="23"/>
@@ -16180,22 +16268,22 @@
     </row>
     <row r="296" spans="1:11">
       <c r="A296" s="21" t="s">
-        <v>1087</v>
+        <v>1073</v>
       </c>
       <c r="B296" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1082</v>
+        <v>1062</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1083</v>
+        <v>1063</v>
       </c>
       <c r="F296" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G296" s="20"/>
       <c r="H296" s="23"/>
@@ -16205,22 +16293,22 @@
     </row>
     <row r="297" spans="1:11">
       <c r="A297" s="21" t="s">
-        <v>1090</v>
+        <v>1076</v>
       </c>
       <c r="B297" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1085</v>
+        <v>1065</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1086</v>
+        <v>1066</v>
       </c>
       <c r="F297" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G297" s="20"/>
       <c r="H297" s="23"/>
@@ -16230,22 +16318,22 @@
     </row>
     <row r="298" spans="1:11">
       <c r="A298" s="21" t="s">
-        <v>1094</v>
+        <v>1079</v>
       </c>
       <c r="B298" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1088</v>
+        <v>1068</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1089</v>
+        <v>1069</v>
       </c>
       <c r="F298" s="22" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G298" s="20"/>
       <c r="H298" s="23"/>
@@ -16255,22 +16343,22 @@
     </row>
     <row r="299" spans="1:11">
       <c r="A299" s="21" t="s">
-        <v>1098</v>
+        <v>1082</v>
       </c>
       <c r="B299" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1091</v>
+        <v>1071</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1092</v>
+        <v>1072</v>
       </c>
       <c r="F299" s="22" t="s">
-        <v>1093</v>
+        <v>1057</v>
       </c>
       <c r="G299" s="20"/>
       <c r="H299" s="23"/>
@@ -16280,22 +16368,22 @@
     </row>
     <row r="300" spans="1:11">
       <c r="A300" s="21" t="s">
-        <v>1101</v>
+        <v>1085</v>
       </c>
       <c r="B300" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1095</v>
+        <v>1074</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1096</v>
+        <v>1075</v>
       </c>
       <c r="F300" s="22" t="s">
-        <v>1097</v>
+        <v>1057</v>
       </c>
       <c r="G300" s="20"/>
       <c r="H300" s="23"/>
@@ -16305,22 +16393,22 @@
     </row>
     <row r="301" spans="1:11">
       <c r="A301" s="21" t="s">
-        <v>1104</v>
+        <v>1088</v>
       </c>
       <c r="B301" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1099</v>
+        <v>1077</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1100</v>
+        <v>1078</v>
       </c>
       <c r="F301" s="22" t="s">
-        <v>1097</v>
+        <v>1057</v>
       </c>
       <c r="G301" s="20"/>
       <c r="H301" s="23"/>
@@ -16330,22 +16418,22 @@
     </row>
     <row r="302" spans="1:11">
       <c r="A302" s="21" t="s">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="B302" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1102</v>
+        <v>1080</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1103</v>
+        <v>1081</v>
       </c>
       <c r="F302" s="22" t="s">
-        <v>1097</v>
+        <v>1057</v>
       </c>
       <c r="G302" s="20"/>
       <c r="H302" s="23"/>
@@ -16355,22 +16443,22 @@
     </row>
     <row r="303" spans="1:11">
       <c r="A303" s="21" t="s">
-        <v>1111</v>
+        <v>1096</v>
       </c>
       <c r="B303" s="21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1105</v>
+        <v>1083</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1106</v>
+        <v>1084</v>
       </c>
       <c r="F303" s="22" t="s">
-        <v>1107</v>
+        <v>1057</v>
       </c>
       <c r="G303" s="20"/>
       <c r="H303" s="23"/>
@@ -16380,22 +16468,22 @@
     </row>
     <row r="304" spans="1:11">
       <c r="A304" s="21" t="s">
-        <v>1114</v>
+        <v>1099</v>
       </c>
       <c r="B304" s="21" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1109</v>
+        <v>1086</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1110</v>
+        <v>1087</v>
       </c>
       <c r="F304" s="22" t="s">
-        <v>1107</v>
+        <v>1057</v>
       </c>
       <c r="G304" s="20"/>
       <c r="H304" s="23"/>
@@ -16405,22 +16493,22 @@
     </row>
     <row r="305" spans="1:11">
       <c r="A305" s="21" t="s">
-        <v>1118</v>
+        <v>1102</v>
       </c>
       <c r="B305" s="21" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1112</v>
+        <v>1089</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1113</v>
+        <v>1090</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>1107</v>
+        <v>1091</v>
       </c>
       <c r="G305" s="20"/>
       <c r="H305" s="23"/>
@@ -16430,22 +16518,22 @@
     </row>
     <row r="306" spans="1:11">
       <c r="A306" s="21" t="s">
-        <v>1121</v>
+        <v>1106</v>
       </c>
       <c r="B306" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C306" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1115</v>
+        <v>1093</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1116</v>
+        <v>1094</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>1117</v>
+        <v>1095</v>
       </c>
       <c r="G306" s="20"/>
       <c r="H306" s="23"/>
@@ -16455,22 +16543,22 @@
     </row>
     <row r="307" spans="1:11">
       <c r="A307" s="21" t="s">
-        <v>1124</v>
+        <v>1109</v>
       </c>
       <c r="B307" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C307" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1119</v>
+        <v>1097</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1120</v>
+        <v>1098</v>
       </c>
       <c r="F307" s="22" t="s">
-        <v>1117</v>
+        <v>1095</v>
       </c>
       <c r="G307" s="20"/>
       <c r="H307" s="23"/>
@@ -16480,22 +16568,22 @@
     </row>
     <row r="308" spans="1:11">
       <c r="A308" s="21" t="s">
-        <v>1125</v>
+        <v>1112</v>
       </c>
       <c r="B308" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C308" s="21" t="s">
         <v>190</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1122</v>
+        <v>1100</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1123</v>
+        <v>1101</v>
       </c>
       <c r="F308" s="22" t="s">
-        <v>1117</v>
+        <v>1095</v>
       </c>
       <c r="G308" s="20"/>
       <c r="H308" s="23"/>
@@ -16505,22 +16593,22 @@
     </row>
     <row r="309" spans="1:11">
       <c r="A309" s="21" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="B309" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="F309" s="22" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="G309" s="20"/>
       <c r="H309" s="23"/>
@@ -16530,22 +16618,22 @@
     </row>
     <row r="310" spans="1:11">
       <c r="A310" s="21" t="s">
-        <v>1131</v>
+        <v>1119</v>
       </c>
       <c r="B310" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1126</v>
+        <v>1107</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1127</v>
+        <v>1108</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="G310" s="20"/>
       <c r="H310" s="23"/>
@@ -16555,22 +16643,22 @@
     </row>
     <row r="311" spans="1:11">
       <c r="A311" s="21" t="s">
-        <v>1135</v>
+        <v>1122</v>
       </c>
       <c r="B311" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1129</v>
+        <v>1110</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="F311" s="22" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="G311" s="20"/>
       <c r="H311" s="23"/>
@@ -16580,22 +16668,22 @@
     </row>
     <row r="312" spans="1:11">
       <c r="A312" s="21" t="s">
-        <v>1138</v>
+        <v>1123</v>
       </c>
       <c r="B312" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C312" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1133</v>
+        <v>1114</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>1134</v>
+        <v>1115</v>
       </c>
       <c r="G312" s="20"/>
       <c r="H312" s="23"/>
@@ -16605,22 +16693,22 @@
     </row>
     <row r="313" spans="1:11">
       <c r="A313" s="21" t="s">
-        <v>1142</v>
+        <v>1126</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C313" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1136</v>
+        <v>1117</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1137</v>
+        <v>1118</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>1134</v>
+        <v>1115</v>
       </c>
       <c r="G313" s="20"/>
       <c r="H313" s="23"/>
@@ -16630,22 +16718,22 @@
     </row>
     <row r="314" spans="1:11">
       <c r="A314" s="21" t="s">
-        <v>1145</v>
+        <v>1129</v>
       </c>
       <c r="B314" s="21" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C314" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1139</v>
+        <v>1120</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1140</v>
+        <v>1121</v>
       </c>
       <c r="F314" s="22" t="s">
-        <v>1141</v>
+        <v>1115</v>
       </c>
       <c r="G314" s="20"/>
       <c r="H314" s="23"/>
@@ -16655,22 +16743,22 @@
     </row>
     <row r="315" spans="1:11">
       <c r="A315" s="21" t="s">
-        <v>1149</v>
+        <v>1133</v>
       </c>
       <c r="B315" s="21" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C315" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1143</v>
+        <v>1113</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1144</v>
+        <v>1114</v>
       </c>
       <c r="F315" s="22" t="s">
-        <v>1141</v>
+        <v>1115</v>
       </c>
       <c r="G315" s="20"/>
       <c r="H315" s="23"/>
@@ -16680,22 +16768,22 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="21" t="s">
-        <v>1152</v>
+        <v>1136</v>
       </c>
       <c r="B316" s="21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1146</v>
+        <v>1124</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1147</v>
+        <v>1125</v>
       </c>
       <c r="F316" s="22" t="s">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="G316" s="20"/>
       <c r="H316" s="23"/>
@@ -16705,22 +16793,22 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="21" t="s">
-        <v>1155</v>
+        <v>1140</v>
       </c>
       <c r="B317" s="21" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D317" s="22" t="s">
-        <v>1150</v>
+        <v>1127</v>
       </c>
       <c r="E317" s="21" t="s">
-        <v>1151</v>
+        <v>1128</v>
       </c>
       <c r="F317" s="22" t="s">
-        <v>1148</v>
+        <v>1115</v>
       </c>
       <c r="G317" s="20"/>
       <c r="H317" s="23"/>
@@ -16730,22 +16818,22 @@
     </row>
     <row r="318" spans="1:11">
       <c r="A318" s="21" t="s">
-        <v>1158</v>
+        <v>1143</v>
       </c>
       <c r="B318" s="21" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1153</v>
+        <v>1130</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1154</v>
+        <v>1131</v>
       </c>
       <c r="F318" s="22" t="s">
-        <v>1148</v>
+        <v>1132</v>
       </c>
       <c r="G318" s="20"/>
       <c r="H318" s="23"/>
@@ -16755,22 +16843,22 @@
     </row>
     <row r="319" spans="1:11">
       <c r="A319" s="21" t="s">
-        <v>1161</v>
+        <v>1147</v>
       </c>
       <c r="B319" s="21" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1156</v>
+        <v>1134</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1157</v>
+        <v>1135</v>
       </c>
       <c r="F319" s="22" t="s">
-        <v>1148</v>
+        <v>1132</v>
       </c>
       <c r="G319" s="20"/>
       <c r="H319" s="23"/>
@@ -16780,22 +16868,22 @@
     </row>
     <row r="320" spans="1:11">
       <c r="A320" s="21" t="s">
-        <v>1164</v>
+        <v>1150</v>
       </c>
       <c r="B320" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1159</v>
+        <v>1137</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1160</v>
+        <v>1138</v>
       </c>
       <c r="F320" s="22" t="s">
-        <v>1148</v>
+        <v>1139</v>
       </c>
       <c r="G320" s="20"/>
       <c r="H320" s="23"/>
@@ -16805,22 +16893,22 @@
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="21" t="s">
-        <v>1167</v>
+        <v>1153</v>
       </c>
       <c r="B321" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1162</v>
+        <v>1141</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1163</v>
+        <v>1142</v>
       </c>
       <c r="F321" s="22" t="s">
-        <v>1148</v>
+        <v>1139</v>
       </c>
       <c r="G321" s="20"/>
       <c r="H321" s="23"/>
@@ -16830,22 +16918,22 @@
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="21" t="s">
-        <v>1170</v>
+        <v>1156</v>
       </c>
       <c r="B322" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1165</v>
+        <v>1144</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1166</v>
+        <v>1145</v>
       </c>
       <c r="F322" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G322" s="20"/>
       <c r="H322" s="23"/>
@@ -16855,22 +16943,22 @@
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="21" t="s">
-        <v>1173</v>
+        <v>1159</v>
       </c>
       <c r="B323" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1168</v>
+        <v>1148</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1169</v>
+        <v>1149</v>
       </c>
       <c r="F323" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G323" s="20"/>
       <c r="H323" s="23"/>
@@ -16880,22 +16968,22 @@
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="21" t="s">
-        <v>1176</v>
+        <v>1162</v>
       </c>
       <c r="B324" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1171</v>
+        <v>1151</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1172</v>
+        <v>1152</v>
       </c>
       <c r="F324" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G324" s="20"/>
       <c r="H324" s="23"/>
@@ -16905,22 +16993,22 @@
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="21" t="s">
-        <v>1179</v>
+        <v>1165</v>
       </c>
       <c r="B325" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1174</v>
+        <v>1154</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1175</v>
+        <v>1155</v>
       </c>
       <c r="F325" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G325" s="20"/>
       <c r="H325" s="23"/>
@@ -16930,22 +17018,22 @@
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="21" t="s">
-        <v>1182</v>
+        <v>1168</v>
       </c>
       <c r="B326" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1177</v>
+        <v>1157</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1178</v>
+        <v>1158</v>
       </c>
       <c r="F326" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G326" s="20"/>
       <c r="H326" s="23"/>
@@ -16955,22 +17043,22 @@
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="21" t="s">
-        <v>1185</v>
+        <v>1171</v>
       </c>
       <c r="B327" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1180</v>
+        <v>1160</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1181</v>
+        <v>1161</v>
       </c>
       <c r="F327" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G327" s="20"/>
       <c r="H327" s="23"/>
@@ -16980,22 +17068,22 @@
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="21" t="s">
-        <v>1188</v>
+        <v>1174</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>304</v>
+        <v>206</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1183</v>
+        <v>1163</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1184</v>
+        <v>1164</v>
       </c>
       <c r="F328" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G328" s="20"/>
       <c r="H328" s="23"/>
@@ -17005,22 +17093,22 @@
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="21" t="s">
-        <v>1191</v>
+        <v>1177</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>308</v>
+        <v>210</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1186</v>
+        <v>1166</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1187</v>
+        <v>1167</v>
       </c>
       <c r="F329" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G329" s="20"/>
       <c r="H329" s="23"/>
@@ -17030,22 +17118,22 @@
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="21" t="s">
-        <v>1194</v>
+        <v>1180</v>
       </c>
       <c r="B330" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>312</v>
+        <v>258</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1189</v>
+        <v>1169</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="F330" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G330" s="20"/>
       <c r="H330" s="23"/>
@@ -17055,22 +17143,22 @@
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="21" t="s">
-        <v>1197</v>
+        <v>1183</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>316</v>
+        <v>262</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1192</v>
+        <v>1172</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>1193</v>
+        <v>1173</v>
       </c>
       <c r="F331" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G331" s="20"/>
       <c r="H331" s="23"/>
@@ -17080,22 +17168,22 @@
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="21" t="s">
-        <v>1199</v>
+        <v>1186</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1195</v>
+        <v>1175</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1196</v>
+        <v>1176</v>
       </c>
       <c r="F332" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G332" s="20"/>
       <c r="H332" s="23"/>
@@ -17105,22 +17193,22 @@
     </row>
     <row r="333" spans="1:11">
       <c r="A333" s="21" t="s">
-        <v>1202</v>
+        <v>1189</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1198</v>
+        <v>1178</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>188</v>
+        <v>1179</v>
       </c>
       <c r="F333" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G333" s="20"/>
       <c r="H333" s="23"/>
@@ -17130,22 +17218,22 @@
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="21" t="s">
-        <v>1205</v>
+        <v>1192</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1200</v>
+        <v>1181</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1201</v>
+        <v>1182</v>
       </c>
       <c r="F334" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G334" s="20"/>
       <c r="H334" s="23"/>
@@ -17155,22 +17243,22 @@
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="21" t="s">
-        <v>1208</v>
+        <v>1195</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>332</v>
+        <v>308</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1203</v>
+        <v>1184</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1204</v>
+        <v>1185</v>
       </c>
       <c r="F335" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G335" s="20"/>
       <c r="H335" s="23"/>
@@ -17180,22 +17268,22 @@
     </row>
     <row r="336" spans="1:11">
       <c r="A336" s="21" t="s">
-        <v>1211</v>
+        <v>1197</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1206</v>
+        <v>1187</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1207</v>
+        <v>1188</v>
       </c>
       <c r="F336" s="22" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="G336" s="20"/>
       <c r="H336" s="23"/>
@@ -17205,22 +17293,22 @@
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="21" t="s">
-        <v>1214</v>
+        <v>1200</v>
       </c>
       <c r="B337" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>174</v>
+        <v>316</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1209</v>
+        <v>1190</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1163</v>
+        <v>1191</v>
       </c>
       <c r="F337" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G337" s="20"/>
       <c r="H337" s="23"/>
@@ -17230,22 +17318,22 @@
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="21" t="s">
-        <v>1217</v>
+        <v>1203</v>
       </c>
       <c r="B338" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1212</v>
+        <v>1193</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1213</v>
+        <v>1194</v>
       </c>
       <c r="F338" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G338" s="20"/>
       <c r="H338" s="23"/>
@@ -17255,22 +17343,22 @@
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="21" t="s">
-        <v>1220</v>
+        <v>1206</v>
       </c>
       <c r="B339" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>190</v>
+        <v>324</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1215</v>
+        <v>1196</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>1216</v>
+        <v>188</v>
       </c>
       <c r="F339" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G339" s="20"/>
       <c r="H339" s="23"/>
@@ -17280,22 +17368,22 @@
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="21" t="s">
-        <v>1223</v>
+        <v>1209</v>
       </c>
       <c r="B340" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>194</v>
+        <v>328</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1218</v>
+        <v>1198</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>1219</v>
+        <v>1199</v>
       </c>
       <c r="F340" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G340" s="20"/>
       <c r="H340" s="23"/>
@@ -17305,22 +17393,22 @@
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="21" t="s">
-        <v>1226</v>
+        <v>1212</v>
       </c>
       <c r="B341" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>198</v>
+        <v>332</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1221</v>
+        <v>1201</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>1222</v>
+        <v>1202</v>
       </c>
       <c r="F341" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G341" s="20"/>
       <c r="H341" s="23"/>
@@ -17330,22 +17418,22 @@
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="21" t="s">
-        <v>1229</v>
+        <v>1215</v>
       </c>
       <c r="B342" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>202</v>
+        <v>336</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1224</v>
+        <v>1204</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1225</v>
+        <v>1205</v>
       </c>
       <c r="F342" s="22" t="s">
-        <v>1210</v>
+        <v>1146</v>
       </c>
       <c r="G342" s="20"/>
       <c r="H342" s="23"/>
@@ -17355,22 +17443,22 @@
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="21" t="s">
-        <v>1232</v>
+        <v>1218</v>
       </c>
       <c r="B343" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1227</v>
+        <v>1207</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1228</v>
+        <v>1161</v>
       </c>
       <c r="F343" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G343" s="20"/>
       <c r="H343" s="23"/>
@@ -17380,22 +17468,22 @@
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="21" t="s">
-        <v>1235</v>
+        <v>1221</v>
       </c>
       <c r="B344" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1230</v>
+        <v>1210</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1231</v>
+        <v>1211</v>
       </c>
       <c r="F344" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G344" s="20"/>
       <c r="H344" s="23"/>
@@ -17405,22 +17493,22 @@
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="21" t="s">
-        <v>1238</v>
+        <v>1224</v>
       </c>
       <c r="B345" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>258</v>
+        <v>190</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1233</v>
+        <v>1213</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1234</v>
+        <v>1214</v>
       </c>
       <c r="F345" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G345" s="20"/>
       <c r="H345" s="23"/>
@@ -17430,22 +17518,22 @@
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="21" t="s">
-        <v>1241</v>
+        <v>1227</v>
       </c>
       <c r="B346" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1236</v>
+        <v>1216</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1237</v>
+        <v>1217</v>
       </c>
       <c r="F346" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G346" s="20"/>
       <c r="H346" s="23"/>
@@ -17455,22 +17543,22 @@
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="21" t="s">
-        <v>1244</v>
+        <v>1230</v>
       </c>
       <c r="B347" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>296</v>
+        <v>198</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1240</v>
+        <v>1220</v>
       </c>
       <c r="F347" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G347" s="20"/>
       <c r="H347" s="23"/>
@@ -17480,22 +17568,22 @@
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="21" t="s">
-        <v>1247</v>
+        <v>1233</v>
       </c>
       <c r="B348" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1242</v>
+        <v>1222</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1243</v>
+        <v>1223</v>
       </c>
       <c r="F348" s="22" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="G348" s="20"/>
       <c r="H348" s="23"/>
@@ -17505,22 +17593,22 @@
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="21" t="s">
-        <v>1250</v>
+        <v>1236</v>
       </c>
       <c r="B349" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1245</v>
+        <v>1225</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1246</v>
+        <v>1226</v>
       </c>
       <c r="F349" s="22" t="s">
-        <v>877</v>
+        <v>1208</v>
       </c>
       <c r="G349" s="20"/>
       <c r="H349" s="23"/>
@@ -17530,22 +17618,22 @@
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="21" t="s">
-        <v>1253</v>
+        <v>1239</v>
       </c>
       <c r="B350" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1248</v>
+        <v>1228</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1249</v>
+        <v>1229</v>
       </c>
       <c r="F350" s="22" t="s">
-        <v>877</v>
+        <v>1208</v>
       </c>
       <c r="G350" s="20"/>
       <c r="H350" s="23"/>
@@ -17555,22 +17643,22 @@
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="21" t="s">
-        <v>1256</v>
+        <v>1242</v>
       </c>
       <c r="B351" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>190</v>
+        <v>258</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1251</v>
+        <v>1231</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1252</v>
+        <v>1232</v>
       </c>
       <c r="F351" s="22" t="s">
-        <v>877</v>
+        <v>1208</v>
       </c>
       <c r="G351" s="20"/>
       <c r="H351" s="23"/>
@@ -17580,22 +17668,22 @@
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="21" t="s">
-        <v>1283</v>
+        <v>1245</v>
       </c>
       <c r="B352" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
       <c r="D352" s="22" t="s">
-        <v>1254</v>
+        <v>1234</v>
       </c>
       <c r="E352" s="21" t="s">
-        <v>1255</v>
+        <v>1235</v>
       </c>
       <c r="F352" s="22" t="s">
-        <v>877</v>
+        <v>1208</v>
       </c>
       <c r="G352" s="20"/>
       <c r="H352" s="23"/>
@@ -17605,22 +17693,22 @@
     </row>
     <row r="353" spans="1:11">
       <c r="A353" s="21" t="s">
-        <v>1284</v>
+        <v>1248</v>
       </c>
       <c r="B353" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C353" s="21" t="s">
-        <v>198</v>
+        <v>296</v>
       </c>
       <c r="D353" s="22" t="s">
-        <v>1257</v>
+        <v>1237</v>
       </c>
       <c r="E353" s="21" t="s">
-        <v>1258</v>
+        <v>1238</v>
       </c>
       <c r="F353" s="22" t="s">
-        <v>877</v>
+        <v>1208</v>
       </c>
       <c r="G353" s="20"/>
       <c r="H353" s="23"/>
@@ -17629,12 +17717,24 @@
       <c r="K353" s="23"/>
     </row>
     <row r="354" spans="1:11">
-      <c r="A354" s="21"/>
-      <c r="B354" s="21"/>
-      <c r="C354" s="21"/>
-      <c r="D354" s="22"/>
-      <c r="E354" s="21"/>
-      <c r="F354" s="22"/>
+      <c r="A354" s="21" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B354" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="C354" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="D354" s="22" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E354" s="21" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F354" s="22" t="s">
+        <v>1208</v>
+      </c>
       <c r="G354" s="20"/>
       <c r="H354" s="23"/>
       <c r="I354" s="23"/>
@@ -17642,12 +17742,24 @@
       <c r="K354" s="23"/>
     </row>
     <row r="355" spans="1:11">
-      <c r="A355" s="21"/>
-      <c r="B355" s="21"/>
-      <c r="C355" s="21"/>
-      <c r="D355" s="22"/>
-      <c r="E355" s="21"/>
-      <c r="F355" s="22"/>
+      <c r="A355" s="21" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B355" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C355" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D355" s="22" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E355" s="21" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F355" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G355" s="20"/>
       <c r="H355" s="23"/>
       <c r="I355" s="23"/>
@@ -17655,12 +17767,24 @@
       <c r="K355" s="23"/>
     </row>
     <row r="356" spans="1:11">
-      <c r="A356" s="21"/>
-      <c r="B356" s="21"/>
-      <c r="C356" s="21"/>
-      <c r="D356" s="22"/>
-      <c r="E356" s="21"/>
-      <c r="F356" s="22"/>
+      <c r="A356" s="21" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B356" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C356" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D356" s="22" t="s">
+        <v>1246</v>
+      </c>
+      <c r="E356" s="21" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F356" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G356" s="20"/>
       <c r="H356" s="23"/>
       <c r="I356" s="23"/>
@@ -17668,12 +17792,24 @@
       <c r="K356" s="23"/>
     </row>
     <row r="357" spans="1:11">
-      <c r="A357" s="21"/>
-      <c r="B357" s="21"/>
-      <c r="C357" s="21"/>
-      <c r="D357" s="22"/>
-      <c r="E357" s="21"/>
-      <c r="F357" s="22"/>
+      <c r="A357" s="21" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B357" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C357" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D357" s="22" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E357" s="21" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F357" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G357" s="20"/>
       <c r="H357" s="23"/>
       <c r="I357" s="23"/>
@@ -17681,12 +17817,24 @@
       <c r="K357" s="23"/>
     </row>
     <row r="358" spans="1:11">
-      <c r="A358" s="21"/>
-      <c r="B358" s="21"/>
-      <c r="C358" s="21"/>
-      <c r="D358" s="22"/>
-      <c r="E358" s="21"/>
-      <c r="F358" s="22"/>
+      <c r="A358" s="21" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B358" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C358" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D358" s="22" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E358" s="21" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F358" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G358" s="20"/>
       <c r="H358" s="23"/>
       <c r="I358" s="23"/>
@@ -17694,12 +17842,24 @@
       <c r="K358" s="23"/>
     </row>
     <row r="359" spans="1:11">
-      <c r="A359" s="21"/>
-      <c r="B359" s="21"/>
-      <c r="C359" s="21"/>
-      <c r="D359" s="22"/>
-      <c r="E359" s="21"/>
-      <c r="F359" s="22"/>
+      <c r="A359" s="21" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B359" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C359" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D359" s="22" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E359" s="21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F359" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G359" s="20"/>
       <c r="H359" s="23"/>
       <c r="I359" s="23"/>
@@ -18350,7 +18510,7 @@
       <c r="D409" s="22"/>
       <c r="E409" s="21"/>
       <c r="F409" s="22"/>
-      <c r="G409" s="18"/>
+      <c r="G409" s="20"/>
       <c r="H409" s="23"/>
       <c r="I409" s="23"/>
       <c r="J409" s="23"/>
@@ -18363,7 +18523,7 @@
       <c r="D410" s="22"/>
       <c r="E410" s="21"/>
       <c r="F410" s="22"/>
-      <c r="G410" s="18"/>
+      <c r="G410" s="20"/>
       <c r="H410" s="23"/>
       <c r="I410" s="23"/>
       <c r="J410" s="23"/>
@@ -18376,7 +18536,7 @@
       <c r="D411" s="22"/>
       <c r="E411" s="21"/>
       <c r="F411" s="22"/>
-      <c r="G411" s="18"/>
+      <c r="G411" s="20"/>
       <c r="H411" s="23"/>
       <c r="I411" s="23"/>
       <c r="J411" s="23"/>
@@ -18389,7 +18549,7 @@
       <c r="D412" s="22"/>
       <c r="E412" s="21"/>
       <c r="F412" s="22"/>
-      <c r="G412" s="18"/>
+      <c r="G412" s="20"/>
       <c r="H412" s="23"/>
       <c r="I412" s="23"/>
       <c r="J412" s="23"/>
@@ -18402,7 +18562,7 @@
       <c r="D413" s="22"/>
       <c r="E413" s="21"/>
       <c r="F413" s="22"/>
-      <c r="G413" s="18"/>
+      <c r="G413" s="20"/>
       <c r="H413" s="23"/>
       <c r="I413" s="23"/>
       <c r="J413" s="23"/>
@@ -18415,7 +18575,7 @@
       <c r="D414" s="22"/>
       <c r="E414" s="21"/>
       <c r="F414" s="22"/>
-      <c r="G414" s="18"/>
+      <c r="G414" s="20"/>
       <c r="H414" s="23"/>
       <c r="I414" s="23"/>
       <c r="J414" s="23"/>
@@ -39050,7 +39210,7 @@
       <c r="H2001" s="23"/>
       <c r="I2001" s="23"/>
       <c r="J2001" s="23"/>
-      <c r="K2001" s="33"/>
+      <c r="K2001" s="23"/>
     </row>
     <row r="2002" spans="1:11">
       <c r="A2002" s="21"/>
@@ -39063,21 +39223,99 @@
       <c r="H2002" s="23"/>
       <c r="I2002" s="23"/>
       <c r="J2002" s="23"/>
-      <c r="K2002" s="33"/>
+      <c r="K2002" s="23"/>
+    </row>
+    <row r="2003" spans="1:11">
+      <c r="A2003" s="21"/>
+      <c r="B2003" s="21"/>
+      <c r="C2003" s="21"/>
+      <c r="D2003" s="22"/>
+      <c r="E2003" s="21"/>
+      <c r="F2003" s="22"/>
+      <c r="G2003" s="18"/>
+      <c r="H2003" s="23"/>
+      <c r="I2003" s="23"/>
+      <c r="J2003" s="23"/>
+      <c r="K2003" s="23"/>
+    </row>
+    <row r="2004" spans="1:11">
+      <c r="A2004" s="21"/>
+      <c r="B2004" s="21"/>
+      <c r="C2004" s="21"/>
+      <c r="D2004" s="22"/>
+      <c r="E2004" s="21"/>
+      <c r="F2004" s="22"/>
+      <c r="G2004" s="18"/>
+      <c r="H2004" s="23"/>
+      <c r="I2004" s="23"/>
+      <c r="J2004" s="23"/>
+      <c r="K2004" s="23"/>
+    </row>
+    <row r="2005" spans="1:11">
+      <c r="A2005" s="21"/>
+      <c r="B2005" s="21"/>
+      <c r="C2005" s="21"/>
+      <c r="D2005" s="22"/>
+      <c r="E2005" s="21"/>
+      <c r="F2005" s="22"/>
+      <c r="G2005" s="18"/>
+      <c r="H2005" s="23"/>
+      <c r="I2005" s="23"/>
+      <c r="J2005" s="23"/>
+      <c r="K2005" s="23"/>
+    </row>
+    <row r="2006" spans="1:11">
+      <c r="A2006" s="21"/>
+      <c r="B2006" s="21"/>
+      <c r="C2006" s="21"/>
+      <c r="D2006" s="22"/>
+      <c r="E2006" s="21"/>
+      <c r="F2006" s="22"/>
+      <c r="G2006" s="18"/>
+      <c r="H2006" s="23"/>
+      <c r="I2006" s="23"/>
+      <c r="J2006" s="23"/>
+      <c r="K2006" s="23"/>
+    </row>
+    <row r="2007" spans="1:11">
+      <c r="A2007" s="21"/>
+      <c r="B2007" s="21"/>
+      <c r="C2007" s="21"/>
+      <c r="D2007" s="22"/>
+      <c r="E2007" s="21"/>
+      <c r="F2007" s="22"/>
+      <c r="G2007" s="18"/>
+      <c r="H2007" s="23"/>
+      <c r="I2007" s="23"/>
+      <c r="J2007" s="23"/>
+      <c r="K2007" s="33"/>
+    </row>
+    <row r="2008" spans="1:11">
+      <c r="A2008" s="21"/>
+      <c r="B2008" s="21"/>
+      <c r="C2008" s="21"/>
+      <c r="D2008" s="22"/>
+      <c r="E2008" s="21"/>
+      <c r="F2008" s="22"/>
+      <c r="G2008" s="18"/>
+      <c r="H2008" s="23"/>
+      <c r="I2008" s="23"/>
+      <c r="J2008" s="23"/>
+      <c r="K2008" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1998:A2002">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+  <conditionalFormatting sqref="A2004:A2008">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A1997">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+  <conditionalFormatting sqref="A4:A2003">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H2002" xr:uid="{74B10176-32C1-4DCE-B9A9-308EB3B34100}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H1:H1048576" xr:uid="{74B10176-32C1-4DCE-B9A9-308EB3B34100}">
       <formula1>"Daily 60 Days, Daily 120 Days, Weekly 12W, Weekly 24W, Monthly 3M, Monthly 6M, 60-Day Asset, 120-Day Asset, Weekly 12W Asset, Weekly 24W Asset, Monthly 3M Asset, Monthly 6M Asset"</formula1>
     </dataValidation>
   </dataValidations>
@@ -39103,48 +39341,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="45" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="A1" s="37" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="39" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
+      <c r="A2" s="45" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C3" s="28" t="s">
         <v>1261</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>1263</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="28" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -39153,10 +39391,10 @@
         <v>47</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="s">
@@ -39175,10 +39413,10 @@
         <v>47</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9" t="s">
@@ -39197,14 +39435,14 @@
         <v>47</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="9" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>70</v>
@@ -39219,10 +39457,10 @@
         <v>47</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9" t="s">
@@ -39268,10 +39506,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="28" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2"/>

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8083B6CD-485B-4D51-A6A5-89C90FAF0EC9}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46062980-C33F-44A2-AF4F-C191BFE649C3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="1297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="1321">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -3880,12 +3880,6 @@
     <t>Talabi Folashade</t>
   </si>
   <si>
-    <t>32550</t>
-  </si>
-  <si>
-    <t>23150</t>
-  </si>
-  <si>
     <t>Mary Daramola</t>
   </si>
   <si>
@@ -3917,6 +3911,84 @@
   </si>
   <si>
     <t>09035404634</t>
+  </si>
+  <si>
+    <t>GRP-50</t>
+  </si>
+  <si>
+    <t>5000</t>
+  </si>
+  <si>
+    <t>Olagunju Janet</t>
+  </si>
+  <si>
+    <t>Oloniyo Comfort</t>
+  </si>
+  <si>
+    <t>22675</t>
+  </si>
+  <si>
+    <t>MEM-353</t>
+  </si>
+  <si>
+    <t>MEM-354</t>
+  </si>
+  <si>
+    <t>MEM-355</t>
+  </si>
+  <si>
+    <t>MEM-356</t>
+  </si>
+  <si>
+    <t>MEM-357</t>
+  </si>
+  <si>
+    <t>MEM-358</t>
+  </si>
+  <si>
+    <t>MEM-359</t>
+  </si>
+  <si>
+    <t>MEM-360</t>
+  </si>
+  <si>
+    <t>MEM-361</t>
+  </si>
+  <si>
+    <t>MEM-362</t>
+  </si>
+  <si>
+    <t>09067855535</t>
+  </si>
+  <si>
+    <t>Giwa str, Carribean, Ogijo</t>
+  </si>
+  <si>
+    <t>Adah Toyin</t>
+  </si>
+  <si>
+    <t>Kemi Johnson</t>
+  </si>
+  <si>
+    <t>Oyin Aderemi</t>
+  </si>
+  <si>
+    <t>Rhoda Areo</t>
+  </si>
+  <si>
+    <t>08080154210</t>
+  </si>
+  <si>
+    <t>09151989273</t>
+  </si>
+  <si>
+    <t>08112371144</t>
+  </si>
+  <si>
+    <t>09034089855</t>
+  </si>
+  <si>
+    <t>Weekly 12W Asset</t>
   </si>
 </sst>
 </file>
@@ -4116,7 +4188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4216,36 +4288,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4255,6 +4298,36 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4728,7 +4801,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2008" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2009" dataDxfId="14">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="12"/>
@@ -4905,28 +4978,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -4949,10 +5022,10 @@
       <c r="D4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="38"/>
-      <c r="H4" s="38"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -4960,13 +5033,13 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="43"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4974,13 +5047,13 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="41"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="43"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -4988,13 +5061,13 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="41"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="43"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -5002,13 +5075,13 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="43"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -5016,25 +5089,25 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="41"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="43"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="41"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="43"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -5047,142 +5120,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38"/>
-      <c r="H12" s="38"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="41"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+      <c r="H13" s="43"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="48" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="41"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
-      <c r="E15" s="40"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="39" t="s">
+      <c r="B16" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="41"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="43"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="41"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+      <c r="H17" s="43"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="43"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="39" t="s">
+      <c r="B19" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="40"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="41"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="39" t="s">
+      <c r="B20" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="41"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="42"/>
+      <c r="H20" s="43"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="44" t="s">
+      <c r="B21" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="41"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -5195,6 +5268,13 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:H4"/>
@@ -5207,13 +5287,6 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5236,30 +5309,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="45"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5740,9 +5813,7 @@
       <c r="H21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="14" t="s">
-        <v>1284</v>
-      </c>
+      <c r="I21" s="14"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
@@ -5769,9 +5840,7 @@
       <c r="H22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="14" t="s">
-        <v>1285</v>
-      </c>
+      <c r="I22" s="14"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
@@ -5783,7 +5852,9 @@
       <c r="C23" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6" t="s">
+        <v>1297</v>
+      </c>
       <c r="E23" s="6" t="s">
         <v>94</v>
       </c>
@@ -5796,7 +5867,9 @@
       <c r="H23" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I23" s="14"/>
+      <c r="I23" s="14" t="s">
+        <v>1299</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6" t="s">
@@ -6031,7 +6104,7 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="51"/>
+      <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -6534,15 +6607,33 @@
       <c r="I52" s="14"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="14"/>
+      <c r="A53" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F53" s="7">
+        <v>46224</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I53" s="14" t="s">
+        <v>1296</v>
+      </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="6"/>
@@ -8762,7 +8853,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2008"/>
+  <dimension ref="A1:K2009"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22.09765625" style="27" customWidth="1"/>
@@ -8774,34 +8865,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54"/>
+      <c r="K1" s="54"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="52" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -12516,21 +12607,11 @@
       <c r="F151" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G151" s="20">
-        <v>12500</v>
-      </c>
-      <c r="H151" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I151" s="23">
-        <v>150000</v>
-      </c>
-      <c r="J151" s="23">
-        <v>150000</v>
-      </c>
-      <c r="K151" s="23">
-        <v>50000</v>
-      </c>
+      <c r="G151" s="20"/>
+      <c r="H151" s="23"/>
+      <c r="I151" s="23"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="23"/>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="21" t="s">
@@ -12551,21 +12632,11 @@
       <c r="F152" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G152" s="20">
-        <v>33100</v>
-      </c>
-      <c r="H152" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I152" s="23">
-        <v>290000</v>
-      </c>
-      <c r="J152" s="23">
-        <v>288000</v>
-      </c>
-      <c r="K152" s="23">
-        <v>120000</v>
-      </c>
+      <c r="G152" s="20"/>
+      <c r="H152" s="23"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="23"/>
+      <c r="K152" s="23"/>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="21" t="s">
@@ -12586,12 +12657,8 @@
       <c r="F153" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G153" s="20">
-        <v>23950</v>
-      </c>
-      <c r="H153" s="23" t="s">
-        <v>1275</v>
-      </c>
+      <c r="G153" s="20"/>
+      <c r="H153" s="23"/>
       <c r="I153" s="23"/>
       <c r="J153" s="23"/>
       <c r="K153" s="23"/>
@@ -12615,21 +12682,11 @@
       <c r="F154" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G154" s="20">
-        <v>5650</v>
-      </c>
-      <c r="H154" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I154" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J154" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K154" s="23">
-        <v>41250</v>
-      </c>
+      <c r="G154" s="20"/>
+      <c r="H154" s="23"/>
+      <c r="I154" s="23"/>
+      <c r="J154" s="23"/>
+      <c r="K154" s="23"/>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="21" t="s">
@@ -12650,21 +12707,11 @@
       <c r="F155" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G155" s="20">
-        <v>16050</v>
-      </c>
-      <c r="H155" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I155" s="23">
-        <v>150000</v>
-      </c>
-      <c r="J155" s="23">
-        <v>150000</v>
-      </c>
-      <c r="K155" s="23">
-        <v>50000</v>
-      </c>
+      <c r="G155" s="20"/>
+      <c r="H155" s="23"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="23"/>
+      <c r="K155" s="23"/>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="21" t="s">
@@ -12685,21 +12732,11 @@
       <c r="F156" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G156" s="20">
-        <v>6750</v>
-      </c>
-      <c r="H156" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I156" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J156" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K156" s="23">
-        <v>57750</v>
-      </c>
+      <c r="G156" s="20"/>
+      <c r="H156" s="23"/>
+      <c r="I156" s="23"/>
+      <c r="J156" s="23"/>
+      <c r="K156" s="23"/>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="21" t="s">
@@ -12721,9 +12758,7 @@
         <v>650</v>
       </c>
       <c r="G157" s="20"/>
-      <c r="H157" s="23" t="s">
-        <v>1275</v>
-      </c>
+      <c r="H157" s="23"/>
       <c r="I157" s="23"/>
       <c r="J157" s="23"/>
       <c r="K157" s="23"/>
@@ -12747,12 +12782,8 @@
       <c r="F158" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G158" s="20">
-        <v>15750</v>
-      </c>
-      <c r="H158" s="23" t="s">
-        <v>1275</v>
-      </c>
+      <c r="G158" s="20"/>
+      <c r="H158" s="23"/>
       <c r="I158" s="23"/>
       <c r="J158" s="23"/>
       <c r="K158" s="23"/>
@@ -12776,21 +12807,11 @@
       <c r="F159" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G159" s="20">
-        <v>10550</v>
-      </c>
-      <c r="H159" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I159" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J159" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K159" s="23">
-        <v>8250</v>
-      </c>
+      <c r="G159" s="20"/>
+      <c r="H159" s="23"/>
+      <c r="I159" s="23"/>
+      <c r="J159" s="23"/>
+      <c r="K159" s="23"/>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="21" t="s">
@@ -12811,21 +12832,11 @@
       <c r="F160" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G160" s="20">
-        <v>24000</v>
-      </c>
-      <c r="H160" s="23" t="s">
-        <v>1276</v>
-      </c>
-      <c r="I160" s="23">
-        <v>290000</v>
-      </c>
-      <c r="J160" s="23">
-        <v>288000</v>
-      </c>
-      <c r="K160" s="23">
-        <v>240000</v>
-      </c>
+      <c r="G160" s="20"/>
+      <c r="H160" s="23"/>
+      <c r="I160" s="23"/>
+      <c r="J160" s="23"/>
+      <c r="K160" s="23"/>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="21" t="s">
@@ -12844,21 +12855,11 @@
       <c r="F161" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G161" s="20">
-        <v>16575</v>
-      </c>
-      <c r="H161" s="23" t="s">
-        <v>1276</v>
-      </c>
-      <c r="I161" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J161" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K161" s="23">
-        <v>45375</v>
-      </c>
+      <c r="G161" s="20"/>
+      <c r="H161" s="23"/>
+      <c r="I161" s="23"/>
+      <c r="J161" s="23"/>
+      <c r="K161" s="23"/>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="21" t="s">
@@ -12879,12 +12880,8 @@
       <c r="F162" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G162" s="20">
-        <v>29625</v>
-      </c>
-      <c r="H162" s="23" t="s">
-        <v>1276</v>
-      </c>
+      <c r="G162" s="20"/>
+      <c r="H162" s="23"/>
       <c r="I162" s="23"/>
       <c r="J162" s="23"/>
       <c r="K162" s="23"/>
@@ -12899,30 +12896,20 @@
       <c r="C163" s="21" t="s">
         <v>304</v>
       </c>
-      <c r="D163" s="53" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E163" s="52" t="s">
-        <v>1287</v>
+      <c r="D163" s="40" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E163" s="39" t="s">
+        <v>1285</v>
       </c>
       <c r="F163" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G163" s="35">
-        <v>4750</v>
-      </c>
-      <c r="H163" s="33" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I163" s="33">
-        <v>100000</v>
-      </c>
-      <c r="J163" s="33">
-        <v>99000</v>
-      </c>
-      <c r="K163" s="33">
-        <v>74250</v>
-      </c>
+      <c r="G163" s="35"/>
+      <c r="H163" s="33"/>
+      <c r="I163" s="33"/>
+      <c r="J163" s="33"/>
+      <c r="K163" s="33"/>
     </row>
     <row r="164" spans="1:11" s="36" customFormat="1">
       <c r="A164" s="21" t="s">
@@ -12934,28 +12921,18 @@
       <c r="C164" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="D164" s="53" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E164" s="52"/>
+      <c r="D164" s="40" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E164" s="39"/>
       <c r="F164" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G164" s="35">
-        <v>6250</v>
-      </c>
-      <c r="H164" s="33" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I164" s="33">
-        <v>100000</v>
-      </c>
-      <c r="J164" s="33">
-        <v>99000</v>
-      </c>
-      <c r="K164" s="33">
-        <v>57750</v>
-      </c>
+      <c r="G164" s="35"/>
+      <c r="H164" s="33"/>
+      <c r="I164" s="33"/>
+      <c r="J164" s="33"/>
+      <c r="K164" s="33"/>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="21" t="s">
@@ -12976,21 +12953,11 @@
       <c r="F165" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G165" s="20">
-        <v>6700</v>
-      </c>
-      <c r="H165" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I165" s="23">
-        <v>150000</v>
-      </c>
-      <c r="J165" s="23">
-        <v>150000</v>
-      </c>
-      <c r="K165" s="23">
-        <v>137500</v>
-      </c>
+      <c r="G165" s="20"/>
+      <c r="H165" s="23"/>
+      <c r="I165" s="23"/>
+      <c r="J165" s="23"/>
+      <c r="K165" s="23"/>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="21" t="s">
@@ -13011,21 +12978,11 @@
       <c r="F166" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G166" s="20">
-        <v>24900</v>
-      </c>
-      <c r="H166" s="23" t="s">
-        <v>1276</v>
-      </c>
-      <c r="I166" s="23">
-        <v>200000</v>
-      </c>
-      <c r="J166" s="23">
-        <v>198000</v>
-      </c>
-      <c r="K166" s="23">
-        <v>57750</v>
-      </c>
+      <c r="G166" s="20"/>
+      <c r="H166" s="23"/>
+      <c r="I166" s="23"/>
+      <c r="J166" s="23"/>
+      <c r="K166" s="23"/>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="21" t="s">
@@ -13046,12 +13003,8 @@
       <c r="F167" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G167" s="20">
-        <v>41800</v>
-      </c>
-      <c r="H167" s="23" t="s">
-        <v>1276</v>
-      </c>
+      <c r="G167" s="20"/>
+      <c r="H167" s="23"/>
       <c r="I167" s="23"/>
       <c r="J167" s="23"/>
       <c r="K167" s="23"/>
@@ -13075,137 +13028,113 @@
       <c r="F168" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G168" s="20">
-        <v>22350</v>
-      </c>
-      <c r="H168" s="23" t="s">
-        <v>1276</v>
-      </c>
-      <c r="I168" s="23">
-        <v>150000</v>
-      </c>
-      <c r="J168" s="23">
-        <v>150000</v>
-      </c>
-      <c r="K168" s="23">
-        <v>50000</v>
-      </c>
+      <c r="G168" s="20"/>
+      <c r="H168" s="23"/>
+      <c r="I168" s="23"/>
+      <c r="J168" s="23"/>
+      <c r="K168" s="23"/>
     </row>
     <row r="169" spans="1:11" s="36" customFormat="1">
-      <c r="A169" s="52"/>
+      <c r="A169" s="21" t="s">
+        <v>700</v>
+      </c>
       <c r="B169" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C169" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="D169" s="53" t="s">
-        <v>1291</v>
-      </c>
-      <c r="E169" s="52" t="s">
-        <v>1292</v>
+      <c r="D169" s="40" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E169" s="39" t="s">
+        <v>1290</v>
       </c>
       <c r="F169" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G169" s="35">
-        <v>25600</v>
-      </c>
-      <c r="H169" s="33" t="s">
-        <v>1276</v>
-      </c>
+      <c r="G169" s="35"/>
+      <c r="H169" s="33"/>
       <c r="I169" s="33"/>
       <c r="J169" s="33"/>
       <c r="K169" s="33"/>
     </row>
     <row r="170" spans="1:11" s="36" customFormat="1">
-      <c r="A170" s="52"/>
+      <c r="A170" s="21" t="s">
+        <v>703</v>
+      </c>
       <c r="B170" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C170" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="D170" s="53" t="s">
-        <v>1293</v>
-      </c>
-      <c r="E170" s="52"/>
+      <c r="D170" s="40" t="s">
+        <v>1291</v>
+      </c>
+      <c r="E170" s="39"/>
       <c r="F170" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G170" s="35">
-        <v>4750</v>
-      </c>
-      <c r="H170" s="33" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I170" s="33">
-        <v>100000</v>
-      </c>
-      <c r="J170" s="33">
-        <v>99000</v>
-      </c>
-      <c r="K170" s="33">
-        <v>66000</v>
-      </c>
+      <c r="G170" s="35"/>
+      <c r="H170" s="33"/>
+      <c r="I170" s="33"/>
+      <c r="J170" s="33"/>
+      <c r="K170" s="33"/>
     </row>
     <row r="171" spans="1:11" s="36" customFormat="1">
-      <c r="A171" s="52"/>
+      <c r="A171" s="21" t="s">
+        <v>706</v>
+      </c>
       <c r="B171" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C171" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="D171" s="53" t="s">
+      <c r="D171" s="40" t="s">
         <v>1283</v>
       </c>
-      <c r="E171" s="52" t="s">
-        <v>1295</v>
+      <c r="E171" s="39" t="s">
+        <v>1293</v>
       </c>
       <c r="F171" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G171" s="35">
-        <v>3000</v>
-      </c>
-      <c r="H171" s="33" t="s">
-        <v>1275</v>
-      </c>
+      <c r="G171" s="35"/>
+      <c r="H171" s="33"/>
       <c r="I171" s="33"/>
       <c r="J171" s="33"/>
       <c r="K171" s="33"/>
     </row>
     <row r="172" spans="1:11" s="36" customFormat="1">
-      <c r="A172" s="52"/>
+      <c r="A172" s="21" t="s">
+        <v>710</v>
+      </c>
       <c r="B172" s="21" t="s">
         <v>90</v>
       </c>
       <c r="C172" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="D172" s="53" t="s">
+      <c r="D172" s="40" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E172" s="39" t="s">
         <v>1294</v>
-      </c>
-      <c r="E172" s="52" t="s">
-        <v>1296</v>
       </c>
       <c r="F172" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G172" s="35">
-        <v>5000</v>
-      </c>
-      <c r="H172" s="33" t="s">
-        <v>1275</v>
-      </c>
+      <c r="G172" s="35"/>
+      <c r="H172" s="33"/>
       <c r="I172" s="33"/>
       <c r="J172" s="33"/>
       <c r="K172" s="33"/>
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="21" t="s">
-        <v>700</v>
+        <v>713</v>
       </c>
       <c r="B173" s="21" t="s">
         <v>92</v>
@@ -13222,15 +13151,25 @@
       <c r="F173" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G173" s="20"/>
-      <c r="H173" s="23"/>
-      <c r="I173" s="23"/>
-      <c r="J173" s="23"/>
-      <c r="K173" s="23"/>
+      <c r="G173" s="20">
+        <v>14200</v>
+      </c>
+      <c r="H173" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I173" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J173" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K173" s="23">
+        <v>66000</v>
+      </c>
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="21" t="s">
-        <v>703</v>
+        <v>716</v>
       </c>
       <c r="B174" s="21" t="s">
         <v>92</v>
@@ -13247,15 +13186,25 @@
       <c r="F174" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G174" s="20"/>
-      <c r="H174" s="23"/>
-      <c r="I174" s="23"/>
-      <c r="J174" s="23"/>
-      <c r="K174" s="23"/>
+      <c r="G174" s="20">
+        <v>38750</v>
+      </c>
+      <c r="H174" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I174" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J174" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K174" s="23">
+        <v>96000</v>
+      </c>
     </row>
     <row r="175" spans="1:11">
       <c r="A175" s="21" t="s">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="B175" s="21" t="s">
         <v>92</v>
@@ -13272,15 +13221,25 @@
       <c r="F175" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G175" s="20"/>
-      <c r="H175" s="23"/>
-      <c r="I175" s="23"/>
-      <c r="J175" s="23"/>
-      <c r="K175" s="23"/>
+      <c r="G175" s="20">
+        <v>8500</v>
+      </c>
+      <c r="H175" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I175" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J175" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K175" s="23">
+        <v>198000</v>
+      </c>
     </row>
     <row r="176" spans="1:11">
       <c r="A176" s="21" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="B176" s="21" t="s">
         <v>92</v>
@@ -13297,15 +13256,25 @@
       <c r="F176" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G176" s="20"/>
-      <c r="H176" s="23"/>
-      <c r="I176" s="23"/>
-      <c r="J176" s="23"/>
-      <c r="K176" s="23"/>
+      <c r="G176" s="20">
+        <v>4475</v>
+      </c>
+      <c r="H176" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I176" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J176" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K176" s="23">
+        <v>57750</v>
+      </c>
     </row>
     <row r="177" spans="1:11">
       <c r="A177" s="21" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="B177" s="21" t="s">
         <v>92</v>
@@ -13322,15 +13291,19 @@
       <c r="F177" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="G177" s="20"/>
-      <c r="H177" s="23"/>
+      <c r="G177" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H177" s="23" t="s">
+        <v>1275</v>
+      </c>
       <c r="I177" s="23"/>
       <c r="J177" s="23"/>
       <c r="K177" s="23"/>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="21" t="s">
-        <v>716</v>
+        <v>729</v>
       </c>
       <c r="B178" s="21" t="s">
         <v>92</v>
@@ -13347,15 +13320,19 @@
       <c r="F178" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G178" s="20"/>
-      <c r="H178" s="23"/>
+      <c r="G178" s="20">
+        <v>37000</v>
+      </c>
+      <c r="H178" s="23" t="s">
+        <v>1275</v>
+      </c>
       <c r="I178" s="23"/>
       <c r="J178" s="23"/>
       <c r="K178" s="23"/>
     </row>
     <row r="179" spans="1:11">
       <c r="A179" s="21" t="s">
-        <v>719</v>
+        <v>732</v>
       </c>
       <c r="B179" s="21" t="s">
         <v>92</v>
@@ -13372,15 +13349,25 @@
       <c r="F179" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="G179" s="20"/>
-      <c r="H179" s="23"/>
-      <c r="I179" s="23"/>
-      <c r="J179" s="23"/>
-      <c r="K179" s="23"/>
+      <c r="G179" s="20">
+        <v>14000</v>
+      </c>
+      <c r="H179" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I179" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J179" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K179" s="23">
+        <v>225500</v>
+      </c>
     </row>
     <row r="180" spans="1:11">
       <c r="A180" s="21" t="s">
-        <v>722</v>
+        <v>736</v>
       </c>
       <c r="B180" s="21" t="s">
         <v>92</v>
@@ -13397,15 +13384,25 @@
       <c r="F180" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G180" s="20"/>
-      <c r="H180" s="23"/>
-      <c r="I180" s="23"/>
-      <c r="J180" s="23"/>
-      <c r="K180" s="23"/>
+      <c r="G180" s="20">
+        <v>9350</v>
+      </c>
+      <c r="H180" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I180" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J180" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K180" s="23">
+        <v>33000</v>
+      </c>
     </row>
     <row r="181" spans="1:11">
       <c r="A181" s="21" t="s">
-        <v>725</v>
+        <v>739</v>
       </c>
       <c r="B181" s="21" t="s">
         <v>92</v>
@@ -13422,15 +13419,25 @@
       <c r="F181" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G181" s="20"/>
-      <c r="H181" s="23"/>
-      <c r="I181" s="23"/>
-      <c r="J181" s="23"/>
-      <c r="K181" s="23"/>
+      <c r="G181" s="20">
+        <v>12925</v>
+      </c>
+      <c r="H181" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="I181" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J181" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K181" s="23">
+        <v>12375</v>
+      </c>
     </row>
     <row r="182" spans="1:11">
       <c r="A182" s="21" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="B182" s="21" t="s">
         <v>92</v>
@@ -13447,52 +13454,64 @@
       <c r="F182" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G182" s="20"/>
-      <c r="H182" s="23"/>
+      <c r="G182" s="20">
+        <v>21500</v>
+      </c>
+      <c r="H182" s="23" t="s">
+        <v>1276</v>
+      </c>
       <c r="I182" s="23"/>
       <c r="J182" s="23"/>
       <c r="K182" s="23"/>
     </row>
-    <row r="183" spans="1:11">
+    <row r="183" spans="1:11" s="37" customFormat="1">
       <c r="A183" s="21" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C183" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D183" s="22" t="s">
-        <v>726</v>
-      </c>
-      <c r="E183" s="21" t="s">
-        <v>727</v>
+        <v>92</v>
+      </c>
+      <c r="C183" s="39" t="s">
+        <v>296</v>
+      </c>
+      <c r="D183" s="40" t="s">
+        <v>711</v>
+      </c>
+      <c r="E183" s="39" t="s">
+        <v>712</v>
       </c>
       <c r="F183" s="22" t="s">
-        <v>728</v>
-      </c>
-      <c r="G183" s="20"/>
-      <c r="H183" s="23"/>
-      <c r="I183" s="23"/>
-      <c r="J183" s="23"/>
-      <c r="K183" s="23"/>
+        <v>696</v>
+      </c>
+      <c r="G183" s="35"/>
+      <c r="H183" s="33" t="s">
+        <v>1320</v>
+      </c>
+      <c r="I183" s="33">
+        <v>36000</v>
+      </c>
+      <c r="J183" s="33">
+        <v>24000</v>
+      </c>
+      <c r="K183" s="33">
+        <v>10000</v>
+      </c>
     </row>
     <row r="184" spans="1:11">
       <c r="A184" s="21" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="B184" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C184" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D184" s="22" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E184" s="21" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F184" s="22" t="s">
         <v>728</v>
@@ -13505,22 +13524,22 @@
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="21" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="B185" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E185" s="21" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F185" s="22" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G185" s="20"/>
       <c r="H185" s="23"/>
@@ -13530,19 +13549,19 @@
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="21" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="B186" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D186" s="22" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E186" s="21" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F186" s="22" t="s">
         <v>735</v>
@@ -13555,19 +13574,19 @@
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="21" t="s">
-        <v>744</v>
+        <v>754</v>
       </c>
       <c r="B187" s="21" t="s">
         <v>95</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>349</v>
+        <v>737</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>350</v>
+        <v>738</v>
       </c>
       <c r="F187" s="22" t="s">
         <v>735</v>
@@ -13580,22 +13599,22 @@
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="21" t="s">
-        <v>747</v>
+        <v>756</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>741</v>
+        <v>349</v>
       </c>
       <c r="E188" s="21" t="s">
-        <v>742</v>
+        <v>350</v>
       </c>
       <c r="F188" s="22" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="G188" s="20"/>
       <c r="H188" s="23"/>
@@ -13605,19 +13624,19 @@
     </row>
     <row r="189" spans="1:11">
       <c r="A189" s="21" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B189" s="21" t="s">
         <v>98</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E189" s="21" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F189" s="22" t="s">
         <v>743</v>
@@ -13630,19 +13649,19 @@
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="21" t="s">
-        <v>752</v>
+        <v>762</v>
       </c>
       <c r="B190" s="21" t="s">
         <v>98</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D190" s="22" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E190" s="21" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F190" s="22" t="s">
         <v>743</v>
@@ -13655,18 +13674,20 @@
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="21" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="B191" s="21" t="s">
         <v>98</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>751</v>
-      </c>
-      <c r="E191" s="21"/>
+        <v>748</v>
+      </c>
+      <c r="E191" s="21" t="s">
+        <v>749</v>
+      </c>
       <c r="F191" s="22" t="s">
         <v>743</v>
       </c>
@@ -13678,20 +13699,20 @@
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="21" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D192" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E192" s="21"/>
       <c r="F192" s="22" t="s">
-        <v>709</v>
+        <v>743</v>
       </c>
       <c r="G192" s="20"/>
       <c r="H192" s="23"/>
@@ -13701,20 +13722,20 @@
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="21" t="s">
-        <v>758</v>
+        <v>771</v>
       </c>
       <c r="B193" s="21" t="s">
         <v>101</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D193" s="22" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E193" s="21"/>
       <c r="F193" s="22" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="G193" s="20"/>
       <c r="H193" s="23"/>
@@ -13724,16 +13745,16 @@
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="21" t="s">
-        <v>762</v>
+        <v>775</v>
       </c>
       <c r="B194" s="21" t="s">
         <v>101</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D194" s="22" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E194" s="21"/>
       <c r="F194" s="22" t="s">
@@ -13747,22 +13768,20 @@
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="21" t="s">
-        <v>765</v>
+        <v>778</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D195" s="22" t="s">
-        <v>759</v>
-      </c>
-      <c r="E195" s="21" t="s">
-        <v>760</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="E195" s="21"/>
       <c r="F195" s="22" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="G195" s="20"/>
       <c r="H195" s="23"/>
@@ -13772,19 +13791,19 @@
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="21" t="s">
-        <v>768</v>
+        <v>781</v>
       </c>
       <c r="B196" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D196" s="22" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E196" s="21" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F196" s="22" t="s">
         <v>761</v>
@@ -13797,19 +13816,19 @@
     </row>
     <row r="197" spans="1:11">
       <c r="A197" s="21" t="s">
-        <v>771</v>
+        <v>784</v>
       </c>
       <c r="B197" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D197" s="22" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E197" s="21" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F197" s="22" t="s">
         <v>761</v>
@@ -13822,19 +13841,19 @@
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="21" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B198" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D198" s="22" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="F198" s="22" t="s">
         <v>761</v>
@@ -13847,22 +13866,22 @@
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="21" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="B199" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D199" s="22" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E199" s="21" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F199" s="22" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="G199" s="20"/>
       <c r="H199" s="23"/>
@@ -13872,19 +13891,19 @@
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="21" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="B200" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D200" s="22" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="E200" s="21" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F200" s="22" t="s">
         <v>774</v>
@@ -13897,19 +13916,19 @@
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="21" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="B201" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D201" s="22" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E201" s="21" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F201" s="22" t="s">
         <v>774</v>
@@ -13922,19 +13941,19 @@
     </row>
     <row r="202" spans="1:11">
       <c r="A202" s="21" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="B202" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E202" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F202" s="22" t="s">
         <v>774</v>
@@ -13947,18 +13966,20 @@
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="21" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="B203" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D203" s="22" t="s">
-        <v>785</v>
-      </c>
-      <c r="E203" s="21"/>
+        <v>782</v>
+      </c>
+      <c r="E203" s="21" t="s">
+        <v>783</v>
+      </c>
       <c r="F203" s="22" t="s">
         <v>774</v>
       </c>
@@ -13970,20 +13991,18 @@
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="21" t="s">
-        <v>792</v>
+        <v>805</v>
       </c>
       <c r="B204" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D204" s="22" t="s">
-        <v>787</v>
-      </c>
-      <c r="E204" s="21" t="s">
-        <v>788</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="E204" s="21"/>
       <c r="F204" s="22" t="s">
         <v>774</v>
       </c>
@@ -13995,19 +14014,19 @@
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="21" t="s">
-        <v>795</v>
+        <v>808</v>
       </c>
       <c r="B205" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E205" s="21" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="F205" s="22" t="s">
         <v>774</v>
@@ -14020,19 +14039,19 @@
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="21" t="s">
-        <v>798</v>
+        <v>811</v>
       </c>
       <c r="B206" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E206" s="21" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F206" s="22" t="s">
         <v>774</v>
@@ -14045,19 +14064,19 @@
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="21" t="s">
-        <v>801</v>
+        <v>814</v>
       </c>
       <c r="B207" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D207" s="22" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E207" s="21" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F207" s="22" t="s">
         <v>774</v>
@@ -14070,19 +14089,19 @@
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="21" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="B208" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D208" s="22" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="F208" s="22" t="s">
         <v>774</v>
@@ -14095,22 +14114,22 @@
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="21" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="B209" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F209" s="22" t="s">
-        <v>804</v>
+        <v>774</v>
       </c>
       <c r="G209" s="20"/>
       <c r="H209" s="23"/>
@@ -14120,19 +14139,19 @@
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="21" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="B210" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F210" s="22" t="s">
         <v>804</v>
@@ -14145,19 +14164,19 @@
     </row>
     <row r="211" spans="1:11">
       <c r="A211" s="21" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="B211" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E211" s="21" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="F211" s="22" t="s">
         <v>804</v>
@@ -14170,19 +14189,19 @@
     </row>
     <row r="212" spans="1:11">
       <c r="A212" s="21" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="B212" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D212" s="22" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F212" s="22" t="s">
         <v>804</v>
@@ -14195,19 +14214,19 @@
     </row>
     <row r="213" spans="1:11">
       <c r="A213" s="21" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="B213" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D213" s="22" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E213" s="21" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F213" s="22" t="s">
         <v>804</v>
@@ -14220,19 +14239,19 @@
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="21" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="B214" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E214" s="21" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="F214" s="22" t="s">
         <v>804</v>
@@ -14245,44 +14264,44 @@
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="21" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="B215" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>1277</v>
+        <v>818</v>
       </c>
       <c r="E215" s="21" t="s">
-        <v>1278</v>
+        <v>819</v>
       </c>
       <c r="F215" s="22" t="s">
         <v>804</v>
       </c>
-      <c r="G215" s="35"/>
+      <c r="G215" s="20"/>
       <c r="H215" s="23"/>
       <c r="I215" s="23"/>
       <c r="J215" s="23"/>
-      <c r="K215" s="33"/>
+      <c r="K215" s="23"/>
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="21" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="B216" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D216" s="22" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E216" s="21" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="F216" s="22" t="s">
         <v>804</v>
@@ -14295,47 +14314,47 @@
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="B217" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>821</v>
+        <v>1279</v>
       </c>
       <c r="E217" s="21" t="s">
-        <v>822</v>
+        <v>1280</v>
       </c>
       <c r="F217" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="G217" s="20"/>
+        <v>804</v>
+      </c>
+      <c r="G217" s="35"/>
       <c r="H217" s="23"/>
       <c r="I217" s="23"/>
       <c r="J217" s="23"/>
-      <c r="K217" s="23"/>
+      <c r="K217" s="33"/>
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="21" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="B218" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F218" s="22" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="G218" s="20"/>
       <c r="H218" s="23"/>
@@ -14345,19 +14364,19 @@
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
-        <v>838</v>
+        <v>848</v>
       </c>
       <c r="B219" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F219" s="22" t="s">
         <v>696</v>
@@ -14370,22 +14389,22 @@
     </row>
     <row r="220" spans="1:11">
       <c r="A220" s="21" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="B220" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="F220" s="22" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="G220" s="20"/>
       <c r="H220" s="23"/>
@@ -14395,19 +14414,19 @@
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="21" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="B221" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F221" s="22" t="s">
         <v>709</v>
@@ -14420,22 +14439,22 @@
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="B222" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>1269</v>
+        <v>833</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F222" s="22" t="s">
-        <v>837</v>
+        <v>709</v>
       </c>
       <c r="G222" s="20"/>
       <c r="H222" s="23"/>
@@ -14445,19 +14464,19 @@
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
-        <v>848</v>
+        <v>858</v>
       </c>
       <c r="B223" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>839</v>
+        <v>1269</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="F223" s="22" t="s">
         <v>837</v>
@@ -14470,19 +14489,19 @@
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="B224" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F224" s="22" t="s">
         <v>837</v>
@@ -14495,19 +14514,19 @@
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="B225" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F225" s="22" t="s">
         <v>837</v>
@@ -14520,19 +14539,19 @@
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="B226" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>1270</v>
+        <v>845</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>1272</v>
+        <v>846</v>
       </c>
       <c r="F226" s="22" t="s">
         <v>837</v>
@@ -14545,19 +14564,19 @@
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="B227" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E227" s="21" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F227" s="22" t="s">
         <v>837</v>
@@ -14570,19 +14589,19 @@
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="21" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="B228" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>850</v>
+        <v>1271</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>851</v>
+        <v>1273</v>
       </c>
       <c r="F228" s="22" t="s">
         <v>837</v>
@@ -14595,19 +14614,19 @@
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="21" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
       <c r="B229" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="E229" s="21" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F229" s="22" t="s">
         <v>837</v>
@@ -14620,19 +14639,19 @@
     </row>
     <row r="230" spans="1:11">
       <c r="A230" s="21" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="B230" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="F230" s="22" t="s">
         <v>837</v>
@@ -14645,19 +14664,19 @@
     </row>
     <row r="231" spans="1:11">
       <c r="A231" s="21" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="B231" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F231" s="22" t="s">
         <v>837</v>
@@ -14670,19 +14689,19 @@
     </row>
     <row r="232" spans="1:11">
       <c r="A232" s="21" t="s">
-        <v>872</v>
+        <v>885</v>
       </c>
       <c r="B232" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="F232" s="22" t="s">
         <v>837</v>
@@ -14695,19 +14714,19 @@
     </row>
     <row r="233" spans="1:11">
       <c r="A233" s="21" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="B233" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F233" s="22" t="s">
         <v>837</v>
@@ -14720,19 +14739,19 @@
     </row>
     <row r="234" spans="1:11">
       <c r="A234" s="21" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="B234" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F234" s="22" t="s">
         <v>837</v>
@@ -14745,18 +14764,20 @@
     </row>
     <row r="235" spans="1:11">
       <c r="A235" s="21" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="B235" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>871</v>
-      </c>
-      <c r="E235" s="21"/>
+        <v>868</v>
+      </c>
+      <c r="E235" s="21" t="s">
+        <v>869</v>
+      </c>
       <c r="F235" s="22" t="s">
         <v>837</v>
       </c>
@@ -14768,22 +14789,20 @@
     </row>
     <row r="236" spans="1:11">
       <c r="A236" s="21" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="B236" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>873</v>
-      </c>
-      <c r="E236" s="21" t="s">
-        <v>874</v>
-      </c>
+        <v>871</v>
+      </c>
+      <c r="E236" s="21"/>
       <c r="F236" s="22" t="s">
-        <v>875</v>
+        <v>837</v>
       </c>
       <c r="G236" s="20"/>
       <c r="H236" s="23"/>
@@ -14793,19 +14812,19 @@
     </row>
     <row r="237" spans="1:11">
       <c r="A237" s="21" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E237" s="21" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F237" s="22" t="s">
         <v>875</v>
@@ -14818,19 +14837,19 @@
     </row>
     <row r="238" spans="1:11">
       <c r="A238" s="21" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="B238" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F238" s="22" t="s">
         <v>875</v>
@@ -14843,19 +14862,19 @@
     </row>
     <row r="239" spans="1:11">
       <c r="A239" s="21" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="B239" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="F239" s="22" t="s">
         <v>875</v>
@@ -14868,19 +14887,19 @@
     </row>
     <row r="240" spans="1:11">
       <c r="A240" s="21" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
       <c r="B240" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="F240" s="22" t="s">
         <v>875</v>
@@ -14893,19 +14912,19 @@
     </row>
     <row r="241" spans="1:11">
       <c r="A241" s="21" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="B241" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="F241" s="22" t="s">
         <v>875</v>
@@ -14918,19 +14937,19 @@
     </row>
     <row r="242" spans="1:11">
       <c r="A242" s="21" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="B242" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F242" s="22" t="s">
         <v>875</v>
@@ -14943,19 +14962,19 @@
     </row>
     <row r="243" spans="1:11">
       <c r="A243" s="21" t="s">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="B243" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="F243" s="22" t="s">
         <v>875</v>
@@ -14968,19 +14987,19 @@
     </row>
     <row r="244" spans="1:11">
       <c r="A244" s="21" t="s">
-        <v>909</v>
+        <v>922</v>
       </c>
       <c r="B244" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="F244" s="22" t="s">
         <v>875</v>
@@ -14993,19 +15012,19 @@
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="21" t="s">
-        <v>912</v>
+        <v>925</v>
       </c>
       <c r="B245" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="F245" s="22" t="s">
         <v>875</v>
@@ -15018,19 +15037,19 @@
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="21" t="s">
-        <v>915</v>
+        <v>928</v>
       </c>
       <c r="B246" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="F246" s="22" t="s">
         <v>875</v>
@@ -15043,19 +15062,19 @@
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="21" t="s">
-        <v>919</v>
+        <v>931</v>
       </c>
       <c r="B247" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="F247" s="22" t="s">
         <v>875</v>
@@ -15068,19 +15087,19 @@
     </row>
     <row r="248" spans="1:11">
       <c r="A248" s="21" t="s">
-        <v>922</v>
+        <v>934</v>
       </c>
       <c r="B248" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="F248" s="22" t="s">
         <v>875</v>
@@ -15093,19 +15112,19 @@
     </row>
     <row r="249" spans="1:11">
       <c r="A249" s="21" t="s">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="B249" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F249" s="22" t="s">
         <v>875</v>
@@ -15118,22 +15137,22 @@
     </row>
     <row r="250" spans="1:11">
       <c r="A250" s="21" t="s">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="B250" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="F250" s="22" t="s">
-        <v>918</v>
+        <v>875</v>
       </c>
       <c r="G250" s="20"/>
       <c r="H250" s="23"/>
@@ -15143,19 +15162,19 @@
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="21" t="s">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="B251" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="F251" s="22" t="s">
         <v>918</v>
@@ -15168,19 +15187,19 @@
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="21" t="s">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="B252" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="F252" s="22" t="s">
         <v>918</v>
@@ -15193,19 +15212,19 @@
     </row>
     <row r="253" spans="1:11">
       <c r="A253" s="21" t="s">
-        <v>937</v>
+        <v>950</v>
       </c>
       <c r="B253" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="F253" s="22" t="s">
         <v>918</v>
@@ -15218,19 +15237,19 @@
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="21" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="B254" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="F254" s="22" t="s">
         <v>918</v>
@@ -15243,19 +15262,19 @@
     </row>
     <row r="255" spans="1:11">
       <c r="A255" s="21" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="B255" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F255" s="22" t="s">
         <v>918</v>
@@ -15268,19 +15287,19 @@
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="21" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
       <c r="B256" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="F256" s="22" t="s">
         <v>918</v>
@@ -15293,22 +15312,22 @@
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="21" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="B257" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="F257" s="22" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="G257" s="20"/>
       <c r="H257" s="23"/>
@@ -15318,19 +15337,19 @@
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="21" t="s">
-        <v>952</v>
+        <v>964</v>
       </c>
       <c r="B258" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="F258" s="22" t="s">
         <v>940</v>
@@ -15343,19 +15362,19 @@
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="21" t="s">
-        <v>955</v>
+        <v>967</v>
       </c>
       <c r="B259" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="F259" s="22" t="s">
         <v>940</v>
@@ -15368,19 +15387,19 @@
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="21" t="s">
-        <v>958</v>
+        <v>970</v>
       </c>
       <c r="B260" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="F260" s="22" t="s">
         <v>940</v>
@@ -15393,19 +15412,19 @@
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="21" t="s">
-        <v>961</v>
+        <v>973</v>
       </c>
       <c r="B261" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>929</v>
+        <v>948</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F261" s="22" t="s">
         <v>940</v>
@@ -15418,19 +15437,19 @@
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="21" t="s">
-        <v>964</v>
+        <v>976</v>
       </c>
       <c r="B262" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="F262" s="22" t="s">
         <v>940</v>
@@ -15443,19 +15462,19 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="21" t="s">
-        <v>967</v>
+        <v>979</v>
       </c>
       <c r="B263" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="F263" s="22" t="s">
         <v>940</v>
@@ -15468,19 +15487,19 @@
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="21" t="s">
-        <v>970</v>
+        <v>983</v>
       </c>
       <c r="B264" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F264" s="22" t="s">
         <v>940</v>
@@ -15493,19 +15512,19 @@
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="21" t="s">
-        <v>973</v>
+        <v>986</v>
       </c>
       <c r="B265" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F265" s="22" t="s">
         <v>940</v>
@@ -15518,19 +15537,19 @@
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="21" t="s">
-        <v>976</v>
+        <v>989</v>
       </c>
       <c r="B266" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="F266" s="22" t="s">
         <v>940</v>
@@ -15543,19 +15562,19 @@
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="21" t="s">
-        <v>979</v>
+        <v>992</v>
       </c>
       <c r="B267" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F267" s="22" t="s">
         <v>940</v>
@@ -15568,19 +15587,19 @@
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="21" t="s">
-        <v>983</v>
+        <v>995</v>
       </c>
       <c r="B268" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F268" s="22" t="s">
         <v>940</v>
@@ -15593,19 +15612,19 @@
     </row>
     <row r="269" spans="1:11">
       <c r="A269" s="21" t="s">
-        <v>986</v>
+        <v>998</v>
       </c>
       <c r="B269" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="F269" s="22" t="s">
         <v>940</v>
@@ -15618,19 +15637,19 @@
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="21" t="s">
-        <v>989</v>
+        <v>1001</v>
       </c>
       <c r="B270" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F270" s="22" t="s">
         <v>940</v>
@@ -15643,22 +15662,22 @@
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="21" t="s">
-        <v>992</v>
+        <v>1005</v>
       </c>
       <c r="B271" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="F271" s="22" t="s">
-        <v>982</v>
+        <v>940</v>
       </c>
       <c r="G271" s="20"/>
       <c r="H271" s="23"/>
@@ -15668,19 +15687,19 @@
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="21" t="s">
-        <v>995</v>
+        <v>1008</v>
       </c>
       <c r="B272" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="F272" s="22" t="s">
         <v>982</v>
@@ -15693,19 +15712,19 @@
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="21" t="s">
-        <v>998</v>
+        <v>1012</v>
       </c>
       <c r="B273" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="F273" s="22" t="s">
         <v>982</v>
@@ -15718,19 +15737,19 @@
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="21" t="s">
-        <v>1001</v>
+        <v>1015</v>
       </c>
       <c r="B274" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="F274" s="22" t="s">
         <v>982</v>
@@ -15743,19 +15762,19 @@
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="21" t="s">
-        <v>1005</v>
+        <v>1018</v>
       </c>
       <c r="B275" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F275" s="22" t="s">
         <v>982</v>
@@ -15768,19 +15787,19 @@
     </row>
     <row r="276" spans="1:11">
       <c r="A276" s="21" t="s">
-        <v>1008</v>
+        <v>1021</v>
       </c>
       <c r="B276" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="F276" s="22" t="s">
         <v>982</v>
@@ -15793,19 +15812,19 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="21" t="s">
-        <v>1012</v>
+        <v>1025</v>
       </c>
       <c r="B277" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="F277" s="22" t="s">
         <v>982</v>
@@ -15818,22 +15837,22 @@
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="21" t="s">
-        <v>1015</v>
+        <v>1029</v>
       </c>
       <c r="B278" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="G278" s="20"/>
       <c r="H278" s="23"/>
@@ -15843,19 +15862,19 @@
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="21" t="s">
-        <v>1018</v>
+        <v>1032</v>
       </c>
       <c r="B279" s="21" t="s">
         <v>130</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F279" s="22" t="s">
         <v>1004</v>
@@ -15868,22 +15887,22 @@
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="21" t="s">
-        <v>1021</v>
+        <v>1035</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="G280" s="20"/>
       <c r="H280" s="23"/>
@@ -15893,19 +15912,19 @@
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="21" t="s">
-        <v>1025</v>
+        <v>1038</v>
       </c>
       <c r="B281" s="21" t="s">
         <v>132</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F281" s="22" t="s">
         <v>1011</v>
@@ -15918,19 +15937,19 @@
     </row>
     <row r="282" spans="1:11">
       <c r="A282" s="21" t="s">
-        <v>1029</v>
+        <v>1041</v>
       </c>
       <c r="B282" s="21" t="s">
         <v>132</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="F282" s="22" t="s">
         <v>1011</v>
@@ -15943,19 +15962,19 @@
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="21" t="s">
-        <v>1032</v>
+        <v>1045</v>
       </c>
       <c r="B283" s="21" t="s">
         <v>132</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="F283" s="22" t="s">
         <v>1011</v>
@@ -15968,22 +15987,22 @@
     </row>
     <row r="284" spans="1:11">
       <c r="A284" s="21" t="s">
-        <v>1035</v>
+        <v>1048</v>
       </c>
       <c r="B284" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="F284" s="22" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="G284" s="20"/>
       <c r="H284" s="23"/>
@@ -15993,22 +16012,22 @@
     </row>
     <row r="285" spans="1:11">
       <c r="A285" s="21" t="s">
-        <v>1038</v>
+        <v>1051</v>
       </c>
       <c r="B285" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C285" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G285" s="20"/>
       <c r="H285" s="23"/>
@@ -16018,19 +16037,19 @@
     </row>
     <row r="286" spans="1:11">
       <c r="A286" s="21" t="s">
-        <v>1041</v>
+        <v>1054</v>
       </c>
       <c r="B286" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C286" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="F286" s="22" t="s">
         <v>1028</v>
@@ -16043,19 +16062,19 @@
     </row>
     <row r="287" spans="1:11">
       <c r="A287" s="21" t="s">
-        <v>1045</v>
+        <v>1058</v>
       </c>
       <c r="B287" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F287" s="22" t="s">
         <v>1028</v>
@@ -16068,19 +16087,19 @@
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="21" t="s">
-        <v>1048</v>
+        <v>1061</v>
       </c>
       <c r="B288" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F288" s="22" t="s">
         <v>1028</v>
@@ -16093,19 +16112,19 @@
     </row>
     <row r="289" spans="1:11">
       <c r="A289" s="21" t="s">
-        <v>1051</v>
+        <v>1064</v>
       </c>
       <c r="B289" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="F289" s="22" t="s">
         <v>1028</v>
@@ -16118,22 +16137,22 @@
     </row>
     <row r="290" spans="1:11">
       <c r="A290" s="21" t="s">
-        <v>1054</v>
+        <v>1067</v>
       </c>
       <c r="B290" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="F290" s="22" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="G290" s="20"/>
       <c r="H290" s="23"/>
@@ -16143,19 +16162,19 @@
     </row>
     <row r="291" spans="1:11">
       <c r="A291" s="21" t="s">
-        <v>1058</v>
+        <v>1070</v>
       </c>
       <c r="B291" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F291" s="22" t="s">
         <v>1044</v>
@@ -16168,19 +16187,19 @@
     </row>
     <row r="292" spans="1:11">
       <c r="A292" s="21" t="s">
-        <v>1061</v>
+        <v>1073</v>
       </c>
       <c r="B292" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F292" s="22" t="s">
         <v>1044</v>
@@ -16193,19 +16212,19 @@
     </row>
     <row r="293" spans="1:11">
       <c r="A293" s="21" t="s">
-        <v>1064</v>
+        <v>1076</v>
       </c>
       <c r="B293" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="F293" s="22" t="s">
         <v>1044</v>
@@ -16218,22 +16237,22 @@
     </row>
     <row r="294" spans="1:11">
       <c r="A294" s="21" t="s">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="B294" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F294" s="22" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="G294" s="20"/>
       <c r="H294" s="23"/>
@@ -16243,19 +16262,19 @@
     </row>
     <row r="295" spans="1:11">
       <c r="A295" s="21" t="s">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="B295" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="F295" s="22" t="s">
         <v>1057</v>
@@ -16268,19 +16287,19 @@
     </row>
     <row r="296" spans="1:11">
       <c r="A296" s="21" t="s">
-        <v>1073</v>
+        <v>1085</v>
       </c>
       <c r="B296" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F296" s="22" t="s">
         <v>1057</v>
@@ -16293,19 +16312,19 @@
     </row>
     <row r="297" spans="1:11">
       <c r="A297" s="21" t="s">
-        <v>1076</v>
+        <v>1088</v>
       </c>
       <c r="B297" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F297" s="22" t="s">
         <v>1057</v>
@@ -16318,19 +16337,19 @@
     </row>
     <row r="298" spans="1:11">
       <c r="A298" s="21" t="s">
-        <v>1079</v>
+        <v>1092</v>
       </c>
       <c r="B298" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F298" s="22" t="s">
         <v>1057</v>
@@ -16343,19 +16362,19 @@
     </row>
     <row r="299" spans="1:11">
       <c r="A299" s="21" t="s">
-        <v>1082</v>
+        <v>1096</v>
       </c>
       <c r="B299" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F299" s="22" t="s">
         <v>1057</v>
@@ -16368,19 +16387,19 @@
     </row>
     <row r="300" spans="1:11">
       <c r="A300" s="21" t="s">
-        <v>1085</v>
+        <v>1099</v>
       </c>
       <c r="B300" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F300" s="22" t="s">
         <v>1057</v>
@@ -16393,19 +16412,19 @@
     </row>
     <row r="301" spans="1:11">
       <c r="A301" s="21" t="s">
-        <v>1088</v>
+        <v>1102</v>
       </c>
       <c r="B301" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="F301" s="22" t="s">
         <v>1057</v>
@@ -16418,19 +16437,19 @@
     </row>
     <row r="302" spans="1:11">
       <c r="A302" s="21" t="s">
-        <v>1092</v>
+        <v>1106</v>
       </c>
       <c r="B302" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F302" s="22" t="s">
         <v>1057</v>
@@ -16443,19 +16462,19 @@
     </row>
     <row r="303" spans="1:11">
       <c r="A303" s="21" t="s">
-        <v>1096</v>
+        <v>1109</v>
       </c>
       <c r="B303" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F303" s="22" t="s">
         <v>1057</v>
@@ -16468,19 +16487,19 @@
     </row>
     <row r="304" spans="1:11">
       <c r="A304" s="21" t="s">
-        <v>1099</v>
+        <v>1112</v>
       </c>
       <c r="B304" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="F304" s="22" t="s">
         <v>1057</v>
@@ -16493,22 +16512,22 @@
     </row>
     <row r="305" spans="1:11">
       <c r="A305" s="21" t="s">
-        <v>1102</v>
+        <v>1116</v>
       </c>
       <c r="B305" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>1091</v>
+        <v>1057</v>
       </c>
       <c r="G305" s="20"/>
       <c r="H305" s="23"/>
@@ -16518,22 +16537,22 @@
     </row>
     <row r="306" spans="1:11">
       <c r="A306" s="21" t="s">
-        <v>1106</v>
+        <v>1119</v>
       </c>
       <c r="B306" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C306" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G306" s="20"/>
       <c r="H306" s="23"/>
@@ -16543,19 +16562,19 @@
     </row>
     <row r="307" spans="1:11">
       <c r="A307" s="21" t="s">
-        <v>1109</v>
+        <v>1122</v>
       </c>
       <c r="B307" s="21" t="s">
         <v>146</v>
       </c>
       <c r="C307" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="F307" s="22" t="s">
         <v>1095</v>
@@ -16568,19 +16587,19 @@
     </row>
     <row r="308" spans="1:11">
       <c r="A308" s="21" t="s">
-        <v>1112</v>
+        <v>1123</v>
       </c>
       <c r="B308" s="21" t="s">
         <v>146</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="F308" s="22" t="s">
         <v>1095</v>
@@ -16593,22 +16612,22 @@
     </row>
     <row r="309" spans="1:11">
       <c r="A309" s="21" t="s">
-        <v>1116</v>
+        <v>1126</v>
       </c>
       <c r="B309" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="F309" s="22" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="G309" s="20"/>
       <c r="H309" s="23"/>
@@ -16618,19 +16637,19 @@
     </row>
     <row r="310" spans="1:11">
       <c r="A310" s="21" t="s">
-        <v>1119</v>
+        <v>1129</v>
       </c>
       <c r="B310" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="F310" s="22" t="s">
         <v>1105</v>
@@ -16643,19 +16662,19 @@
     </row>
     <row r="311" spans="1:11">
       <c r="A311" s="21" t="s">
-        <v>1122</v>
+        <v>1133</v>
       </c>
       <c r="B311" s="21" t="s">
         <v>147</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="F311" s="22" t="s">
         <v>1105</v>
@@ -16668,22 +16687,22 @@
     </row>
     <row r="312" spans="1:11">
       <c r="A312" s="21" t="s">
-        <v>1123</v>
+        <v>1136</v>
       </c>
       <c r="B312" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C312" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="G312" s="20"/>
       <c r="H312" s="23"/>
@@ -16693,19 +16712,19 @@
     </row>
     <row r="313" spans="1:11">
       <c r="A313" s="21" t="s">
-        <v>1126</v>
+        <v>1140</v>
       </c>
       <c r="B313" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C313" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="F313" s="22" t="s">
         <v>1115</v>
@@ -16718,19 +16737,19 @@
     </row>
     <row r="314" spans="1:11">
       <c r="A314" s="21" t="s">
-        <v>1129</v>
+        <v>1143</v>
       </c>
       <c r="B314" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C314" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="F314" s="22" t="s">
         <v>1115</v>
@@ -16743,19 +16762,19 @@
     </row>
     <row r="315" spans="1:11">
       <c r="A315" s="21" t="s">
-        <v>1133</v>
+        <v>1147</v>
       </c>
       <c r="B315" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C315" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="F315" s="22" t="s">
         <v>1115</v>
@@ -16768,19 +16787,19 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="21" t="s">
-        <v>1136</v>
+        <v>1150</v>
       </c>
       <c r="B316" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1124</v>
+        <v>1113</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1125</v>
+        <v>1114</v>
       </c>
       <c r="F316" s="22" t="s">
         <v>1115</v>
@@ -16793,19 +16812,19 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="21" t="s">
-        <v>1140</v>
+        <v>1153</v>
       </c>
       <c r="B317" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D317" s="22" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="E317" s="21" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="F317" s="22" t="s">
         <v>1115</v>
@@ -16818,22 +16837,22 @@
     </row>
     <row r="318" spans="1:11">
       <c r="A318" s="21" t="s">
-        <v>1143</v>
+        <v>1156</v>
       </c>
       <c r="B318" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="F318" s="22" t="s">
-        <v>1132</v>
+        <v>1115</v>
       </c>
       <c r="G318" s="20"/>
       <c r="H318" s="23"/>
@@ -16843,19 +16862,19 @@
     </row>
     <row r="319" spans="1:11">
       <c r="A319" s="21" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="B319" s="21" t="s">
         <v>150</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="F319" s="22" t="s">
         <v>1132</v>
@@ -16868,22 +16887,22 @@
     </row>
     <row r="320" spans="1:11">
       <c r="A320" s="21" t="s">
-        <v>1150</v>
+        <v>1162</v>
       </c>
       <c r="B320" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="F320" s="22" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G320" s="20"/>
       <c r="H320" s="23"/>
@@ -16893,19 +16912,19 @@
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="21" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="B321" s="21" t="s">
         <v>153</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="F321" s="22" t="s">
         <v>1139</v>
@@ -16918,22 +16937,22 @@
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="21" t="s">
-        <v>1156</v>
+        <v>1168</v>
       </c>
       <c r="B322" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="F322" s="22" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="G322" s="20"/>
       <c r="H322" s="23"/>
@@ -16943,19 +16962,19 @@
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="21" t="s">
-        <v>1159</v>
+        <v>1171</v>
       </c>
       <c r="B323" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="F323" s="22" t="s">
         <v>1146</v>
@@ -16968,19 +16987,19 @@
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="21" t="s">
-        <v>1162</v>
+        <v>1174</v>
       </c>
       <c r="B324" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="F324" s="22" t="s">
         <v>1146</v>
@@ -16993,19 +17012,19 @@
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="21" t="s">
-        <v>1165</v>
+        <v>1177</v>
       </c>
       <c r="B325" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="F325" s="22" t="s">
         <v>1146</v>
@@ -17018,19 +17037,19 @@
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="21" t="s">
-        <v>1168</v>
+        <v>1180</v>
       </c>
       <c r="B326" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F326" s="22" t="s">
         <v>1146</v>
@@ -17043,19 +17062,19 @@
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="21" t="s">
-        <v>1171</v>
+        <v>1183</v>
       </c>
       <c r="B327" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="F327" s="22" t="s">
         <v>1146</v>
@@ -17068,19 +17087,19 @@
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="21" t="s">
-        <v>1174</v>
+        <v>1186</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="F328" s="22" t="s">
         <v>1146</v>
@@ -17093,19 +17112,19 @@
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="21" t="s">
-        <v>1177</v>
+        <v>1189</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="F329" s="22" t="s">
         <v>1146</v>
@@ -17118,19 +17137,19 @@
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="21" t="s">
-        <v>1180</v>
+        <v>1192</v>
       </c>
       <c r="B330" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="F330" s="22" t="s">
         <v>1146</v>
@@ -17143,19 +17162,19 @@
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="21" t="s">
-        <v>1183</v>
+        <v>1195</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="F331" s="22" t="s">
         <v>1146</v>
@@ -17168,19 +17187,19 @@
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="21" t="s">
-        <v>1186</v>
+        <v>1197</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="F332" s="22" t="s">
         <v>1146</v>
@@ -17193,19 +17212,19 @@
     </row>
     <row r="333" spans="1:11">
       <c r="A333" s="21" t="s">
-        <v>1189</v>
+        <v>1200</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="F333" s="22" t="s">
         <v>1146</v>
@@ -17218,19 +17237,19 @@
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="21" t="s">
-        <v>1192</v>
+        <v>1203</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="F334" s="22" t="s">
         <v>1146</v>
@@ -17243,19 +17262,19 @@
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="21" t="s">
-        <v>1195</v>
+        <v>1206</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F335" s="22" t="s">
         <v>1146</v>
@@ -17268,19 +17287,19 @@
     </row>
     <row r="336" spans="1:11">
       <c r="A336" s="21" t="s">
-        <v>1197</v>
+        <v>1209</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="F336" s="22" t="s">
         <v>1146</v>
@@ -17293,19 +17312,19 @@
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="21" t="s">
-        <v>1200</v>
+        <v>1212</v>
       </c>
       <c r="B337" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="F337" s="22" t="s">
         <v>1146</v>
@@ -17318,19 +17337,19 @@
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="21" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="B338" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="F338" s="22" t="s">
         <v>1146</v>
@@ -17343,19 +17362,19 @@
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="21" t="s">
-        <v>1206</v>
+        <v>1218</v>
       </c>
       <c r="B339" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>188</v>
+        <v>1194</v>
       </c>
       <c r="F339" s="22" t="s">
         <v>1146</v>
@@ -17368,19 +17387,19 @@
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="21" t="s">
-        <v>1209</v>
+        <v>1221</v>
       </c>
       <c r="B340" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>1199</v>
+        <v>188</v>
       </c>
       <c r="F340" s="22" t="s">
         <v>1146</v>
@@ -17393,19 +17412,19 @@
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="21" t="s">
-        <v>1212</v>
+        <v>1224</v>
       </c>
       <c r="B341" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="F341" s="22" t="s">
         <v>1146</v>
@@ -17418,19 +17437,19 @@
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="21" t="s">
-        <v>1215</v>
+        <v>1227</v>
       </c>
       <c r="B342" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F342" s="22" t="s">
         <v>1146</v>
@@ -17443,22 +17462,22 @@
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="21" t="s">
-        <v>1218</v>
+        <v>1230</v>
       </c>
       <c r="B343" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1161</v>
+        <v>1205</v>
       </c>
       <c r="F343" s="22" t="s">
-        <v>1208</v>
+        <v>1146</v>
       </c>
       <c r="G343" s="20"/>
       <c r="H343" s="23"/>
@@ -17468,19 +17487,19 @@
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="21" t="s">
-        <v>1221</v>
+        <v>1233</v>
       </c>
       <c r="B344" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1211</v>
+        <v>1161</v>
       </c>
       <c r="F344" s="22" t="s">
         <v>1208</v>
@@ -17493,19 +17512,19 @@
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="21" t="s">
-        <v>1224</v>
+        <v>1236</v>
       </c>
       <c r="B345" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="F345" s="22" t="s">
         <v>1208</v>
@@ -17518,19 +17537,19 @@
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="21" t="s">
-        <v>1227</v>
+        <v>1239</v>
       </c>
       <c r="B346" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="F346" s="22" t="s">
         <v>1208</v>
@@ -17543,19 +17562,19 @@
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="21" t="s">
-        <v>1230</v>
+        <v>1242</v>
       </c>
       <c r="B347" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F347" s="22" t="s">
         <v>1208</v>
@@ -17568,19 +17587,19 @@
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="21" t="s">
-        <v>1233</v>
+        <v>1245</v>
       </c>
       <c r="B348" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F348" s="22" t="s">
         <v>1208</v>
@@ -17593,19 +17612,19 @@
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="21" t="s">
-        <v>1236</v>
+        <v>1248</v>
       </c>
       <c r="B349" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F349" s="22" t="s">
         <v>1208</v>
@@ -17618,19 +17637,19 @@
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="21" t="s">
-        <v>1239</v>
+        <v>1251</v>
       </c>
       <c r="B350" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="F350" s="22" t="s">
         <v>1208</v>
@@ -17643,19 +17662,19 @@
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="21" t="s">
-        <v>1242</v>
+        <v>1254</v>
       </c>
       <c r="B351" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="F351" s="22" t="s">
         <v>1208</v>
@@ -17668,19 +17687,19 @@
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="21" t="s">
-        <v>1245</v>
+        <v>1281</v>
       </c>
       <c r="B352" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D352" s="22" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="E352" s="21" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F352" s="22" t="s">
         <v>1208</v>
@@ -17693,19 +17712,19 @@
     </row>
     <row r="353" spans="1:11">
       <c r="A353" s="21" t="s">
-        <v>1248</v>
+        <v>1282</v>
       </c>
       <c r="B353" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C353" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D353" s="22" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="E353" s="21" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F353" s="22" t="s">
         <v>1208</v>
@@ -17718,19 +17737,19 @@
     </row>
     <row r="354" spans="1:11">
       <c r="A354" s="21" t="s">
-        <v>1251</v>
+        <v>1286</v>
       </c>
       <c r="B354" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C354" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D354" s="22" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="E354" s="21" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F354" s="22" t="s">
         <v>1208</v>
@@ -17743,22 +17762,22 @@
     </row>
     <row r="355" spans="1:11">
       <c r="A355" s="21" t="s">
-        <v>1254</v>
+        <v>1288</v>
       </c>
       <c r="B355" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="D355" s="22" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="E355" s="21" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="F355" s="22" t="s">
-        <v>875</v>
+        <v>1208</v>
       </c>
       <c r="G355" s="20"/>
       <c r="H355" s="23"/>
@@ -17768,19 +17787,19 @@
     </row>
     <row r="356" spans="1:11">
       <c r="A356" s="21" t="s">
-        <v>1281</v>
+        <v>1300</v>
       </c>
       <c r="B356" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D356" s="22" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="E356" s="21" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="F356" s="22" t="s">
         <v>875</v>
@@ -17793,19 +17812,19 @@
     </row>
     <row r="357" spans="1:11">
       <c r="A357" s="21" t="s">
-        <v>1282</v>
+        <v>1301</v>
       </c>
       <c r="B357" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D357" s="22" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E357" s="21" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="F357" s="22" t="s">
         <v>875</v>
@@ -17818,19 +17837,19 @@
     </row>
     <row r="358" spans="1:11">
       <c r="A358" s="21" t="s">
-        <v>1288</v>
+        <v>1302</v>
       </c>
       <c r="B358" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D358" s="22" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="E358" s="21" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="F358" s="22" t="s">
         <v>875</v>
@@ -17843,19 +17862,19 @@
     </row>
     <row r="359" spans="1:11">
       <c r="A359" s="21" t="s">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="B359" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C359" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D359" s="22" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="E359" s="21" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="F359" s="22" t="s">
         <v>875</v>
@@ -17867,12 +17886,24 @@
       <c r="K359" s="23"/>
     </row>
     <row r="360" spans="1:11">
-      <c r="A360" s="21"/>
-      <c r="B360" s="21"/>
-      <c r="C360" s="21"/>
-      <c r="D360" s="22"/>
-      <c r="E360" s="21"/>
-      <c r="F360" s="22"/>
+      <c r="A360" s="21" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B360" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="C360" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D360" s="22" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E360" s="21" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F360" s="22" t="s">
+        <v>875</v>
+      </c>
       <c r="G360" s="20"/>
       <c r="H360" s="23"/>
       <c r="I360" s="23"/>
@@ -17880,69 +17911,179 @@
       <c r="K360" s="23"/>
     </row>
     <row r="361" spans="1:11">
-      <c r="A361" s="21"/>
-      <c r="B361" s="21"/>
-      <c r="C361" s="21"/>
-      <c r="D361" s="22"/>
-      <c r="E361" s="21"/>
-      <c r="F361" s="22"/>
-      <c r="G361" s="20"/>
-      <c r="H361" s="23"/>
-      <c r="I361" s="23"/>
-      <c r="J361" s="23"/>
-      <c r="K361" s="23"/>
+      <c r="A361" s="21" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B361" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C361" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D361" s="22" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E361" s="21" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F361" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G361" s="20">
+        <v>4500</v>
+      </c>
+      <c r="H361" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I361" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J361" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K361" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="362" spans="1:11">
-      <c r="A362" s="21"/>
-      <c r="B362" s="21"/>
-      <c r="C362" s="21"/>
-      <c r="D362" s="22"/>
-      <c r="E362" s="21"/>
-      <c r="F362" s="22"/>
-      <c r="G362" s="20"/>
-      <c r="H362" s="23"/>
-      <c r="I362" s="23"/>
-      <c r="J362" s="23"/>
-      <c r="K362" s="23"/>
+      <c r="A362" s="21" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B362" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C362" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D362" s="22" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E362" s="21" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F362" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G362" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H362" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I362" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J362" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K362" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="363" spans="1:11">
-      <c r="A363" s="21"/>
-      <c r="B363" s="21"/>
-      <c r="C363" s="21"/>
-      <c r="D363" s="22"/>
-      <c r="E363" s="21"/>
-      <c r="F363" s="22"/>
-      <c r="G363" s="20"/>
-      <c r="H363" s="23"/>
-      <c r="I363" s="23"/>
-      <c r="J363" s="23"/>
-      <c r="K363" s="23"/>
+      <c r="A363" s="21" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B363" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C363" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D363" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E363" s="21" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F363" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G363" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H363" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I363" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J363" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K363" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="364" spans="1:11">
-      <c r="A364" s="21"/>
-      <c r="B364" s="21"/>
-      <c r="C364" s="21"/>
-      <c r="D364" s="22"/>
-      <c r="E364" s="21"/>
-      <c r="F364" s="22"/>
-      <c r="G364" s="20"/>
-      <c r="H364" s="23"/>
-      <c r="I364" s="23"/>
-      <c r="J364" s="23"/>
-      <c r="K364" s="23"/>
+      <c r="A364" s="21" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B364" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C364" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D364" s="22" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E364" s="21" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F364" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G364" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H364" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I364" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J364" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K364" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="365" spans="1:11">
-      <c r="A365" s="21"/>
-      <c r="B365" s="21"/>
-      <c r="C365" s="21"/>
-      <c r="D365" s="22"/>
-      <c r="E365" s="21"/>
-      <c r="F365" s="22"/>
-      <c r="G365" s="20"/>
-      <c r="H365" s="23"/>
-      <c r="I365" s="23"/>
-      <c r="J365" s="23"/>
-      <c r="K365" s="23"/>
+      <c r="A365" s="21" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B365" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C365" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D365" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E365" s="21" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F365" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G365" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H365" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I365" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J365" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K365" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="366" spans="1:11">
       <c r="A366" s="21"/>
@@ -18588,7 +18729,7 @@
       <c r="D415" s="22"/>
       <c r="E415" s="21"/>
       <c r="F415" s="22"/>
-      <c r="G415" s="18"/>
+      <c r="G415" s="20"/>
       <c r="H415" s="23"/>
       <c r="I415" s="23"/>
       <c r="J415" s="23"/>
@@ -39288,7 +39429,7 @@
       <c r="H2007" s="23"/>
       <c r="I2007" s="23"/>
       <c r="J2007" s="23"/>
-      <c r="K2007" s="33"/>
+      <c r="K2007" s="23"/>
     </row>
     <row r="2008" spans="1:11">
       <c r="A2008" s="21"/>
@@ -39303,15 +39444,28 @@
       <c r="J2008" s="23"/>
       <c r="K2008" s="33"/>
     </row>
+    <row r="2009" spans="1:11">
+      <c r="A2009" s="21"/>
+      <c r="B2009" s="21"/>
+      <c r="C2009" s="21"/>
+      <c r="D2009" s="22"/>
+      <c r="E2009" s="21"/>
+      <c r="F2009" s="22"/>
+      <c r="G2009" s="18"/>
+      <c r="H2009" s="23"/>
+      <c r="I2009" s="23"/>
+      <c r="J2009" s="23"/>
+      <c r="K2009" s="33"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2004:A2008">
+  <conditionalFormatting sqref="A2005:A2009">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A2003">
+  <conditionalFormatting sqref="A4:A2004">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -39341,27 +39495,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="50" t="s">
         <v>1257</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="44" t="s">
         <v>1258</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46062980-C33F-44A2-AF4F-C191BFE649C3}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D70E60-EC68-4E08-81C4-B8691B728FC5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2575" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1324">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -3989,6 +3989,15 @@
   </si>
   <si>
     <t>Weekly 12W Asset</t>
+  </si>
+  <si>
+    <t>Awokoya Busayo</t>
+  </si>
+  <si>
+    <t>08070658141</t>
+  </si>
+  <si>
+    <t>MEM-363</t>
   </si>
 </sst>
 </file>
@@ -4188,7 +4197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4298,31 +4307,32 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4801,7 +4811,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2009" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2010" dataDxfId="14">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="12"/>
@@ -4978,28 +4988,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -5019,13 +5029,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -5036,10 +5046,10 @@
       <c r="D5" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
     </row>
     <row r="6" spans="1:8" ht="27.9" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -5050,10 +5060,10 @@
       <c r="D6" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="43"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="46"/>
     </row>
     <row r="7" spans="1:8" ht="27.9" customHeight="1">
       <c r="A7" s="3" t="s">
@@ -5064,10 +5074,10 @@
       <c r="D7" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="46"/>
     </row>
     <row r="8" spans="1:8" ht="27.9" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -5078,10 +5088,10 @@
       <c r="D8" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="46"/>
     </row>
     <row r="9" spans="1:8" ht="27.9" customHeight="1">
       <c r="A9" s="3" t="s">
@@ -5092,10 +5102,10 @@
       <c r="D9" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="43"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="46"/>
     </row>
     <row r="10" spans="1:8" ht="27.9" customHeight="1">
       <c r="A10" s="2"/>
@@ -5104,10 +5114,10 @@
       <c r="D10" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="46"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="2"/>
@@ -5120,142 +5130,142 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="45"/>
-      <c r="C12" s="45"/>
-      <c r="D12" s="45"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
+      <c r="B12" s="43"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="43"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="43"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="52" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="43"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="43"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+      <c r="H14" s="46"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="43"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="46"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="43"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+      <c r="H16" s="46"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="43"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="46"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="42"/>
-      <c r="H18" s="43"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+      <c r="H18" s="46"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="43"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="46"/>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="43"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="46"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="46"/>
     </row>
   </sheetData>
   <autoFilter ref="A12:H21" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -5268,13 +5278,6 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:H4"/>
@@ -5287,6 +5290,13 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B15:H15"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5309,30 +5319,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -8853,7 +8863,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2009"/>
+  <dimension ref="A1:K2010"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22.09765625" style="27" customWidth="1"/>
@@ -8865,34 +8875,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54"/>
-      <c r="K1" s="54"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="53" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+      <c r="J2" s="54"/>
+      <c r="K2" s="54"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -13497,30 +13507,34 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="184" spans="1:11">
+    <row r="184" spans="1:11" s="41" customFormat="1">
       <c r="A184" s="21" t="s">
         <v>747</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C184" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D184" s="22" t="s">
-        <v>726</v>
-      </c>
-      <c r="E184" s="21" t="s">
-        <v>727</v>
+        <v>92</v>
+      </c>
+      <c r="C184" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="D184" s="40" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E184" s="39" t="s">
+        <v>1322</v>
       </c>
       <c r="F184" s="22" t="s">
-        <v>728</v>
-      </c>
-      <c r="G184" s="20"/>
-      <c r="H184" s="23"/>
-      <c r="I184" s="23"/>
-      <c r="J184" s="23"/>
-      <c r="K184" s="23"/>
+        <v>696</v>
+      </c>
+      <c r="G184" s="35">
+        <v>11000</v>
+      </c>
+      <c r="H184" s="33" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I184" s="33"/>
+      <c r="J184" s="33"/>
+      <c r="K184" s="33"/>
     </row>
     <row r="185" spans="1:11">
       <c r="A185" s="21" t="s">
@@ -13530,13 +13544,13 @@
         <v>95</v>
       </c>
       <c r="C185" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D185" s="22" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E185" s="21" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="F185" s="22" t="s">
         <v>728</v>
@@ -13555,16 +13569,16 @@
         <v>95</v>
       </c>
       <c r="C186" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D186" s="22" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E186" s="21" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="F186" s="22" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="G186" s="20"/>
       <c r="H186" s="23"/>
@@ -13580,13 +13594,13 @@
         <v>95</v>
       </c>
       <c r="C187" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D187" s="22" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="E187" s="21" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="F187" s="22" t="s">
         <v>735</v>
@@ -13605,13 +13619,13 @@
         <v>95</v>
       </c>
       <c r="C188" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D188" s="22" t="s">
-        <v>349</v>
+        <v>737</v>
       </c>
       <c r="E188" s="21" t="s">
-        <v>350</v>
+        <v>738</v>
       </c>
       <c r="F188" s="22" t="s">
         <v>735</v>
@@ -13627,19 +13641,19 @@
         <v>758</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C189" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>741</v>
+        <v>349</v>
       </c>
       <c r="E189" s="21" t="s">
-        <v>742</v>
+        <v>350</v>
       </c>
       <c r="F189" s="22" t="s">
-        <v>743</v>
+        <v>735</v>
       </c>
       <c r="G189" s="20"/>
       <c r="H189" s="23"/>
@@ -13655,13 +13669,13 @@
         <v>98</v>
       </c>
       <c r="C190" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D190" s="22" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="E190" s="21" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="F190" s="22" t="s">
         <v>743</v>
@@ -13680,13 +13694,13 @@
         <v>98</v>
       </c>
       <c r="C191" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D191" s="22" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E191" s="21" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="F191" s="22" t="s">
         <v>743</v>
@@ -13705,12 +13719,14 @@
         <v>98</v>
       </c>
       <c r="C192" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D192" s="22" t="s">
-        <v>751</v>
-      </c>
-      <c r="E192" s="21"/>
+        <v>748</v>
+      </c>
+      <c r="E192" s="21" t="s">
+        <v>749</v>
+      </c>
       <c r="F192" s="22" t="s">
         <v>743</v>
       </c>
@@ -13725,17 +13741,17 @@
         <v>771</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C193" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D193" s="22" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="E193" s="21"/>
       <c r="F193" s="22" t="s">
-        <v>709</v>
+        <v>743</v>
       </c>
       <c r="G193" s="20"/>
       <c r="H193" s="23"/>
@@ -13751,14 +13767,14 @@
         <v>101</v>
       </c>
       <c r="C194" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D194" s="22" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E194" s="21"/>
       <c r="F194" s="22" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="G194" s="20"/>
       <c r="H194" s="23"/>
@@ -13774,10 +13790,10 @@
         <v>101</v>
       </c>
       <c r="C195" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D195" s="22" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="E195" s="21"/>
       <c r="F195" s="22" t="s">
@@ -13794,19 +13810,17 @@
         <v>781</v>
       </c>
       <c r="B196" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C196" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D196" s="22" t="s">
-        <v>759</v>
-      </c>
-      <c r="E196" s="21" t="s">
-        <v>760</v>
-      </c>
+        <v>757</v>
+      </c>
+      <c r="E196" s="21"/>
       <c r="F196" s="22" t="s">
-        <v>761</v>
+        <v>696</v>
       </c>
       <c r="G196" s="20"/>
       <c r="H196" s="23"/>
@@ -13822,13 +13836,13 @@
         <v>103</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D197" s="22" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E197" s="21" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F197" s="22" t="s">
         <v>761</v>
@@ -13847,13 +13861,13 @@
         <v>103</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D198" s="22" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="F198" s="22" t="s">
         <v>761</v>
@@ -13872,13 +13886,13 @@
         <v>103</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D199" s="22" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="E199" s="21" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="F199" s="22" t="s">
         <v>761</v>
@@ -13894,19 +13908,19 @@
         <v>792</v>
       </c>
       <c r="B200" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D200" s="22" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="E200" s="21" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F200" s="22" t="s">
-        <v>774</v>
+        <v>761</v>
       </c>
       <c r="G200" s="20"/>
       <c r="H200" s="23"/>
@@ -13922,13 +13936,13 @@
         <v>105</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D201" s="22" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="E201" s="21" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F201" s="22" t="s">
         <v>774</v>
@@ -13947,13 +13961,13 @@
         <v>105</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="E202" s="21" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="F202" s="22" t="s">
         <v>774</v>
@@ -13972,13 +13986,13 @@
         <v>105</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D203" s="22" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E203" s="21" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="F203" s="22" t="s">
         <v>774</v>
@@ -13997,12 +14011,14 @@
         <v>105</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D204" s="22" t="s">
-        <v>785</v>
-      </c>
-      <c r="E204" s="21"/>
+        <v>782</v>
+      </c>
+      <c r="E204" s="21" t="s">
+        <v>783</v>
+      </c>
       <c r="F204" s="22" t="s">
         <v>774</v>
       </c>
@@ -14020,14 +14036,12 @@
         <v>105</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>787</v>
-      </c>
-      <c r="E205" s="21" t="s">
-        <v>788</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="E205" s="21"/>
       <c r="F205" s="22" t="s">
         <v>774</v>
       </c>
@@ -14045,13 +14059,13 @@
         <v>105</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E206" s="21" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="F206" s="22" t="s">
         <v>774</v>
@@ -14070,13 +14084,13 @@
         <v>105</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D207" s="22" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="E207" s="21" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="F207" s="22" t="s">
         <v>774</v>
@@ -14095,13 +14109,13 @@
         <v>105</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D208" s="22" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="F208" s="22" t="s">
         <v>774</v>
@@ -14120,13 +14134,13 @@
         <v>105</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="F209" s="22" t="s">
         <v>774</v>
@@ -14142,19 +14156,19 @@
         <v>823</v>
       </c>
       <c r="B210" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="F210" s="22" t="s">
-        <v>804</v>
+        <v>774</v>
       </c>
       <c r="G210" s="20"/>
       <c r="H210" s="23"/>
@@ -14170,13 +14184,13 @@
         <v>108</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="E211" s="21" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="F211" s="22" t="s">
         <v>804</v>
@@ -14195,13 +14209,13 @@
         <v>108</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D212" s="22" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="F212" s="22" t="s">
         <v>804</v>
@@ -14220,13 +14234,13 @@
         <v>108</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D213" s="22" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="E213" s="21" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="F213" s="22" t="s">
         <v>804</v>
@@ -14245,13 +14259,13 @@
         <v>108</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="E214" s="21" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="F214" s="22" t="s">
         <v>804</v>
@@ -14270,13 +14284,13 @@
         <v>108</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E215" s="21" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="F215" s="22" t="s">
         <v>804</v>
@@ -14295,22 +14309,22 @@
         <v>108</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D216" s="22" t="s">
-        <v>1277</v>
+        <v>818</v>
       </c>
       <c r="E216" s="21" t="s">
-        <v>1278</v>
+        <v>819</v>
       </c>
       <c r="F216" s="22" t="s">
         <v>804</v>
       </c>
-      <c r="G216" s="35"/>
+      <c r="G216" s="20"/>
       <c r="H216" s="23"/>
       <c r="I216" s="23"/>
       <c r="J216" s="23"/>
-      <c r="K216" s="33"/>
+      <c r="K216" s="23"/>
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
@@ -14320,13 +14334,13 @@
         <v>108</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="E217" s="21" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="F217" s="22" t="s">
         <v>804</v>
@@ -14342,25 +14356,25 @@
         <v>847</v>
       </c>
       <c r="B218" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>821</v>
+        <v>1279</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>822</v>
+        <v>1280</v>
       </c>
       <c r="F218" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="G218" s="20"/>
+        <v>804</v>
+      </c>
+      <c r="G218" s="35"/>
       <c r="H218" s="23"/>
       <c r="I218" s="23"/>
       <c r="J218" s="23"/>
-      <c r="K218" s="23"/>
+      <c r="K218" s="33"/>
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
@@ -14370,16 +14384,16 @@
         <v>110</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="F219" s="22" t="s">
-        <v>696</v>
+        <v>709</v>
       </c>
       <c r="G219" s="20"/>
       <c r="H219" s="23"/>
@@ -14395,13 +14409,13 @@
         <v>110</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="F220" s="22" t="s">
         <v>696</v>
@@ -14420,16 +14434,16 @@
         <v>110</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="F221" s="22" t="s">
-        <v>709</v>
+        <v>696</v>
       </c>
       <c r="G221" s="20"/>
       <c r="H221" s="23"/>
@@ -14445,13 +14459,13 @@
         <v>110</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F222" s="22" t="s">
         <v>709</v>
@@ -14467,19 +14481,19 @@
         <v>858</v>
       </c>
       <c r="B223" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>1269</v>
+        <v>833</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F223" s="22" t="s">
-        <v>837</v>
+        <v>709</v>
       </c>
       <c r="G223" s="20"/>
       <c r="H223" s="23"/>
@@ -14495,13 +14509,13 @@
         <v>112</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>839</v>
+        <v>1269</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="F224" s="22" t="s">
         <v>837</v>
@@ -14520,13 +14534,13 @@
         <v>112</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="F225" s="22" t="s">
         <v>837</v>
@@ -14545,13 +14559,13 @@
         <v>112</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="F226" s="22" t="s">
         <v>837</v>
@@ -14570,13 +14584,13 @@
         <v>112</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>1270</v>
+        <v>845</v>
       </c>
       <c r="E227" s="21" t="s">
-        <v>1272</v>
+        <v>846</v>
       </c>
       <c r="F227" s="22" t="s">
         <v>837</v>
@@ -14595,13 +14609,13 @@
         <v>112</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="F228" s="22" t="s">
         <v>837</v>
@@ -14620,13 +14634,13 @@
         <v>112</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>850</v>
+        <v>1271</v>
       </c>
       <c r="E229" s="21" t="s">
-        <v>851</v>
+        <v>1273</v>
       </c>
       <c r="F229" s="22" t="s">
         <v>837</v>
@@ -14645,13 +14659,13 @@
         <v>112</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F230" s="22" t="s">
         <v>837</v>
@@ -14670,13 +14684,13 @@
         <v>112</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="F231" s="22" t="s">
         <v>837</v>
@@ -14692,16 +14706,16 @@
         <v>885</v>
       </c>
       <c r="B232" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="F232" s="22" t="s">
         <v>837</v>
@@ -14720,13 +14734,13 @@
         <v>115</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="F233" s="22" t="s">
         <v>837</v>
@@ -14745,13 +14759,13 @@
         <v>115</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="F234" s="22" t="s">
         <v>837</v>
@@ -14770,13 +14784,13 @@
         <v>115</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D235" s="22" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="E235" s="21" t="s">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="F235" s="22" t="s">
         <v>837</v>
@@ -14795,12 +14809,14 @@
         <v>115</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>871</v>
-      </c>
-      <c r="E236" s="21"/>
+        <v>868</v>
+      </c>
+      <c r="E236" s="21" t="s">
+        <v>869</v>
+      </c>
       <c r="F236" s="22" t="s">
         <v>837</v>
       </c>
@@ -14815,19 +14831,17 @@
         <v>900</v>
       </c>
       <c r="B237" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>873</v>
-      </c>
-      <c r="E237" s="21" t="s">
-        <v>874</v>
-      </c>
+        <v>871</v>
+      </c>
+      <c r="E237" s="21"/>
       <c r="F237" s="22" t="s">
-        <v>875</v>
+        <v>837</v>
       </c>
       <c r="G237" s="20"/>
       <c r="H237" s="23"/>
@@ -14843,13 +14857,13 @@
         <v>117</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="F238" s="22" t="s">
         <v>875</v>
@@ -14868,13 +14882,13 @@
         <v>117</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="F239" s="22" t="s">
         <v>875</v>
@@ -14893,13 +14907,13 @@
         <v>117</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="E240" s="21" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="F240" s="22" t="s">
         <v>875</v>
@@ -14918,13 +14932,13 @@
         <v>117</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="F241" s="22" t="s">
         <v>875</v>
@@ -14943,13 +14957,13 @@
         <v>117</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="F242" s="22" t="s">
         <v>875</v>
@@ -14968,13 +14982,13 @@
         <v>117</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="F243" s="22" t="s">
         <v>875</v>
@@ -14993,13 +15007,13 @@
         <v>117</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="F244" s="22" t="s">
         <v>875</v>
@@ -15018,13 +15032,13 @@
         <v>117</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="F245" s="22" t="s">
         <v>875</v>
@@ -15043,13 +15057,13 @@
         <v>117</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="F246" s="22" t="s">
         <v>875</v>
@@ -15068,13 +15082,13 @@
         <v>117</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="F247" s="22" t="s">
         <v>875</v>
@@ -15093,13 +15107,13 @@
         <v>117</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="F248" s="22" t="s">
         <v>875</v>
@@ -15118,13 +15132,13 @@
         <v>117</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="F249" s="22" t="s">
         <v>875</v>
@@ -15143,13 +15157,13 @@
         <v>117</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="F250" s="22" t="s">
         <v>875</v>
@@ -15165,19 +15179,19 @@
         <v>944</v>
       </c>
       <c r="B251" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="F251" s="22" t="s">
-        <v>918</v>
+        <v>875</v>
       </c>
       <c r="G251" s="20"/>
       <c r="H251" s="23"/>
@@ -15193,13 +15207,13 @@
         <v>122</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="F252" s="22" t="s">
         <v>918</v>
@@ -15218,13 +15232,13 @@
         <v>122</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="F253" s="22" t="s">
         <v>918</v>
@@ -15243,13 +15257,13 @@
         <v>122</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="F254" s="22" t="s">
         <v>918</v>
@@ -15268,13 +15282,13 @@
         <v>122</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
       <c r="F255" s="22" t="s">
         <v>918</v>
@@ -15293,13 +15307,13 @@
         <v>122</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
       <c r="F256" s="22" t="s">
         <v>918</v>
@@ -15318,13 +15332,13 @@
         <v>122</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>935</v>
+        <v>932</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>936</v>
+        <v>933</v>
       </c>
       <c r="F257" s="22" t="s">
         <v>918</v>
@@ -15340,19 +15354,19 @@
         <v>964</v>
       </c>
       <c r="B258" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>938</v>
+        <v>935</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>939</v>
+        <v>936</v>
       </c>
       <c r="F258" s="22" t="s">
-        <v>940</v>
+        <v>918</v>
       </c>
       <c r="G258" s="20"/>
       <c r="H258" s="23"/>
@@ -15368,13 +15382,13 @@
         <v>125</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="F259" s="22" t="s">
         <v>940</v>
@@ -15393,13 +15407,13 @@
         <v>125</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="F260" s="22" t="s">
         <v>940</v>
@@ -15418,13 +15432,13 @@
         <v>125</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="F261" s="22" t="s">
         <v>940</v>
@@ -15443,13 +15457,13 @@
         <v>125</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>929</v>
+        <v>948</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="F262" s="22" t="s">
         <v>940</v>
@@ -15468,13 +15482,13 @@
         <v>125</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>953</v>
+        <v>929</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="F263" s="22" t="s">
         <v>940</v>
@@ -15493,13 +15507,13 @@
         <v>125</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>956</v>
+        <v>953</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>957</v>
+        <v>954</v>
       </c>
       <c r="F264" s="22" t="s">
         <v>940</v>
@@ -15518,13 +15532,13 @@
         <v>125</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>959</v>
+        <v>956</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>960</v>
+        <v>957</v>
       </c>
       <c r="F265" s="22" t="s">
         <v>940</v>
@@ -15543,13 +15557,13 @@
         <v>125</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>962</v>
+        <v>959</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>963</v>
+        <v>960</v>
       </c>
       <c r="F266" s="22" t="s">
         <v>940</v>
@@ -15568,13 +15582,13 @@
         <v>125</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>965</v>
+        <v>962</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>966</v>
+        <v>963</v>
       </c>
       <c r="F267" s="22" t="s">
         <v>940</v>
@@ -15593,13 +15607,13 @@
         <v>125</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>968</v>
+        <v>965</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>969</v>
+        <v>966</v>
       </c>
       <c r="F268" s="22" t="s">
         <v>940</v>
@@ -15618,13 +15632,13 @@
         <v>125</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>971</v>
+        <v>968</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>972</v>
+        <v>969</v>
       </c>
       <c r="F269" s="22" t="s">
         <v>940</v>
@@ -15643,13 +15657,13 @@
         <v>125</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>974</v>
+        <v>971</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>975</v>
+        <v>972</v>
       </c>
       <c r="F270" s="22" t="s">
         <v>940</v>
@@ -15668,13 +15682,13 @@
         <v>125</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>978</v>
+        <v>975</v>
       </c>
       <c r="F271" s="22" t="s">
         <v>940</v>
@@ -15690,19 +15704,19 @@
         <v>1008</v>
       </c>
       <c r="B272" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>174</v>
+        <v>308</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>980</v>
+        <v>977</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>981</v>
+        <v>978</v>
       </c>
       <c r="F272" s="22" t="s">
-        <v>982</v>
+        <v>940</v>
       </c>
       <c r="G272" s="20"/>
       <c r="H272" s="23"/>
@@ -15718,13 +15732,13 @@
         <v>128</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="F273" s="22" t="s">
         <v>982</v>
@@ -15743,13 +15757,13 @@
         <v>128</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>988</v>
+        <v>985</v>
       </c>
       <c r="F274" s="22" t="s">
         <v>982</v>
@@ -15768,13 +15782,13 @@
         <v>128</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>990</v>
+        <v>987</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>991</v>
+        <v>988</v>
       </c>
       <c r="F275" s="22" t="s">
         <v>982</v>
@@ -15793,13 +15807,13 @@
         <v>128</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="F276" s="22" t="s">
         <v>982</v>
@@ -15818,13 +15832,13 @@
         <v>128</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>996</v>
+        <v>993</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="F277" s="22" t="s">
         <v>982</v>
@@ -15843,13 +15857,13 @@
         <v>128</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="F278" s="22" t="s">
         <v>982</v>
@@ -15865,19 +15879,19 @@
         <v>1032</v>
       </c>
       <c r="B279" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>1002</v>
+        <v>999</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>1004</v>
+        <v>982</v>
       </c>
       <c r="G279" s="20"/>
       <c r="H279" s="23"/>
@@ -15893,13 +15907,13 @@
         <v>130</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F280" s="22" t="s">
         <v>1004</v>
@@ -15915,19 +15929,19 @@
         <v>1038</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>1011</v>
+        <v>1004</v>
       </c>
       <c r="G281" s="20"/>
       <c r="H281" s="23"/>
@@ -15943,13 +15957,13 @@
         <v>132</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F282" s="22" t="s">
         <v>1011</v>
@@ -15968,13 +15982,13 @@
         <v>132</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="F283" s="22" t="s">
         <v>1011</v>
@@ -15993,13 +16007,13 @@
         <v>132</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="F284" s="22" t="s">
         <v>1011</v>
@@ -16015,19 +16029,19 @@
         <v>1051</v>
       </c>
       <c r="B285" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1024</v>
+        <v>1011</v>
       </c>
       <c r="G285" s="20"/>
       <c r="H285" s="23"/>
@@ -16040,19 +16054,19 @@
         <v>1054</v>
       </c>
       <c r="B286" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C286" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G286" s="20"/>
       <c r="H286" s="23"/>
@@ -16068,13 +16082,13 @@
         <v>135</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="F287" s="22" t="s">
         <v>1028</v>
@@ -16093,13 +16107,13 @@
         <v>135</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="F288" s="22" t="s">
         <v>1028</v>
@@ -16118,13 +16132,13 @@
         <v>135</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
       <c r="F289" s="22" t="s">
         <v>1028</v>
@@ -16143,13 +16157,13 @@
         <v>135</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1039</v>
+        <v>1036</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1040</v>
+        <v>1037</v>
       </c>
       <c r="F290" s="22" t="s">
         <v>1028</v>
@@ -16165,19 +16179,19 @@
         <v>1070</v>
       </c>
       <c r="B291" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1043</v>
+        <v>1040</v>
       </c>
       <c r="F291" s="22" t="s">
-        <v>1044</v>
+        <v>1028</v>
       </c>
       <c r="G291" s="20"/>
       <c r="H291" s="23"/>
@@ -16193,13 +16207,13 @@
         <v>137</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F292" s="22" t="s">
         <v>1044</v>
@@ -16218,13 +16232,13 @@
         <v>137</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1050</v>
+        <v>1047</v>
       </c>
       <c r="F293" s="22" t="s">
         <v>1044</v>
@@ -16243,13 +16257,13 @@
         <v>137</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1052</v>
+        <v>1049</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="F294" s="22" t="s">
         <v>1044</v>
@@ -16265,19 +16279,19 @@
         <v>1082</v>
       </c>
       <c r="B295" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="F295" s="22" t="s">
-        <v>1057</v>
+        <v>1044</v>
       </c>
       <c r="G295" s="20"/>
       <c r="H295" s="23"/>
@@ -16293,13 +16307,13 @@
         <v>140</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="F296" s="22" t="s">
         <v>1057</v>
@@ -16318,13 +16332,13 @@
         <v>140</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="F297" s="22" t="s">
         <v>1057</v>
@@ -16343,13 +16357,13 @@
         <v>140</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="F298" s="22" t="s">
         <v>1057</v>
@@ -16365,16 +16379,16 @@
         <v>1096</v>
       </c>
       <c r="B299" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="F299" s="22" t="s">
         <v>1057</v>
@@ -16393,13 +16407,13 @@
         <v>142</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="F300" s="22" t="s">
         <v>1057</v>
@@ -16418,13 +16432,13 @@
         <v>142</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1074</v>
+        <v>1071</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1075</v>
+        <v>1072</v>
       </c>
       <c r="F301" s="22" t="s">
         <v>1057</v>
@@ -16443,13 +16457,13 @@
         <v>142</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="F302" s="22" t="s">
         <v>1057</v>
@@ -16468,13 +16482,13 @@
         <v>142</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="F303" s="22" t="s">
         <v>1057</v>
@@ -16493,13 +16507,13 @@
         <v>142</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1083</v>
+        <v>1080</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1084</v>
+        <v>1081</v>
       </c>
       <c r="F304" s="22" t="s">
         <v>1057</v>
@@ -16518,13 +16532,13 @@
         <v>142</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1086</v>
+        <v>1083</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1087</v>
+        <v>1084</v>
       </c>
       <c r="F305" s="22" t="s">
         <v>1057</v>
@@ -16540,19 +16554,19 @@
         <v>1119</v>
       </c>
       <c r="B306" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C306" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1089</v>
+        <v>1086</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1090</v>
+        <v>1087</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>1091</v>
+        <v>1057</v>
       </c>
       <c r="G306" s="20"/>
       <c r="H306" s="23"/>
@@ -16565,19 +16579,19 @@
         <v>1122</v>
       </c>
       <c r="B307" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C307" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="F307" s="22" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="G307" s="20"/>
       <c r="H307" s="23"/>
@@ -16593,13 +16607,13 @@
         <v>146</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="F308" s="22" t="s">
         <v>1095</v>
@@ -16618,13 +16632,13 @@
         <v>146</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1101</v>
+        <v>1098</v>
       </c>
       <c r="F309" s="22" t="s">
         <v>1095</v>
@@ -16640,19 +16654,19 @@
         <v>1129</v>
       </c>
       <c r="B310" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>1105</v>
+        <v>1095</v>
       </c>
       <c r="G310" s="20"/>
       <c r="H310" s="23"/>
@@ -16668,13 +16682,13 @@
         <v>147</v>
       </c>
       <c r="C311" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="F311" s="22" t="s">
         <v>1105</v>
@@ -16693,13 +16707,13 @@
         <v>147</v>
       </c>
       <c r="C312" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1110</v>
+        <v>1107</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="F312" s="22" t="s">
         <v>1105</v>
@@ -16715,19 +16729,19 @@
         <v>1140</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C313" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1114</v>
+        <v>1111</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="G313" s="20"/>
       <c r="H313" s="23"/>
@@ -16743,13 +16757,13 @@
         <v>148</v>
       </c>
       <c r="C314" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="F314" s="22" t="s">
         <v>1115</v>
@@ -16768,13 +16782,13 @@
         <v>148</v>
       </c>
       <c r="C315" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="F315" s="22" t="s">
         <v>1115</v>
@@ -16793,13 +16807,13 @@
         <v>148</v>
       </c>
       <c r="C316" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="F316" s="22" t="s">
         <v>1115</v>
@@ -16818,13 +16832,13 @@
         <v>148</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D317" s="22" t="s">
-        <v>1124</v>
+        <v>1113</v>
       </c>
       <c r="E317" s="21" t="s">
-        <v>1125</v>
+        <v>1114</v>
       </c>
       <c r="F317" s="22" t="s">
         <v>1115</v>
@@ -16843,13 +16857,13 @@
         <v>148</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1127</v>
+        <v>1124</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1128</v>
+        <v>1125</v>
       </c>
       <c r="F318" s="22" t="s">
         <v>1115</v>
@@ -16865,19 +16879,19 @@
         <v>1159</v>
       </c>
       <c r="B319" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="F319" s="22" t="s">
-        <v>1132</v>
+        <v>1115</v>
       </c>
       <c r="G319" s="20"/>
       <c r="H319" s="23"/>
@@ -16893,13 +16907,13 @@
         <v>150</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="F320" s="22" t="s">
         <v>1132</v>
@@ -16915,19 +16929,19 @@
         <v>1165</v>
       </c>
       <c r="B321" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1138</v>
+        <v>1135</v>
       </c>
       <c r="F321" s="22" t="s">
-        <v>1139</v>
+        <v>1132</v>
       </c>
       <c r="G321" s="20"/>
       <c r="H321" s="23"/>
@@ -16943,13 +16957,13 @@
         <v>153</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="F322" s="22" t="s">
         <v>1139</v>
@@ -16965,19 +16979,19 @@
         <v>1171</v>
       </c>
       <c r="B323" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1144</v>
+        <v>1141</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1145</v>
+        <v>1142</v>
       </c>
       <c r="F323" s="22" t="s">
-        <v>1146</v>
+        <v>1139</v>
       </c>
       <c r="G323" s="20"/>
       <c r="H323" s="23"/>
@@ -16993,13 +17007,13 @@
         <v>155</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="F324" s="22" t="s">
         <v>1146</v>
@@ -17018,13 +17032,13 @@
         <v>155</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="F325" s="22" t="s">
         <v>1146</v>
@@ -17043,13 +17057,13 @@
         <v>155</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="F326" s="22" t="s">
         <v>1146</v>
@@ -17068,13 +17082,13 @@
         <v>155</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1157</v>
+        <v>1154</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1158</v>
+        <v>1155</v>
       </c>
       <c r="F327" s="22" t="s">
         <v>1146</v>
@@ -17093,13 +17107,13 @@
         <v>155</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="F328" s="22" t="s">
         <v>1146</v>
@@ -17118,13 +17132,13 @@
         <v>155</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="F329" s="22" t="s">
         <v>1146</v>
@@ -17143,13 +17157,13 @@
         <v>155</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="F330" s="22" t="s">
         <v>1146</v>
@@ -17168,13 +17182,13 @@
         <v>155</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="F331" s="22" t="s">
         <v>1146</v>
@@ -17193,13 +17207,13 @@
         <v>155</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="F332" s="22" t="s">
         <v>1146</v>
@@ -17218,13 +17232,13 @@
         <v>155</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="F333" s="22" t="s">
         <v>1146</v>
@@ -17243,13 +17257,13 @@
         <v>155</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="F334" s="22" t="s">
         <v>1146</v>
@@ -17268,13 +17282,13 @@
         <v>155</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1181</v>
+        <v>1178</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="F335" s="22" t="s">
         <v>1146</v>
@@ -17293,13 +17307,13 @@
         <v>155</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="F336" s="22" t="s">
         <v>1146</v>
@@ -17318,13 +17332,13 @@
         <v>155</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1188</v>
+        <v>1185</v>
       </c>
       <c r="F337" s="22" t="s">
         <v>1146</v>
@@ -17343,13 +17357,13 @@
         <v>155</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1190</v>
+        <v>1187</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1191</v>
+        <v>1188</v>
       </c>
       <c r="F338" s="22" t="s">
         <v>1146</v>
@@ -17368,13 +17382,13 @@
         <v>155</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="F339" s="22" t="s">
         <v>1146</v>
@@ -17393,13 +17407,13 @@
         <v>155</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>188</v>
+        <v>1194</v>
       </c>
       <c r="F340" s="22" t="s">
         <v>1146</v>
@@ -17418,13 +17432,13 @@
         <v>155</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>1199</v>
+        <v>188</v>
       </c>
       <c r="F341" s="22" t="s">
         <v>1146</v>
@@ -17443,13 +17457,13 @@
         <v>155</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1201</v>
+        <v>1198</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1202</v>
+        <v>1199</v>
       </c>
       <c r="F342" s="22" t="s">
         <v>1146</v>
@@ -17468,13 +17482,13 @@
         <v>155</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1204</v>
+        <v>1201</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="F343" s="22" t="s">
         <v>1146</v>
@@ -17490,19 +17504,19 @@
         <v>1233</v>
       </c>
       <c r="B344" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1207</v>
+        <v>1204</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1161</v>
+        <v>1205</v>
       </c>
       <c r="F344" s="22" t="s">
-        <v>1208</v>
+        <v>1146</v>
       </c>
       <c r="G344" s="20"/>
       <c r="H344" s="23"/>
@@ -17518,13 +17532,13 @@
         <v>156</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1211</v>
+        <v>1161</v>
       </c>
       <c r="F345" s="22" t="s">
         <v>1208</v>
@@ -17543,13 +17557,13 @@
         <v>156</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="F346" s="22" t="s">
         <v>1208</v>
@@ -17568,13 +17582,13 @@
         <v>156</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1216</v>
+        <v>1213</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1217</v>
+        <v>1214</v>
       </c>
       <c r="F347" s="22" t="s">
         <v>1208</v>
@@ -17593,13 +17607,13 @@
         <v>156</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1219</v>
+        <v>1216</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1220</v>
+        <v>1217</v>
       </c>
       <c r="F348" s="22" t="s">
         <v>1208</v>
@@ -17618,13 +17632,13 @@
         <v>156</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1223</v>
+        <v>1220</v>
       </c>
       <c r="F349" s="22" t="s">
         <v>1208</v>
@@ -17643,13 +17657,13 @@
         <v>156</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1225</v>
+        <v>1222</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1226</v>
+        <v>1223</v>
       </c>
       <c r="F350" s="22" t="s">
         <v>1208</v>
@@ -17668,13 +17682,13 @@
         <v>156</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1228</v>
+        <v>1225</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1229</v>
+        <v>1226</v>
       </c>
       <c r="F351" s="22" t="s">
         <v>1208</v>
@@ -17693,13 +17707,13 @@
         <v>156</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>258</v>
+        <v>210</v>
       </c>
       <c r="D352" s="22" t="s">
-        <v>1231</v>
+        <v>1228</v>
       </c>
       <c r="E352" s="21" t="s">
-        <v>1232</v>
+        <v>1229</v>
       </c>
       <c r="F352" s="22" t="s">
         <v>1208</v>
@@ -17718,13 +17732,13 @@
         <v>156</v>
       </c>
       <c r="C353" s="21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="D353" s="22" t="s">
-        <v>1234</v>
+        <v>1231</v>
       </c>
       <c r="E353" s="21" t="s">
-        <v>1235</v>
+        <v>1232</v>
       </c>
       <c r="F353" s="22" t="s">
         <v>1208</v>
@@ -17743,13 +17757,13 @@
         <v>156</v>
       </c>
       <c r="C354" s="21" t="s">
-        <v>296</v>
+        <v>262</v>
       </c>
       <c r="D354" s="22" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="E354" s="21" t="s">
-        <v>1238</v>
+        <v>1235</v>
       </c>
       <c r="F354" s="22" t="s">
         <v>1208</v>
@@ -17768,13 +17782,13 @@
         <v>156</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D355" s="22" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="E355" s="21" t="s">
-        <v>1241</v>
+        <v>1238</v>
       </c>
       <c r="F355" s="22" t="s">
         <v>1208</v>
@@ -17790,19 +17804,19 @@
         <v>1300</v>
       </c>
       <c r="B356" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="D356" s="22" t="s">
-        <v>1243</v>
+        <v>1240</v>
       </c>
       <c r="E356" s="21" t="s">
-        <v>1244</v>
+        <v>1241</v>
       </c>
       <c r="F356" s="22" t="s">
-        <v>875</v>
+        <v>1208</v>
       </c>
       <c r="G356" s="20"/>
       <c r="H356" s="23"/>
@@ -17818,13 +17832,13 @@
         <v>158</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D357" s="22" t="s">
-        <v>1246</v>
+        <v>1243</v>
       </c>
       <c r="E357" s="21" t="s">
-        <v>1247</v>
+        <v>1244</v>
       </c>
       <c r="F357" s="22" t="s">
         <v>875</v>
@@ -17843,13 +17857,13 @@
         <v>158</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D358" s="22" t="s">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="E358" s="21" t="s">
-        <v>1250</v>
+        <v>1247</v>
       </c>
       <c r="F358" s="22" t="s">
         <v>875</v>
@@ -17868,13 +17882,13 @@
         <v>158</v>
       </c>
       <c r="C359" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D359" s="22" t="s">
-        <v>1252</v>
+        <v>1249</v>
       </c>
       <c r="E359" s="21" t="s">
-        <v>1253</v>
+        <v>1250</v>
       </c>
       <c r="F359" s="22" t="s">
         <v>875</v>
@@ -17893,13 +17907,13 @@
         <v>158</v>
       </c>
       <c r="C360" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D360" s="22" t="s">
-        <v>1255</v>
+        <v>1252</v>
       </c>
       <c r="E360" s="21" t="s">
-        <v>1256</v>
+        <v>1253</v>
       </c>
       <c r="F360" s="22" t="s">
         <v>875</v>
@@ -17915,35 +17929,25 @@
         <v>1305</v>
       </c>
       <c r="B361" s="21" t="s">
-        <v>1295</v>
+        <v>158</v>
       </c>
       <c r="C361" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D361" s="22" t="s">
-        <v>1298</v>
+        <v>1255</v>
       </c>
       <c r="E361" s="21" t="s">
-        <v>1310</v>
+        <v>1256</v>
       </c>
       <c r="F361" s="22" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G361" s="20">
-        <v>4500</v>
-      </c>
-      <c r="H361" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I361" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J361" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K361" s="23">
-        <v>82500</v>
-      </c>
+        <v>875</v>
+      </c>
+      <c r="G361" s="20"/>
+      <c r="H361" s="23"/>
+      <c r="I361" s="23"/>
+      <c r="J361" s="23"/>
+      <c r="K361" s="23"/>
     </row>
     <row r="362" spans="1:11">
       <c r="A362" s="21" t="s">
@@ -17953,19 +17957,19 @@
         <v>1295</v>
       </c>
       <c r="C362" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D362" s="22" t="s">
-        <v>1312</v>
+        <v>1298</v>
       </c>
       <c r="E362" s="21" t="s">
-        <v>1316</v>
+        <v>1310</v>
       </c>
       <c r="F362" s="22" t="s">
         <v>1311</v>
       </c>
       <c r="G362" s="20">
-        <v>5000</v>
+        <v>4500</v>
       </c>
       <c r="H362" s="23" t="s">
         <v>1275</v>
@@ -17988,13 +17992,13 @@
         <v>1295</v>
       </c>
       <c r="C363" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D363" s="22" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="E363" s="21" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="F363" s="22" t="s">
         <v>1311</v>
@@ -18023,13 +18027,13 @@
         <v>1295</v>
       </c>
       <c r="C364" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D364" s="22" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="E364" s="21" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F364" s="22" t="s">
         <v>1311</v>
@@ -18058,13 +18062,13 @@
         <v>1295</v>
       </c>
       <c r="C365" s="21" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D365" s="22" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="E365" s="21" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="F365" s="22" t="s">
         <v>1311</v>
@@ -18086,17 +18090,39 @@
       </c>
     </row>
     <row r="366" spans="1:11">
-      <c r="A366" s="21"/>
-      <c r="B366" s="21"/>
-      <c r="C366" s="21"/>
-      <c r="D366" s="22"/>
-      <c r="E366" s="21"/>
-      <c r="F366" s="22"/>
-      <c r="G366" s="20"/>
-      <c r="H366" s="23"/>
-      <c r="I366" s="23"/>
-      <c r="J366" s="23"/>
-      <c r="K366" s="23"/>
+      <c r="A366" s="21" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B366" s="21" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C366" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D366" s="22" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E366" s="21" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F366" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G366" s="20">
+        <v>5000</v>
+      </c>
+      <c r="H366" s="23" t="s">
+        <v>1275</v>
+      </c>
+      <c r="I366" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J366" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K366" s="23">
+        <v>82500</v>
+      </c>
     </row>
     <row r="367" spans="1:11">
       <c r="A367" s="21"/>
@@ -18742,7 +18768,7 @@
       <c r="D416" s="22"/>
       <c r="E416" s="21"/>
       <c r="F416" s="22"/>
-      <c r="G416" s="18"/>
+      <c r="G416" s="20"/>
       <c r="H416" s="23"/>
       <c r="I416" s="23"/>
       <c r="J416" s="23"/>
@@ -39442,7 +39468,7 @@
       <c r="H2008" s="23"/>
       <c r="I2008" s="23"/>
       <c r="J2008" s="23"/>
-      <c r="K2008" s="33"/>
+      <c r="K2008" s="23"/>
     </row>
     <row r="2009" spans="1:11">
       <c r="A2009" s="21"/>
@@ -39457,15 +39483,28 @@
       <c r="J2009" s="23"/>
       <c r="K2009" s="33"/>
     </row>
+    <row r="2010" spans="1:11">
+      <c r="A2010" s="21"/>
+      <c r="B2010" s="21"/>
+      <c r="C2010" s="21"/>
+      <c r="D2010" s="22"/>
+      <c r="E2010" s="21"/>
+      <c r="F2010" s="22"/>
+      <c r="G2010" s="18"/>
+      <c r="H2010" s="23"/>
+      <c r="I2010" s="23"/>
+      <c r="J2010" s="23"/>
+      <c r="K2010" s="33"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2005:A2009">
+  <conditionalFormatting sqref="A2006:A2010">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A2004">
+  <conditionalFormatting sqref="A4:A2005">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -39495,27 +39534,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="42" t="s">
         <v>1257</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="50" t="s">
         <v>1258</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">

--- a/icare-group-member-onboarding-template.xlsx
+++ b/icare-group-member-onboarding-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Master_ AY Projects\trustmicro-credit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1D70E60-EC68-4E08-81C4-B8691B728FC5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA664A8-8AD9-4CA4-A636-D8F726FDC337}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2692" uniqueCount="1341">
   <si>
     <t>ICARE Group and Member Onboarding Template</t>
   </si>
@@ -2305,9 +2305,6 @@
     <t>MEM-186</t>
   </si>
   <si>
-    <t>Olamide Gbadamosi</t>
-  </si>
-  <si>
     <t>07033547391</t>
   </si>
   <si>
@@ -2578,9 +2575,6 @@
     <t>MEM-217</t>
   </si>
   <si>
-    <t>Koleosho Sheriffat</t>
-  </si>
-  <si>
     <t>07042434723</t>
   </si>
   <si>
@@ -3998,6 +3992,63 @@
   </si>
   <si>
     <t>MEM-363</t>
+  </si>
+  <si>
+    <t>Abdullahi Rafatu</t>
+  </si>
+  <si>
+    <t>09066046838</t>
+  </si>
+  <si>
+    <t>Olaide Gbadamosi</t>
+  </si>
+  <si>
+    <t>07064134410</t>
+  </si>
+  <si>
+    <t>MEM-364</t>
+  </si>
+  <si>
+    <t>MEM-365</t>
+  </si>
+  <si>
+    <t>36550</t>
+  </si>
+  <si>
+    <t>23150</t>
+  </si>
+  <si>
+    <t>8225</t>
+  </si>
+  <si>
+    <t>7950</t>
+  </si>
+  <si>
+    <t>11000</t>
+  </si>
+  <si>
+    <t>29800</t>
+  </si>
+  <si>
+    <t>11750</t>
+  </si>
+  <si>
+    <t>7000</t>
+  </si>
+  <si>
+    <t>17000</t>
+  </si>
+  <si>
+    <t>36925</t>
+  </si>
+  <si>
+    <t>25125</t>
+  </si>
+  <si>
+    <t>Muibat Oladapo</t>
+  </si>
+  <si>
+    <t>MEM-366</t>
   </si>
 </sst>
 </file>
@@ -4197,7 +4248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -4308,31 +4359,33 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4811,7 +4864,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2010" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="MemberOnboardingTable" displayName="MemberOnboardingTable" ref="A3:K2013" dataDxfId="14">
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Member Reference*" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Group Reference*" dataDxfId="12"/>
@@ -4988,28 +5041,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="2"/>
@@ -5029,13 +5082,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2"/>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
     </row>
     <row r="5" spans="1:8" ht="27.9" customHeight="1">
       <c r="A5" s="3" t="s">
@@ -5043,7 +5096,7 @@
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="2"/>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="50" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="45"/>
@@ -5057,7 +5110,7 @@
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2"/>
-      <c r="D6" s="47" t="s">
+      <c r="D6" s="50" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="45"/>
@@ -5071,7 +5124,7 @@
       </c>
       <c r="B7" s="3"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="50" t="s">
         <v>10</v>
       </c>
       <c r="E7" s="45"/>
@@ -5085,7 +5138,7 @@
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="47" t="s">
+      <c r="D8" s="50" t="s">
         <v>12</v>
       </c>
       <c r="E8" s="45"/>
@@ -5099,7 +5152,7 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="50" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="45"/>
@@ -5111,7 +5164,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="47" t="s">
+      <c r="D10" s="50" t="s">
         <v>15</v>
       </c>
       <c r="E10" s="45"/>
@@ -5130,16 +5183,16 @@
       <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="48" t="s">
+      <c r="A12" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="43"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="43"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="43"/>
-      <c r="H12" s="43"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
     </row>
     <row r="13" spans="1:8" ht="38.1" customHeight="1">
       <c r="A13" s="28" t="s">
@@ -5159,7 +5212,7 @@
       <c r="A14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="B14" s="51" t="s">
         <v>20</v>
       </c>
       <c r="C14" s="45"/>
@@ -5173,7 +5226,7 @@
       <c r="A15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="44" t="s">
+      <c r="B15" s="51" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="45"/>
@@ -5187,7 +5240,7 @@
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="44" t="s">
+      <c r="B16" s="51" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="45"/>
@@ -5201,7 +5254,7 @@
       <c r="A17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="51" t="s">
         <v>26</v>
       </c>
       <c r="C17" s="45"/>
@@ -5215,7 +5268,7 @@
       <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="44" t="s">
+      <c r="B18" s="51" t="s">
         <v>28</v>
       </c>
       <c r="C18" s="45"/>
@@ -5229,7 +5282,7 @@
       <c r="A19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="51" t="s">
         <v>30</v>
       </c>
       <c r="C19" s="45"/>
@@ -5243,7 +5296,7 @@
       <c r="A20" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="44" t="s">
+      <c r="B20" s="51" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="45"/>
@@ -5257,7 +5310,7 @@
       <c r="A21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="44" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="45"/>
@@ -5278,6 +5331,13 @@
     <filterColumn colId="6" showButton="0"/>
   </autoFilter>
   <mergeCells count="19">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B18:H18"/>
     <mergeCell ref="B21:H21"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="D4:H4"/>
@@ -5290,13 +5350,6 @@
     <mergeCell ref="B19:H19"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B15:H15"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B18:H18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5319,30 +5372,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:9" ht="30" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
     </row>
     <row r="3" spans="1:9" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -5823,7 +5876,9 @@
       <c r="H21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="14"/>
+      <c r="I21" s="14" t="s">
+        <v>1328</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6" t="s">
@@ -5836,7 +5891,7 @@
         <v>91</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>87</v>
@@ -5850,7 +5905,9 @@
       <c r="H22" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="14"/>
+      <c r="I22" s="14" t="s">
+        <v>1329</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6" t="s">
@@ -5863,7 +5920,7 @@
         <v>93</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>94</v>
@@ -5878,7 +5935,7 @@
         <v>89</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -5891,7 +5948,9 @@
       <c r="C24" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6" t="s">
+        <v>733</v>
+      </c>
       <c r="E24" s="6" t="s">
         <v>97</v>
       </c>
@@ -5904,7 +5963,9 @@
       <c r="H24" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="14"/>
+      <c r="I24" s="14" t="s">
+        <v>1330</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6" t="s">
@@ -5916,7 +5977,9 @@
       <c r="C25" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6" t="s">
+        <v>745</v>
+      </c>
       <c r="E25" s="6" t="s">
         <v>100</v>
       </c>
@@ -5929,7 +5992,9 @@
       <c r="H25" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I25" s="14"/>
+      <c r="I25" s="14" t="s">
+        <v>1331</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6" t="s">
@@ -5941,7 +6006,9 @@
       <c r="C26" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6" t="s">
+        <v>755</v>
+      </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
       </c>
@@ -5954,7 +6021,9 @@
       <c r="H26" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I26" s="14"/>
+      <c r="I26" s="14" t="s">
+        <v>1332</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6" t="s">
@@ -5966,7 +6035,9 @@
       <c r="C27" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D27" s="6"/>
+      <c r="D27" s="6" t="s">
+        <v>1324</v>
+      </c>
       <c r="E27" s="6" t="s">
         <v>97</v>
       </c>
@@ -5979,7 +6050,9 @@
       <c r="H27" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I27" s="14"/>
+      <c r="I27" s="14" t="s">
+        <v>1333</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6" t="s">
@@ -5992,7 +6065,7 @@
         <v>106</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -6006,7 +6079,9 @@
       <c r="H28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I28" s="14"/>
+      <c r="I28" s="14" t="s">
+        <v>1334</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6" t="s">
@@ -6019,7 +6094,7 @@
         <v>109</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>107</v>
@@ -6033,7 +6108,9 @@
       <c r="H29" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I29" s="14"/>
+      <c r="I29" s="14" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6" t="s">
@@ -6046,7 +6123,7 @@
         <v>111</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>107</v>
@@ -6060,7 +6137,9 @@
       <c r="H30" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="14"/>
+      <c r="I30" s="14" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6" t="s">
@@ -6073,7 +6152,7 @@
         <v>113</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="E31" s="6" t="s">
         <v>114</v>
@@ -6087,7 +6166,9 @@
       <c r="H31" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I31" s="34"/>
+      <c r="I31" s="34" t="s">
+        <v>1337</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6" t="s">
@@ -6100,7 +6181,7 @@
         <v>116</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>114</v>
@@ -6114,7 +6195,9 @@
       <c r="H32" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I32" s="38"/>
+      <c r="I32" s="38" t="s">
+        <v>1338</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6" t="s">
@@ -6618,7 +6701,7 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="6" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>126</v>
@@ -6627,7 +6710,7 @@
         <v>133</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>124</v>
@@ -6642,7 +6725,7 @@
         <v>89</v>
       </c>
       <c r="I53" s="14" t="s">
-        <v>1296</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -8863,7 +8946,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K2010"/>
+  <dimension ref="A1:K2013"/>
   <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="2" width="22.09765625" style="27" customWidth="1"/>
@@ -8875,34 +8958,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57"/>
+      <c r="K1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="55" t="s">
         <v>162</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="1:11" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
@@ -12617,11 +12700,21 @@
       <c r="F151" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G151" s="20"/>
-      <c r="H151" s="23"/>
-      <c r="I151" s="23"/>
-      <c r="J151" s="23"/>
-      <c r="K151" s="23"/>
+      <c r="G151" s="20">
+        <v>12500</v>
+      </c>
+      <c r="H151" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I151" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J151" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K151" s="23">
+        <v>37500</v>
+      </c>
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="21" t="s">
@@ -12642,11 +12735,21 @@
       <c r="F152" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G152" s="20"/>
-      <c r="H152" s="23"/>
-      <c r="I152" s="23"/>
-      <c r="J152" s="23"/>
-      <c r="K152" s="23"/>
+      <c r="G152" s="20">
+        <v>34100</v>
+      </c>
+      <c r="H152" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I152" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J152" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K152" s="23">
+        <v>96000</v>
+      </c>
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="21" t="s">
@@ -12667,11 +12770,21 @@
       <c r="F153" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G153" s="20"/>
-      <c r="H153" s="23"/>
-      <c r="I153" s="23"/>
-      <c r="J153" s="23"/>
-      <c r="K153" s="23"/>
+      <c r="G153" s="20">
+        <v>10250</v>
+      </c>
+      <c r="H153" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I153" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J153" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K153" s="23">
+        <v>198000</v>
+      </c>
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="21" t="s">
@@ -12692,11 +12805,21 @@
       <c r="F154" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G154" s="20"/>
-      <c r="H154" s="23"/>
-      <c r="I154" s="23"/>
-      <c r="J154" s="23"/>
-      <c r="K154" s="23"/>
+      <c r="G154" s="20">
+        <v>6400</v>
+      </c>
+      <c r="H154" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I154" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J154" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K154" s="23">
+        <v>33000</v>
+      </c>
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="21" t="s">
@@ -12717,11 +12840,21 @@
       <c r="F155" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G155" s="20"/>
-      <c r="H155" s="23"/>
-      <c r="I155" s="23"/>
-      <c r="J155" s="23"/>
-      <c r="K155" s="23"/>
+      <c r="G155" s="20">
+        <v>16550</v>
+      </c>
+      <c r="H155" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I155" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J155" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K155" s="23">
+        <v>37500</v>
+      </c>
     </row>
     <row r="156" spans="1:11">
       <c r="A156" s="21" t="s">
@@ -12742,11 +12875,21 @@
       <c r="F156" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G156" s="20"/>
-      <c r="H156" s="23"/>
-      <c r="I156" s="23"/>
-      <c r="J156" s="23"/>
-      <c r="K156" s="23"/>
+      <c r="G156" s="20">
+        <v>7500</v>
+      </c>
+      <c r="H156" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I156" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J156" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K156" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="157" spans="1:11">
       <c r="A157" s="21" t="s">
@@ -12768,7 +12911,9 @@
         <v>650</v>
       </c>
       <c r="G157" s="20"/>
-      <c r="H157" s="23"/>
+      <c r="H157" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I157" s="23"/>
       <c r="J157" s="23"/>
       <c r="K157" s="23"/>
@@ -12792,11 +12937,21 @@
       <c r="F158" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G158" s="20"/>
-      <c r="H158" s="23"/>
-      <c r="I158" s="23"/>
-      <c r="J158" s="23"/>
-      <c r="K158" s="23"/>
+      <c r="G158" s="20">
+        <v>10750</v>
+      </c>
+      <c r="H158" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I158" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J158" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K158" s="23">
+        <v>150000</v>
+      </c>
     </row>
     <row r="159" spans="1:11">
       <c r="A159" s="21" t="s">
@@ -12817,11 +12972,21 @@
       <c r="F159" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G159" s="20"/>
-      <c r="H159" s="23"/>
-      <c r="I159" s="23"/>
-      <c r="J159" s="23"/>
-      <c r="K159" s="23"/>
+      <c r="G159" s="20">
+        <v>7300</v>
+      </c>
+      <c r="H159" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I159" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J159" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K159" s="23">
+        <v>150000</v>
+      </c>
     </row>
     <row r="160" spans="1:11">
       <c r="A160" s="21" t="s">
@@ -12842,11 +13007,21 @@
       <c r="F160" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G160" s="20"/>
-      <c r="H160" s="23"/>
-      <c r="I160" s="23"/>
-      <c r="J160" s="23"/>
-      <c r="K160" s="23"/>
+      <c r="G160" s="20">
+        <v>26000</v>
+      </c>
+      <c r="H160" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I160" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J160" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K160" s="23">
+        <v>228000</v>
+      </c>
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="21" t="s">
@@ -12865,11 +13040,21 @@
       <c r="F161" s="22" t="s">
         <v>646</v>
       </c>
-      <c r="G161" s="20"/>
-      <c r="H161" s="23"/>
-      <c r="I161" s="23"/>
-      <c r="J161" s="23"/>
-      <c r="K161" s="23"/>
+      <c r="G161" s="20">
+        <v>17450</v>
+      </c>
+      <c r="H161" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I161" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J161" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K161" s="23">
+        <v>41250</v>
+      </c>
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="21" t="s">
@@ -12890,11 +13075,21 @@
       <c r="F162" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G162" s="20"/>
-      <c r="H162" s="23"/>
-      <c r="I162" s="23"/>
-      <c r="J162" s="23"/>
-      <c r="K162" s="23"/>
+      <c r="G162" s="20">
+        <v>8625</v>
+      </c>
+      <c r="H162" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I162" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J162" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K162" s="23">
+        <v>150000</v>
+      </c>
     </row>
     <row r="163" spans="1:11" s="36" customFormat="1">
       <c r="A163" s="21" t="s">
@@ -12907,19 +13102,29 @@
         <v>304</v>
       </c>
       <c r="D163" s="40" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="E163" s="39" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="F163" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G163" s="35"/>
-      <c r="H163" s="33"/>
-      <c r="I163" s="33"/>
-      <c r="J163" s="33"/>
-      <c r="K163" s="33"/>
+      <c r="G163" s="35">
+        <v>5500</v>
+      </c>
+      <c r="H163" s="33" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I163" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J163" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K163" s="33">
+        <v>66000</v>
+      </c>
     </row>
     <row r="164" spans="1:11" s="36" customFormat="1">
       <c r="A164" s="21" t="s">
@@ -12932,17 +13137,27 @@
         <v>308</v>
       </c>
       <c r="D164" s="40" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="E164" s="39"/>
       <c r="F164" s="22" t="s">
         <v>650</v>
       </c>
-      <c r="G164" s="35"/>
-      <c r="H164" s="33"/>
-      <c r="I164" s="33"/>
-      <c r="J164" s="33"/>
-      <c r="K164" s="33"/>
+      <c r="G164" s="35">
+        <v>7000</v>
+      </c>
+      <c r="H164" s="33" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I164" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J164" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K164" s="33">
+        <v>49500</v>
+      </c>
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="21" t="s">
@@ -12963,11 +13178,21 @@
       <c r="F165" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G165" s="20"/>
-      <c r="H165" s="23"/>
-      <c r="I165" s="23"/>
-      <c r="J165" s="23"/>
-      <c r="K165" s="23"/>
+      <c r="G165" s="20">
+        <v>8200</v>
+      </c>
+      <c r="H165" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I165" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J165" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K165" s="23">
+        <v>125000</v>
+      </c>
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="21" t="s">
@@ -12988,11 +13213,21 @@
       <c r="F166" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G166" s="20"/>
-      <c r="H166" s="23"/>
-      <c r="I166" s="23"/>
-      <c r="J166" s="23"/>
-      <c r="K166" s="23"/>
+      <c r="G166" s="20">
+        <v>25150</v>
+      </c>
+      <c r="H166" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I166" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J166" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K166" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="21" t="s">
@@ -13014,7 +13249,9 @@
         <v>683</v>
       </c>
       <c r="G167" s="20"/>
-      <c r="H167" s="23"/>
+      <c r="H167" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I167" s="23"/>
       <c r="J167" s="23"/>
       <c r="K167" s="23"/>
@@ -13038,11 +13275,21 @@
       <c r="F168" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G168" s="20"/>
-      <c r="H168" s="23"/>
-      <c r="I168" s="23"/>
-      <c r="J168" s="23"/>
-      <c r="K168" s="23"/>
+      <c r="G168" s="20">
+        <v>22350</v>
+      </c>
+      <c r="H168" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I168" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J168" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K168" s="23">
+        <v>43750</v>
+      </c>
     </row>
     <row r="169" spans="1:11" s="36" customFormat="1">
       <c r="A169" s="21" t="s">
@@ -13055,16 +13302,20 @@
         <v>198</v>
       </c>
       <c r="D169" s="40" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="E169" s="39" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="F169" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G169" s="35"/>
-      <c r="H169" s="33"/>
+      <c r="G169" s="35">
+        <v>25600</v>
+      </c>
+      <c r="H169" s="33" t="s">
+        <v>1274</v>
+      </c>
       <c r="I169" s="33"/>
       <c r="J169" s="33"/>
       <c r="K169" s="33"/>
@@ -13080,17 +13331,27 @@
         <v>202</v>
       </c>
       <c r="D170" s="40" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E170" s="39"/>
       <c r="F170" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G170" s="35"/>
-      <c r="H170" s="33"/>
-      <c r="I170" s="33"/>
-      <c r="J170" s="33"/>
-      <c r="K170" s="33"/>
+      <c r="G170" s="35">
+        <v>5500</v>
+      </c>
+      <c r="H170" s="33" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I170" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J170" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K170" s="33">
+        <v>57750</v>
+      </c>
     </row>
     <row r="171" spans="1:11" s="36" customFormat="1">
       <c r="A171" s="21" t="s">
@@ -13103,16 +13364,20 @@
         <v>206</v>
       </c>
       <c r="D171" s="40" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="E171" s="39" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="F171" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G171" s="35"/>
-      <c r="H171" s="33"/>
+      <c r="G171" s="35">
+        <v>3500</v>
+      </c>
+      <c r="H171" s="33" t="s">
+        <v>1273</v>
+      </c>
       <c r="I171" s="33"/>
       <c r="J171" s="33"/>
       <c r="K171" s="33"/>
@@ -13128,16 +13393,20 @@
         <v>210</v>
       </c>
       <c r="D172" s="40" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E172" s="39" t="s">
         <v>1292</v>
-      </c>
-      <c r="E172" s="39" t="s">
-        <v>1294</v>
       </c>
       <c r="F172" s="22" t="s">
         <v>683</v>
       </c>
-      <c r="G172" s="35"/>
-      <c r="H172" s="33"/>
+      <c r="G172" s="35">
+        <v>5000</v>
+      </c>
+      <c r="H172" s="33" t="s">
+        <v>1273</v>
+      </c>
       <c r="I172" s="33"/>
       <c r="J172" s="33"/>
       <c r="K172" s="33"/>
@@ -13162,10 +13431,10 @@
         <v>696</v>
       </c>
       <c r="G173" s="20">
-        <v>14200</v>
+        <v>14550</v>
       </c>
       <c r="H173" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I173" s="23">
         <v>100000</v>
@@ -13174,7 +13443,7 @@
         <v>99000</v>
       </c>
       <c r="K173" s="23">
-        <v>66000</v>
+        <v>57750</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -13197,10 +13466,10 @@
         <v>696</v>
       </c>
       <c r="G174" s="20">
-        <v>38750</v>
+        <v>42750</v>
       </c>
       <c r="H174" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I174" s="23">
         <v>290000</v>
@@ -13209,7 +13478,7 @@
         <v>288000</v>
       </c>
       <c r="K174" s="23">
-        <v>96000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -13232,10 +13501,10 @@
         <v>696</v>
       </c>
       <c r="G175" s="20">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="H175" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I175" s="23">
         <v>200000</v>
@@ -13244,7 +13513,7 @@
         <v>198000</v>
       </c>
       <c r="K175" s="23">
-        <v>198000</v>
+        <v>181500</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -13267,10 +13536,10 @@
         <v>696</v>
       </c>
       <c r="G176" s="20">
-        <v>4475</v>
+        <v>4725</v>
       </c>
       <c r="H176" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I176" s="23">
         <v>100000</v>
@@ -13279,7 +13548,7 @@
         <v>99000</v>
       </c>
       <c r="K176" s="23">
-        <v>57750</v>
+        <v>49500</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -13301,15 +13570,19 @@
       <c r="F177" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="G177" s="20">
-        <v>5000</v>
-      </c>
+      <c r="G177" s="20"/>
       <c r="H177" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I177" s="23"/>
-      <c r="J177" s="23"/>
-      <c r="K177" s="23"/>
+        <v>1318</v>
+      </c>
+      <c r="I177" s="23">
+        <v>40000</v>
+      </c>
+      <c r="J177" s="23">
+        <v>30000</v>
+      </c>
+      <c r="K177" s="23">
+        <v>30000</v>
+      </c>
     </row>
     <row r="178" spans="1:11">
       <c r="A178" s="21" t="s">
@@ -13331,10 +13604,10 @@
         <v>696</v>
       </c>
       <c r="G178" s="20">
-        <v>37000</v>
+        <v>39000</v>
       </c>
       <c r="H178" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I178" s="23"/>
       <c r="J178" s="23"/>
@@ -13360,10 +13633,10 @@
         <v>709</v>
       </c>
       <c r="G179" s="20">
-        <v>14000</v>
+        <v>15500</v>
       </c>
       <c r="H179" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I179" s="23">
         <v>250000</v>
@@ -13372,7 +13645,7 @@
         <v>246000</v>
       </c>
       <c r="K179" s="23">
-        <v>225500</v>
+        <v>205000</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -13395,10 +13668,10 @@
         <v>696</v>
       </c>
       <c r="G180" s="20">
-        <v>9350</v>
+        <v>10100</v>
       </c>
       <c r="H180" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I180" s="23">
         <v>100000</v>
@@ -13407,7 +13680,7 @@
         <v>99000</v>
       </c>
       <c r="K180" s="23">
-        <v>33000</v>
+        <v>24750</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -13430,10 +13703,10 @@
         <v>696</v>
       </c>
       <c r="G181" s="20">
-        <v>12925</v>
+        <v>13000</v>
       </c>
       <c r="H181" s="23" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="I181" s="23">
         <v>100000</v>
@@ -13442,7 +13715,7 @@
         <v>99000</v>
       </c>
       <c r="K181" s="23">
-        <v>12375</v>
+        <v>8250</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -13465,10 +13738,10 @@
         <v>696</v>
       </c>
       <c r="G182" s="20">
-        <v>21500</v>
+        <v>23000</v>
       </c>
       <c r="H182" s="23" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="I182" s="23"/>
       <c r="J182" s="23"/>
@@ -13495,7 +13768,7 @@
       </c>
       <c r="G183" s="35"/>
       <c r="H183" s="33" t="s">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="I183" s="33">
         <v>36000</v>
@@ -13504,7 +13777,7 @@
         <v>24000</v>
       </c>
       <c r="K183" s="33">
-        <v>10000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="184" spans="1:11" s="41" customFormat="1">
@@ -13518,19 +13791,19 @@
         <v>300</v>
       </c>
       <c r="D184" s="40" t="s">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="E184" s="39" t="s">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="F184" s="22" t="s">
         <v>696</v>
       </c>
       <c r="G184" s="35">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H184" s="33" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I184" s="33"/>
       <c r="J184" s="33"/>
@@ -13555,11 +13828,21 @@
       <c r="F185" s="22" t="s">
         <v>728</v>
       </c>
-      <c r="G185" s="20"/>
-      <c r="H185" s="23"/>
-      <c r="I185" s="23"/>
-      <c r="J185" s="23"/>
-      <c r="K185" s="23"/>
+      <c r="G185" s="20">
+        <v>76400</v>
+      </c>
+      <c r="H185" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I185" s="23">
+        <v>400000</v>
+      </c>
+      <c r="J185" s="23">
+        <v>390000</v>
+      </c>
+      <c r="K185" s="23">
+        <v>357500</v>
+      </c>
     </row>
     <row r="186" spans="1:11">
       <c r="A186" s="21" t="s">
@@ -13580,11 +13863,21 @@
       <c r="F186" s="22" t="s">
         <v>728</v>
       </c>
-      <c r="G186" s="20"/>
-      <c r="H186" s="23"/>
-      <c r="I186" s="23"/>
-      <c r="J186" s="23"/>
-      <c r="K186" s="23"/>
+      <c r="G186" s="20">
+        <v>20575</v>
+      </c>
+      <c r="H186" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I186" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J186" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K186" s="23">
+        <v>53625</v>
+      </c>
     </row>
     <row r="187" spans="1:11">
       <c r="A187" s="21" t="s">
@@ -13605,11 +13898,21 @@
       <c r="F187" s="22" t="s">
         <v>735</v>
       </c>
-      <c r="G187" s="20"/>
-      <c r="H187" s="23"/>
-      <c r="I187" s="23"/>
-      <c r="J187" s="23"/>
-      <c r="K187" s="23"/>
+      <c r="G187" s="20">
+        <v>36600</v>
+      </c>
+      <c r="H187" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I187" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J187" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K187" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="188" spans="1:11">
       <c r="A188" s="21" t="s">
@@ -13630,8 +13933,12 @@
       <c r="F188" s="22" t="s">
         <v>735</v>
       </c>
-      <c r="G188" s="20"/>
-      <c r="H188" s="23"/>
+      <c r="G188" s="20">
+        <v>23500</v>
+      </c>
+      <c r="H188" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I188" s="23"/>
       <c r="J188" s="23"/>
       <c r="K188" s="23"/>
@@ -13647,23 +13954,33 @@
         <v>198</v>
       </c>
       <c r="D189" s="22" t="s">
-        <v>349</v>
+        <v>1322</v>
       </c>
       <c r="E189" s="21" t="s">
-        <v>350</v>
+        <v>1323</v>
       </c>
       <c r="F189" s="22" t="s">
         <v>735</v>
       </c>
-      <c r="G189" s="20"/>
-      <c r="H189" s="23"/>
-      <c r="I189" s="23"/>
-      <c r="J189" s="23"/>
-      <c r="K189" s="23"/>
+      <c r="G189" s="20">
+        <v>12500</v>
+      </c>
+      <c r="H189" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I189" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J189" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K189" s="23">
+        <v>66000</v>
+      </c>
     </row>
     <row r="190" spans="1:11">
       <c r="A190" s="21" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B190" s="21" t="s">
         <v>98</v>
@@ -13681,14 +13998,16 @@
         <v>743</v>
       </c>
       <c r="G190" s="20"/>
-      <c r="H190" s="23"/>
+      <c r="H190" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I190" s="23"/>
       <c r="J190" s="23"/>
       <c r="K190" s="23"/>
     </row>
     <row r="191" spans="1:11">
       <c r="A191" s="21" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B191" s="21" t="s">
         <v>98</v>
@@ -13705,15 +14024,19 @@
       <c r="F191" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="G191" s="20"/>
-      <c r="H191" s="23"/>
+      <c r="G191" s="20">
+        <v>32475</v>
+      </c>
+      <c r="H191" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I191" s="23"/>
       <c r="J191" s="23"/>
       <c r="K191" s="23"/>
     </row>
     <row r="192" spans="1:11">
       <c r="A192" s="21" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B192" s="21" t="s">
         <v>98</v>
@@ -13730,15 +14053,19 @@
       <c r="F192" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="G192" s="20"/>
-      <c r="H192" s="23"/>
+      <c r="G192" s="20">
+        <v>16800</v>
+      </c>
+      <c r="H192" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I192" s="23"/>
       <c r="J192" s="23"/>
       <c r="K192" s="23"/>
     </row>
     <row r="193" spans="1:11">
       <c r="A193" s="21" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B193" s="21" t="s">
         <v>98</v>
@@ -13753,15 +14080,25 @@
       <c r="F193" s="22" t="s">
         <v>743</v>
       </c>
-      <c r="G193" s="20"/>
-      <c r="H193" s="23"/>
-      <c r="I193" s="23"/>
-      <c r="J193" s="23"/>
-      <c r="K193" s="23"/>
+      <c r="G193" s="20">
+        <v>44250</v>
+      </c>
+      <c r="H193" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I193" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J193" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K193" s="23">
+        <v>41250</v>
+      </c>
     </row>
     <row r="194" spans="1:11">
       <c r="A194" s="21" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B194" s="21" t="s">
         <v>101</v>
@@ -13776,15 +14113,25 @@
       <c r="F194" s="22" t="s">
         <v>709</v>
       </c>
-      <c r="G194" s="20"/>
-      <c r="H194" s="23"/>
-      <c r="I194" s="23"/>
-      <c r="J194" s="23"/>
-      <c r="K194" s="23"/>
+      <c r="G194" s="20">
+        <v>6200</v>
+      </c>
+      <c r="H194" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I194" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J194" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K194" s="23">
+        <v>74250</v>
+      </c>
     </row>
     <row r="195" spans="1:11">
       <c r="A195" s="21" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B195" s="21" t="s">
         <v>101</v>
@@ -13799,15 +14146,19 @@
       <c r="F195" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G195" s="20"/>
-      <c r="H195" s="23"/>
+      <c r="G195" s="20">
+        <v>12000</v>
+      </c>
+      <c r="H195" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I195" s="23"/>
       <c r="J195" s="23"/>
       <c r="K195" s="23"/>
     </row>
     <row r="196" spans="1:11">
       <c r="A196" s="21" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B196" s="21" t="s">
         <v>101</v>
@@ -13822,1126 +14173,1510 @@
       <c r="F196" s="22" t="s">
         <v>696</v>
       </c>
-      <c r="G196" s="20"/>
-      <c r="H196" s="23"/>
+      <c r="G196" s="20">
+        <v>6500</v>
+      </c>
+      <c r="H196" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I196" s="23"/>
       <c r="J196" s="23"/>
       <c r="K196" s="23"/>
     </row>
-    <row r="197" spans="1:11">
+    <row r="197" spans="1:11" s="42" customFormat="1">
       <c r="A197" s="21" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C197" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="D197" s="22" t="s">
-        <v>759</v>
-      </c>
-      <c r="E197" s="21" t="s">
-        <v>760</v>
+        <v>194</v>
+      </c>
+      <c r="D197" s="40" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E197" s="39" t="s">
+        <v>1325</v>
       </c>
       <c r="F197" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="G197" s="20"/>
-      <c r="H197" s="23"/>
-      <c r="I197" s="23"/>
-      <c r="J197" s="23"/>
-      <c r="K197" s="23"/>
+        <v>696</v>
+      </c>
+      <c r="G197" s="35">
+        <v>4150</v>
+      </c>
+      <c r="H197" s="33" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I197" s="33">
+        <v>100000</v>
+      </c>
+      <c r="J197" s="33">
+        <v>99000</v>
+      </c>
+      <c r="K197" s="33">
+        <v>74250</v>
+      </c>
     </row>
     <row r="198" spans="1:11">
       <c r="A198" s="21" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B198" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C198" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D198" s="22" t="s">
-        <v>763</v>
+        <v>1324</v>
       </c>
       <c r="E198" s="21" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="F198" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="G198" s="20"/>
-      <c r="H198" s="23"/>
-      <c r="I198" s="23"/>
-      <c r="J198" s="23"/>
-      <c r="K198" s="23"/>
+        <v>760</v>
+      </c>
+      <c r="G198" s="20">
+        <v>49950</v>
+      </c>
+      <c r="H198" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I198" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J198" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K198" s="23">
+        <v>10250</v>
+      </c>
     </row>
     <row r="199" spans="1:11">
       <c r="A199" s="21" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B199" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C199" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D199" s="22" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E199" s="21" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="F199" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="G199" s="20"/>
-      <c r="H199" s="23"/>
-      <c r="I199" s="23"/>
-      <c r="J199" s="23"/>
-      <c r="K199" s="23"/>
+        <v>760</v>
+      </c>
+      <c r="G199" s="20">
+        <v>37350</v>
+      </c>
+      <c r="H199" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I199" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J199" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K199" s="23">
+        <v>180000</v>
+      </c>
     </row>
     <row r="200" spans="1:11">
       <c r="A200" s="21" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B200" s="21" t="s">
         <v>103</v>
       </c>
       <c r="C200" s="21" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D200" s="22" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="E200" s="21" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="F200" s="22" t="s">
-        <v>761</v>
-      </c>
-      <c r="G200" s="20"/>
-      <c r="H200" s="23"/>
-      <c r="I200" s="23"/>
-      <c r="J200" s="23"/>
-      <c r="K200" s="23"/>
+        <v>760</v>
+      </c>
+      <c r="G200" s="20">
+        <v>31525</v>
+      </c>
+      <c r="H200" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I200" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J200" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K200" s="23">
+        <v>125000</v>
+      </c>
     </row>
     <row r="201" spans="1:11">
       <c r="A201" s="21" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B201" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C201" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D201" s="22" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E201" s="21" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F201" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G201" s="20"/>
-      <c r="H201" s="23"/>
-      <c r="I201" s="23"/>
-      <c r="J201" s="23"/>
-      <c r="K201" s="23"/>
-    </row>
-    <row r="202" spans="1:11">
+        <v>760</v>
+      </c>
+      <c r="G201" s="20">
+        <v>25000</v>
+      </c>
+      <c r="H201" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I201" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J201" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K201" s="23">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" s="42" customFormat="1">
       <c r="A202" s="21" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B202" s="21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C202" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D202" s="22" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
       <c r="E202" s="21" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="F202" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G202" s="20"/>
-      <c r="H202" s="23"/>
-      <c r="I202" s="23"/>
-      <c r="J202" s="23"/>
-      <c r="K202" s="23"/>
+        <v>760</v>
+      </c>
+      <c r="G202" s="35"/>
+      <c r="H202" s="33" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I202" s="33">
+        <v>80000</v>
+      </c>
+      <c r="J202" s="33">
+        <v>66000</v>
+      </c>
+      <c r="K202" s="33">
+        <v>11000</v>
+      </c>
     </row>
     <row r="203" spans="1:11">
       <c r="A203" s="21" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B203" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C203" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D203" s="22" t="s">
-        <v>779</v>
+        <v>771</v>
       </c>
       <c r="E203" s="21" t="s">
-        <v>780</v>
+        <v>772</v>
       </c>
       <c r="F203" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G203" s="20"/>
-      <c r="H203" s="23"/>
-      <c r="I203" s="23"/>
-      <c r="J203" s="23"/>
-      <c r="K203" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G203" s="20">
+        <v>25550</v>
+      </c>
+      <c r="H203" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I203" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J203" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K203" s="23">
+        <v>66000</v>
+      </c>
     </row>
     <row r="204" spans="1:11">
       <c r="A204" s="21" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B204" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C204" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D204" s="22" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="E204" s="21" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="F204" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G204" s="20"/>
-      <c r="H204" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G204" s="20">
+        <v>22700</v>
+      </c>
+      <c r="H204" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I204" s="23"/>
       <c r="J204" s="23"/>
       <c r="K204" s="23"/>
     </row>
     <row r="205" spans="1:11">
       <c r="A205" s="21" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B205" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C205" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D205" s="22" t="s">
-        <v>785</v>
-      </c>
-      <c r="E205" s="21"/>
+        <v>778</v>
+      </c>
+      <c r="E205" s="21" t="s">
+        <v>779</v>
+      </c>
       <c r="F205" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G205" s="20"/>
-      <c r="H205" s="23"/>
-      <c r="I205" s="23"/>
-      <c r="J205" s="23"/>
-      <c r="K205" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G205" s="20">
+        <v>17000</v>
+      </c>
+      <c r="H205" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I205" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J205" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K205" s="23">
+        <v>264000</v>
+      </c>
     </row>
     <row r="206" spans="1:11">
       <c r="A206" s="21" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B206" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C206" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D206" s="22" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="E206" s="21" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F206" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G206" s="20"/>
-      <c r="H206" s="23"/>
-      <c r="I206" s="23"/>
-      <c r="J206" s="23"/>
-      <c r="K206" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G206" s="20">
+        <v>14000</v>
+      </c>
+      <c r="H206" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I206" s="23">
+        <v>70000</v>
+      </c>
+      <c r="J206" s="23">
+        <v>60000</v>
+      </c>
+      <c r="K206" s="23">
+        <v>5000</v>
+      </c>
     </row>
     <row r="207" spans="1:11">
       <c r="A207" s="21" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B207" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C207" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D207" s="22" t="s">
-        <v>790</v>
-      </c>
-      <c r="E207" s="21" t="s">
-        <v>791</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="E207" s="21"/>
       <c r="F207" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G207" s="20"/>
-      <c r="H207" s="23"/>
-      <c r="I207" s="23"/>
-      <c r="J207" s="23"/>
-      <c r="K207" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G207" s="20">
+        <v>11000</v>
+      </c>
+      <c r="H207" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I207" s="23">
+        <v>150000</v>
+      </c>
+      <c r="J207" s="23">
+        <v>150000</v>
+      </c>
+      <c r="K207" s="23">
+        <v>87500</v>
+      </c>
     </row>
     <row r="208" spans="1:11">
       <c r="A208" s="21" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B208" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C208" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D208" s="22" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="E208" s="21" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="F208" s="22" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G208" s="20"/>
-      <c r="H208" s="23"/>
+      <c r="H208" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I208" s="23"/>
       <c r="J208" s="23"/>
       <c r="K208" s="23"/>
     </row>
     <row r="209" spans="1:11">
       <c r="A209" s="21" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B209" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C209" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D209" s="22" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="E209" s="21" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="F209" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G209" s="20"/>
-      <c r="H209" s="23"/>
-      <c r="I209" s="23"/>
-      <c r="J209" s="23"/>
-      <c r="K209" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G209" s="20">
+        <v>23850</v>
+      </c>
+      <c r="H209" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I209" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J209" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K209" s="23">
+        <v>33000</v>
+      </c>
     </row>
     <row r="210" spans="1:11">
       <c r="A210" s="21" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B210" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C210" s="21" t="s">
-        <v>262</v>
+        <v>210</v>
       </c>
       <c r="D210" s="22" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="E210" s="21" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="F210" s="22" t="s">
-        <v>774</v>
-      </c>
-      <c r="G210" s="20"/>
-      <c r="H210" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G210" s="20">
+        <v>63400</v>
+      </c>
+      <c r="H210" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I210" s="23"/>
       <c r="J210" s="23"/>
       <c r="K210" s="23"/>
     </row>
     <row r="211" spans="1:11">
       <c r="A211" s="21" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B211" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C211" s="21" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="D211" s="22" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="E211" s="21" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="F211" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G211" s="20"/>
-      <c r="H211" s="23"/>
-      <c r="I211" s="23"/>
-      <c r="J211" s="23"/>
-      <c r="K211" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G211" s="20">
+        <v>19600</v>
+      </c>
+      <c r="H211" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I211" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J211" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K211" s="23">
+        <v>24750</v>
+      </c>
     </row>
     <row r="212" spans="1:11">
       <c r="A212" s="21" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B212" s="21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C212" s="21" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="D212" s="22" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="E212" s="21" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="F212" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G212" s="20"/>
-      <c r="H212" s="23"/>
+        <v>773</v>
+      </c>
+      <c r="G212" s="20">
+        <v>89000</v>
+      </c>
+      <c r="H212" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I212" s="23"/>
       <c r="J212" s="23"/>
       <c r="K212" s="23"/>
     </row>
     <row r="213" spans="1:11">
       <c r="A213" s="21" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B213" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C213" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D213" s="22" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="E213" s="21" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="F213" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G213" s="20"/>
-      <c r="H213" s="23"/>
-      <c r="I213" s="23"/>
-      <c r="J213" s="23"/>
-      <c r="K213" s="23"/>
+        <v>803</v>
+      </c>
+      <c r="G213" s="20">
+        <v>6700</v>
+      </c>
+      <c r="H213" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I213" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J213" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K213" s="23">
+        <v>16500</v>
+      </c>
     </row>
     <row r="214" spans="1:11">
       <c r="A214" s="21" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B214" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C214" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D214" s="22" t="s">
-        <v>812</v>
+        <v>805</v>
       </c>
       <c r="E214" s="21" t="s">
-        <v>813</v>
+        <v>806</v>
       </c>
       <c r="F214" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G214" s="20"/>
-      <c r="H214" s="23"/>
-      <c r="I214" s="23"/>
-      <c r="J214" s="23"/>
-      <c r="K214" s="23"/>
+        <v>803</v>
+      </c>
+      <c r="G214" s="20">
+        <v>5500</v>
+      </c>
+      <c r="H214" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I214" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J214" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K214" s="23">
+        <v>24750</v>
+      </c>
     </row>
     <row r="215" spans="1:11">
       <c r="A215" s="21" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B215" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C215" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D215" s="22" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="E215" s="21" t="s">
-        <v>816</v>
+        <v>809</v>
       </c>
       <c r="F215" s="22" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G215" s="20"/>
-      <c r="H215" s="23"/>
-      <c r="I215" s="23"/>
-      <c r="J215" s="23"/>
-      <c r="K215" s="23"/>
+      <c r="H215" s="23" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I215" s="23">
+        <v>360000</v>
+      </c>
+      <c r="J215" s="23">
+        <v>279000</v>
+      </c>
+      <c r="K215" s="23">
+        <v>23250</v>
+      </c>
     </row>
     <row r="216" spans="1:11">
       <c r="A216" s="21" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B216" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C216" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D216" s="22" t="s">
-        <v>818</v>
+        <v>811</v>
       </c>
       <c r="E216" s="21" t="s">
-        <v>819</v>
+        <v>812</v>
       </c>
       <c r="F216" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G216" s="20"/>
-      <c r="H216" s="23"/>
-      <c r="I216" s="23"/>
-      <c r="J216" s="23"/>
-      <c r="K216" s="23"/>
+        <v>803</v>
+      </c>
+      <c r="G216" s="20">
+        <v>5750</v>
+      </c>
+      <c r="H216" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I216" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J216" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K216" s="23">
+        <v>16500</v>
+      </c>
     </row>
     <row r="217" spans="1:11">
       <c r="A217" s="21" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B217" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C217" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D217" s="22" t="s">
-        <v>1277</v>
+        <v>814</v>
       </c>
       <c r="E217" s="21" t="s">
-        <v>1278</v>
+        <v>815</v>
       </c>
       <c r="F217" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G217" s="35"/>
-      <c r="H217" s="23"/>
-      <c r="I217" s="23"/>
-      <c r="J217" s="23"/>
-      <c r="K217" s="33"/>
+        <v>803</v>
+      </c>
+      <c r="G217" s="20">
+        <v>5500</v>
+      </c>
+      <c r="H217" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I217" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J217" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K217" s="23">
+        <v>24750</v>
+      </c>
     </row>
     <row r="218" spans="1:11">
       <c r="A218" s="21" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B218" s="21" t="s">
         <v>108</v>
       </c>
       <c r="C218" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D218" s="22" t="s">
-        <v>1279</v>
+        <v>817</v>
       </c>
       <c r="E218" s="21" t="s">
-        <v>1280</v>
+        <v>818</v>
       </c>
       <c r="F218" s="22" t="s">
-        <v>804</v>
-      </c>
-      <c r="G218" s="35"/>
-      <c r="H218" s="23"/>
-      <c r="I218" s="23"/>
-      <c r="J218" s="23"/>
-      <c r="K218" s="33"/>
+        <v>803</v>
+      </c>
+      <c r="G218" s="20">
+        <v>3000</v>
+      </c>
+      <c r="H218" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I218" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J218" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K218" s="23">
+        <v>49500</v>
+      </c>
     </row>
     <row r="219" spans="1:11">
       <c r="A219" s="21" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B219" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C219" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D219" s="22" t="s">
-        <v>821</v>
+        <v>1275</v>
       </c>
       <c r="E219" s="21" t="s">
-        <v>822</v>
+        <v>1276</v>
       </c>
       <c r="F219" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="G219" s="20"/>
-      <c r="H219" s="23"/>
-      <c r="I219" s="23"/>
-      <c r="J219" s="23"/>
-      <c r="K219" s="23"/>
+        <v>803</v>
+      </c>
+      <c r="G219" s="35">
+        <v>3500</v>
+      </c>
+      <c r="H219" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I219" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J219" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K219" s="33">
+        <v>57750</v>
+      </c>
     </row>
     <row r="220" spans="1:11">
       <c r="A220" s="21" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B220" s="21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C220" s="21" t="s">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="D220" s="22" t="s">
-        <v>824</v>
+        <v>1277</v>
       </c>
       <c r="E220" s="21" t="s">
-        <v>825</v>
+        <v>1278</v>
       </c>
       <c r="F220" s="22" t="s">
-        <v>696</v>
-      </c>
-      <c r="G220" s="20"/>
-      <c r="H220" s="23"/>
-      <c r="I220" s="23"/>
-      <c r="J220" s="23"/>
-      <c r="K220" s="23"/>
+        <v>803</v>
+      </c>
+      <c r="G220" s="35">
+        <v>3500</v>
+      </c>
+      <c r="H220" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I220" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J220" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K220" s="33">
+        <v>57750</v>
+      </c>
     </row>
     <row r="221" spans="1:11">
       <c r="A221" s="21" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="B221" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C221" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D221" s="22" t="s">
-        <v>827</v>
+        <v>820</v>
       </c>
       <c r="E221" s="21" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="F221" s="22" t="s">
-        <v>696</v>
-      </c>
-      <c r="G221" s="20"/>
-      <c r="H221" s="23"/>
-      <c r="I221" s="23"/>
-      <c r="J221" s="23"/>
-      <c r="K221" s="23"/>
+        <v>709</v>
+      </c>
+      <c r="G221" s="20">
+        <v>22200</v>
+      </c>
+      <c r="H221" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I221" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J221" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K221" s="23">
+        <v>264000</v>
+      </c>
     </row>
     <row r="222" spans="1:11">
       <c r="A222" s="21" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="B222" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C222" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D222" s="22" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="E222" s="21" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="F222" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="G222" s="20"/>
-      <c r="H222" s="23"/>
-      <c r="I222" s="23"/>
-      <c r="J222" s="23"/>
-      <c r="K222" s="23"/>
+        <v>696</v>
+      </c>
+      <c r="G222" s="20">
+        <v>14700</v>
+      </c>
+      <c r="H222" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I222" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J222" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K222" s="23">
+        <v>264000</v>
+      </c>
     </row>
     <row r="223" spans="1:11">
       <c r="A223" s="21" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="B223" s="21" t="s">
         <v>110</v>
       </c>
       <c r="C223" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="E223" s="21" t="s">
-        <v>834</v>
+        <v>827</v>
       </c>
       <c r="F223" s="22" t="s">
-        <v>709</v>
-      </c>
-      <c r="G223" s="20"/>
-      <c r="H223" s="23"/>
-      <c r="I223" s="23"/>
-      <c r="J223" s="23"/>
-      <c r="K223" s="23"/>
+        <v>696</v>
+      </c>
+      <c r="G223" s="20">
+        <v>13700</v>
+      </c>
+      <c r="H223" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I223" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J223" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K223" s="23">
+        <v>225500</v>
+      </c>
     </row>
     <row r="224" spans="1:11">
       <c r="A224" s="21" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B224" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C224" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D224" s="22" t="s">
-        <v>1269</v>
+        <v>829</v>
       </c>
       <c r="E224" s="21" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="F224" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G224" s="20"/>
-      <c r="H224" s="23"/>
-      <c r="I224" s="23"/>
-      <c r="J224" s="23"/>
-      <c r="K224" s="23"/>
+        <v>709</v>
+      </c>
+      <c r="G224" s="20">
+        <v>14000</v>
+      </c>
+      <c r="H224" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I224" s="23">
+        <v>290000</v>
+      </c>
+      <c r="J224" s="23">
+        <v>288000</v>
+      </c>
+      <c r="K224" s="23">
+        <v>264000</v>
+      </c>
     </row>
     <row r="225" spans="1:11">
       <c r="A225" s="21" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B225" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C225" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D225" s="22" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="E225" s="21" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
       <c r="F225" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G225" s="20"/>
-      <c r="H225" s="23"/>
-      <c r="I225" s="23"/>
-      <c r="J225" s="23"/>
-      <c r="K225" s="23"/>
+        <v>709</v>
+      </c>
+      <c r="G225" s="20">
+        <v>10000</v>
+      </c>
+      <c r="H225" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I225" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J225" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K225" s="23">
+        <v>16500</v>
+      </c>
     </row>
     <row r="226" spans="1:11">
       <c r="A226" s="21" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B226" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C226" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D226" s="22" t="s">
-        <v>842</v>
+        <v>1267</v>
       </c>
       <c r="E226" s="21" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="F226" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G226" s="20"/>
-      <c r="H226" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G226" s="20">
+        <v>22100</v>
+      </c>
+      <c r="H226" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I226" s="23"/>
       <c r="J226" s="23"/>
       <c r="K226" s="23"/>
     </row>
     <row r="227" spans="1:11">
       <c r="A227" s="21" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B227" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C227" s="21" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D227" s="22" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="E227" s="21" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="F227" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G227" s="20"/>
-      <c r="H227" s="23"/>
-      <c r="I227" s="23"/>
-      <c r="J227" s="23"/>
-      <c r="K227" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G227" s="20">
+        <v>17100</v>
+      </c>
+      <c r="H227" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I227" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J227" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K227" s="23">
+        <v>115500</v>
+      </c>
     </row>
     <row r="228" spans="1:11">
       <c r="A228" s="21" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B228" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C228" s="21" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="D228" s="22" t="s">
-        <v>1270</v>
+        <v>841</v>
       </c>
       <c r="E228" s="21" t="s">
-        <v>1272</v>
+        <v>842</v>
       </c>
       <c r="F228" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G228" s="20"/>
-      <c r="H228" s="23"/>
-      <c r="I228" s="23"/>
-      <c r="J228" s="23"/>
-      <c r="K228" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G228" s="20">
+        <v>19000</v>
+      </c>
+      <c r="H228" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I228" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J228" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K228" s="23">
+        <v>115500</v>
+      </c>
     </row>
     <row r="229" spans="1:11">
       <c r="A229" s="21" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B229" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C229" s="21" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="D229" s="22" t="s">
-        <v>1271</v>
+        <v>844</v>
       </c>
       <c r="E229" s="21" t="s">
+        <v>845</v>
+      </c>
+      <c r="F229" s="22" t="s">
+        <v>836</v>
+      </c>
+      <c r="G229" s="20">
+        <v>36000</v>
+      </c>
+      <c r="H229" s="23" t="s">
         <v>1273</v>
       </c>
-      <c r="F229" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G229" s="20"/>
-      <c r="H229" s="23"/>
       <c r="I229" s="23"/>
       <c r="J229" s="23"/>
       <c r="K229" s="23"/>
     </row>
     <row r="230" spans="1:11">
       <c r="A230" s="21" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B230" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C230" s="21" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="D230" s="22" t="s">
-        <v>850</v>
+        <v>1268</v>
       </c>
       <c r="E230" s="21" t="s">
-        <v>851</v>
+        <v>1270</v>
       </c>
       <c r="F230" s="22" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G230" s="20"/>
-      <c r="H230" s="23"/>
+      <c r="H230" s="23" t="s">
+        <v>1273</v>
+      </c>
       <c r="I230" s="23"/>
       <c r="J230" s="23"/>
       <c r="K230" s="23"/>
     </row>
     <row r="231" spans="1:11">
       <c r="A231" s="21" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B231" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C231" s="21" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D231" s="22" t="s">
-        <v>853</v>
+        <v>1269</v>
       </c>
       <c r="E231" s="21" t="s">
-        <v>854</v>
+        <v>1271</v>
       </c>
       <c r="F231" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G231" s="20"/>
-      <c r="H231" s="23"/>
-      <c r="I231" s="23"/>
-      <c r="J231" s="23"/>
-      <c r="K231" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G231" s="20">
+        <v>3750</v>
+      </c>
+      <c r="H231" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I231" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J231" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K231" s="23">
+        <v>90750</v>
+      </c>
     </row>
     <row r="232" spans="1:11">
       <c r="A232" s="21" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B232" s="21" t="s">
         <v>112</v>
       </c>
       <c r="C232" s="21" t="s">
-        <v>258</v>
+        <v>206</v>
       </c>
       <c r="D232" s="22" t="s">
-        <v>856</v>
+        <v>1272</v>
       </c>
       <c r="E232" s="21" t="s">
-        <v>857</v>
+        <v>849</v>
       </c>
       <c r="F232" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G232" s="20"/>
-      <c r="H232" s="23"/>
-      <c r="I232" s="23"/>
-      <c r="J232" s="23"/>
-      <c r="K232" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G232" s="20">
+        <v>56500</v>
+      </c>
+      <c r="H232" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I232" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J232" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K232" s="23">
+        <v>82000</v>
+      </c>
     </row>
     <row r="233" spans="1:11">
       <c r="A233" s="21" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B233" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C233" s="21" t="s">
-        <v>174</v>
+        <v>210</v>
       </c>
       <c r="D233" s="22" t="s">
-        <v>859</v>
+        <v>851</v>
       </c>
       <c r="E233" s="21" t="s">
-        <v>860</v>
+        <v>852</v>
       </c>
       <c r="F233" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G233" s="20"/>
-      <c r="H233" s="23"/>
-      <c r="I233" s="23"/>
-      <c r="J233" s="23"/>
-      <c r="K233" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G233" s="20">
+        <v>31400</v>
+      </c>
+      <c r="H233" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I233" s="23">
+        <v>250000</v>
+      </c>
+      <c r="J233" s="23">
+        <v>246000</v>
+      </c>
+      <c r="K233" s="23">
+        <v>92250</v>
+      </c>
     </row>
     <row r="234" spans="1:11">
       <c r="A234" s="21" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B234" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C234" s="21" t="s">
-        <v>179</v>
+        <v>258</v>
       </c>
       <c r="D234" s="22" t="s">
-        <v>862</v>
+        <v>854</v>
       </c>
       <c r="E234" s="21" t="s">
-        <v>863</v>
+        <v>855</v>
       </c>
       <c r="F234" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G234" s="20"/>
-      <c r="H234" s="23"/>
-      <c r="I234" s="23"/>
-      <c r="J234" s="23"/>
-      <c r="K234" s="23"/>
-    </row>
-    <row r="235" spans="1:11">
+        <v>836</v>
+      </c>
+      <c r="G234" s="20">
+        <v>22750</v>
+      </c>
+      <c r="H234" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I234" s="23">
+        <v>200000</v>
+      </c>
+      <c r="J234" s="23">
+        <v>198000</v>
+      </c>
+      <c r="K234" s="23">
+        <v>82500</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" s="43" customFormat="1">
       <c r="A235" s="21" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B235" s="21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C235" s="21" t="s">
-        <v>190</v>
-      </c>
-      <c r="D235" s="22" t="s">
-        <v>865</v>
-      </c>
-      <c r="E235" s="21" t="s">
-        <v>866</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="D235" s="40" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E235" s="39"/>
       <c r="F235" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G235" s="20"/>
-      <c r="H235" s="23"/>
-      <c r="I235" s="23"/>
-      <c r="J235" s="23"/>
-      <c r="K235" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G235" s="35"/>
+      <c r="H235" s="33" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I235" s="33">
+        <v>81000</v>
+      </c>
+      <c r="J235" s="33">
+        <v>60000</v>
+      </c>
+      <c r="K235" s="33">
+        <v>60000</v>
+      </c>
     </row>
     <row r="236" spans="1:11">
       <c r="A236" s="21" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B236" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C236" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D236" s="22" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="E236" s="21" t="s">
-        <v>869</v>
+        <v>858</v>
       </c>
       <c r="F236" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G236" s="20"/>
-      <c r="H236" s="23"/>
-      <c r="I236" s="23"/>
-      <c r="J236" s="23"/>
-      <c r="K236" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G236" s="20">
+        <v>14250</v>
+      </c>
+      <c r="H236" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I236" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J236" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K236" s="23">
+        <v>41250</v>
+      </c>
     </row>
     <row r="237" spans="1:11">
       <c r="A237" s="21" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B237" s="21" t="s">
         <v>115</v>
       </c>
       <c r="C237" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D237" s="22" t="s">
-        <v>871</v>
-      </c>
-      <c r="E237" s="21"/>
+        <v>860</v>
+      </c>
+      <c r="E237" s="21" t="s">
+        <v>861</v>
+      </c>
       <c r="F237" s="22" t="s">
-        <v>837</v>
-      </c>
-      <c r="G237" s="20"/>
-      <c r="H237" s="23"/>
-      <c r="I237" s="23"/>
-      <c r="J237" s="23"/>
-      <c r="K237" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G237" s="20">
+        <v>8200</v>
+      </c>
+      <c r="H237" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I237" s="23">
+        <v>50000</v>
+      </c>
+      <c r="J237" s="23">
+        <v>48000</v>
+      </c>
+      <c r="K237" s="23">
+        <v>28000</v>
+      </c>
     </row>
     <row r="238" spans="1:11">
       <c r="A238" s="21" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="B238" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C238" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D238" s="22" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="E238" s="21" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="F238" s="22" t="s">
-        <v>875</v>
-      </c>
-      <c r="G238" s="20"/>
-      <c r="H238" s="23"/>
-      <c r="I238" s="23"/>
-      <c r="J238" s="23"/>
-      <c r="K238" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G238" s="20">
+        <v>13400</v>
+      </c>
+      <c r="H238" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I238" s="23">
+        <v>80000</v>
+      </c>
+      <c r="J238" s="23">
+        <v>78000</v>
+      </c>
+      <c r="K238" s="23">
+        <v>39000</v>
+      </c>
     </row>
     <row r="239" spans="1:11">
       <c r="A239" s="21" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="B239" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C239" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D239" s="22" t="s">
-        <v>877</v>
+        <v>866</v>
       </c>
       <c r="E239" s="21" t="s">
-        <v>878</v>
+        <v>867</v>
       </c>
       <c r="F239" s="22" t="s">
-        <v>875</v>
-      </c>
-      <c r="G239" s="20"/>
-      <c r="H239" s="23"/>
-      <c r="I239" s="23"/>
-      <c r="J239" s="23"/>
-      <c r="K239" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G239" s="20">
+        <v>9475</v>
+      </c>
+      <c r="H239" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I239" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J239" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K239" s="23">
+        <v>41250</v>
+      </c>
     </row>
     <row r="240" spans="1:11">
       <c r="A240" s="21" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="B240" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C240" s="21" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D240" s="22" t="s">
-        <v>880</v>
-      </c>
-      <c r="E240" s="21" t="s">
-        <v>881</v>
-      </c>
+        <v>869</v>
+      </c>
+      <c r="E240" s="21"/>
       <c r="F240" s="22" t="s">
-        <v>875</v>
-      </c>
-      <c r="G240" s="20"/>
-      <c r="H240" s="23"/>
+        <v>836</v>
+      </c>
+      <c r="G240" s="20">
+        <v>42925</v>
+      </c>
+      <c r="H240" s="23" t="s">
+        <v>1274</v>
+      </c>
       <c r="I240" s="23"/>
       <c r="J240" s="23"/>
       <c r="K240" s="23"/>
     </row>
     <row r="241" spans="1:11">
       <c r="A241" s="21" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="B241" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C241" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D241" s="22" t="s">
-        <v>883</v>
+        <v>871</v>
       </c>
       <c r="E241" s="21" t="s">
-        <v>884</v>
+        <v>872</v>
       </c>
       <c r="F241" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G241" s="20"/>
       <c r="H241" s="23"/>
@@ -14951,22 +15686,22 @@
     </row>
     <row r="242" spans="1:11">
       <c r="A242" s="21" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="B242" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C242" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D242" s="22" t="s">
-        <v>886</v>
+        <v>875</v>
       </c>
       <c r="E242" s="21" t="s">
-        <v>887</v>
+        <v>876</v>
       </c>
       <c r="F242" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G242" s="20"/>
       <c r="H242" s="23"/>
@@ -14976,22 +15711,22 @@
     </row>
     <row r="243" spans="1:11">
       <c r="A243" s="21" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="B243" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C243" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D243" s="22" t="s">
-        <v>889</v>
+        <v>878</v>
       </c>
       <c r="E243" s="21" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="F243" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G243" s="20"/>
       <c r="H243" s="23"/>
@@ -15001,22 +15736,22 @@
     </row>
     <row r="244" spans="1:11">
       <c r="A244" s="21" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="B244" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C244" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D244" s="22" t="s">
-        <v>892</v>
+        <v>881</v>
       </c>
       <c r="E244" s="21" t="s">
-        <v>893</v>
+        <v>882</v>
       </c>
       <c r="F244" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G244" s="20"/>
       <c r="H244" s="23"/>
@@ -15026,22 +15761,22 @@
     </row>
     <row r="245" spans="1:11">
       <c r="A245" s="21" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="B245" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C245" s="21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D245" s="22" t="s">
-        <v>895</v>
+        <v>884</v>
       </c>
       <c r="E245" s="21" t="s">
-        <v>896</v>
+        <v>885</v>
       </c>
       <c r="F245" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G245" s="20"/>
       <c r="H245" s="23"/>
@@ -15051,22 +15786,22 @@
     </row>
     <row r="246" spans="1:11">
       <c r="A246" s="21" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="B246" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C246" s="21" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="D246" s="22" t="s">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="E246" s="21" t="s">
-        <v>899</v>
+        <v>888</v>
       </c>
       <c r="F246" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G246" s="20"/>
       <c r="H246" s="23"/>
@@ -15076,22 +15811,22 @@
     </row>
     <row r="247" spans="1:11">
       <c r="A247" s="21" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="B247" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C247" s="21" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D247" s="22" t="s">
-        <v>901</v>
+        <v>890</v>
       </c>
       <c r="E247" s="21" t="s">
-        <v>902</v>
+        <v>891</v>
       </c>
       <c r="F247" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G247" s="20"/>
       <c r="H247" s="23"/>
@@ -15101,22 +15836,22 @@
     </row>
     <row r="248" spans="1:11">
       <c r="A248" s="21" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="B248" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C248" s="21" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="D248" s="22" t="s">
-        <v>904</v>
+        <v>893</v>
       </c>
       <c r="E248" s="21" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="F248" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G248" s="20"/>
       <c r="H248" s="23"/>
@@ -15126,22 +15861,22 @@
     </row>
     <row r="249" spans="1:11">
       <c r="A249" s="21" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B249" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C249" s="21" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="D249" s="22" t="s">
-        <v>907</v>
+        <v>896</v>
       </c>
       <c r="E249" s="21" t="s">
-        <v>908</v>
+        <v>897</v>
       </c>
       <c r="F249" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G249" s="20"/>
       <c r="H249" s="23"/>
@@ -15151,22 +15886,22 @@
     </row>
     <row r="250" spans="1:11">
       <c r="A250" s="21" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="B250" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C250" s="21" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D250" s="22" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="E250" s="21" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="F250" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G250" s="20"/>
       <c r="H250" s="23"/>
@@ -15176,22 +15911,22 @@
     </row>
     <row r="251" spans="1:11">
       <c r="A251" s="21" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="B251" s="21" t="s">
         <v>117</v>
       </c>
       <c r="C251" s="21" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D251" s="22" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="E251" s="21" t="s">
-        <v>914</v>
+        <v>903</v>
       </c>
       <c r="F251" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G251" s="20"/>
       <c r="H251" s="23"/>
@@ -15201,22 +15936,22 @@
     </row>
     <row r="252" spans="1:11">
       <c r="A252" s="21" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="B252" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C252" s="21" t="s">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="D252" s="22" t="s">
-        <v>916</v>
+        <v>905</v>
       </c>
       <c r="E252" s="21" t="s">
-        <v>917</v>
+        <v>906</v>
       </c>
       <c r="F252" s="22" t="s">
-        <v>918</v>
+        <v>873</v>
       </c>
       <c r="G252" s="20"/>
       <c r="H252" s="23"/>
@@ -15226,22 +15961,22 @@
     </row>
     <row r="253" spans="1:11">
       <c r="A253" s="21" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="B253" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C253" s="21" t="s">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="D253" s="22" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="E253" s="21" t="s">
-        <v>921</v>
+        <v>909</v>
       </c>
       <c r="F253" s="22" t="s">
-        <v>918</v>
+        <v>873</v>
       </c>
       <c r="G253" s="20"/>
       <c r="H253" s="23"/>
@@ -15251,22 +15986,22 @@
     </row>
     <row r="254" spans="1:11">
       <c r="A254" s="21" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="B254" s="21" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C254" s="21" t="s">
-        <v>190</v>
+        <v>308</v>
       </c>
       <c r="D254" s="22" t="s">
-        <v>923</v>
+        <v>911</v>
       </c>
       <c r="E254" s="21" t="s">
-        <v>924</v>
+        <v>912</v>
       </c>
       <c r="F254" s="22" t="s">
-        <v>918</v>
+        <v>873</v>
       </c>
       <c r="G254" s="20"/>
       <c r="H254" s="23"/>
@@ -15276,22 +16011,22 @@
     </row>
     <row r="255" spans="1:11">
       <c r="A255" s="21" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="B255" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C255" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D255" s="22" t="s">
-        <v>926</v>
+        <v>914</v>
       </c>
       <c r="E255" s="21" t="s">
-        <v>927</v>
+        <v>915</v>
       </c>
       <c r="F255" s="22" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G255" s="20"/>
       <c r="H255" s="23"/>
@@ -15301,22 +16036,22 @@
     </row>
     <row r="256" spans="1:11">
       <c r="A256" s="21" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B256" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C256" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D256" s="22" t="s">
-        <v>929</v>
+        <v>918</v>
       </c>
       <c r="E256" s="21" t="s">
-        <v>930</v>
+        <v>919</v>
       </c>
       <c r="F256" s="22" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G256" s="20"/>
       <c r="H256" s="23"/>
@@ -15326,22 +16061,22 @@
     </row>
     <row r="257" spans="1:11">
       <c r="A257" s="21" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="B257" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C257" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D257" s="22" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="E257" s="21" t="s">
-        <v>933</v>
+        <v>922</v>
       </c>
       <c r="F257" s="22" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G257" s="20"/>
       <c r="H257" s="23"/>
@@ -15351,22 +16086,22 @@
     </row>
     <row r="258" spans="1:11">
       <c r="A258" s="21" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B258" s="21" t="s">
         <v>122</v>
       </c>
       <c r="C258" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D258" s="22" t="s">
-        <v>935</v>
+        <v>924</v>
       </c>
       <c r="E258" s="21" t="s">
-        <v>936</v>
+        <v>925</v>
       </c>
       <c r="F258" s="22" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="G258" s="20"/>
       <c r="H258" s="23"/>
@@ -15376,22 +16111,22 @@
     </row>
     <row r="259" spans="1:11">
       <c r="A259" s="21" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="B259" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C259" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D259" s="22" t="s">
-        <v>938</v>
+        <v>927</v>
       </c>
       <c r="E259" s="21" t="s">
-        <v>939</v>
+        <v>928</v>
       </c>
       <c r="F259" s="22" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="G259" s="20"/>
       <c r="H259" s="23"/>
@@ -15401,22 +16136,22 @@
     </row>
     <row r="260" spans="1:11">
       <c r="A260" s="21" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="B260" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C260" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D260" s="22" t="s">
-        <v>942</v>
+        <v>930</v>
       </c>
       <c r="E260" s="21" t="s">
-        <v>943</v>
+        <v>931</v>
       </c>
       <c r="F260" s="22" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="G260" s="20"/>
       <c r="H260" s="23"/>
@@ -15426,22 +16161,22 @@
     </row>
     <row r="261" spans="1:11">
       <c r="A261" s="21" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="B261" s="21" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C261" s="21" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="D261" s="22" t="s">
-        <v>945</v>
+        <v>933</v>
       </c>
       <c r="E261" s="21" t="s">
-        <v>946</v>
+        <v>934</v>
       </c>
       <c r="F261" s="22" t="s">
-        <v>940</v>
+        <v>916</v>
       </c>
       <c r="G261" s="20"/>
       <c r="H261" s="23"/>
@@ -15451,22 +16186,22 @@
     </row>
     <row r="262" spans="1:11">
       <c r="A262" s="21" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B262" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C262" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D262" s="22" t="s">
-        <v>948</v>
+        <v>936</v>
       </c>
       <c r="E262" s="21" t="s">
-        <v>949</v>
+        <v>937</v>
       </c>
       <c r="F262" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G262" s="20"/>
       <c r="H262" s="23"/>
@@ -15476,22 +16211,22 @@
     </row>
     <row r="263" spans="1:11">
       <c r="A263" s="21" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="B263" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C263" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D263" s="22" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="E263" s="21" t="s">
-        <v>951</v>
+        <v>941</v>
       </c>
       <c r="F263" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G263" s="20"/>
       <c r="H263" s="23"/>
@@ -15501,22 +16236,22 @@
     </row>
     <row r="264" spans="1:11">
       <c r="A264" s="21" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="B264" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C264" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D264" s="22" t="s">
-        <v>953</v>
+        <v>943</v>
       </c>
       <c r="E264" s="21" t="s">
-        <v>954</v>
+        <v>944</v>
       </c>
       <c r="F264" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G264" s="20"/>
       <c r="H264" s="23"/>
@@ -15526,22 +16261,22 @@
     </row>
     <row r="265" spans="1:11">
       <c r="A265" s="21" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="B265" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C265" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D265" s="22" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="E265" s="21" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="F265" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G265" s="20"/>
       <c r="H265" s="23"/>
@@ -15551,22 +16286,22 @@
     </row>
     <row r="266" spans="1:11">
       <c r="A266" s="21" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B266" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C266" s="21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D266" s="22" t="s">
-        <v>959</v>
+        <v>927</v>
       </c>
       <c r="E266" s="21" t="s">
-        <v>960</v>
+        <v>949</v>
       </c>
       <c r="F266" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G266" s="20"/>
       <c r="H266" s="23"/>
@@ -15576,22 +16311,22 @@
     </row>
     <row r="267" spans="1:11">
       <c r="A267" s="21" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="B267" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C267" s="21" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="D267" s="22" t="s">
-        <v>962</v>
+        <v>951</v>
       </c>
       <c r="E267" s="21" t="s">
-        <v>963</v>
+        <v>952</v>
       </c>
       <c r="F267" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G267" s="20"/>
       <c r="H267" s="23"/>
@@ -15601,22 +16336,22 @@
     </row>
     <row r="268" spans="1:11">
       <c r="A268" s="21" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="B268" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C268" s="21" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D268" s="22" t="s">
-        <v>965</v>
+        <v>954</v>
       </c>
       <c r="E268" s="21" t="s">
-        <v>966</v>
+        <v>955</v>
       </c>
       <c r="F268" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G268" s="20"/>
       <c r="H268" s="23"/>
@@ -15626,22 +16361,22 @@
     </row>
     <row r="269" spans="1:11">
       <c r="A269" s="21" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="B269" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C269" s="21" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="D269" s="22" t="s">
-        <v>968</v>
+        <v>957</v>
       </c>
       <c r="E269" s="21" t="s">
-        <v>969</v>
+        <v>958</v>
       </c>
       <c r="F269" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G269" s="20"/>
       <c r="H269" s="23"/>
@@ -15651,22 +16386,22 @@
     </row>
     <row r="270" spans="1:11">
       <c r="A270" s="21" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="B270" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C270" s="21" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="D270" s="22" t="s">
-        <v>971</v>
+        <v>960</v>
       </c>
       <c r="E270" s="21" t="s">
-        <v>972</v>
+        <v>961</v>
       </c>
       <c r="F270" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G270" s="20"/>
       <c r="H270" s="23"/>
@@ -15676,22 +16411,22 @@
     </row>
     <row r="271" spans="1:11">
       <c r="A271" s="21" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="B271" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C271" s="21" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D271" s="22" t="s">
-        <v>974</v>
+        <v>963</v>
       </c>
       <c r="E271" s="21" t="s">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="F271" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G271" s="20"/>
       <c r="H271" s="23"/>
@@ -15701,22 +16436,22 @@
     </row>
     <row r="272" spans="1:11">
       <c r="A272" s="21" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="B272" s="21" t="s">
         <v>125</v>
       </c>
       <c r="C272" s="21" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D272" s="22" t="s">
-        <v>977</v>
+        <v>966</v>
       </c>
       <c r="E272" s="21" t="s">
-        <v>978</v>
+        <v>967</v>
       </c>
       <c r="F272" s="22" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G272" s="20"/>
       <c r="H272" s="23"/>
@@ -15726,22 +16461,22 @@
     </row>
     <row r="273" spans="1:11">
       <c r="A273" s="21" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B273" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C273" s="21" t="s">
-        <v>174</v>
+        <v>300</v>
       </c>
       <c r="D273" s="22" t="s">
-        <v>980</v>
+        <v>969</v>
       </c>
       <c r="E273" s="21" t="s">
-        <v>981</v>
+        <v>970</v>
       </c>
       <c r="F273" s="22" t="s">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="G273" s="20"/>
       <c r="H273" s="23"/>
@@ -15751,22 +16486,22 @@
     </row>
     <row r="274" spans="1:11">
       <c r="A274" s="21" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B274" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C274" s="21" t="s">
-        <v>179</v>
+        <v>304</v>
       </c>
       <c r="D274" s="22" t="s">
-        <v>984</v>
+        <v>972</v>
       </c>
       <c r="E274" s="21" t="s">
-        <v>985</v>
+        <v>973</v>
       </c>
       <c r="F274" s="22" t="s">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="G274" s="20"/>
       <c r="H274" s="23"/>
@@ -15776,22 +16511,22 @@
     </row>
     <row r="275" spans="1:11">
       <c r="A275" s="21" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B275" s="21" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C275" s="21" t="s">
-        <v>190</v>
+        <v>308</v>
       </c>
       <c r="D275" s="22" t="s">
-        <v>987</v>
+        <v>975</v>
       </c>
       <c r="E275" s="21" t="s">
-        <v>988</v>
+        <v>976</v>
       </c>
       <c r="F275" s="22" t="s">
-        <v>982</v>
+        <v>938</v>
       </c>
       <c r="G275" s="20"/>
       <c r="H275" s="23"/>
@@ -15801,22 +16536,22 @@
     </row>
     <row r="276" spans="1:11">
       <c r="A276" s="21" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B276" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C276" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D276" s="22" t="s">
-        <v>990</v>
+        <v>978</v>
       </c>
       <c r="E276" s="21" t="s">
-        <v>991</v>
+        <v>979</v>
       </c>
       <c r="F276" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G276" s="20"/>
       <c r="H276" s="23"/>
@@ -15826,22 +16561,22 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="21" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="B277" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C277" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D277" s="22" t="s">
-        <v>993</v>
+        <v>982</v>
       </c>
       <c r="E277" s="21" t="s">
-        <v>994</v>
+        <v>983</v>
       </c>
       <c r="F277" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G277" s="20"/>
       <c r="H277" s="23"/>
@@ -15851,22 +16586,22 @@
     </row>
     <row r="278" spans="1:11">
       <c r="A278" s="21" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="B278" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C278" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D278" s="22" t="s">
-        <v>996</v>
+        <v>985</v>
       </c>
       <c r="E278" s="21" t="s">
-        <v>997</v>
+        <v>986</v>
       </c>
       <c r="F278" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G278" s="20"/>
       <c r="H278" s="23"/>
@@ -15876,22 +16611,22 @@
     </row>
     <row r="279" spans="1:11">
       <c r="A279" s="21" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="B279" s="21" t="s">
         <v>128</v>
       </c>
       <c r="C279" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D279" s="22" t="s">
-        <v>999</v>
+        <v>988</v>
       </c>
       <c r="E279" s="21" t="s">
-        <v>1000</v>
+        <v>989</v>
       </c>
       <c r="F279" s="22" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="G279" s="20"/>
       <c r="H279" s="23"/>
@@ -15901,22 +16636,22 @@
     </row>
     <row r="280" spans="1:11">
       <c r="A280" s="21" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B280" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C280" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D280" s="22" t="s">
-        <v>1002</v>
+        <v>991</v>
       </c>
       <c r="E280" s="21" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
       <c r="F280" s="22" t="s">
-        <v>1004</v>
+        <v>980</v>
       </c>
       <c r="G280" s="20"/>
       <c r="H280" s="23"/>
@@ -15926,22 +16661,22 @@
     </row>
     <row r="281" spans="1:11">
       <c r="A281" s="21" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B281" s="21" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C281" s="21" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="D281" s="22" t="s">
-        <v>1006</v>
+        <v>994</v>
       </c>
       <c r="E281" s="21" t="s">
-        <v>1007</v>
+        <v>995</v>
       </c>
       <c r="F281" s="22" t="s">
-        <v>1004</v>
+        <v>980</v>
       </c>
       <c r="G281" s="20"/>
       <c r="H281" s="23"/>
@@ -15951,22 +16686,22 @@
     </row>
     <row r="282" spans="1:11">
       <c r="A282" s="21" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B282" s="21" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C282" s="21" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
       <c r="D282" s="22" t="s">
-        <v>1009</v>
+        <v>997</v>
       </c>
       <c r="E282" s="21" t="s">
-        <v>1010</v>
+        <v>998</v>
       </c>
       <c r="F282" s="22" t="s">
-        <v>1011</v>
+        <v>980</v>
       </c>
       <c r="G282" s="20"/>
       <c r="H282" s="23"/>
@@ -15976,22 +16711,22 @@
     </row>
     <row r="283" spans="1:11">
       <c r="A283" s="21" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B283" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C283" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D283" s="22" t="s">
-        <v>1013</v>
+        <v>1000</v>
       </c>
       <c r="E283" s="21" t="s">
-        <v>1014</v>
+        <v>1001</v>
       </c>
       <c r="F283" s="22" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="G283" s="20"/>
       <c r="H283" s="23"/>
@@ -16001,22 +16736,22 @@
     </row>
     <row r="284" spans="1:11">
       <c r="A284" s="21" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B284" s="21" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C284" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D284" s="22" t="s">
-        <v>1016</v>
+        <v>1004</v>
       </c>
       <c r="E284" s="21" t="s">
-        <v>1017</v>
+        <v>1005</v>
       </c>
       <c r="F284" s="22" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="G284" s="20"/>
       <c r="H284" s="23"/>
@@ -16026,22 +16761,22 @@
     </row>
     <row r="285" spans="1:11">
       <c r="A285" s="21" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B285" s="21" t="s">
         <v>132</v>
       </c>
       <c r="C285" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D285" s="22" t="s">
-        <v>1019</v>
+        <v>1007</v>
       </c>
       <c r="E285" s="21" t="s">
-        <v>1020</v>
+        <v>1008</v>
       </c>
       <c r="F285" s="22" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="G285" s="20"/>
       <c r="H285" s="23"/>
@@ -16051,22 +16786,22 @@
     </row>
     <row r="286" spans="1:11">
       <c r="A286" s="21" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B286" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C286" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D286" s="22" t="s">
-        <v>1022</v>
+        <v>1011</v>
       </c>
       <c r="E286" s="21" t="s">
-        <v>1023</v>
+        <v>1012</v>
       </c>
       <c r="F286" s="22" t="s">
-        <v>1024</v>
+        <v>1009</v>
       </c>
       <c r="G286" s="20"/>
       <c r="H286" s="23"/>
@@ -16076,22 +16811,22 @@
     </row>
     <row r="287" spans="1:11">
       <c r="A287" s="21" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B287" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C287" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D287" s="22" t="s">
-        <v>1026</v>
+        <v>1014</v>
       </c>
       <c r="E287" s="21" t="s">
-        <v>1027</v>
+        <v>1015</v>
       </c>
       <c r="F287" s="22" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="G287" s="20"/>
       <c r="H287" s="23"/>
@@ -16101,22 +16836,22 @@
     </row>
     <row r="288" spans="1:11">
       <c r="A288" s="21" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B288" s="21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C288" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D288" s="22" t="s">
-        <v>1030</v>
+        <v>1017</v>
       </c>
       <c r="E288" s="21" t="s">
-        <v>1031</v>
+        <v>1018</v>
       </c>
       <c r="F288" s="22" t="s">
-        <v>1028</v>
+        <v>1009</v>
       </c>
       <c r="G288" s="20"/>
       <c r="H288" s="23"/>
@@ -16126,22 +16861,22 @@
     </row>
     <row r="289" spans="1:11">
       <c r="A289" s="21" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B289" s="21" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C289" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D289" s="22" t="s">
-        <v>1033</v>
+        <v>1020</v>
       </c>
       <c r="E289" s="21" t="s">
-        <v>1034</v>
+        <v>1021</v>
       </c>
       <c r="F289" s="22" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="G289" s="20"/>
       <c r="H289" s="23"/>
@@ -16151,22 +16886,22 @@
     </row>
     <row r="290" spans="1:11">
       <c r="A290" s="21" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B290" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C290" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D290" s="22" t="s">
-        <v>1036</v>
+        <v>1024</v>
       </c>
       <c r="E290" s="21" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="F290" s="22" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G290" s="20"/>
       <c r="H290" s="23"/>
@@ -16176,22 +16911,22 @@
     </row>
     <row r="291" spans="1:11">
       <c r="A291" s="21" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B291" s="21" t="s">
         <v>135</v>
       </c>
       <c r="C291" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D291" s="22" t="s">
-        <v>1039</v>
+        <v>1028</v>
       </c>
       <c r="E291" s="21" t="s">
-        <v>1040</v>
+        <v>1029</v>
       </c>
       <c r="F291" s="22" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G291" s="20"/>
       <c r="H291" s="23"/>
@@ -16201,22 +16936,22 @@
     </row>
     <row r="292" spans="1:11">
       <c r="A292" s="21" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B292" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C292" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D292" s="22" t="s">
-        <v>1042</v>
+        <v>1031</v>
       </c>
       <c r="E292" s="21" t="s">
-        <v>1043</v>
+        <v>1032</v>
       </c>
       <c r="F292" s="22" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="G292" s="20"/>
       <c r="H292" s="23"/>
@@ -16226,22 +16961,22 @@
     </row>
     <row r="293" spans="1:11">
       <c r="A293" s="21" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B293" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C293" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D293" s="22" t="s">
-        <v>1046</v>
+        <v>1034</v>
       </c>
       <c r="E293" s="21" t="s">
-        <v>1047</v>
+        <v>1035</v>
       </c>
       <c r="F293" s="22" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="G293" s="20"/>
       <c r="H293" s="23"/>
@@ -16251,22 +16986,22 @@
     </row>
     <row r="294" spans="1:11">
       <c r="A294" s="21" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B294" s="21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C294" s="21" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D294" s="22" t="s">
-        <v>1049</v>
+        <v>1037</v>
       </c>
       <c r="E294" s="21" t="s">
-        <v>1050</v>
+        <v>1038</v>
       </c>
       <c r="F294" s="22" t="s">
-        <v>1044</v>
+        <v>1026</v>
       </c>
       <c r="G294" s="20"/>
       <c r="H294" s="23"/>
@@ -16276,22 +17011,22 @@
     </row>
     <row r="295" spans="1:11">
       <c r="A295" s="21" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B295" s="21" t="s">
         <v>137</v>
       </c>
       <c r="C295" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D295" s="22" t="s">
-        <v>1052</v>
+        <v>1040</v>
       </c>
       <c r="E295" s="21" t="s">
-        <v>1053</v>
+        <v>1041</v>
       </c>
       <c r="F295" s="22" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="G295" s="20"/>
       <c r="H295" s="23"/>
@@ -16301,22 +17036,22 @@
     </row>
     <row r="296" spans="1:11">
       <c r="A296" s="21" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B296" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C296" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D296" s="22" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
       <c r="E296" s="21" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="F296" s="22" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="G296" s="20"/>
       <c r="H296" s="23"/>
@@ -16326,22 +17061,22 @@
     </row>
     <row r="297" spans="1:11">
       <c r="A297" s="21" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B297" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C297" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D297" s="22" t="s">
-        <v>1059</v>
+        <v>1047</v>
       </c>
       <c r="E297" s="21" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="F297" s="22" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="G297" s="20"/>
       <c r="H297" s="23"/>
@@ -16351,22 +17086,22 @@
     </row>
     <row r="298" spans="1:11">
       <c r="A298" s="21" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B298" s="21" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C298" s="21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D298" s="22" t="s">
-        <v>1062</v>
+        <v>1050</v>
       </c>
       <c r="E298" s="21" t="s">
-        <v>1063</v>
+        <v>1051</v>
       </c>
       <c r="F298" s="22" t="s">
-        <v>1057</v>
+        <v>1042</v>
       </c>
       <c r="G298" s="20"/>
       <c r="H298" s="23"/>
@@ -16376,22 +17111,22 @@
     </row>
     <row r="299" spans="1:11">
       <c r="A299" s="21" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B299" s="21" t="s">
         <v>140</v>
       </c>
       <c r="C299" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D299" s="22" t="s">
-        <v>1065</v>
+        <v>1053</v>
       </c>
       <c r="E299" s="21" t="s">
-        <v>1066</v>
+        <v>1054</v>
       </c>
       <c r="F299" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G299" s="20"/>
       <c r="H299" s="23"/>
@@ -16401,22 +17136,22 @@
     </row>
     <row r="300" spans="1:11">
       <c r="A300" s="21" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B300" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C300" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D300" s="22" t="s">
-        <v>1068</v>
+        <v>1057</v>
       </c>
       <c r="E300" s="21" t="s">
-        <v>1069</v>
+        <v>1058</v>
       </c>
       <c r="F300" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G300" s="20"/>
       <c r="H300" s="23"/>
@@ -16426,22 +17161,22 @@
     </row>
     <row r="301" spans="1:11">
       <c r="A301" s="21" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="B301" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C301" s="21" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="D301" s="22" t="s">
-        <v>1071</v>
+        <v>1060</v>
       </c>
       <c r="E301" s="21" t="s">
-        <v>1072</v>
+        <v>1061</v>
       </c>
       <c r="F301" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G301" s="20"/>
       <c r="H301" s="23"/>
@@ -16451,22 +17186,22 @@
     </row>
     <row r="302" spans="1:11">
       <c r="A302" s="21" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="B302" s="21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C302" s="21" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D302" s="22" t="s">
-        <v>1074</v>
+        <v>1063</v>
       </c>
       <c r="E302" s="21" t="s">
-        <v>1075</v>
+        <v>1064</v>
       </c>
       <c r="F302" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G302" s="20"/>
       <c r="H302" s="23"/>
@@ -16476,22 +17211,22 @@
     </row>
     <row r="303" spans="1:11">
       <c r="A303" s="21" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="B303" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C303" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D303" s="22" t="s">
-        <v>1077</v>
+        <v>1066</v>
       </c>
       <c r="E303" s="21" t="s">
-        <v>1078</v>
+        <v>1067</v>
       </c>
       <c r="F303" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G303" s="20"/>
       <c r="H303" s="23"/>
@@ -16501,22 +17236,22 @@
     </row>
     <row r="304" spans="1:11">
       <c r="A304" s="21" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="B304" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C304" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D304" s="22" t="s">
-        <v>1080</v>
+        <v>1069</v>
       </c>
       <c r="E304" s="21" t="s">
-        <v>1081</v>
+        <v>1070</v>
       </c>
       <c r="F304" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G304" s="20"/>
       <c r="H304" s="23"/>
@@ -16526,22 +17261,22 @@
     </row>
     <row r="305" spans="1:11">
       <c r="A305" s="21" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="B305" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C305" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D305" s="22" t="s">
-        <v>1083</v>
+        <v>1072</v>
       </c>
       <c r="E305" s="21" t="s">
-        <v>1084</v>
+        <v>1073</v>
       </c>
       <c r="F305" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G305" s="20"/>
       <c r="H305" s="23"/>
@@ -16551,22 +17286,22 @@
     </row>
     <row r="306" spans="1:11">
       <c r="A306" s="21" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B306" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C306" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D306" s="22" t="s">
-        <v>1086</v>
+        <v>1075</v>
       </c>
       <c r="E306" s="21" t="s">
-        <v>1087</v>
+        <v>1076</v>
       </c>
       <c r="F306" s="22" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="G306" s="20"/>
       <c r="H306" s="23"/>
@@ -16576,22 +17311,22 @@
     </row>
     <row r="307" spans="1:11">
       <c r="A307" s="21" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="B307" s="21" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C307" s="21" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="D307" s="22" t="s">
-        <v>1089</v>
+        <v>1078</v>
       </c>
       <c r="E307" s="21" t="s">
-        <v>1090</v>
+        <v>1079</v>
       </c>
       <c r="F307" s="22" t="s">
-        <v>1091</v>
+        <v>1055</v>
       </c>
       <c r="G307" s="20"/>
       <c r="H307" s="23"/>
@@ -16601,22 +17336,22 @@
     </row>
     <row r="308" spans="1:11">
       <c r="A308" s="21" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="B308" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C308" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D308" s="22" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
       <c r="E308" s="21" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="F308" s="22" t="s">
-        <v>1095</v>
+        <v>1055</v>
       </c>
       <c r="G308" s="20"/>
       <c r="H308" s="23"/>
@@ -16626,22 +17361,22 @@
     </row>
     <row r="309" spans="1:11">
       <c r="A309" s="21" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B309" s="21" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C309" s="21" t="s">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="D309" s="22" t="s">
-        <v>1097</v>
+        <v>1084</v>
       </c>
       <c r="E309" s="21" t="s">
-        <v>1098</v>
+        <v>1085</v>
       </c>
       <c r="F309" s="22" t="s">
-        <v>1095</v>
+        <v>1055</v>
       </c>
       <c r="G309" s="20"/>
       <c r="H309" s="23"/>
@@ -16651,22 +17386,22 @@
     </row>
     <row r="310" spans="1:11">
       <c r="A310" s="21" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
       <c r="B310" s="21" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C310" s="21" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D310" s="22" t="s">
-        <v>1100</v>
+        <v>1087</v>
       </c>
       <c r="E310" s="21" t="s">
-        <v>1101</v>
+        <v>1088</v>
       </c>
       <c r="F310" s="22" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="G310" s="20"/>
       <c r="H310" s="23"/>
@@ -16676,22 +17411,22 @@
     </row>
     <row r="311" spans="1:11">
       <c r="A311" s="21" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="B311" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C311" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D311" s="22" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
       <c r="E311" s="21" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="F311" s="22" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="G311" s="20"/>
       <c r="H311" s="23"/>
@@ -16701,22 +17436,22 @@
     </row>
     <row r="312" spans="1:11">
       <c r="A312" s="21" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="B312" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C312" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D312" s="22" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
       <c r="E312" s="21" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="F312" s="22" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="G312" s="20"/>
       <c r="H312" s="23"/>
@@ -16726,22 +17461,22 @@
     </row>
     <row r="313" spans="1:11">
       <c r="A313" s="21" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="B313" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C313" s="21" t="s">
         <v>190</v>
       </c>
       <c r="D313" s="22" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="E313" s="21" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
       <c r="F313" s="22" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
       <c r="G313" s="20"/>
       <c r="H313" s="23"/>
@@ -16751,22 +17486,22 @@
     </row>
     <row r="314" spans="1:11">
       <c r="A314" s="21" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B314" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C314" s="21" t="s">
         <v>174</v>
       </c>
       <c r="D314" s="22" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
       <c r="E314" s="21" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="F314" s="22" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="G314" s="20"/>
       <c r="H314" s="23"/>
@@ -16776,22 +17511,22 @@
     </row>
     <row r="315" spans="1:11">
       <c r="A315" s="21" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B315" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C315" s="21" t="s">
         <v>179</v>
       </c>
       <c r="D315" s="22" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
       <c r="E315" s="21" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="F315" s="22" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="G315" s="20"/>
       <c r="H315" s="23"/>
@@ -16801,22 +17536,22 @@
     </row>
     <row r="316" spans="1:11">
       <c r="A316" s="21" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="B316" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C316" s="21" t="s">
         <v>190</v>
       </c>
       <c r="D316" s="22" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="E316" s="21" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
       <c r="F316" s="22" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
       <c r="G316" s="20"/>
       <c r="H316" s="23"/>
@@ -16826,22 +17561,22 @@
     </row>
     <row r="317" spans="1:11">
       <c r="A317" s="21" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B317" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C317" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D317" s="22" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E317" s="21" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F317" s="22" t="s">
         <v>1113</v>
-      </c>
-      <c r="E317" s="21" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F317" s="22" t="s">
-        <v>1115</v>
       </c>
       <c r="G317" s="20"/>
       <c r="H317" s="23"/>
@@ -16851,22 +17586,22 @@
     </row>
     <row r="318" spans="1:11">
       <c r="A318" s="21" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B318" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C318" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D318" s="22" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="E318" s="21" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
       <c r="F318" s="22" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G318" s="20"/>
       <c r="H318" s="23"/>
@@ -16876,22 +17611,22 @@
     </row>
     <row r="319" spans="1:11">
       <c r="A319" s="21" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="B319" s="21" t="s">
         <v>148</v>
       </c>
       <c r="C319" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D319" s="22" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="E319" s="21" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
       <c r="F319" s="22" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="G319" s="20"/>
       <c r="H319" s="23"/>
@@ -16901,22 +17636,22 @@
     </row>
     <row r="320" spans="1:11">
       <c r="A320" s="21" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B320" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C320" s="21" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="D320" s="22" t="s">
-        <v>1130</v>
+        <v>1111</v>
       </c>
       <c r="E320" s="21" t="s">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="F320" s="22" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="G320" s="20"/>
       <c r="H320" s="23"/>
@@ -16926,22 +17661,22 @@
     </row>
     <row r="321" spans="1:11">
       <c r="A321" s="21" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="B321" s="21" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C321" s="21" t="s">
-        <v>179</v>
+        <v>198</v>
       </c>
       <c r="D321" s="22" t="s">
-        <v>1134</v>
+        <v>1122</v>
       </c>
       <c r="E321" s="21" t="s">
-        <v>1135</v>
+        <v>1123</v>
       </c>
       <c r="F321" s="22" t="s">
-        <v>1132</v>
+        <v>1113</v>
       </c>
       <c r="G321" s="20"/>
       <c r="H321" s="23"/>
@@ -16951,22 +17686,22 @@
     </row>
     <row r="322" spans="1:11">
       <c r="A322" s="21" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B322" s="21" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C322" s="21" t="s">
-        <v>174</v>
+        <v>202</v>
       </c>
       <c r="D322" s="22" t="s">
-        <v>1137</v>
+        <v>1125</v>
       </c>
       <c r="E322" s="21" t="s">
-        <v>1138</v>
+        <v>1126</v>
       </c>
       <c r="F322" s="22" t="s">
-        <v>1139</v>
+        <v>1113</v>
       </c>
       <c r="G322" s="20"/>
       <c r="H322" s="23"/>
@@ -16976,22 +17711,22 @@
     </row>
     <row r="323" spans="1:11">
       <c r="A323" s="21" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B323" s="21" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C323" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D323" s="22" t="s">
-        <v>1141</v>
+        <v>1128</v>
       </c>
       <c r="E323" s="21" t="s">
-        <v>1142</v>
+        <v>1129</v>
       </c>
       <c r="F323" s="22" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="G323" s="20"/>
       <c r="H323" s="23"/>
@@ -17001,22 +17736,22 @@
     </row>
     <row r="324" spans="1:11">
       <c r="A324" s="21" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="B324" s="21" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C324" s="21" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D324" s="22" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="E324" s="21" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
       <c r="F324" s="22" t="s">
-        <v>1146</v>
+        <v>1130</v>
       </c>
       <c r="G324" s="20"/>
       <c r="H324" s="23"/>
@@ -17026,22 +17761,22 @@
     </row>
     <row r="325" spans="1:11">
       <c r="A325" s="21" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B325" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C325" s="21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D325" s="22" t="s">
-        <v>1148</v>
+        <v>1135</v>
       </c>
       <c r="E325" s="21" t="s">
-        <v>1149</v>
+        <v>1136</v>
       </c>
       <c r="F325" s="22" t="s">
-        <v>1146</v>
+        <v>1137</v>
       </c>
       <c r="G325" s="20"/>
       <c r="H325" s="23"/>
@@ -17051,22 +17786,22 @@
     </row>
     <row r="326" spans="1:11">
       <c r="A326" s="21" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="B326" s="21" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C326" s="21" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="D326" s="22" t="s">
-        <v>1151</v>
+        <v>1139</v>
       </c>
       <c r="E326" s="21" t="s">
-        <v>1152</v>
+        <v>1140</v>
       </c>
       <c r="F326" s="22" t="s">
-        <v>1146</v>
+        <v>1137</v>
       </c>
       <c r="G326" s="20"/>
       <c r="H326" s="23"/>
@@ -17076,22 +17811,22 @@
     </row>
     <row r="327" spans="1:11">
       <c r="A327" s="21" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B327" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C327" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D327" s="22" t="s">
-        <v>1154</v>
+        <v>1142</v>
       </c>
       <c r="E327" s="21" t="s">
-        <v>1155</v>
+        <v>1143</v>
       </c>
       <c r="F327" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G327" s="20"/>
       <c r="H327" s="23"/>
@@ -17101,22 +17836,22 @@
     </row>
     <row r="328" spans="1:11">
       <c r="A328" s="21" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="B328" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C328" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D328" s="22" t="s">
-        <v>1157</v>
+        <v>1146</v>
       </c>
       <c r="E328" s="21" t="s">
-        <v>1158</v>
+        <v>1147</v>
       </c>
       <c r="F328" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G328" s="20"/>
       <c r="H328" s="23"/>
@@ -17126,22 +17861,22 @@
     </row>
     <row r="329" spans="1:11">
       <c r="A329" s="21" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B329" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C329" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1160</v>
+        <v>1149</v>
       </c>
       <c r="E329" s="21" t="s">
-        <v>1161</v>
+        <v>1150</v>
       </c>
       <c r="F329" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G329" s="20"/>
       <c r="H329" s="23"/>
@@ -17151,22 +17886,22 @@
     </row>
     <row r="330" spans="1:11">
       <c r="A330" s="21" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B330" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C330" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D330" s="22" t="s">
-        <v>1163</v>
+        <v>1152</v>
       </c>
       <c r="E330" s="21" t="s">
-        <v>1164</v>
+        <v>1153</v>
       </c>
       <c r="F330" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G330" s="20"/>
       <c r="H330" s="23"/>
@@ -17176,22 +17911,22 @@
     </row>
     <row r="331" spans="1:11">
       <c r="A331" s="21" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B331" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C331" s="21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D331" s="22" t="s">
-        <v>1166</v>
+        <v>1155</v>
       </c>
       <c r="E331" s="21" t="s">
-        <v>1167</v>
+        <v>1156</v>
       </c>
       <c r="F331" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G331" s="20"/>
       <c r="H331" s="23"/>
@@ -17201,22 +17936,22 @@
     </row>
     <row r="332" spans="1:11">
       <c r="A332" s="21" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="B332" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C332" s="21" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="D332" s="22" t="s">
-        <v>1169</v>
+        <v>1158</v>
       </c>
       <c r="E332" s="21" t="s">
-        <v>1170</v>
+        <v>1159</v>
       </c>
       <c r="F332" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G332" s="20"/>
       <c r="H332" s="23"/>
@@ -17226,22 +17961,22 @@
     </row>
     <row r="333" spans="1:11">
       <c r="A333" s="21" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B333" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C333" s="21" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D333" s="22" t="s">
-        <v>1172</v>
+        <v>1161</v>
       </c>
       <c r="E333" s="21" t="s">
-        <v>1173</v>
+        <v>1162</v>
       </c>
       <c r="F333" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G333" s="20"/>
       <c r="H333" s="23"/>
@@ -17251,22 +17986,22 @@
     </row>
     <row r="334" spans="1:11">
       <c r="A334" s="21" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="B334" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C334" s="21" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="D334" s="22" t="s">
-        <v>1175</v>
+        <v>1164</v>
       </c>
       <c r="E334" s="21" t="s">
-        <v>1176</v>
+        <v>1165</v>
       </c>
       <c r="F334" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G334" s="20"/>
       <c r="H334" s="23"/>
@@ -17276,22 +18011,22 @@
     </row>
     <row r="335" spans="1:11">
       <c r="A335" s="21" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B335" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C335" s="21" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="D335" s="22" t="s">
-        <v>1178</v>
+        <v>1167</v>
       </c>
       <c r="E335" s="21" t="s">
-        <v>1179</v>
+        <v>1168</v>
       </c>
       <c r="F335" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G335" s="20"/>
       <c r="H335" s="23"/>
@@ -17301,22 +18036,22 @@
     </row>
     <row r="336" spans="1:11">
       <c r="A336" s="21" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="B336" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C336" s="21" t="s">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="D336" s="22" t="s">
-        <v>1181</v>
+        <v>1170</v>
       </c>
       <c r="E336" s="21" t="s">
-        <v>1182</v>
+        <v>1171</v>
       </c>
       <c r="F336" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G336" s="20"/>
       <c r="H336" s="23"/>
@@ -17326,22 +18061,22 @@
     </row>
     <row r="337" spans="1:11">
       <c r="A337" s="21" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B337" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C337" s="21" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D337" s="22" t="s">
-        <v>1184</v>
+        <v>1173</v>
       </c>
       <c r="E337" s="21" t="s">
-        <v>1185</v>
+        <v>1174</v>
       </c>
       <c r="F337" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G337" s="20"/>
       <c r="H337" s="23"/>
@@ -17351,22 +18086,22 @@
     </row>
     <row r="338" spans="1:11">
       <c r="A338" s="21" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="B338" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C338" s="21" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="D338" s="22" t="s">
-        <v>1187</v>
+        <v>1176</v>
       </c>
       <c r="E338" s="21" t="s">
-        <v>1188</v>
+        <v>1177</v>
       </c>
       <c r="F338" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G338" s="20"/>
       <c r="H338" s="23"/>
@@ -17376,22 +18111,22 @@
     </row>
     <row r="339" spans="1:11">
       <c r="A339" s="21" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B339" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C339" s="21" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D339" s="22" t="s">
-        <v>1190</v>
+        <v>1179</v>
       </c>
       <c r="E339" s="21" t="s">
-        <v>1191</v>
+        <v>1180</v>
       </c>
       <c r="F339" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G339" s="20"/>
       <c r="H339" s="23"/>
@@ -17401,22 +18136,22 @@
     </row>
     <row r="340" spans="1:11">
       <c r="A340" s="21" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B340" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C340" s="21" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D340" s="22" t="s">
-        <v>1193</v>
+        <v>1182</v>
       </c>
       <c r="E340" s="21" t="s">
-        <v>1194</v>
+        <v>1183</v>
       </c>
       <c r="F340" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G340" s="20"/>
       <c r="H340" s="23"/>
@@ -17426,22 +18161,22 @@
     </row>
     <row r="341" spans="1:11">
       <c r="A341" s="21" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B341" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C341" s="21" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D341" s="22" t="s">
-        <v>1196</v>
+        <v>1185</v>
       </c>
       <c r="E341" s="21" t="s">
-        <v>188</v>
+        <v>1186</v>
       </c>
       <c r="F341" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G341" s="20"/>
       <c r="H341" s="23"/>
@@ -17451,22 +18186,22 @@
     </row>
     <row r="342" spans="1:11">
       <c r="A342" s="21" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B342" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C342" s="21" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="D342" s="22" t="s">
-        <v>1198</v>
+        <v>1188</v>
       </c>
       <c r="E342" s="21" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="F342" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G342" s="20"/>
       <c r="H342" s="23"/>
@@ -17476,22 +18211,22 @@
     </row>
     <row r="343" spans="1:11">
       <c r="A343" s="21" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B343" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C343" s="21" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="D343" s="22" t="s">
-        <v>1201</v>
+        <v>1191</v>
       </c>
       <c r="E343" s="21" t="s">
-        <v>1202</v>
+        <v>1192</v>
       </c>
       <c r="F343" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G343" s="20"/>
       <c r="H343" s="23"/>
@@ -17501,22 +18236,22 @@
     </row>
     <row r="344" spans="1:11">
       <c r="A344" s="21" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B344" s="21" t="s">
         <v>155</v>
       </c>
       <c r="C344" s="21" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D344" s="22" t="s">
-        <v>1204</v>
+        <v>1194</v>
       </c>
       <c r="E344" s="21" t="s">
-        <v>1205</v>
+        <v>188</v>
       </c>
       <c r="F344" s="22" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="G344" s="20"/>
       <c r="H344" s="23"/>
@@ -17526,22 +18261,22 @@
     </row>
     <row r="345" spans="1:11">
       <c r="A345" s="21" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B345" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C345" s="21" t="s">
-        <v>174</v>
+        <v>328</v>
       </c>
       <c r="D345" s="22" t="s">
-        <v>1207</v>
+        <v>1196</v>
       </c>
       <c r="E345" s="21" t="s">
-        <v>1161</v>
+        <v>1197</v>
       </c>
       <c r="F345" s="22" t="s">
-        <v>1208</v>
+        <v>1144</v>
       </c>
       <c r="G345" s="20"/>
       <c r="H345" s="23"/>
@@ -17551,22 +18286,22 @@
     </row>
     <row r="346" spans="1:11">
       <c r="A346" s="21" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B346" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C346" s="21" t="s">
-        <v>179</v>
+        <v>332</v>
       </c>
       <c r="D346" s="22" t="s">
-        <v>1210</v>
+        <v>1199</v>
       </c>
       <c r="E346" s="21" t="s">
-        <v>1211</v>
+        <v>1200</v>
       </c>
       <c r="F346" s="22" t="s">
-        <v>1208</v>
+        <v>1144</v>
       </c>
       <c r="G346" s="20"/>
       <c r="H346" s="23"/>
@@ -17576,22 +18311,22 @@
     </row>
     <row r="347" spans="1:11">
       <c r="A347" s="21" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B347" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C347" s="21" t="s">
-        <v>190</v>
+        <v>336</v>
       </c>
       <c r="D347" s="22" t="s">
-        <v>1213</v>
+        <v>1202</v>
       </c>
       <c r="E347" s="21" t="s">
-        <v>1214</v>
+        <v>1203</v>
       </c>
       <c r="F347" s="22" t="s">
-        <v>1208</v>
+        <v>1144</v>
       </c>
       <c r="G347" s="20"/>
       <c r="H347" s="23"/>
@@ -17601,22 +18336,22 @@
     </row>
     <row r="348" spans="1:11">
       <c r="A348" s="21" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B348" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C348" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D348" s="22" t="s">
-        <v>1216</v>
+        <v>1205</v>
       </c>
       <c r="E348" s="21" t="s">
-        <v>1217</v>
+        <v>1159</v>
       </c>
       <c r="F348" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G348" s="20"/>
       <c r="H348" s="23"/>
@@ -17626,22 +18361,22 @@
     </row>
     <row r="349" spans="1:11">
       <c r="A349" s="21" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B349" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C349" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D349" s="22" t="s">
-        <v>1219</v>
+        <v>1208</v>
       </c>
       <c r="E349" s="21" t="s">
-        <v>1220</v>
+        <v>1209</v>
       </c>
       <c r="F349" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G349" s="20"/>
       <c r="H349" s="23"/>
@@ -17651,22 +18386,22 @@
     </row>
     <row r="350" spans="1:11">
       <c r="A350" s="21" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B350" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C350" s="21" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D350" s="22" t="s">
-        <v>1222</v>
+        <v>1211</v>
       </c>
       <c r="E350" s="21" t="s">
-        <v>1223</v>
+        <v>1212</v>
       </c>
       <c r="F350" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G350" s="20"/>
       <c r="H350" s="23"/>
@@ -17676,22 +18411,22 @@
     </row>
     <row r="351" spans="1:11">
       <c r="A351" s="21" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B351" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C351" s="21" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="D351" s="22" t="s">
-        <v>1225</v>
+        <v>1214</v>
       </c>
       <c r="E351" s="21" t="s">
-        <v>1226</v>
+        <v>1215</v>
       </c>
       <c r="F351" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G351" s="20"/>
       <c r="H351" s="23"/>
@@ -17701,22 +18436,22 @@
     </row>
     <row r="352" spans="1:11">
       <c r="A352" s="21" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B352" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C352" s="21" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="D352" s="22" t="s">
-        <v>1228</v>
+        <v>1217</v>
       </c>
       <c r="E352" s="21" t="s">
-        <v>1229</v>
+        <v>1218</v>
       </c>
       <c r="F352" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G352" s="20"/>
       <c r="H352" s="23"/>
@@ -17726,22 +18461,22 @@
     </row>
     <row r="353" spans="1:11">
       <c r="A353" s="21" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B353" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C353" s="21" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="D353" s="22" t="s">
-        <v>1231</v>
+        <v>1220</v>
       </c>
       <c r="E353" s="21" t="s">
-        <v>1232</v>
+        <v>1221</v>
       </c>
       <c r="F353" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G353" s="20"/>
       <c r="H353" s="23"/>
@@ -17751,22 +18486,22 @@
     </row>
     <row r="354" spans="1:11">
       <c r="A354" s="21" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B354" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C354" s="21" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="D354" s="22" t="s">
-        <v>1234</v>
+        <v>1223</v>
       </c>
       <c r="E354" s="21" t="s">
-        <v>1235</v>
+        <v>1224</v>
       </c>
       <c r="F354" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G354" s="20"/>
       <c r="H354" s="23"/>
@@ -17776,22 +18511,22 @@
     </row>
     <row r="355" spans="1:11">
       <c r="A355" s="21" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="B355" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C355" s="21" t="s">
-        <v>296</v>
+        <v>210</v>
       </c>
       <c r="D355" s="22" t="s">
-        <v>1237</v>
+        <v>1226</v>
       </c>
       <c r="E355" s="21" t="s">
-        <v>1238</v>
+        <v>1227</v>
       </c>
       <c r="F355" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G355" s="20"/>
       <c r="H355" s="23"/>
@@ -17801,22 +18536,22 @@
     </row>
     <row r="356" spans="1:11">
       <c r="A356" s="21" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B356" s="21" t="s">
         <v>156</v>
       </c>
       <c r="C356" s="21" t="s">
-        <v>300</v>
+        <v>258</v>
       </c>
       <c r="D356" s="22" t="s">
-        <v>1240</v>
+        <v>1229</v>
       </c>
       <c r="E356" s="21" t="s">
-        <v>1241</v>
+        <v>1230</v>
       </c>
       <c r="F356" s="22" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="G356" s="20"/>
       <c r="H356" s="23"/>
@@ -17826,22 +18561,22 @@
     </row>
     <row r="357" spans="1:11">
       <c r="A357" s="21" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B357" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C357" s="21" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
       <c r="D357" s="22" t="s">
-        <v>1243</v>
+        <v>1232</v>
       </c>
       <c r="E357" s="21" t="s">
-        <v>1244</v>
+        <v>1233</v>
       </c>
       <c r="F357" s="22" t="s">
-        <v>875</v>
+        <v>1206</v>
       </c>
       <c r="G357" s="20"/>
       <c r="H357" s="23"/>
@@ -17851,22 +18586,22 @@
     </row>
     <row r="358" spans="1:11">
       <c r="A358" s="21" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B358" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C358" s="21" t="s">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="D358" s="22" t="s">
-        <v>1246</v>
+        <v>1235</v>
       </c>
       <c r="E358" s="21" t="s">
-        <v>1247</v>
+        <v>1236</v>
       </c>
       <c r="F358" s="22" t="s">
-        <v>875</v>
+        <v>1206</v>
       </c>
       <c r="G358" s="20"/>
       <c r="H358" s="23"/>
@@ -17876,22 +18611,22 @@
     </row>
     <row r="359" spans="1:11">
       <c r="A359" s="21" t="s">
-        <v>1303</v>
+        <v>1301</v>
       </c>
       <c r="B359" s="21" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C359" s="21" t="s">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="D359" s="22" t="s">
-        <v>1249</v>
+        <v>1238</v>
       </c>
       <c r="E359" s="21" t="s">
-        <v>1250</v>
+        <v>1239</v>
       </c>
       <c r="F359" s="22" t="s">
-        <v>875</v>
+        <v>1206</v>
       </c>
       <c r="G359" s="20"/>
       <c r="H359" s="23"/>
@@ -17901,22 +18636,22 @@
     </row>
     <row r="360" spans="1:11">
       <c r="A360" s="21" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B360" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C360" s="21" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="D360" s="22" t="s">
-        <v>1252</v>
+        <v>1241</v>
       </c>
       <c r="E360" s="21" t="s">
-        <v>1253</v>
+        <v>1242</v>
       </c>
       <c r="F360" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G360" s="20"/>
       <c r="H360" s="23"/>
@@ -17926,22 +18661,22 @@
     </row>
     <row r="361" spans="1:11">
       <c r="A361" s="21" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B361" s="21" t="s">
         <v>158</v>
       </c>
       <c r="C361" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D361" s="22" t="s">
-        <v>1255</v>
+        <v>1244</v>
       </c>
       <c r="E361" s="21" t="s">
-        <v>1256</v>
+        <v>1245</v>
       </c>
       <c r="F361" s="22" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G361" s="20"/>
       <c r="H361" s="23"/>
@@ -17951,133 +18686,103 @@
     </row>
     <row r="362" spans="1:11">
       <c r="A362" s="21" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B362" s="21" t="s">
-        <v>1295</v>
+        <v>158</v>
       </c>
       <c r="C362" s="21" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="D362" s="22" t="s">
-        <v>1298</v>
+        <v>1247</v>
       </c>
       <c r="E362" s="21" t="s">
-        <v>1310</v>
+        <v>1248</v>
       </c>
       <c r="F362" s="22" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G362" s="20">
-        <v>4500</v>
-      </c>
-      <c r="H362" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I362" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J362" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K362" s="23">
-        <v>82500</v>
-      </c>
+        <v>873</v>
+      </c>
+      <c r="G362" s="20"/>
+      <c r="H362" s="23"/>
+      <c r="I362" s="23"/>
+      <c r="J362" s="23"/>
+      <c r="K362" s="23"/>
     </row>
     <row r="363" spans="1:11">
       <c r="A363" s="21" t="s">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="B363" s="21" t="s">
-        <v>1295</v>
+        <v>158</v>
       </c>
       <c r="C363" s="21" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D363" s="22" t="s">
-        <v>1312</v>
+        <v>1250</v>
       </c>
       <c r="E363" s="21" t="s">
-        <v>1316</v>
+        <v>1251</v>
       </c>
       <c r="F363" s="22" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G363" s="20">
-        <v>5000</v>
-      </c>
-      <c r="H363" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I363" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J363" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K363" s="23">
-        <v>82500</v>
-      </c>
+        <v>873</v>
+      </c>
+      <c r="G363" s="20"/>
+      <c r="H363" s="23"/>
+      <c r="I363" s="23"/>
+      <c r="J363" s="23"/>
+      <c r="K363" s="23"/>
     </row>
     <row r="364" spans="1:11">
       <c r="A364" s="21" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B364" s="21" t="s">
-        <v>1295</v>
+        <v>158</v>
       </c>
       <c r="C364" s="21" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="D364" s="22" t="s">
-        <v>1313</v>
+        <v>1253</v>
       </c>
       <c r="E364" s="21" t="s">
-        <v>1317</v>
+        <v>1254</v>
       </c>
       <c r="F364" s="22" t="s">
-        <v>1311</v>
-      </c>
-      <c r="G364" s="20">
-        <v>5000</v>
-      </c>
-      <c r="H364" s="23" t="s">
-        <v>1275</v>
-      </c>
-      <c r="I364" s="23">
-        <v>100000</v>
-      </c>
-      <c r="J364" s="23">
-        <v>99000</v>
-      </c>
-      <c r="K364" s="23">
-        <v>82500</v>
-      </c>
+        <v>873</v>
+      </c>
+      <c r="G364" s="20"/>
+      <c r="H364" s="23"/>
+      <c r="I364" s="23"/>
+      <c r="J364" s="23"/>
+      <c r="K364" s="23"/>
     </row>
     <row r="365" spans="1:11">
       <c r="A365" s="21" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B365" s="21" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C365" s="21" t="s">
+        <v>174</v>
+      </c>
+      <c r="D365" s="22" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E365" s="21" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F365" s="22" t="s">
         <v>1309</v>
       </c>
-      <c r="B365" s="21" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C365" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="D365" s="22" t="s">
-        <v>1314</v>
-      </c>
-      <c r="E365" s="21" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F365" s="22" t="s">
-        <v>1311</v>
-      </c>
       <c r="G365" s="20">
-        <v>5000</v>
+        <v>5250</v>
       </c>
       <c r="H365" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I365" s="23">
         <v>100000</v>
@@ -18086,33 +18791,33 @@
         <v>99000</v>
       </c>
       <c r="K365" s="23">
-        <v>82500</v>
+        <v>74250</v>
       </c>
     </row>
     <row r="366" spans="1:11">
       <c r="A366" s="21" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="B366" s="21" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C366" s="21" t="s">
-        <v>198</v>
+        <v>179</v>
       </c>
       <c r="D366" s="22" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="E366" s="21" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="F366" s="22" t="s">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="G366" s="20">
-        <v>5000</v>
+        <v>5750</v>
       </c>
       <c r="H366" s="23" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="I366" s="23">
         <v>100000</v>
@@ -18121,47 +18826,113 @@
         <v>99000</v>
       </c>
       <c r="K366" s="23">
-        <v>82500</v>
+        <v>74250</v>
       </c>
     </row>
     <row r="367" spans="1:11">
-      <c r="A367" s="21"/>
-      <c r="B367" s="21"/>
-      <c r="C367" s="21"/>
-      <c r="D367" s="22"/>
-      <c r="E367" s="21"/>
-      <c r="F367" s="22"/>
-      <c r="G367" s="20"/>
-      <c r="H367" s="23"/>
-      <c r="I367" s="23"/>
-      <c r="J367" s="23"/>
-      <c r="K367" s="23"/>
+      <c r="A367" s="21" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B367" s="21" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C367" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="D367" s="22" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E367" s="21" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F367" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G367" s="20">
+        <v>5750</v>
+      </c>
+      <c r="H367" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I367" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J367" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K367" s="23">
+        <v>74250</v>
+      </c>
     </row>
     <row r="368" spans="1:11">
-      <c r="A368" s="21"/>
-      <c r="B368" s="21"/>
-      <c r="C368" s="21"/>
-      <c r="D368" s="22"/>
-      <c r="E368" s="21"/>
-      <c r="F368" s="22"/>
-      <c r="G368" s="20"/>
-      <c r="H368" s="23"/>
-      <c r="I368" s="23"/>
-      <c r="J368" s="23"/>
-      <c r="K368" s="23"/>
+      <c r="A368" s="21" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B368" s="21" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C368" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="D368" s="22" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E368" s="21" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F368" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G368" s="20">
+        <v>5750</v>
+      </c>
+      <c r="H368" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I368" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J368" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K368" s="23">
+        <v>74250</v>
+      </c>
     </row>
     <row r="369" spans="1:11">
-      <c r="A369" s="21"/>
-      <c r="B369" s="21"/>
-      <c r="C369" s="21"/>
-      <c r="D369" s="22"/>
-      <c r="E369" s="21"/>
-      <c r="F369" s="22"/>
-      <c r="G369" s="20"/>
-      <c r="H369" s="23"/>
-      <c r="I369" s="23"/>
-      <c r="J369" s="23"/>
-      <c r="K369" s="23"/>
+      <c r="A369" s="21" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B369" s="21" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C369" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D369" s="22" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E369" s="21" t="s">
+        <v>1317</v>
+      </c>
+      <c r="F369" s="22" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G369" s="20">
+        <v>5750</v>
+      </c>
+      <c r="H369" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="I369" s="23">
+        <v>100000</v>
+      </c>
+      <c r="J369" s="23">
+        <v>99000</v>
+      </c>
+      <c r="K369" s="23">
+        <v>74250</v>
+      </c>
     </row>
     <row r="370" spans="1:11">
       <c r="A370" s="21"/>
@@ -18781,7 +19552,7 @@
       <c r="D417" s="22"/>
       <c r="E417" s="21"/>
       <c r="F417" s="22"/>
-      <c r="G417" s="18"/>
+      <c r="G417" s="20"/>
       <c r="H417" s="23"/>
       <c r="I417" s="23"/>
       <c r="J417" s="23"/>
@@ -18794,7 +19565,7 @@
       <c r="D418" s="22"/>
       <c r="E418" s="21"/>
       <c r="F418" s="22"/>
-      <c r="G418" s="18"/>
+      <c r="G418" s="20"/>
       <c r="H418" s="23"/>
       <c r="I418" s="23"/>
       <c r="J418" s="23"/>
@@ -18807,7 +19578,7 @@
       <c r="D419" s="22"/>
       <c r="E419" s="21"/>
       <c r="F419" s="22"/>
-      <c r="G419" s="18"/>
+      <c r="G419" s="20"/>
       <c r="H419" s="23"/>
       <c r="I419" s="23"/>
       <c r="J419" s="23"/>
@@ -39481,7 +40252,7 @@
       <c r="H2009" s="23"/>
       <c r="I2009" s="23"/>
       <c r="J2009" s="23"/>
-      <c r="K2009" s="33"/>
+      <c r="K2009" s="23"/>
     </row>
     <row r="2010" spans="1:11">
       <c r="A2010" s="21"/>
@@ -39494,17 +40265,56 @@
       <c r="H2010" s="23"/>
       <c r="I2010" s="23"/>
       <c r="J2010" s="23"/>
-      <c r="K2010" s="33"/>
+      <c r="K2010" s="23"/>
+    </row>
+    <row r="2011" spans="1:11">
+      <c r="A2011" s="21"/>
+      <c r="B2011" s="21"/>
+      <c r="C2011" s="21"/>
+      <c r="D2011" s="22"/>
+      <c r="E2011" s="21"/>
+      <c r="F2011" s="22"/>
+      <c r="G2011" s="18"/>
+      <c r="H2011" s="23"/>
+      <c r="I2011" s="23"/>
+      <c r="J2011" s="23"/>
+      <c r="K2011" s="23"/>
+    </row>
+    <row r="2012" spans="1:11">
+      <c r="A2012" s="21"/>
+      <c r="B2012" s="21"/>
+      <c r="C2012" s="21"/>
+      <c r="D2012" s="22"/>
+      <c r="E2012" s="21"/>
+      <c r="F2012" s="22"/>
+      <c r="G2012" s="18"/>
+      <c r="H2012" s="23"/>
+      <c r="I2012" s="23"/>
+      <c r="J2012" s="23"/>
+      <c r="K2012" s="33"/>
+    </row>
+    <row r="2013" spans="1:11">
+      <c r="A2013" s="21"/>
+      <c r="B2013" s="21"/>
+      <c r="C2013" s="21"/>
+      <c r="D2013" s="22"/>
+      <c r="E2013" s="21"/>
+      <c r="F2013" s="22"/>
+      <c r="G2013" s="18"/>
+      <c r="H2013" s="23"/>
+      <c r="I2013" s="23"/>
+      <c r="J2013" s="23"/>
+      <c r="K2013" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2006:A2010">
+  <conditionalFormatting sqref="A2009:A2013">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A2005">
+  <conditionalFormatting sqref="A4:A2008">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -39534,48 +40344,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="33.9" customHeight="1">
-      <c r="A1" s="42" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
+      <c r="A1" s="53" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
       <c r="H1" s="29"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1">
-      <c r="A2" s="50" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
+      <c r="A2" s="47" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
       <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="38.1" customHeight="1">
       <c r="A3" s="28" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C3" s="28" t="s">
         <v>1259</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>1261</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="28" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="F3" s="28" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G3" s="24" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="H3" s="30"/>
     </row>
@@ -39584,10 +40394,10 @@
         <v>47</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="9" t="s">
@@ -39606,10 +40416,10 @@
         <v>47</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D5" s="10"/>
       <c r="E5" s="9" t="s">
@@ -39628,14 +40438,14 @@
         <v>47</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D6" s="10"/>
       <c r="E6" s="9" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>70</v>
@@ -39650,10 +40460,10 @@
         <v>47</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D7" s="10"/>
       <c r="E7" s="9" t="s">
@@ -39699,10 +40509,10 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="28" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="2"/>
